--- a/ativos.xlsx
+++ b/ativos.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\INVESTIMENTOS VARIAVEL\Bybit\bybit_setups\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D39FD286-1BBC-4BF4-B886-4A470EB0DD14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F1BE5EE-3958-4A8C-8D1D-071948C7601B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="422">
   <si>
     <t>Par</t>
   </si>
@@ -47,21 +50,9 @@
     <t>1000000MOGUSDT</t>
   </si>
   <si>
-    <t>10000LADYSUSDT</t>
-  </si>
-  <si>
     <t>1000BONKUSDT</t>
   </si>
   <si>
-    <t>1000BTTUSDT</t>
-  </si>
-  <si>
-    <t>1000LUNCUSDT</t>
-  </si>
-  <si>
-    <t>1000PEPEUSDT</t>
-  </si>
-  <si>
     <t>1INCHUSDT</t>
   </si>
   <si>
@@ -80,9 +71,6 @@
     <t>ARCUSDT</t>
   </si>
   <si>
-    <t>AVAAIUSDT</t>
-  </si>
-  <si>
     <t>AVAXUSDT</t>
   </si>
   <si>
@@ -122,12 +110,6 @@
     <t>FARTCOINUSDT</t>
   </si>
   <si>
-    <t>FLMUSDT</t>
-  </si>
-  <si>
-    <t>FUELUSDT</t>
-  </si>
-  <si>
     <t>FUSDT</t>
   </si>
   <si>
@@ -170,9 +152,6 @@
     <t>MORPHOUSDT</t>
   </si>
   <si>
-    <t>MYROUSDT</t>
-  </si>
-  <si>
     <t>NEARUSDT</t>
   </si>
   <si>
@@ -191,15 +170,9 @@
     <t>PENDLEUSDT</t>
   </si>
   <si>
-    <t>PERPUSDT</t>
-  </si>
-  <si>
     <t>POPCATUSDT</t>
   </si>
   <si>
-    <t>PRCLUSDT</t>
-  </si>
-  <si>
     <t>PROMUSDT</t>
   </si>
   <si>
@@ -254,54 +227,15 @@
     <t>1000000BABYDOGEUSDT</t>
   </si>
   <si>
-    <t>1000000PEIPEIUSDT</t>
-  </si>
-  <si>
-    <t>10000COQUSDT</t>
-  </si>
-  <si>
-    <t>10000ELONUSDT</t>
-  </si>
-  <si>
-    <t>10000QUBICUSDT</t>
-  </si>
-  <si>
-    <t>10000SATSUSDT</t>
-  </si>
-  <si>
-    <t>10000WENUSDT</t>
-  </si>
-  <si>
-    <t>10000WHYUSDT</t>
-  </si>
-  <si>
     <t>1000CATUSDT</t>
   </si>
   <si>
-    <t>1000FLOKIUSDT</t>
-  </si>
-  <si>
-    <t>1000NEIROCTOUSDT</t>
-  </si>
-  <si>
-    <t>1000TOSHIUSDT</t>
-  </si>
-  <si>
-    <t>1000TURBOUSDT</t>
-  </si>
-  <si>
-    <t>1000XUSDT</t>
-  </si>
-  <si>
     <t>1000XECUSDT</t>
   </si>
   <si>
     <t>AUSDT</t>
   </si>
   <si>
-    <t>A8USDT</t>
-  </si>
-  <si>
     <t>AAVEUSDT</t>
   </si>
   <si>
@@ -332,21 +266,6 @@
     <t>AGLDUSDT</t>
   </si>
   <si>
-    <t>AGTUSDT</t>
-  </si>
-  <si>
-    <t>AIUSDT</t>
-  </si>
-  <si>
-    <t>AI16ZUSDT</t>
-  </si>
-  <si>
-    <t>AINUSDT</t>
-  </si>
-  <si>
-    <t>AIOZUSDT</t>
-  </si>
-  <si>
     <t>AIXBTUSDT</t>
   </si>
   <si>
@@ -356,21 +275,12 @@
     <t>ALCHUSDT</t>
   </si>
   <si>
-    <t>ALEOUSDT</t>
-  </si>
-  <si>
     <t>ALICEUSDT</t>
   </si>
   <si>
-    <t>ALPHAUSDT</t>
-  </si>
-  <si>
     <t>ALTUSDT</t>
   </si>
   <si>
-    <t>ALUUSDT</t>
-  </si>
-  <si>
     <t>ANIMEUSDT</t>
   </si>
   <si>
@@ -392,15 +302,9 @@
     <t>ARPAUSDT</t>
   </si>
   <si>
-    <t>ASPUSDT</t>
-  </si>
-  <si>
     <t>ASTRUSDT</t>
   </si>
   <si>
-    <t>ATAUSDT</t>
-  </si>
-  <si>
     <t>ATHUSDT</t>
   </si>
   <si>
@@ -410,18 +314,9 @@
     <t>AUCTIONUSDT</t>
   </si>
   <si>
-    <t>AUDIOUSDT</t>
-  </si>
-  <si>
     <t>AVAUSDT</t>
   </si>
   <si>
-    <t>AVAILUSDT</t>
-  </si>
-  <si>
-    <t>AVLUSDT</t>
-  </si>
-  <si>
     <t>AWEUSDT</t>
   </si>
   <si>
@@ -440,12 +335,6 @@
     <t>BABYUSDT</t>
   </si>
   <si>
-    <t>BADGERUSDT</t>
-  </si>
-  <si>
-    <t>BAKEUSDT</t>
-  </si>
-  <si>
     <t>BANUSDT</t>
   </si>
   <si>
@@ -467,9 +356,6 @@
     <t>BCHUSDT</t>
   </si>
   <si>
-    <t>BDXNUSDT</t>
-  </si>
-  <si>
     <t>BEAMUSDT</t>
   </si>
   <si>
@@ -506,12 +392,6 @@
     <t>BSVUSDT</t>
   </si>
   <si>
-    <t>BSWUSDT</t>
-  </si>
-  <si>
-    <t>BTCUSDT</t>
-  </si>
-  <si>
     <t>CUSDT</t>
   </si>
   <si>
@@ -530,9 +410,6 @@
     <t>CELOUSDT</t>
   </si>
   <si>
-    <t>CELRUSDT</t>
-  </si>
-  <si>
     <t>CETUSUSDT</t>
   </si>
   <si>
@@ -542,9 +419,6 @@
     <t>CGPTUSDT</t>
   </si>
   <si>
-    <t>CHESSUSDT</t>
-  </si>
-  <si>
     <t>CHILLGUYUSDT</t>
   </si>
   <si>
@@ -560,21 +434,12 @@
     <t>CLOUDUSDT</t>
   </si>
   <si>
-    <t>COOKUSDT</t>
-  </si>
-  <si>
     <t>COOKIEUSDT</t>
   </si>
   <si>
-    <t>COSUSDT</t>
-  </si>
-  <si>
     <t>COWUSDT</t>
   </si>
   <si>
-    <t>CPOOLUSDT</t>
-  </si>
-  <si>
     <t>CROUSDT</t>
   </si>
   <si>
@@ -587,9 +452,6 @@
     <t>CTCUSDT</t>
   </si>
   <si>
-    <t>CTSIUSDT</t>
-  </si>
-  <si>
     <t>CVCUSDT</t>
   </si>
   <si>
@@ -611,30 +473,15 @@
     <t>DEGENUSDT</t>
   </si>
   <si>
-    <t>DENTUSDT</t>
-  </si>
-  <si>
     <t>DEXEUSDT</t>
   </si>
   <si>
-    <t>DGBUSDT</t>
-  </si>
-  <si>
     <t>DIAUSDT</t>
   </si>
   <si>
-    <t>DMCUSDT</t>
-  </si>
-  <si>
-    <t>DODOUSDT</t>
-  </si>
-  <si>
     <t>DOGUSDT</t>
   </si>
   <si>
-    <t>DOGSUSDT</t>
-  </si>
-  <si>
     <t>DOODUSDT</t>
   </si>
   <si>
@@ -644,9 +491,6 @@
     <t>DRIFTUSDT</t>
   </si>
   <si>
-    <t>DUCKUSDT</t>
-  </si>
-  <si>
     <t>DUSKUSDT</t>
   </si>
   <si>
@@ -665,9 +509,6 @@
     <t>EIGENUSDT</t>
   </si>
   <si>
-    <t>ELXUSDT</t>
-  </si>
-  <si>
     <t>ENJUSDT</t>
   </si>
   <si>
@@ -677,9 +518,6 @@
     <t>EPICUSDT</t>
   </si>
   <si>
-    <t>EPTUSDT</t>
-  </si>
-  <si>
     <t>ERAUSDT</t>
   </si>
   <si>
@@ -695,955 +533,775 @@
     <t>ETHFIUSDT</t>
   </si>
   <si>
-    <t>ETHWUSDT</t>
-  </si>
-  <si>
-    <t>FBUSDT</t>
+    <t>FIDAUSDT</t>
+  </si>
+  <si>
+    <t>FILUSDT</t>
+  </si>
+  <si>
+    <t>FIOUSDT</t>
+  </si>
+  <si>
+    <t>FLOCKUSDT</t>
+  </si>
+  <si>
+    <t>FLOWUSDT</t>
+  </si>
+  <si>
+    <t>FLRUSDT</t>
+  </si>
+  <si>
+    <t>FLUXUSDT</t>
+  </si>
+  <si>
+    <t>FORMUSDT</t>
+  </si>
+  <si>
+    <t>GASUSDT</t>
+  </si>
+  <si>
+    <t>GIGAUSDT</t>
+  </si>
+  <si>
+    <t>GLMUSDT</t>
+  </si>
+  <si>
+    <t>GMXUSDT</t>
+  </si>
+  <si>
+    <t>GNOUSDT</t>
+  </si>
+  <si>
+    <t>GOATUSDT</t>
+  </si>
+  <si>
+    <t>GODSUSDT</t>
+  </si>
+  <si>
+    <t>GPSUSDT</t>
+  </si>
+  <si>
+    <t>GRASSUSDT</t>
+  </si>
+  <si>
+    <t>GRIFFAINUSDT</t>
+  </si>
+  <si>
+    <t>GRTUSDT</t>
+  </si>
+  <si>
+    <t>GUNUSDT</t>
+  </si>
+  <si>
+    <t>HUSDT</t>
+  </si>
+  <si>
+    <t>HAEDALUSDT</t>
+  </si>
+  <si>
+    <t>HBARUSDT</t>
+  </si>
+  <si>
+    <t>HEIUSDT</t>
+  </si>
+  <si>
+    <t>HFTUSDT</t>
+  </si>
+  <si>
+    <t>HIGHUSDT</t>
+  </si>
+  <si>
+    <t>HIPPOUSDT</t>
+  </si>
+  <si>
+    <t>HIVEUSDT</t>
+  </si>
+  <si>
+    <t>HMSTRUSDT</t>
+  </si>
+  <si>
+    <t>HNTUSDT</t>
+  </si>
+  <si>
+    <t>HOMEUSDT</t>
+  </si>
+  <si>
+    <t>HPOS10IUSDT</t>
+  </si>
+  <si>
+    <t>HUMAUSDT</t>
+  </si>
+  <si>
+    <t>HYPEUSDT</t>
+  </si>
+  <si>
+    <t>HYPERUSDT</t>
+  </si>
+  <si>
+    <t>ICNTUSDT</t>
+  </si>
+  <si>
+    <t>ICXUSDT</t>
+  </si>
+  <si>
+    <t>IDUSDT</t>
+  </si>
+  <si>
+    <t>ILVUSDT</t>
+  </si>
+  <si>
+    <t>IMXUSDT</t>
+  </si>
+  <si>
+    <t>INITUSDT</t>
+  </si>
+  <si>
+    <t>INJUSDT</t>
+  </si>
+  <si>
+    <t>IOUSDT</t>
+  </si>
+  <si>
+    <t>IOSTUSDT</t>
+  </si>
+  <si>
+    <t>IOTAUSDT</t>
+  </si>
+  <si>
+    <t>IOTXUSDT</t>
+  </si>
+  <si>
+    <t>IPUSDT</t>
+  </si>
+  <si>
+    <t>JELLYJELLYUSDT</t>
+  </si>
+  <si>
+    <t>JSTUSDT</t>
+  </si>
+  <si>
+    <t>KAIAUSDT</t>
+  </si>
+  <si>
+    <t>KAITOUSDT</t>
+  </si>
+  <si>
+    <t>KAVAUSDT</t>
+  </si>
+  <si>
+    <t>KNCUSDT</t>
+  </si>
+  <si>
+    <t>KSMUSDT</t>
+  </si>
+  <si>
+    <t>LAUSDT</t>
+  </si>
+  <si>
+    <t>LDOUSDT</t>
+  </si>
+  <si>
+    <t>LISTAUSDT</t>
+  </si>
+  <si>
+    <t>LPTUSDT</t>
+  </si>
+  <si>
+    <t>LQTYUSDT</t>
+  </si>
+  <si>
+    <t>LRCUSDT</t>
+  </si>
+  <si>
+    <t>LSKUSDT</t>
+  </si>
+  <si>
+    <t>LTCUSDT</t>
+  </si>
+  <si>
+    <t>LUMIAUSDT</t>
+  </si>
+  <si>
+    <t>LUNA2USDT</t>
+  </si>
+  <si>
+    <t>MUSDT</t>
+  </si>
+  <si>
+    <t>MAGICUSDT</t>
+  </si>
+  <si>
+    <t>MANTAUSDT</t>
+  </si>
+  <si>
+    <t>MASKUSDT</t>
+  </si>
+  <si>
+    <t>MAVUSDT</t>
+  </si>
+  <si>
+    <t>MAVIAUSDT</t>
+  </si>
+  <si>
+    <t>MBOXUSDT</t>
+  </si>
+  <si>
+    <t>MEUSDT</t>
+  </si>
+  <si>
+    <t>MELANIAUSDT</t>
+  </si>
+  <si>
+    <t>MEMEUSDT</t>
+  </si>
+  <si>
+    <t>MERLUSDT</t>
+  </si>
+  <si>
+    <t>METISUSDT</t>
+  </si>
+  <si>
+    <t>MINAUSDT</t>
+  </si>
+  <si>
+    <t>MLNUSDT</t>
+  </si>
+  <si>
+    <t>MOCAUSDT</t>
+  </si>
+  <si>
+    <t>MOVEUSDT</t>
+  </si>
+  <si>
+    <t>MOVRUSDT</t>
+  </si>
+  <si>
+    <t>MTLUSDT</t>
+  </si>
+  <si>
+    <t>MUBARAKUSDT</t>
+  </si>
+  <si>
+    <t>NEOUSDT</t>
+  </si>
+  <si>
+    <t>NEWTUSDT</t>
+  </si>
+  <si>
+    <t>NILUSDT</t>
+  </si>
+  <si>
+    <t>NMRUSDT</t>
+  </si>
+  <si>
+    <t>NXPCUSDT</t>
+  </si>
+  <si>
+    <t>OGUSDT</t>
+  </si>
+  <si>
+    <t>OGNUSDT</t>
+  </si>
+  <si>
+    <t>OLUSDT</t>
+  </si>
+  <si>
+    <t>ONGUSDT</t>
+  </si>
+  <si>
+    <t>ONTUSDT</t>
+  </si>
+  <si>
+    <t>ORBSUSDT</t>
+  </si>
+  <si>
+    <t>ORDERUSDT</t>
+  </si>
+  <si>
+    <t>ORDIUSDT</t>
+  </si>
+  <si>
+    <t>OXTUSDT</t>
+  </si>
+  <si>
+    <t>PARTIUSDT</t>
+  </si>
+  <si>
+    <t>PAXGUSDT</t>
+  </si>
+  <si>
+    <t>PEAQUSDT</t>
+  </si>
+  <si>
+    <t>PENGUUSDT</t>
+  </si>
+  <si>
+    <t>PEOPLEUSDT</t>
+  </si>
+  <si>
+    <t>PHAUSDT</t>
+  </si>
+  <si>
+    <t>PIPPINUSDT</t>
+  </si>
+  <si>
+    <t>PIXELUSDT</t>
+  </si>
+  <si>
+    <t>PLUMEUSDT</t>
+  </si>
+  <si>
+    <t>PNUTUSDT</t>
+  </si>
+  <si>
+    <t>POLUSDT</t>
+  </si>
+  <si>
+    <t>POLYXUSDT</t>
+  </si>
+  <si>
+    <t>PORTALUSDT</t>
+  </si>
+  <si>
+    <t>POWRUSDT</t>
+  </si>
+  <si>
+    <t>PROMPTUSDT</t>
+  </si>
+  <si>
+    <t>PUFFERUSDT</t>
+  </si>
+  <si>
+    <t>PUMPBTCUSDT</t>
+  </si>
+  <si>
+    <t>PUMPFUNUSDT</t>
+  </si>
+  <si>
+    <t>PYRUSDT</t>
+  </si>
+  <si>
+    <t>QNTUSDT</t>
+  </si>
+  <si>
+    <t>QTUMUSDT</t>
+  </si>
+  <si>
+    <t>RAREUSDT</t>
+  </si>
+  <si>
+    <t>RAYDIUMUSDT</t>
+  </si>
+  <si>
+    <t>RDNTUSDT</t>
+  </si>
+  <si>
+    <t>REDUSDT</t>
+  </si>
+  <si>
+    <t>RENDERUSDT</t>
+  </si>
+  <si>
+    <t>RESOLVUSDT</t>
+  </si>
+  <si>
+    <t>REZUSDT</t>
+  </si>
+  <si>
+    <t>RLCUSDT</t>
+  </si>
+  <si>
+    <t>ROAMUSDT</t>
+  </si>
+  <si>
+    <t>ROSEUSDT</t>
+  </si>
+  <si>
+    <t>RPLUSDT</t>
+  </si>
+  <si>
+    <t>RSRUSDT</t>
+  </si>
+  <si>
+    <t>RVNUSDT</t>
+  </si>
+  <si>
+    <t>SUSDT</t>
+  </si>
+  <si>
+    <t>SAFEUSDT</t>
+  </si>
+  <si>
+    <t>SAGAUSDT</t>
+  </si>
+  <si>
+    <t>SAHARAUSDT</t>
+  </si>
+  <si>
+    <t>SANDUSDT</t>
+  </si>
+  <si>
+    <t>SCUSDT</t>
+  </si>
+  <si>
+    <t>SCRUSDT</t>
+  </si>
+  <si>
+    <t>SCRTUSDT</t>
+  </si>
+  <si>
+    <t>SEIUSDT</t>
+  </si>
+  <si>
+    <t>SHELLUSDT</t>
+  </si>
+  <si>
+    <t>SIGNUSDT</t>
+  </si>
+  <si>
+    <t>SIRENUSDT</t>
+  </si>
+  <si>
+    <t>SLPUSDT</t>
+  </si>
+  <si>
+    <t>SNTUSDT</t>
+  </si>
+  <si>
+    <t>SOLAYERUSDT</t>
+  </si>
+  <si>
+    <t>SOLVUSDT</t>
+  </si>
+  <si>
+    <t>SONICUSDT</t>
+  </si>
+  <si>
+    <t>SOONUSDT</t>
+  </si>
+  <si>
+    <t>SOPHUSDT</t>
+  </si>
+  <si>
+    <t>SOSOUSDT</t>
+  </si>
+  <si>
+    <t>SPKUSDT</t>
+  </si>
+  <si>
+    <t>SQDUSDT</t>
+  </si>
+  <si>
+    <t>SSVUSDT</t>
+  </si>
+  <si>
+    <t>STEEMUSDT</t>
+  </si>
+  <si>
+    <t>STGUSDT</t>
+  </si>
+  <si>
+    <t>STOUSDT</t>
+  </si>
+  <si>
+    <t>STORJUSDT</t>
+  </si>
+  <si>
+    <t>STRKUSDT</t>
+  </si>
+  <si>
+    <t>STXUSDT</t>
+  </si>
+  <si>
+    <t>SUIUSDT</t>
+  </si>
+  <si>
+    <t>SUNUSDT</t>
+  </si>
+  <si>
+    <t>SUPERUSDT</t>
+  </si>
+  <si>
+    <t>SUSHIUSDT</t>
+  </si>
+  <si>
+    <t>SWARMSUSDT</t>
+  </si>
+  <si>
+    <t>SYNUSDT</t>
+  </si>
+  <si>
+    <t>SYRUPUSDT</t>
+  </si>
+  <si>
+    <t>TUSDT</t>
+  </si>
+  <si>
+    <t>TAUSDT</t>
+  </si>
+  <si>
+    <t>TACUSDT</t>
+  </si>
+  <si>
+    <t>TAOUSDT</t>
+  </si>
+  <si>
+    <t>THEUSDT</t>
+  </si>
+  <si>
+    <t>THETAUSDT</t>
+  </si>
+  <si>
+    <t>TIAUSDT</t>
+  </si>
+  <si>
+    <t>TLMUSDT</t>
+  </si>
+  <si>
+    <t>TNSRUSDT</t>
+  </si>
+  <si>
+    <t>TRUUSDT</t>
+  </si>
+  <si>
+    <t>TRUMPUSDT</t>
+  </si>
+  <si>
+    <t>TRXUSDT</t>
+  </si>
+  <si>
+    <t>TSTBSCUSDT</t>
+  </si>
+  <si>
+    <t>TUTUSDT</t>
+  </si>
+  <si>
+    <t>TWTUSDT</t>
+  </si>
+  <si>
+    <t>UMAUSDT</t>
+  </si>
+  <si>
+    <t>UNIUSDT</t>
+  </si>
+  <si>
+    <t>USD1USDT</t>
+  </si>
+  <si>
+    <t>USDCUSDT</t>
+  </si>
+  <si>
+    <t>USDEUSDT</t>
+  </si>
+  <si>
+    <t>USELESSUSDT</t>
+  </si>
+  <si>
+    <t>USTCUSDT</t>
+  </si>
+  <si>
+    <t>USUALUSDT</t>
+  </si>
+  <si>
+    <t>VANAUSDT</t>
+  </si>
+  <si>
+    <t>VANRYUSDT</t>
+  </si>
+  <si>
+    <t>VELOUSDT</t>
+  </si>
+  <si>
+    <t>VELODROMEUSDT</t>
+  </si>
+  <si>
+    <t>VELVETUSDT</t>
+  </si>
+  <si>
+    <t>VETUSDT</t>
+  </si>
+  <si>
+    <t>VINEUSDT</t>
+  </si>
+  <si>
+    <t>VIRTUALUSDT</t>
+  </si>
+  <si>
+    <t>VVVUSDT</t>
+  </si>
+  <si>
+    <t>WUSDT</t>
+  </si>
+  <si>
+    <t>WALUSDT</t>
+  </si>
+  <si>
+    <t>WCTUSDT</t>
+  </si>
+  <si>
+    <t>WLDUSDT</t>
+  </si>
+  <si>
+    <t>WOOUSDT</t>
+  </si>
+  <si>
+    <t>XAIUSDT</t>
+  </si>
+  <si>
+    <t>XAUTUSDT</t>
+  </si>
+  <si>
+    <t>XDCUSDT</t>
+  </si>
+  <si>
+    <t>XIONUSDT</t>
+  </si>
+  <si>
+    <t>XMRUSDT</t>
+  </si>
+  <si>
+    <t>XTZUSDT</t>
+  </si>
+  <si>
+    <t>XVGUSDT</t>
+  </si>
+  <si>
+    <t>XVSUSDT</t>
+  </si>
+  <si>
+    <t>YFIUSDT</t>
+  </si>
+  <si>
+    <t>YGGUSDT</t>
+  </si>
+  <si>
+    <t>ZBCNUSDT</t>
+  </si>
+  <si>
+    <t>ZECUSDT</t>
+  </si>
+  <si>
+    <t>ZEREBROUSDT</t>
+  </si>
+  <si>
+    <t>ZETAUSDT</t>
+  </si>
+  <si>
+    <t>ZILUSDT</t>
+  </si>
+  <si>
+    <t>ZKUSDT</t>
+  </si>
+  <si>
+    <t>ZORAUSDT</t>
+  </si>
+  <si>
+    <t>ZROUSDT</t>
+  </si>
+  <si>
+    <t>1000000CHEEMSUSDT</t>
+  </si>
+  <si>
+    <t>1000RATSUSDT</t>
+  </si>
+  <si>
+    <t>ARUSDT</t>
+  </si>
+  <si>
+    <t>BLASTUSDT</t>
+  </si>
+  <si>
+    <t>CKBUSDT</t>
+  </si>
+  <si>
+    <t>ICPUSDT</t>
+  </si>
+  <si>
+    <t>KERNELUSDT</t>
+  </si>
+  <si>
+    <t>PUNDIXUSDT</t>
+  </si>
+  <si>
+    <t>RONINUSDT</t>
+  </si>
+  <si>
+    <t>TAIKOUSDT</t>
+  </si>
+  <si>
+    <t>WAXPUSDT</t>
+  </si>
+  <si>
+    <t>WAVESUSDT</t>
+  </si>
+  <si>
+    <t>MYXUSDT</t>
+  </si>
+  <si>
+    <t>0GUSDT</t>
+  </si>
+  <si>
+    <t>4USDT</t>
+  </si>
+  <si>
+    <t>AIOUSDT</t>
+  </si>
+  <si>
+    <t>ALLOUSDT</t>
+  </si>
+  <si>
+    <t>APRUSDT</t>
+  </si>
+  <si>
+    <t>ARIAUSDT</t>
+  </si>
+  <si>
+    <t>ASRUSDT</t>
+  </si>
+  <si>
+    <t>ASTERUSDT</t>
+  </si>
+  <si>
+    <t>ATUSDT</t>
+  </si>
+  <si>
+    <t>AVNTUSDT</t>
+  </si>
+  <si>
+    <t>GENIUSUSDT</t>
+  </si>
+  <si>
+    <t>BTRUSDT</t>
+  </si>
+  <si>
+    <t>BEATUSDT</t>
+  </si>
+  <si>
+    <t>LIGHTUSDT</t>
   </si>
   <si>
     <t>FHEUSDT</t>
   </si>
   <si>
-    <t>FIDAUSDT</t>
-  </si>
-  <si>
-    <t>FILUSDT</t>
-  </si>
-  <si>
-    <t>FIOUSDT</t>
-  </si>
-  <si>
-    <t>FLOCKUSDT</t>
-  </si>
-  <si>
-    <t>FLOWUSDT</t>
-  </si>
-  <si>
-    <t>FLRUSDT</t>
-  </si>
-  <si>
-    <t>FLUXUSDT</t>
-  </si>
-  <si>
-    <t>FORMUSDT</t>
-  </si>
-  <si>
-    <t>FORTHUSDT</t>
-  </si>
-  <si>
-    <t>FRAGUSDT</t>
-  </si>
-  <si>
-    <t>FWOGUSDT</t>
-  </si>
-  <si>
-    <t>FXSUSDT</t>
-  </si>
-  <si>
-    <t>GUSDT</t>
-  </si>
-  <si>
-    <t>GASUSDT</t>
-  </si>
-  <si>
-    <t>GIGAUSDT</t>
-  </si>
-  <si>
-    <t>GLMUSDT</t>
-  </si>
-  <si>
-    <t>GMXUSDT</t>
-  </si>
-  <si>
-    <t>GNOUSDT</t>
-  </si>
-  <si>
-    <t>GOATUSDT</t>
-  </si>
-  <si>
-    <t>GODSUSDT</t>
-  </si>
-  <si>
-    <t>GORKUSDT</t>
-  </si>
-  <si>
-    <t>GPSUSDT</t>
-  </si>
-  <si>
-    <t>GRASSUSDT</t>
-  </si>
-  <si>
-    <t>GRIFFAINUSDT</t>
-  </si>
-  <si>
-    <t>GRTUSDT</t>
-  </si>
-  <si>
-    <t>GTCUSDT</t>
-  </si>
-  <si>
-    <t>GUNUSDT</t>
-  </si>
-  <si>
-    <t>HUSDT</t>
-  </si>
-  <si>
-    <t>HAEDALUSDT</t>
-  </si>
-  <si>
-    <t>HBARUSDT</t>
-  </si>
-  <si>
-    <t>HEIUSDT</t>
-  </si>
-  <si>
-    <t>HFTUSDT</t>
-  </si>
-  <si>
-    <t>HIFIUSDT</t>
-  </si>
-  <si>
-    <t>HIGHUSDT</t>
-  </si>
-  <si>
-    <t>HIPPOUSDT</t>
-  </si>
-  <si>
-    <t>HIVEUSDT</t>
-  </si>
-  <si>
-    <t>HMSTRUSDT</t>
-  </si>
-  <si>
-    <t>HNTUSDT</t>
-  </si>
-  <si>
-    <t>HOMEUSDT</t>
-  </si>
-  <si>
-    <t>HOOKUSDT</t>
-  </si>
-  <si>
-    <t>HOTUSDT</t>
-  </si>
-  <si>
-    <t>HPOS10IUSDT</t>
-  </si>
-  <si>
-    <t>HUMAUSDT</t>
-  </si>
-  <si>
-    <t>HYPEUSDT</t>
-  </si>
-  <si>
-    <t>HYPERUSDT</t>
-  </si>
-  <si>
-    <t>ICNTUSDT</t>
-  </si>
-  <si>
-    <t>ICXUSDT</t>
-  </si>
-  <si>
-    <t>IDUSDT</t>
-  </si>
-  <si>
-    <t>IDEXUSDT</t>
-  </si>
-  <si>
-    <t>ILVUSDT</t>
-  </si>
-  <si>
-    <t>IMXUSDT</t>
-  </si>
-  <si>
-    <t>INITUSDT</t>
-  </si>
-  <si>
-    <t>INJUSDT</t>
-  </si>
-  <si>
-    <t>IOUSDT</t>
-  </si>
-  <si>
-    <t>IOSTUSDT</t>
-  </si>
-  <si>
-    <t>IOTAUSDT</t>
-  </si>
-  <si>
-    <t>IOTXUSDT</t>
-  </si>
-  <si>
-    <t>IPUSDT</t>
-  </si>
-  <si>
-    <t>JUSDT</t>
-  </si>
-  <si>
-    <t>JELLYJELLYUSDT</t>
-  </si>
-  <si>
-    <t>JOEUSDT</t>
-  </si>
-  <si>
-    <t>JSTUSDT</t>
-  </si>
-  <si>
-    <t>KAIAUSDT</t>
-  </si>
-  <si>
-    <t>KAITOUSDT</t>
-  </si>
-  <si>
-    <t>KAVAUSDT</t>
-  </si>
-  <si>
-    <t>KDAUSDT</t>
-  </si>
-  <si>
-    <t>KNCUSDT</t>
-  </si>
-  <si>
-    <t>KSMUSDT</t>
-  </si>
-  <si>
-    <t>L3USDT</t>
-  </si>
-  <si>
-    <t>LAUSDT</t>
-  </si>
-  <si>
-    <t>LAUNCHCOINUSDT</t>
-  </si>
-  <si>
-    <t>LDOUSDT</t>
-  </si>
-  <si>
-    <t>LISTAUSDT</t>
-  </si>
-  <si>
-    <t>LOOKSUSDT</t>
-  </si>
-  <si>
-    <t>LPTUSDT</t>
-  </si>
-  <si>
-    <t>LQTYUSDT</t>
-  </si>
-  <si>
-    <t>LRCUSDT</t>
-  </si>
-  <si>
-    <t>LSKUSDT</t>
-  </si>
-  <si>
-    <t>LTCUSDT</t>
-  </si>
-  <si>
-    <t>LUMIAUSDT</t>
-  </si>
-  <si>
-    <t>LUNA2USDT</t>
-  </si>
-  <si>
-    <t>MUSDT</t>
-  </si>
-  <si>
-    <t>MAGICUSDT</t>
-  </si>
-  <si>
-    <t>MAJORUSDT</t>
-  </si>
-  <si>
-    <t>MANTAUSDT</t>
-  </si>
-  <si>
-    <t>MASAUSDT</t>
-  </si>
-  <si>
-    <t>MASKUSDT</t>
-  </si>
-  <si>
-    <t>MAVUSDT</t>
-  </si>
-  <si>
-    <t>MAVIAUSDT</t>
-  </si>
-  <si>
-    <t>MBLUSDT</t>
-  </si>
-  <si>
-    <t>MBOXUSDT</t>
-  </si>
-  <si>
-    <t>MEUSDT</t>
-  </si>
-  <si>
-    <t>MELANIAUSDT</t>
-  </si>
-  <si>
-    <t>MEMEUSDT</t>
-  </si>
-  <si>
-    <t>MERLUSDT</t>
-  </si>
-  <si>
-    <t>METISUSDT</t>
-  </si>
-  <si>
-    <t>MILKUSDT</t>
-  </si>
-  <si>
-    <t>MINAUSDT</t>
-  </si>
-  <si>
-    <t>MKRUSDT</t>
-  </si>
-  <si>
-    <t>MLNUSDT</t>
-  </si>
-  <si>
-    <t>MOCAUSDT</t>
-  </si>
-  <si>
-    <t>MOVEUSDT</t>
-  </si>
-  <si>
-    <t>MOVRUSDT</t>
-  </si>
-  <si>
-    <t>MTLUSDT</t>
-  </si>
-  <si>
-    <t>MUBARAKUSDT</t>
-  </si>
-  <si>
-    <t>MVLUSDT</t>
-  </si>
-  <si>
-    <t>MYRIAUSDT</t>
-  </si>
-  <si>
-    <t>NEIROETHUSDT</t>
-  </si>
-  <si>
-    <t>NEOUSDT</t>
-  </si>
-  <si>
-    <t>NEWTUSDT</t>
-  </si>
-  <si>
-    <t>NFPUSDT</t>
-  </si>
-  <si>
-    <t>NILUSDT</t>
-  </si>
-  <si>
-    <t>NKNUSDT</t>
-  </si>
-  <si>
-    <t>NMRUSDT</t>
-  </si>
-  <si>
-    <t>NSUSDT</t>
-  </si>
-  <si>
-    <t>NTRNUSDT</t>
-  </si>
-  <si>
-    <t>NXPCUSDT</t>
-  </si>
-  <si>
-    <t>OBOLUSDT</t>
-  </si>
-  <si>
-    <t>OBTUSDT</t>
-  </si>
-  <si>
-    <t>OGUSDT</t>
-  </si>
-  <si>
-    <t>OGNUSDT</t>
-  </si>
-  <si>
-    <t>OLUSDT</t>
-  </si>
-  <si>
-    <t>OMUSDT</t>
-  </si>
-  <si>
-    <t>OMNIUSDT</t>
-  </si>
-  <si>
-    <t>ONEUSDT</t>
-  </si>
-  <si>
-    <t>ONGUSDT</t>
-  </si>
-  <si>
-    <t>ONTUSDT</t>
-  </si>
-  <si>
-    <t>ORBSUSDT</t>
-  </si>
-  <si>
-    <t>ORDERUSDT</t>
-  </si>
-  <si>
-    <t>ORDIUSDT</t>
-  </si>
-  <si>
-    <t>OSMOUSDT</t>
-  </si>
-  <si>
-    <t>OXTUSDT</t>
-  </si>
-  <si>
-    <t>PARTIUSDT</t>
-  </si>
-  <si>
-    <t>PAXGUSDT</t>
-  </si>
-  <si>
-    <t>PEAQUSDT</t>
-  </si>
-  <si>
-    <t>PENGUUSDT</t>
-  </si>
-  <si>
-    <t>PEOPLEUSDT</t>
-  </si>
-  <si>
-    <t>PHAUSDT</t>
-  </si>
-  <si>
-    <t>PHBUSDT</t>
-  </si>
-  <si>
-    <t>PIPPINUSDT</t>
-  </si>
-  <si>
-    <t>PIXELUSDT</t>
-  </si>
-  <si>
-    <t>PLUMEUSDT</t>
-  </si>
-  <si>
-    <t>PNUTUSDT</t>
-  </si>
-  <si>
-    <t>POLUSDT</t>
-  </si>
-  <si>
-    <t>POLYXUSDT</t>
-  </si>
-  <si>
-    <t>PONKEUSDT</t>
-  </si>
-  <si>
-    <t>PORTALUSDT</t>
-  </si>
-  <si>
-    <t>POWRUSDT</t>
-  </si>
-  <si>
-    <t>PRIMEUSDT</t>
-  </si>
-  <si>
-    <t>PROMPTUSDT</t>
-  </si>
-  <si>
-    <t>PUFFERUSDT</t>
-  </si>
-  <si>
-    <t>PUMPBTCUSDT</t>
-  </si>
-  <si>
-    <t>PUMPFUNUSDT</t>
-  </si>
-  <si>
-    <t>PYRUSDT</t>
-  </si>
-  <si>
-    <t>QIUSDT</t>
-  </si>
-  <si>
-    <t>QNTUSDT</t>
-  </si>
-  <si>
-    <t>QTUMUSDT</t>
-  </si>
-  <si>
-    <t>QUICKUSDT</t>
-  </si>
-  <si>
-    <t>RADUSDT</t>
-  </si>
-  <si>
-    <t>RAREUSDT</t>
-  </si>
-  <si>
-    <t>RAYDIUMUSDT</t>
-  </si>
-  <si>
-    <t>RDNTUSDT</t>
-  </si>
-  <si>
-    <t>REDUSDT</t>
-  </si>
-  <si>
-    <t>RENDERUSDT</t>
-  </si>
-  <si>
-    <t>RESOLVUSDT</t>
-  </si>
-  <si>
-    <t>REXUSDT</t>
-  </si>
-  <si>
-    <t>REZUSDT</t>
-  </si>
-  <si>
-    <t>RFCUSDT</t>
-  </si>
-  <si>
-    <t>RIFUSDT</t>
-  </si>
-  <si>
-    <t>RLCUSDT</t>
-  </si>
-  <si>
-    <t>ROAMUSDT</t>
-  </si>
-  <si>
-    <t>ROSEUSDT</t>
-  </si>
-  <si>
-    <t>RPLUSDT</t>
-  </si>
-  <si>
-    <t>RSRUSDT</t>
-  </si>
-  <si>
-    <t>RSS3USDT</t>
-  </si>
-  <si>
-    <t>RVNUSDT</t>
-  </si>
-  <si>
-    <t>SUSDT</t>
-  </si>
-  <si>
-    <t>SAFEUSDT</t>
-  </si>
-  <si>
-    <t>SAGAUSDT</t>
-  </si>
-  <si>
-    <t>SAHARAUSDT</t>
-  </si>
-  <si>
-    <t>SANDUSDT</t>
-  </si>
-  <si>
-    <t>SAROSUSDT</t>
-  </si>
-  <si>
-    <t>SCUSDT</t>
-  </si>
-  <si>
-    <t>SCAUSDT</t>
-  </si>
-  <si>
-    <t>SCRUSDT</t>
-  </si>
-  <si>
-    <t>SCRTUSDT</t>
-  </si>
-  <si>
-    <t>SDUSDT</t>
-  </si>
-  <si>
-    <t>SEIUSDT</t>
-  </si>
-  <si>
-    <t>SENDUSDT</t>
-  </si>
-  <si>
-    <t>SERAPHUSDT</t>
-  </si>
-  <si>
-    <t>SFPUSDT</t>
-  </si>
-  <si>
-    <t>SHELLUSDT</t>
-  </si>
-  <si>
-    <t>SIGNUSDT</t>
-  </si>
-  <si>
-    <t>SIRENUSDT</t>
-  </si>
-  <si>
-    <t>SKATEUSDT</t>
-  </si>
-  <si>
-    <t>SKYAIUSDT</t>
-  </si>
-  <si>
-    <t>SLERFUSDT</t>
-  </si>
-  <si>
-    <t>SLFUSDT</t>
-  </si>
-  <si>
-    <t>SLPUSDT</t>
-  </si>
-  <si>
-    <t>SNTUSDT</t>
-  </si>
-  <si>
-    <t>SOLAYERUSDT</t>
-  </si>
-  <si>
-    <t>SOLOUSDT</t>
-  </si>
-  <si>
-    <t>SOLVUSDT</t>
-  </si>
-  <si>
-    <t>SONICUSDT</t>
-  </si>
-  <si>
-    <t>SOONUSDT</t>
-  </si>
-  <si>
-    <t>SOPHUSDT</t>
-  </si>
-  <si>
-    <t>SOSOUSDT</t>
-  </si>
-  <si>
-    <t>SPECUSDT</t>
-  </si>
-  <si>
-    <t>SPELLUSDT</t>
-  </si>
-  <si>
-    <t>SPKUSDT</t>
-  </si>
-  <si>
-    <t>SQDUSDT</t>
-  </si>
-  <si>
-    <t>SSVUSDT</t>
-  </si>
-  <si>
-    <t>STEEMUSDT</t>
-  </si>
-  <si>
-    <t>STGUSDT</t>
-  </si>
-  <si>
-    <t>STOUSDT</t>
-  </si>
-  <si>
-    <t>STORJUSDT</t>
-  </si>
-  <si>
-    <t>STRKUSDT</t>
-  </si>
-  <si>
-    <t>STXUSDT</t>
-  </si>
-  <si>
-    <t>SUIUSDT</t>
-  </si>
-  <si>
-    <t>SUNUSDT</t>
-  </si>
-  <si>
-    <t>SUNDOGUSDT</t>
-  </si>
-  <si>
-    <t>SUPERUSDT</t>
-  </si>
-  <si>
-    <t>SUSHIUSDT</t>
-  </si>
-  <si>
-    <t>SWARMSUSDT</t>
-  </si>
-  <si>
-    <t>SWEATUSDT</t>
-  </si>
-  <si>
-    <t>SWELLUSDT</t>
-  </si>
-  <si>
-    <t>SXPUSDT</t>
-  </si>
-  <si>
-    <t>SYNUSDT</t>
-  </si>
-  <si>
-    <t>SYRUPUSDT</t>
-  </si>
-  <si>
-    <t>SYSUSDT</t>
-  </si>
-  <si>
-    <t>TUSDT</t>
-  </si>
-  <si>
-    <t>TAUSDT</t>
-  </si>
-  <si>
-    <t>TACUSDT</t>
-  </si>
-  <si>
-    <t>TAIUSDT</t>
-  </si>
-  <si>
-    <t>TANSSIUSDT</t>
-  </si>
-  <si>
-    <t>TAOUSDT</t>
-  </si>
-  <si>
-    <t>THEUSDT</t>
-  </si>
-  <si>
-    <t>THETAUSDT</t>
-  </si>
-  <si>
-    <t>TIAUSDT</t>
-  </si>
-  <si>
-    <t>TLMUSDT</t>
-  </si>
-  <si>
-    <t>TNSRUSDT</t>
-  </si>
-  <si>
-    <t>TOKENUSDT</t>
-  </si>
-  <si>
-    <t>TRUUSDT</t>
-  </si>
-  <si>
-    <t>TRUMPUSDT</t>
-  </si>
-  <si>
-    <t>TRXUSDT</t>
-  </si>
-  <si>
-    <t>TSTBSCUSDT</t>
-  </si>
-  <si>
-    <t>TUTUSDT</t>
-  </si>
-  <si>
-    <t>TWTUSDT</t>
-  </si>
-  <si>
-    <t>UMAUSDT</t>
-  </si>
-  <si>
-    <t>UNIUSDT</t>
-  </si>
-  <si>
-    <t>USD1USDT</t>
-  </si>
-  <si>
-    <t>USDCUSDT</t>
-  </si>
-  <si>
-    <t>USDEUSDT</t>
-  </si>
-  <si>
-    <t>USELESSUSDT</t>
-  </si>
-  <si>
-    <t>USTCUSDT</t>
-  </si>
-  <si>
-    <t>USUALUSDT</t>
-  </si>
-  <si>
-    <t>VANAUSDT</t>
-  </si>
-  <si>
-    <t>VANRYUSDT</t>
-  </si>
-  <si>
-    <t>VELOUSDT</t>
-  </si>
-  <si>
-    <t>VELODROMEUSDT</t>
-  </si>
-  <si>
-    <t>VELVETUSDT</t>
-  </si>
-  <si>
-    <t>VETUSDT</t>
-  </si>
-  <si>
-    <t>VICUSDT</t>
-  </si>
-  <si>
-    <t>VINEUSDT</t>
-  </si>
-  <si>
-    <t>VIRTUALUSDT</t>
-  </si>
-  <si>
-    <t>VOXELUSDT</t>
-  </si>
-  <si>
-    <t>VRUSDT</t>
-  </si>
-  <si>
-    <t>VTHOUSDT</t>
-  </si>
-  <si>
-    <t>VVVUSDT</t>
-  </si>
-  <si>
-    <t>WUSDT</t>
-  </si>
-  <si>
-    <t>WALUSDT</t>
-  </si>
-  <si>
-    <t>WCTUSDT</t>
-  </si>
-  <si>
-    <t>WLDUSDT</t>
-  </si>
-  <si>
-    <t>WOOUSDT</t>
-  </si>
-  <si>
-    <t>XAIUSDT</t>
-  </si>
-  <si>
-    <t>XAUTUSDT</t>
-  </si>
-  <si>
-    <t>XCHUSDT</t>
-  </si>
-  <si>
-    <t>XDCUSDT</t>
-  </si>
-  <si>
-    <t>XEMUSDT</t>
-  </si>
-  <si>
-    <t>XIONUSDT</t>
-  </si>
-  <si>
-    <t>XMRUSDT</t>
-  </si>
-  <si>
-    <t>XNOUSDT</t>
-  </si>
-  <si>
-    <t>XTERUSDT</t>
-  </si>
-  <si>
-    <t>XTZUSDT</t>
-  </si>
-  <si>
-    <t>XVGUSDT</t>
-  </si>
-  <si>
-    <t>XVSUSDT</t>
-  </si>
-  <si>
-    <t>YFIUSDT</t>
-  </si>
-  <si>
-    <t>YGGUSDT</t>
-  </si>
-  <si>
-    <t>ZBCNUSDT</t>
-  </si>
-  <si>
-    <t>ZECUSDT</t>
-  </si>
-  <si>
-    <t>ZENTUSDT</t>
-  </si>
-  <si>
-    <t>ZEREBROUSDT</t>
-  </si>
-  <si>
-    <t>ZETAUSDT</t>
-  </si>
-  <si>
-    <t>ZEUSUSDT</t>
-  </si>
-  <si>
-    <t>ZILUSDT</t>
-  </si>
-  <si>
-    <t>ZKUSDT</t>
-  </si>
-  <si>
-    <t>ZORAUSDT</t>
-  </si>
-  <si>
-    <t>ZRCUSDT</t>
-  </si>
-  <si>
-    <t>ZROUSDT</t>
-  </si>
-  <si>
-    <t>1000000CHEEMSUSDT</t>
-  </si>
-  <si>
-    <t>1000RATSUSDT</t>
-  </si>
-  <si>
-    <t>ARUSDT</t>
-  </si>
-  <si>
-    <t>BLASTUSDT</t>
-  </si>
-  <si>
-    <t>CKBUSDT</t>
-  </si>
-  <si>
-    <t>CUDISUSDT</t>
-  </si>
-  <si>
-    <t>GLMRUSDT</t>
-  </si>
-  <si>
-    <t>ICPUSDT</t>
-  </si>
-  <si>
-    <t>KERNELUSDT</t>
-  </si>
-  <si>
-    <t>PUNDIXUSDT</t>
-  </si>
-  <si>
-    <t>RONINUSDT</t>
-  </si>
-  <si>
-    <t>TAIKOUSDT</t>
-  </si>
-  <si>
-    <t>WAXPUSDT</t>
-  </si>
-  <si>
-    <t>WAVESUSDT</t>
-  </si>
-  <si>
-    <t>MYXUSDT</t>
+    <t>AKEUSDT</t>
+  </si>
+  <si>
+    <t>NOMUSDT</t>
+  </si>
+  <si>
+    <t>BLUAIUSDT</t>
+  </si>
+  <si>
+    <t>EDGEUSDT</t>
+  </si>
+  <si>
+    <t>MAGMAUSDT</t>
+  </si>
+  <si>
+    <t>FOGOUSDT</t>
+  </si>
+  <si>
+    <t>PIEVERSEUSDT</t>
   </si>
 </sst>
 </file>
@@ -2011,7 +1669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C536"/>
+  <dimension ref="A1:C419"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.5703125" bestFit="1" customWidth="1"/>
@@ -2030,1707 +1688,1707 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>400</v>
       </c>
       <c r="B2">
         <v>240</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>522</v>
+        <v>62</v>
       </c>
       <c r="B3">
         <v>240</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>387</v>
       </c>
       <c r="B4">
         <v>240</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>3</v>
       </c>
       <c r="B5">
         <v>240</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="B6">
         <v>240</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="B7">
         <v>240</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>388</v>
       </c>
       <c r="B8">
         <v>240</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="B9">
         <v>240</v>
       </c>
       <c r="C9" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
       <c r="B10">
         <v>240</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>78</v>
+        <v>401</v>
       </c>
       <c r="B11">
         <v>240</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="B12">
         <v>240</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="B13">
         <v>240</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="B14">
         <v>240</v>
       </c>
       <c r="C14" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="B15">
         <v>240</v>
       </c>
       <c r="C15" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="B16">
         <v>240</v>
       </c>
       <c r="C16" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B17">
         <v>240</v>
       </c>
       <c r="C17" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B18">
         <v>240</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="B19">
         <v>240</v>
       </c>
       <c r="C19" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>523</v>
+        <v>73</v>
       </c>
       <c r="B20">
         <v>240</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="B21">
         <v>240</v>
       </c>
       <c r="C21" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="B22">
         <v>240</v>
       </c>
       <c r="C22" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>402</v>
       </c>
       <c r="B23">
         <v>240</v>
       </c>
       <c r="C23" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B24">
         <v>240</v>
       </c>
       <c r="C24" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>9</v>
+        <v>415</v>
       </c>
       <c r="B25">
         <v>240</v>
       </c>
       <c r="C25" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B26">
         <v>240</v>
       </c>
       <c r="C26" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="B27">
         <v>240</v>
       </c>
       <c r="C27" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>89</v>
+        <v>7</v>
       </c>
       <c r="B28">
         <v>240</v>
       </c>
       <c r="C28" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="B29">
         <v>240</v>
       </c>
       <c r="C29" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>91</v>
+        <v>403</v>
       </c>
       <c r="B30">
         <v>240</v>
       </c>
       <c r="C30" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="B31">
         <v>240</v>
       </c>
       <c r="C31" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="B32">
         <v>240</v>
       </c>
       <c r="C32" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="B33">
         <v>240</v>
       </c>
       <c r="C33" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>94</v>
+        <v>8</v>
       </c>
       <c r="B34">
         <v>240</v>
       </c>
       <c r="C34" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>95</v>
+        <v>9</v>
       </c>
       <c r="B35">
         <v>240</v>
       </c>
       <c r="C35" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>96</v>
+        <v>404</v>
       </c>
       <c r="B36">
         <v>240</v>
       </c>
       <c r="C36" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B37">
         <v>240</v>
       </c>
       <c r="C37" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="B38">
         <v>240</v>
       </c>
       <c r="C38" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="B39">
         <v>240</v>
       </c>
       <c r="C39" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>100</v>
+        <v>405</v>
       </c>
       <c r="B40">
         <v>240</v>
       </c>
       <c r="C40" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="B41">
         <v>240</v>
       </c>
       <c r="C41" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="B42">
         <v>240</v>
       </c>
       <c r="C42" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="B43">
         <v>240</v>
       </c>
       <c r="C43" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>104</v>
+        <v>389</v>
       </c>
       <c r="B44">
         <v>240</v>
       </c>
       <c r="C44" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>105</v>
+        <v>406</v>
       </c>
       <c r="B45">
         <v>240</v>
       </c>
       <c r="C45" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>106</v>
+        <v>407</v>
       </c>
       <c r="B46">
         <v>240</v>
       </c>
       <c r="C46" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="B47">
         <v>240</v>
       </c>
       <c r="C47" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>11</v>
+        <v>89</v>
       </c>
       <c r="B48">
         <v>240</v>
       </c>
       <c r="C48" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="B49">
         <v>240</v>
       </c>
       <c r="C49" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>109</v>
+        <v>408</v>
       </c>
       <c r="B50">
         <v>240</v>
       </c>
       <c r="C50" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="B51">
         <v>240</v>
       </c>
       <c r="C51" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>111</v>
+        <v>65</v>
       </c>
       <c r="B52">
         <v>240</v>
       </c>
       <c r="C52" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="B53">
         <v>240</v>
       </c>
       <c r="C53" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="B54">
         <v>240</v>
       </c>
       <c r="C54" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>12</v>
+        <v>409</v>
       </c>
       <c r="B55">
         <v>240</v>
       </c>
       <c r="C55" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="B56">
         <v>240</v>
       </c>
       <c r="C56" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="B57">
         <v>240</v>
       </c>
       <c r="C57" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>524</v>
+        <v>95</v>
       </c>
       <c r="B58">
         <v>240</v>
       </c>
       <c r="C58" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="B59">
         <v>240</v>
       </c>
       <c r="C59" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="B60">
         <v>240</v>
       </c>
       <c r="C60" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="B61">
         <v>240</v>
       </c>
       <c r="C61" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="B62">
         <v>240</v>
       </c>
       <c r="C62" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="B63">
         <v>240</v>
       </c>
       <c r="C63" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="B64">
         <v>240</v>
       </c>
       <c r="C64" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="B65">
         <v>240</v>
       </c>
       <c r="C65" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="B66">
         <v>240</v>
       </c>
       <c r="C66" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="B67">
         <v>240</v>
       </c>
       <c r="C67" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="B68">
         <v>240</v>
       </c>
       <c r="C68" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B69">
         <v>240</v>
       </c>
       <c r="C69" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>125</v>
+        <v>412</v>
       </c>
       <c r="B70">
         <v>240</v>
       </c>
       <c r="C70" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="B71">
         <v>240</v>
       </c>
       <c r="C71" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="B72">
         <v>240</v>
       </c>
       <c r="C72" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B73">
         <v>240</v>
       </c>
       <c r="C73" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B74">
         <v>240</v>
       </c>
       <c r="C74" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="B75">
         <v>240</v>
       </c>
       <c r="C75" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>129</v>
+        <v>390</v>
       </c>
       <c r="B76">
         <v>240</v>
       </c>
       <c r="C76" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>130</v>
+        <v>417</v>
       </c>
       <c r="B77">
         <v>240</v>
       </c>
       <c r="C77" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="B78">
         <v>240</v>
       </c>
       <c r="C78" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="B79">
         <v>240</v>
       </c>
       <c r="C79" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>133</v>
+        <v>13</v>
       </c>
       <c r="B80">
         <v>240</v>
       </c>
       <c r="C80" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="B81">
         <v>240</v>
       </c>
       <c r="C81" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="B82">
         <v>240</v>
       </c>
       <c r="C82" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="B83">
         <v>240</v>
       </c>
       <c r="C83" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>137</v>
+        <v>14</v>
       </c>
       <c r="B84">
         <v>240</v>
       </c>
       <c r="C84" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="B85">
         <v>240</v>
       </c>
       <c r="C85" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>139</v>
+        <v>15</v>
       </c>
       <c r="B86">
         <v>240</v>
       </c>
       <c r="C86" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="B87">
         <v>240</v>
       </c>
       <c r="C87" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>141</v>
+        <v>411</v>
       </c>
       <c r="B88">
         <v>240</v>
       </c>
       <c r="C88" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="B89">
         <v>240</v>
       </c>
       <c r="C89" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B90">
         <v>240</v>
       </c>
       <c r="C90" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>144</v>
+        <v>121</v>
       </c>
       <c r="B91">
         <v>240</v>
       </c>
       <c r="C91" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="B92">
         <v>240</v>
       </c>
       <c r="C92" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="B93">
         <v>240</v>
       </c>
       <c r="C93" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="B94">
         <v>240</v>
       </c>
       <c r="C94" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="B95">
         <v>240</v>
       </c>
       <c r="C95" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="B96">
         <v>240</v>
       </c>
       <c r="C96" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="B97">
         <v>240</v>
       </c>
       <c r="C97" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>525</v>
+        <v>128</v>
       </c>
       <c r="B98">
         <v>240</v>
       </c>
       <c r="C98" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="B99">
         <v>240</v>
       </c>
       <c r="C99" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>151</v>
+        <v>391</v>
       </c>
       <c r="B100">
         <v>240</v>
       </c>
       <c r="C100" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="B101">
         <v>240</v>
       </c>
       <c r="C101" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="B102">
         <v>240</v>
       </c>
       <c r="C102" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>153</v>
+        <v>16</v>
       </c>
       <c r="B103">
         <v>240</v>
       </c>
       <c r="C103" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="B104">
         <v>240</v>
       </c>
       <c r="C104" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B105">
         <v>240</v>
       </c>
       <c r="C105" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B106">
         <v>240</v>
       </c>
       <c r="C106" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="B107">
         <v>240</v>
       </c>
       <c r="C107" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="B108">
         <v>240</v>
       </c>
       <c r="C108" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>157</v>
+        <v>134</v>
       </c>
       <c r="B109">
         <v>240</v>
       </c>
       <c r="C109" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>158</v>
+        <v>136</v>
       </c>
       <c r="B110">
         <v>240</v>
       </c>
       <c r="C110" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>159</v>
+        <v>137</v>
       </c>
       <c r="B111">
         <v>240</v>
       </c>
       <c r="C111" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>160</v>
+        <v>19</v>
       </c>
       <c r="B112">
         <v>240</v>
       </c>
       <c r="C112" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>161</v>
+        <v>118</v>
       </c>
       <c r="B113">
         <v>240</v>
       </c>
       <c r="C113" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="B114">
         <v>240</v>
       </c>
       <c r="C114" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="B115">
         <v>240</v>
       </c>
       <c r="C115" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="B116">
         <v>240</v>
       </c>
       <c r="C116" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="B117">
         <v>240</v>
       </c>
       <c r="C117" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="B118">
         <v>240</v>
       </c>
       <c r="C118" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="B119">
         <v>240</v>
       </c>
       <c r="C119" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="B120">
         <v>240</v>
       </c>
       <c r="C120" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="B121">
         <v>240</v>
       </c>
       <c r="C121" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="B122">
         <v>240</v>
       </c>
       <c r="C122" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c r="B123">
         <v>240</v>
       </c>
       <c r="C123" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="B124">
         <v>240</v>
       </c>
       <c r="C124" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>526</v>
+        <v>148</v>
       </c>
       <c r="B125">
         <v>240</v>
       </c>
       <c r="C125" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="B126">
         <v>240</v>
       </c>
       <c r="C126" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="B127">
         <v>240</v>
       </c>
       <c r="C127" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>21</v>
+        <v>151</v>
       </c>
       <c r="B128">
         <v>240</v>
       </c>
       <c r="C128" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="B129">
         <v>240</v>
       </c>
       <c r="C129" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="B130">
         <v>240</v>
       </c>
       <c r="C130" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>22</v>
+        <v>418</v>
       </c>
       <c r="B131">
         <v>240</v>
       </c>
       <c r="C131" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="B132">
         <v>240</v>
       </c>
       <c r="C132" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>23</v>
+        <v>155</v>
       </c>
       <c r="B133">
         <v>240</v>
       </c>
       <c r="C133" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="B134">
         <v>240</v>
       </c>
       <c r="C134" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="B135">
         <v>240</v>
       </c>
       <c r="C135" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="B136">
         <v>240</v>
       </c>
       <c r="C136" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="B137">
         <v>240</v>
       </c>
       <c r="C137" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="B138">
         <v>240</v>
       </c>
       <c r="C138" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="B139">
         <v>240</v>
       </c>
       <c r="C139" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="B140">
         <v>240</v>
       </c>
       <c r="C140" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="B141">
         <v>240</v>
       </c>
       <c r="C141" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>527</v>
+        <v>163</v>
       </c>
       <c r="B142">
         <v>240</v>
       </c>
       <c r="C142" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="B143">
         <v>240</v>
       </c>
       <c r="C143" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>186</v>
+        <v>22</v>
       </c>
       <c r="B144">
         <v>240</v>
       </c>
       <c r="C144" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>187</v>
+        <v>23</v>
       </c>
       <c r="B145">
         <v>240</v>
       </c>
       <c r="C145" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>188</v>
+        <v>414</v>
       </c>
       <c r="B146">
         <v>240</v>
       </c>
       <c r="C146" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="B147">
         <v>240</v>
       </c>
       <c r="C147" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="B148">
         <v>240</v>
       </c>
       <c r="C148" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="B149">
         <v>240</v>
       </c>
       <c r="C149" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="B150">
         <v>240</v>
       </c>
       <c r="C150" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="B151">
         <v>240</v>
       </c>
       <c r="C151" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="B152">
         <v>240</v>
       </c>
       <c r="C152" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="B153">
         <v>240</v>
       </c>
       <c r="C153" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>196</v>
+        <v>420</v>
       </c>
       <c r="B154">
         <v>240</v>
       </c>
       <c r="C154" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
       <c r="B155">
         <v>240</v>
       </c>
       <c r="C155" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>198</v>
+        <v>24</v>
       </c>
       <c r="B156">
         <v>240</v>
       </c>
       <c r="C156" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -3741,4179 +3399,2900 @@
         <v>240</v>
       </c>
       <c r="C157" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="B158">
         <v>240</v>
       </c>
       <c r="C158" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>200</v>
+        <v>410</v>
       </c>
       <c r="B159">
         <v>240</v>
       </c>
       <c r="C159" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="B160">
         <v>240</v>
       </c>
       <c r="C160" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>202</v>
+        <v>175</v>
       </c>
       <c r="B161">
         <v>240</v>
       </c>
       <c r="C161" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>203</v>
+        <v>26</v>
       </c>
       <c r="B162">
         <v>240</v>
       </c>
       <c r="C162" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>204</v>
+        <v>176</v>
       </c>
       <c r="B163">
         <v>240</v>
       </c>
       <c r="C163" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>205</v>
+        <v>177</v>
       </c>
       <c r="B164">
         <v>240</v>
       </c>
       <c r="C164" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>206</v>
+        <v>178</v>
       </c>
       <c r="B165">
         <v>240</v>
       </c>
       <c r="C165" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>207</v>
+        <v>179</v>
       </c>
       <c r="B166">
         <v>240</v>
       </c>
       <c r="C166" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>208</v>
+        <v>180</v>
       </c>
       <c r="B167">
         <v>240</v>
       </c>
       <c r="C167" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>209</v>
+        <v>181</v>
       </c>
       <c r="B168">
         <v>240</v>
       </c>
       <c r="C168" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>210</v>
+        <v>182</v>
       </c>
       <c r="B169">
         <v>240</v>
       </c>
       <c r="C169" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>26</v>
+        <v>183</v>
       </c>
       <c r="B170">
         <v>240</v>
       </c>
       <c r="C170" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>211</v>
+        <v>184</v>
       </c>
       <c r="B171">
         <v>240</v>
       </c>
       <c r="C171" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
       <c r="B172">
         <v>240</v>
       </c>
       <c r="C172" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>213</v>
+        <v>187</v>
       </c>
       <c r="B173">
         <v>240</v>
       </c>
       <c r="C173" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>214</v>
+        <v>188</v>
       </c>
       <c r="B174">
         <v>240</v>
       </c>
       <c r="C174" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
       <c r="B175">
         <v>240</v>
       </c>
       <c r="C175" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="B176">
         <v>240</v>
       </c>
       <c r="C176" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>217</v>
+        <v>191</v>
       </c>
       <c r="B177">
         <v>240</v>
       </c>
       <c r="C177" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="B178">
         <v>240</v>
       </c>
       <c r="C178" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="B179">
         <v>240</v>
       </c>
       <c r="C179" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>219</v>
+        <v>194</v>
       </c>
       <c r="B180">
         <v>240</v>
       </c>
       <c r="C180" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="B181">
         <v>240</v>
       </c>
       <c r="C181" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>31</v>
+        <v>196</v>
       </c>
       <c r="B182">
         <v>240</v>
       </c>
       <c r="C182" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>28</v>
+        <v>197</v>
       </c>
       <c r="B183">
         <v>240</v>
       </c>
       <c r="C183" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>221</v>
+        <v>185</v>
       </c>
       <c r="B184">
         <v>240</v>
       </c>
       <c r="C184" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="B185">
         <v>240</v>
       </c>
       <c r="C185" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>223</v>
+        <v>198</v>
       </c>
       <c r="B186">
         <v>240</v>
       </c>
       <c r="C186" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="B187">
         <v>240</v>
       </c>
       <c r="C187" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>225</v>
+        <v>392</v>
       </c>
       <c r="B188">
         <v>240</v>
       </c>
       <c r="C188" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>29</v>
+        <v>201</v>
       </c>
       <c r="B189">
         <v>240</v>
       </c>
       <c r="C189" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="B190">
         <v>240</v>
       </c>
       <c r="C190" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="B191">
         <v>240</v>
       </c>
       <c r="C191" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="B192">
         <v>240</v>
       </c>
       <c r="C192" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="B193">
         <v>240</v>
       </c>
       <c r="C193" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="B194">
         <v>240</v>
       </c>
       <c r="C194" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="B195">
         <v>240</v>
       </c>
       <c r="C195" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="B196">
         <v>240</v>
       </c>
       <c r="C196" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="B197">
         <v>240</v>
       </c>
       <c r="C197" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>233</v>
+        <v>207</v>
       </c>
       <c r="B198">
         <v>240</v>
       </c>
       <c r="C198" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>234</v>
+        <v>211</v>
       </c>
       <c r="B199">
         <v>240</v>
       </c>
       <c r="C199" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>235</v>
+        <v>27</v>
       </c>
       <c r="B200">
         <v>240</v>
       </c>
       <c r="C200" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>32</v>
+        <v>212</v>
       </c>
       <c r="B201">
         <v>240</v>
       </c>
       <c r="C201" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="B202">
         <v>240</v>
       </c>
       <c r="C202" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>237</v>
+        <v>28</v>
       </c>
       <c r="B203">
         <v>240</v>
       </c>
       <c r="C203" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>238</v>
+        <v>29</v>
       </c>
       <c r="B204">
         <v>240</v>
       </c>
       <c r="C204" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>528</v>
+        <v>214</v>
       </c>
       <c r="B205">
         <v>240</v>
       </c>
       <c r="C205" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
       <c r="B206">
         <v>240</v>
       </c>
       <c r="C206" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>239</v>
+        <v>30</v>
       </c>
       <c r="B207">
         <v>240</v>
       </c>
       <c r="C207" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="B208">
         <v>240</v>
       </c>
       <c r="C208" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>241</v>
+        <v>393</v>
       </c>
       <c r="B209">
         <v>240</v>
       </c>
       <c r="C209" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>242</v>
+        <v>31</v>
       </c>
       <c r="B210">
         <v>240</v>
       </c>
       <c r="C210" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="B211">
         <v>240</v>
       </c>
       <c r="C211" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="B212">
         <v>240</v>
       </c>
       <c r="C212" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>245</v>
+        <v>219</v>
       </c>
       <c r="B213">
         <v>240</v>
       </c>
       <c r="C213" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>246</v>
+        <v>220</v>
       </c>
       <c r="B214">
         <v>240</v>
       </c>
       <c r="C214" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>247</v>
+        <v>413</v>
       </c>
       <c r="B215">
         <v>240</v>
       </c>
       <c r="C215" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>248</v>
+        <v>32</v>
       </c>
       <c r="B216">
         <v>240</v>
       </c>
       <c r="C216" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>249</v>
+        <v>221</v>
       </c>
       <c r="B217">
         <v>240</v>
       </c>
       <c r="C217" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>250</v>
+        <v>222</v>
       </c>
       <c r="B218">
         <v>240</v>
       </c>
       <c r="C218" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>251</v>
+        <v>223</v>
       </c>
       <c r="B219">
         <v>240</v>
       </c>
       <c r="C219" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>252</v>
+        <v>224</v>
       </c>
       <c r="B220">
         <v>240</v>
       </c>
       <c r="C220" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>253</v>
+        <v>225</v>
       </c>
       <c r="B221">
         <v>240</v>
       </c>
       <c r="C221" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>254</v>
+        <v>226</v>
       </c>
       <c r="B222">
         <v>240</v>
       </c>
       <c r="C222" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="B223">
         <v>240</v>
       </c>
       <c r="C223" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="B224">
         <v>240</v>
       </c>
       <c r="C224" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>257</v>
+        <v>230</v>
       </c>
       <c r="B225">
         <v>240</v>
       </c>
       <c r="C225" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>258</v>
+        <v>419</v>
       </c>
       <c r="B226">
         <v>240</v>
       </c>
       <c r="C226" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>259</v>
+        <v>33</v>
       </c>
       <c r="B227">
         <v>240</v>
       </c>
       <c r="C227" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>260</v>
+        <v>231</v>
       </c>
       <c r="B228">
         <v>240</v>
       </c>
       <c r="C228" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>261</v>
+        <v>232</v>
       </c>
       <c r="B229">
         <v>240</v>
       </c>
       <c r="C229" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>262</v>
+        <v>234</v>
       </c>
       <c r="B230">
         <v>240</v>
       </c>
       <c r="C230" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>263</v>
+        <v>233</v>
       </c>
       <c r="B231">
         <v>240</v>
       </c>
       <c r="C231" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>264</v>
+        <v>235</v>
       </c>
       <c r="B232">
         <v>240</v>
       </c>
       <c r="C232" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="B233">
         <v>240</v>
       </c>
       <c r="C233" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="B234">
         <v>240</v>
       </c>
       <c r="C234" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
       <c r="B235">
         <v>240</v>
       </c>
       <c r="C235" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>268</v>
+        <v>240</v>
       </c>
       <c r="B236">
         <v>240</v>
       </c>
       <c r="C236" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>529</v>
+        <v>236</v>
       </c>
       <c r="B237">
         <v>240</v>
       </c>
       <c r="C237" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>269</v>
+        <v>34</v>
       </c>
       <c r="B238">
         <v>240</v>
       </c>
       <c r="C238" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="B239">
         <v>240</v>
       </c>
       <c r="C239" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="B240">
         <v>240</v>
       </c>
       <c r="C240" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>272</v>
+        <v>35</v>
       </c>
       <c r="B241">
         <v>240</v>
       </c>
       <c r="C241" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>273</v>
+        <v>243</v>
       </c>
       <c r="B242">
         <v>240</v>
       </c>
       <c r="C242" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>274</v>
+        <v>36</v>
       </c>
       <c r="B243">
         <v>240</v>
       </c>
       <c r="C243" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>275</v>
+        <v>37</v>
       </c>
       <c r="B244">
         <v>240</v>
       </c>
       <c r="C244" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>276</v>
+        <v>244</v>
       </c>
       <c r="B245">
         <v>240</v>
       </c>
       <c r="C245" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>277</v>
+        <v>245</v>
       </c>
       <c r="B246">
         <v>240</v>
       </c>
       <c r="C246" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>278</v>
+        <v>246</v>
       </c>
       <c r="B247">
         <v>240</v>
       </c>
       <c r="C247" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>279</v>
+        <v>247</v>
       </c>
       <c r="B248">
         <v>240</v>
       </c>
       <c r="C248" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>280</v>
+        <v>229</v>
       </c>
       <c r="B249">
         <v>240</v>
       </c>
       <c r="C249" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>281</v>
+        <v>399</v>
       </c>
       <c r="B250">
         <v>240</v>
       </c>
       <c r="C250" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B251">
         <v>240</v>
       </c>
       <c r="C251" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>282</v>
+        <v>248</v>
       </c>
       <c r="B252">
         <v>240</v>
       </c>
       <c r="C252" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>283</v>
+        <v>249</v>
       </c>
       <c r="B253">
         <v>240</v>
       </c>
       <c r="C253" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>284</v>
+        <v>250</v>
       </c>
       <c r="B254">
         <v>240</v>
       </c>
       <c r="C254" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>35</v>
+        <v>251</v>
       </c>
       <c r="B255">
         <v>240</v>
       </c>
       <c r="C255" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>36</v>
+        <v>416</v>
       </c>
       <c r="B256">
         <v>240</v>
       </c>
       <c r="C256" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>285</v>
+        <v>39</v>
       </c>
       <c r="B257">
         <v>240</v>
       </c>
       <c r="C257" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>286</v>
+        <v>252</v>
       </c>
       <c r="B258">
         <v>240</v>
       </c>
       <c r="C258" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>37</v>
+        <v>254</v>
       </c>
       <c r="B259">
         <v>240</v>
       </c>
       <c r="C259" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>287</v>
+        <v>253</v>
       </c>
       <c r="B260">
         <v>240</v>
       </c>
       <c r="C260" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>288</v>
+        <v>255</v>
       </c>
       <c r="B261">
         <v>240</v>
       </c>
       <c r="C261" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>530</v>
+        <v>40</v>
       </c>
       <c r="B262">
         <v>240</v>
       </c>
       <c r="C262" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>38</v>
+        <v>256</v>
       </c>
       <c r="B263">
         <v>240</v>
       </c>
       <c r="C263" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>289</v>
+        <v>257</v>
       </c>
       <c r="B264">
         <v>240</v>
       </c>
       <c r="C264" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>290</v>
+        <v>41</v>
       </c>
       <c r="B265">
         <v>240</v>
       </c>
       <c r="C265" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>291</v>
+        <v>258</v>
       </c>
       <c r="B266">
         <v>240</v>
       </c>
       <c r="C266" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>292</v>
+        <v>42</v>
       </c>
       <c r="B267">
         <v>240</v>
       </c>
       <c r="C267" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="B268">
         <v>240</v>
       </c>
       <c r="C268" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>294</v>
+        <v>260</v>
       </c>
       <c r="B269">
         <v>240</v>
       </c>
       <c r="C269" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>39</v>
+        <v>261</v>
       </c>
       <c r="B270">
         <v>240</v>
       </c>
       <c r="C270" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>295</v>
+        <v>262</v>
       </c>
       <c r="B271">
         <v>240</v>
       </c>
       <c r="C271" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>296</v>
+        <v>263</v>
       </c>
       <c r="B272">
         <v>240</v>
       </c>
       <c r="C272" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>297</v>
+        <v>264</v>
       </c>
       <c r="B273">
         <v>240</v>
       </c>
       <c r="C273" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>298</v>
+        <v>43</v>
       </c>
       <c r="B274">
         <v>240</v>
       </c>
       <c r="C274" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>299</v>
+        <v>265</v>
       </c>
       <c r="B275">
         <v>240</v>
       </c>
       <c r="C275" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>300</v>
+        <v>266</v>
       </c>
       <c r="B276">
         <v>240</v>
       </c>
       <c r="C276" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>301</v>
+        <v>421</v>
       </c>
       <c r="B277">
         <v>240</v>
       </c>
       <c r="C277" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>302</v>
+        <v>267</v>
       </c>
       <c r="B278">
         <v>240</v>
       </c>
       <c r="C278" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>303</v>
+        <v>268</v>
       </c>
       <c r="B279">
         <v>240</v>
       </c>
       <c r="C279" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>304</v>
+        <v>269</v>
       </c>
       <c r="B280">
         <v>240</v>
       </c>
       <c r="C280" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>305</v>
+        <v>270</v>
       </c>
       <c r="B281">
         <v>240</v>
       </c>
       <c r="C281" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>306</v>
+        <v>271</v>
       </c>
       <c r="B282">
         <v>240</v>
       </c>
       <c r="C282" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>40</v>
+        <v>272</v>
       </c>
       <c r="B283">
         <v>240</v>
       </c>
       <c r="C283" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>307</v>
+        <v>273</v>
       </c>
       <c r="B284">
         <v>240</v>
       </c>
       <c r="C284" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>308</v>
+        <v>44</v>
       </c>
       <c r="B285">
         <v>240</v>
       </c>
       <c r="C285" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>309</v>
+        <v>274</v>
       </c>
       <c r="B286">
         <v>240</v>
       </c>
       <c r="C286" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>310</v>
+        <v>275</v>
       </c>
       <c r="B287">
         <v>240</v>
       </c>
       <c r="C287" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>311</v>
+        <v>276</v>
       </c>
       <c r="B288">
         <v>240</v>
       </c>
       <c r="C288" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>312</v>
+        <v>45</v>
       </c>
       <c r="B289">
         <v>240</v>
       </c>
       <c r="C289" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>313</v>
+        <v>277</v>
       </c>
       <c r="B290">
         <v>240</v>
       </c>
       <c r="C290" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>314</v>
+        <v>278</v>
       </c>
       <c r="B291">
         <v>240</v>
       </c>
       <c r="C291" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>315</v>
+        <v>279</v>
       </c>
       <c r="B292">
         <v>240</v>
       </c>
       <c r="C292" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>316</v>
+        <v>394</v>
       </c>
       <c r="B293">
         <v>240</v>
       </c>
       <c r="C293" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>317</v>
+        <v>280</v>
       </c>
       <c r="B294">
         <v>240</v>
       </c>
       <c r="C294" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>318</v>
+        <v>46</v>
       </c>
       <c r="B295">
         <v>240</v>
       </c>
       <c r="C295" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>41</v>
+        <v>281</v>
       </c>
       <c r="B296">
         <v>240</v>
       </c>
       <c r="C296" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>319</v>
+        <v>282</v>
       </c>
       <c r="B297">
         <v>240</v>
       </c>
       <c r="C297" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>320</v>
+        <v>283</v>
       </c>
       <c r="B298">
         <v>240</v>
       </c>
       <c r="C298" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>321</v>
+        <v>284</v>
       </c>
       <c r="B299">
         <v>240</v>
       </c>
       <c r="C299" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>322</v>
+        <v>285</v>
       </c>
       <c r="B300">
         <v>240</v>
       </c>
       <c r="C300" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>42</v>
+        <v>286</v>
       </c>
       <c r="B301">
         <v>240</v>
       </c>
       <c r="C301" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>323</v>
+        <v>287</v>
       </c>
       <c r="B302">
         <v>240</v>
       </c>
       <c r="C302" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B303">
         <v>240</v>
       </c>
       <c r="C303" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>44</v>
+        <v>288</v>
       </c>
       <c r="B304">
         <v>240</v>
       </c>
       <c r="C304" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>324</v>
+        <v>289</v>
       </c>
       <c r="B305">
         <v>240</v>
       </c>
       <c r="C305" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>325</v>
+        <v>290</v>
       </c>
       <c r="B306">
         <v>240</v>
       </c>
       <c r="C306" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>326</v>
+        <v>291</v>
       </c>
       <c r="B307">
         <v>240</v>
       </c>
       <c r="C307" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>327</v>
+        <v>395</v>
       </c>
       <c r="B308">
         <v>240</v>
       </c>
       <c r="C308" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>328</v>
+        <v>292</v>
       </c>
       <c r="B309">
         <v>240</v>
       </c>
       <c r="C309" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>329</v>
+        <v>293</v>
       </c>
       <c r="B310">
         <v>240</v>
       </c>
       <c r="C310" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>45</v>
+        <v>294</v>
       </c>
       <c r="B311">
         <v>240</v>
       </c>
       <c r="C311" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>536</v>
+        <v>48</v>
       </c>
       <c r="B312">
         <v>240</v>
       </c>
       <c r="C312" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>46</v>
+        <v>295</v>
       </c>
       <c r="B313">
         <v>240</v>
       </c>
       <c r="C313" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>330</v>
+        <v>297</v>
       </c>
       <c r="B314">
         <v>240</v>
       </c>
       <c r="C314" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>331</v>
+        <v>298</v>
       </c>
       <c r="B315">
         <v>240</v>
       </c>
       <c r="C315" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>332</v>
+        <v>299</v>
       </c>
       <c r="B316">
         <v>240</v>
       </c>
       <c r="C316" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>333</v>
+        <v>300</v>
       </c>
       <c r="B317">
         <v>240</v>
       </c>
       <c r="C317" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>334</v>
+        <v>303</v>
       </c>
       <c r="B318">
         <v>240</v>
       </c>
       <c r="C318" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>335</v>
+        <v>302</v>
       </c>
       <c r="B319">
         <v>240</v>
       </c>
       <c r="C319" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>336</v>
+        <v>301</v>
       </c>
       <c r="B320">
         <v>240</v>
       </c>
       <c r="C320" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>47</v>
+        <v>304</v>
       </c>
       <c r="B321">
         <v>240</v>
       </c>
       <c r="C321" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>337</v>
+        <v>305</v>
       </c>
       <c r="B322">
         <v>240</v>
       </c>
       <c r="C322" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>338</v>
+        <v>49</v>
       </c>
       <c r="B323">
         <v>240</v>
       </c>
       <c r="C323" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>339</v>
+        <v>306</v>
       </c>
       <c r="B324">
         <v>240</v>
       </c>
       <c r="C324" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>340</v>
+        <v>307</v>
       </c>
       <c r="B325">
         <v>240</v>
       </c>
       <c r="C325" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>341</v>
+        <v>308</v>
       </c>
       <c r="B326">
         <v>240</v>
       </c>
       <c r="C326" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>342</v>
+        <v>309</v>
       </c>
       <c r="B327">
         <v>240</v>
       </c>
       <c r="C327" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>343</v>
+        <v>50</v>
       </c>
       <c r="B328">
         <v>240</v>
       </c>
       <c r="C328" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>344</v>
+        <v>310</v>
       </c>
       <c r="B329">
         <v>240</v>
       </c>
       <c r="C329" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>345</v>
+        <v>51</v>
       </c>
       <c r="B330">
         <v>240</v>
       </c>
       <c r="C330" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>346</v>
+        <v>311</v>
       </c>
       <c r="B331">
         <v>240</v>
       </c>
       <c r="C331" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>48</v>
+        <v>312</v>
       </c>
       <c r="B332">
         <v>240</v>
       </c>
       <c r="C332" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>347</v>
+        <v>313</v>
       </c>
       <c r="B333">
         <v>240</v>
       </c>
       <c r="C333" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>348</v>
+        <v>314</v>
       </c>
       <c r="B334">
         <v>240</v>
       </c>
       <c r="C334" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>349</v>
+        <v>315</v>
       </c>
       <c r="B335">
         <v>240</v>
       </c>
       <c r="C335" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>49</v>
+        <v>316</v>
       </c>
       <c r="B336">
         <v>240</v>
       </c>
       <c r="C336" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>350</v>
+        <v>52</v>
       </c>
       <c r="B337">
         <v>240</v>
       </c>
       <c r="C337" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>50</v>
+        <v>317</v>
       </c>
       <c r="B338">
         <v>240</v>
       </c>
       <c r="C338" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>351</v>
+        <v>318</v>
       </c>
       <c r="B339">
         <v>240</v>
       </c>
       <c r="C339" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>352</v>
+        <v>319</v>
       </c>
       <c r="B340">
         <v>240</v>
       </c>
       <c r="C340" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>353</v>
+        <v>320</v>
       </c>
       <c r="B341">
         <v>240</v>
       </c>
       <c r="C341" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>354</v>
+        <v>322</v>
       </c>
       <c r="B342">
         <v>240</v>
       </c>
       <c r="C342" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>355</v>
+        <v>321</v>
       </c>
       <c r="B343">
         <v>240</v>
       </c>
       <c r="C343" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>356</v>
+        <v>323</v>
       </c>
       <c r="B344">
         <v>240</v>
       </c>
       <c r="C344" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>357</v>
+        <v>324</v>
       </c>
       <c r="B345">
         <v>240</v>
       </c>
       <c r="C345" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>51</v>
+        <v>325</v>
       </c>
       <c r="B346">
         <v>240</v>
       </c>
       <c r="C346" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>358</v>
+        <v>326</v>
       </c>
       <c r="B347">
         <v>240</v>
       </c>
       <c r="C347" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>359</v>
+        <v>327</v>
       </c>
       <c r="B348">
         <v>240</v>
       </c>
       <c r="C348" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>52</v>
+        <v>296</v>
       </c>
       <c r="B349">
         <v>240</v>
       </c>
       <c r="C349" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>360</v>
+        <v>328</v>
       </c>
       <c r="B350">
         <v>240</v>
       </c>
       <c r="C350" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>361</v>
+        <v>329</v>
       </c>
       <c r="B351">
         <v>240</v>
       </c>
       <c r="C351" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>362</v>
+        <v>330</v>
       </c>
       <c r="B352">
         <v>240</v>
       </c>
       <c r="C352" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>363</v>
+        <v>331</v>
       </c>
       <c r="B353">
         <v>240</v>
       </c>
       <c r="C353" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
       <c r="B354">
         <v>240</v>
       </c>
       <c r="C354" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>365</v>
+        <v>396</v>
       </c>
       <c r="B355">
         <v>240</v>
       </c>
       <c r="C355" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>366</v>
+        <v>335</v>
       </c>
       <c r="B356">
         <v>240</v>
       </c>
       <c r="C356" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>367</v>
+        <v>333</v>
       </c>
       <c r="B357">
         <v>240</v>
       </c>
       <c r="C357" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>368</v>
+        <v>337</v>
       </c>
       <c r="B358">
         <v>240</v>
       </c>
       <c r="C358" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>53</v>
+        <v>336</v>
       </c>
       <c r="B359">
         <v>240</v>
       </c>
       <c r="C359" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>369</v>
+        <v>338</v>
       </c>
       <c r="B360">
         <v>240</v>
       </c>
       <c r="C360" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>370</v>
+        <v>339</v>
       </c>
       <c r="B361">
         <v>240</v>
       </c>
       <c r="C361" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>54</v>
+        <v>340</v>
       </c>
       <c r="B362">
         <v>240</v>
       </c>
       <c r="C362" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>371</v>
+        <v>53</v>
       </c>
       <c r="B363">
         <v>240</v>
       </c>
       <c r="C363" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B364">
         <v>240</v>
       </c>
       <c r="C364" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>372</v>
+        <v>342</v>
       </c>
       <c r="B365">
         <v>240</v>
       </c>
       <c r="C365" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>373</v>
+        <v>341</v>
       </c>
       <c r="B366">
         <v>240</v>
       </c>
       <c r="C366" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>374</v>
+        <v>343</v>
       </c>
       <c r="B367">
         <v>240</v>
       </c>
       <c r="C367" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>375</v>
+        <v>344</v>
       </c>
       <c r="B368">
         <v>240</v>
       </c>
       <c r="C368" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>531</v>
+        <v>332</v>
       </c>
       <c r="B369">
         <v>240</v>
       </c>
       <c r="C369" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>376</v>
+        <v>345</v>
       </c>
       <c r="B370">
         <v>240</v>
       </c>
       <c r="C370" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>56</v>
+        <v>346</v>
       </c>
       <c r="B371">
         <v>240</v>
       </c>
       <c r="C371" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>377</v>
+        <v>347</v>
       </c>
       <c r="B372">
         <v>240</v>
       </c>
       <c r="C372" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>378</v>
+        <v>348</v>
       </c>
       <c r="B373">
         <v>240</v>
       </c>
       <c r="C373" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>379</v>
+        <v>349</v>
       </c>
       <c r="B374">
         <v>240</v>
       </c>
       <c r="C374" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="B375">
         <v>240</v>
       </c>
       <c r="C375" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>381</v>
+        <v>351</v>
       </c>
       <c r="B376">
         <v>240</v>
       </c>
       <c r="C376" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>382</v>
+        <v>352</v>
       </c>
       <c r="B377">
         <v>240</v>
       </c>
       <c r="C377" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>383</v>
+        <v>353</v>
       </c>
       <c r="B378">
         <v>240</v>
       </c>
       <c r="C378" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>384</v>
+        <v>354</v>
       </c>
       <c r="B379">
         <v>240</v>
       </c>
       <c r="C379" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>385</v>
+        <v>355</v>
       </c>
       <c r="B380">
         <v>240</v>
       </c>
       <c r="C380" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>386</v>
+        <v>356</v>
       </c>
       <c r="B381">
         <v>240</v>
       </c>
       <c r="C381" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>57</v>
+        <v>358</v>
       </c>
       <c r="B382">
         <v>240</v>
       </c>
       <c r="C382" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>387</v>
+        <v>357</v>
       </c>
       <c r="B383">
         <v>240</v>
       </c>
       <c r="C383" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>388</v>
+        <v>359</v>
       </c>
       <c r="B384">
         <v>240</v>
       </c>
       <c r="C384" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>389</v>
+        <v>360</v>
       </c>
       <c r="B385">
         <v>240</v>
       </c>
       <c r="C385" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>390</v>
+        <v>361</v>
       </c>
       <c r="B386">
         <v>240</v>
       </c>
       <c r="C386" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>391</v>
+        <v>362</v>
       </c>
       <c r="B387">
         <v>240</v>
       </c>
       <c r="C387" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>392</v>
+        <v>363</v>
       </c>
       <c r="B388">
         <v>240</v>
       </c>
       <c r="C388" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>393</v>
+        <v>365</v>
       </c>
       <c r="B389">
         <v>240</v>
       </c>
       <c r="C389" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>532</v>
+        <v>398</v>
       </c>
       <c r="B390">
         <v>240</v>
       </c>
       <c r="C390" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B391">
         <v>240</v>
       </c>
       <c r="C391" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>395</v>
+        <v>366</v>
       </c>
       <c r="B392">
         <v>240</v>
       </c>
       <c r="C392" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>396</v>
+        <v>55</v>
       </c>
       <c r="B393">
         <v>240</v>
       </c>
       <c r="C393" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>397</v>
+        <v>367</v>
       </c>
       <c r="B394">
         <v>240</v>
       </c>
       <c r="C394" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>58</v>
+        <v>368</v>
       </c>
       <c r="B395">
         <v>240</v>
       </c>
       <c r="C395" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>398</v>
+        <v>364</v>
       </c>
       <c r="B396">
         <v>240</v>
       </c>
       <c r="C396" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="B397">
         <v>240</v>
       </c>
       <c r="C397" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>400</v>
+        <v>370</v>
       </c>
       <c r="B398">
         <v>240</v>
       </c>
       <c r="C398" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>401</v>
+        <v>56</v>
       </c>
       <c r="B399">
         <v>240</v>
       </c>
       <c r="C399" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>402</v>
+        <v>371</v>
       </c>
       <c r="B400">
         <v>240</v>
       </c>
       <c r="C400" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>403</v>
+        <v>372</v>
       </c>
       <c r="B401">
         <v>240</v>
       </c>
       <c r="C401" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>404</v>
+        <v>57</v>
       </c>
       <c r="B402">
         <v>240</v>
       </c>
       <c r="C402" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>405</v>
+        <v>373</v>
       </c>
       <c r="B403">
         <v>240</v>
       </c>
       <c r="C403" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>406</v>
+        <v>58</v>
       </c>
       <c r="B404">
         <v>240</v>
       </c>
       <c r="C404" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>407</v>
+        <v>374</v>
       </c>
       <c r="B405">
         <v>240</v>
       </c>
       <c r="C405" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>408</v>
+        <v>375</v>
       </c>
       <c r="B406">
         <v>240</v>
       </c>
       <c r="C406" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>409</v>
+        <v>376</v>
       </c>
       <c r="B407">
         <v>240</v>
       </c>
       <c r="C407" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>410</v>
+        <v>377</v>
       </c>
       <c r="B408">
         <v>240</v>
       </c>
       <c r="C408" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>411</v>
+        <v>378</v>
       </c>
       <c r="B409">
         <v>240</v>
       </c>
       <c r="C409" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>412</v>
+        <v>379</v>
       </c>
       <c r="B410">
         <v>240</v>
       </c>
       <c r="C410" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>413</v>
+        <v>380</v>
       </c>
       <c r="B411">
         <v>240</v>
       </c>
       <c r="C411" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>414</v>
+        <v>59</v>
       </c>
       <c r="B412">
         <v>240</v>
       </c>
       <c r="C412" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>59</v>
+        <v>381</v>
       </c>
       <c r="B413">
         <v>240</v>
       </c>
       <c r="C413" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>415</v>
+        <v>382</v>
       </c>
       <c r="B414">
         <v>240</v>
       </c>
       <c r="C414" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>416</v>
+        <v>383</v>
       </c>
       <c r="B415">
         <v>240</v>
       </c>
       <c r="C415" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>417</v>
+        <v>384</v>
       </c>
       <c r="B416">
         <v>240</v>
       </c>
       <c r="C416" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>417</v>
+        <v>385</v>
       </c>
       <c r="B417">
         <v>240</v>
       </c>
       <c r="C417" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>418</v>
+        <v>386</v>
       </c>
       <c r="B418">
         <v>240</v>
       </c>
       <c r="C418" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>419</v>
+        <v>60</v>
       </c>
       <c r="B419">
         <v>240</v>
       </c>
       <c r="C419" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A420" t="s">
-        <v>420</v>
-      </c>
-      <c r="B420">
-        <v>240</v>
-      </c>
-      <c r="C420" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A421" t="s">
-        <v>421</v>
-      </c>
-      <c r="B421">
-        <v>240</v>
-      </c>
-      <c r="C421" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A422" t="s">
-        <v>422</v>
-      </c>
-      <c r="B422">
-        <v>240</v>
-      </c>
-      <c r="C422" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A423" t="s">
-        <v>60</v>
-      </c>
-      <c r="B423">
-        <v>240</v>
-      </c>
-      <c r="C423" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A424" t="s">
-        <v>61</v>
-      </c>
-      <c r="B424">
-        <v>240</v>
-      </c>
-      <c r="C424" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A425" t="s">
-        <v>423</v>
-      </c>
-      <c r="B425">
-        <v>240</v>
-      </c>
-      <c r="C425" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A426" t="s">
-        <v>424</v>
-      </c>
-      <c r="B426">
-        <v>240</v>
-      </c>
-      <c r="C426" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A427" t="s">
-        <v>425</v>
-      </c>
-      <c r="B427">
-        <v>240</v>
-      </c>
-      <c r="C427" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A428" t="s">
-        <v>426</v>
-      </c>
-      <c r="B428">
-        <v>240</v>
-      </c>
-      <c r="C428" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A429" t="s">
-        <v>427</v>
-      </c>
-      <c r="B429">
-        <v>240</v>
-      </c>
-      <c r="C429" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A430" t="s">
-        <v>428</v>
-      </c>
-      <c r="B430">
-        <v>240</v>
-      </c>
-      <c r="C430" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A431" t="s">
-        <v>429</v>
-      </c>
-      <c r="B431">
-        <v>240</v>
-      </c>
-      <c r="C431" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A432" t="s">
-        <v>430</v>
-      </c>
-      <c r="B432">
-        <v>240</v>
-      </c>
-      <c r="C432" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A433" t="s">
-        <v>431</v>
-      </c>
-      <c r="B433">
-        <v>240</v>
-      </c>
-      <c r="C433" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A434" t="s">
-        <v>432</v>
-      </c>
-      <c r="B434">
-        <v>240</v>
-      </c>
-      <c r="C434" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A435" t="s">
-        <v>62</v>
-      </c>
-      <c r="B435">
-        <v>240</v>
-      </c>
-      <c r="C435" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A436" t="s">
-        <v>433</v>
-      </c>
-      <c r="B436">
-        <v>240</v>
-      </c>
-      <c r="C436" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="437" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A437" t="s">
-        <v>434</v>
-      </c>
-      <c r="B437">
-        <v>240</v>
-      </c>
-      <c r="C437" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="438" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A438" t="s">
-        <v>435</v>
-      </c>
-      <c r="B438">
-        <v>240</v>
-      </c>
-      <c r="C438" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="439" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A439" t="s">
-        <v>436</v>
-      </c>
-      <c r="B439">
-        <v>240</v>
-      </c>
-      <c r="C439" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="440" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A440" t="s">
-        <v>437</v>
-      </c>
-      <c r="B440">
-        <v>240</v>
-      </c>
-      <c r="C440" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="441" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A441" t="s">
-        <v>438</v>
-      </c>
-      <c r="B441">
-        <v>240</v>
-      </c>
-      <c r="C441" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="442" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A442" t="s">
-        <v>439</v>
-      </c>
-      <c r="B442">
-        <v>240</v>
-      </c>
-      <c r="C442" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="443" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A443" t="s">
-        <v>440</v>
-      </c>
-      <c r="B443">
-        <v>240</v>
-      </c>
-      <c r="C443" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="444" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A444" t="s">
-        <v>441</v>
-      </c>
-      <c r="B444">
-        <v>240</v>
-      </c>
-      <c r="C444" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="445" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A445" t="s">
-        <v>442</v>
-      </c>
-      <c r="B445">
-        <v>240</v>
-      </c>
-      <c r="C445" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="446" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A446" t="s">
-        <v>443</v>
-      </c>
-      <c r="B446">
-        <v>240</v>
-      </c>
-      <c r="C446" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="447" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A447" t="s">
-        <v>444</v>
-      </c>
-      <c r="B447">
-        <v>240</v>
-      </c>
-      <c r="C447" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="448" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A448" t="s">
-        <v>445</v>
-      </c>
-      <c r="B448">
-        <v>240</v>
-      </c>
-      <c r="C448" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="449" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A449" t="s">
-        <v>446</v>
-      </c>
-      <c r="B449">
-        <v>240</v>
-      </c>
-      <c r="C449" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A450" t="s">
-        <v>447</v>
-      </c>
-      <c r="B450">
-        <v>240</v>
-      </c>
-      <c r="C450" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="451" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A451" t="s">
-        <v>448</v>
-      </c>
-      <c r="B451">
-        <v>240</v>
-      </c>
-      <c r="C451" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A452" t="s">
-        <v>449</v>
-      </c>
-      <c r="B452">
-        <v>240</v>
-      </c>
-      <c r="C452" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="453" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A453" t="s">
-        <v>450</v>
-      </c>
-      <c r="B453">
-        <v>240</v>
-      </c>
-      <c r="C453" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A454" t="s">
-        <v>450</v>
-      </c>
-      <c r="B454">
-        <v>240</v>
-      </c>
-      <c r="C454" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A455" t="s">
-        <v>451</v>
-      </c>
-      <c r="B455">
-        <v>240</v>
-      </c>
-      <c r="C455" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A456" t="s">
-        <v>452</v>
-      </c>
-      <c r="B456">
-        <v>240</v>
-      </c>
-      <c r="C456" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="457" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A457" t="s">
-        <v>453</v>
-      </c>
-      <c r="B457">
-        <v>240</v>
-      </c>
-      <c r="C457" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="458" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A458" t="s">
-        <v>454</v>
-      </c>
-      <c r="B458">
-        <v>240</v>
-      </c>
-      <c r="C458" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="459" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A459" t="s">
-        <v>455</v>
-      </c>
-      <c r="B459">
-        <v>240</v>
-      </c>
-      <c r="C459" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A460" t="s">
-        <v>456</v>
-      </c>
-      <c r="B460">
-        <v>240</v>
-      </c>
-      <c r="C460" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A461" t="s">
-        <v>533</v>
-      </c>
-      <c r="B461">
-        <v>240</v>
-      </c>
-      <c r="C461" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A462" t="s">
-        <v>457</v>
-      </c>
-      <c r="B462">
-        <v>240</v>
-      </c>
-      <c r="C462" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A463" t="s">
-        <v>458</v>
-      </c>
-      <c r="B463">
-        <v>240</v>
-      </c>
-      <c r="C463" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="464" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A464" t="s">
-        <v>459</v>
-      </c>
-      <c r="B464">
-        <v>240</v>
-      </c>
-      <c r="C464" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="465" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A465" t="s">
-        <v>460</v>
-      </c>
-      <c r="B465">
-        <v>240</v>
-      </c>
-      <c r="C465" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="466" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A466" t="s">
-        <v>461</v>
-      </c>
-      <c r="B466">
-        <v>240</v>
-      </c>
-      <c r="C466" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="467" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A467" t="s">
-        <v>462</v>
-      </c>
-      <c r="B467">
-        <v>240</v>
-      </c>
-      <c r="C467" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A468" t="s">
-        <v>463</v>
-      </c>
-      <c r="B468">
-        <v>240</v>
-      </c>
-      <c r="C468" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="469" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A469" t="s">
-        <v>464</v>
-      </c>
-      <c r="B469">
-        <v>240</v>
-      </c>
-      <c r="C469" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="470" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A470" t="s">
-        <v>63</v>
-      </c>
-      <c r="B470">
-        <v>240</v>
-      </c>
-      <c r="C470" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="471" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A471" t="s">
-        <v>64</v>
-      </c>
-      <c r="B471">
-        <v>240</v>
-      </c>
-      <c r="C471" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="472" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A472" t="s">
-        <v>465</v>
-      </c>
-      <c r="B472">
-        <v>240</v>
-      </c>
-      <c r="C472" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="473" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A473" t="s">
-        <v>466</v>
-      </c>
-      <c r="B473">
-        <v>240</v>
-      </c>
-      <c r="C473" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="474" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A474" t="s">
-        <v>467</v>
-      </c>
-      <c r="B474">
-        <v>240</v>
-      </c>
-      <c r="C474" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="475" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A475" t="s">
-        <v>468</v>
-      </c>
-      <c r="B475">
-        <v>240</v>
-      </c>
-      <c r="C475" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A476" t="s">
-        <v>469</v>
-      </c>
-      <c r="B476">
-        <v>240</v>
-      </c>
-      <c r="C476" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A477" t="s">
-        <v>470</v>
-      </c>
-      <c r="B477">
-        <v>240</v>
-      </c>
-      <c r="C477" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A478" t="s">
-        <v>471</v>
-      </c>
-      <c r="B478">
-        <v>240</v>
-      </c>
-      <c r="C478" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A479" t="s">
-        <v>472</v>
-      </c>
-      <c r="B479">
-        <v>240</v>
-      </c>
-      <c r="C479" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A480" t="s">
-        <v>473</v>
-      </c>
-      <c r="B480">
-        <v>240</v>
-      </c>
-      <c r="C480" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A481" t="s">
-        <v>474</v>
-      </c>
-      <c r="B481">
-        <v>240</v>
-      </c>
-      <c r="C481" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A482" t="s">
-        <v>475</v>
-      </c>
-      <c r="B482">
-        <v>240</v>
-      </c>
-      <c r="C482" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A483" t="s">
-        <v>476</v>
-      </c>
-      <c r="B483">
-        <v>240</v>
-      </c>
-      <c r="C483" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A484" t="s">
-        <v>477</v>
-      </c>
-      <c r="B484">
-        <v>240</v>
-      </c>
-      <c r="C484" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A485" t="s">
-        <v>478</v>
-      </c>
-      <c r="B485">
-        <v>240</v>
-      </c>
-      <c r="C485" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A486" t="s">
-        <v>479</v>
-      </c>
-      <c r="B486">
-        <v>240</v>
-      </c>
-      <c r="C486" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A487" t="s">
-        <v>480</v>
-      </c>
-      <c r="B487">
-        <v>240</v>
-      </c>
-      <c r="C487" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A488" t="s">
-        <v>481</v>
-      </c>
-      <c r="B488">
-        <v>240</v>
-      </c>
-      <c r="C488" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A489" t="s">
-        <v>482</v>
-      </c>
-      <c r="B489">
-        <v>240</v>
-      </c>
-      <c r="C489" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A490" t="s">
-        <v>483</v>
-      </c>
-      <c r="B490">
-        <v>240</v>
-      </c>
-      <c r="C490" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A491" t="s">
-        <v>484</v>
-      </c>
-      <c r="B491">
-        <v>240</v>
-      </c>
-      <c r="C491" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A492" t="s">
-        <v>485</v>
-      </c>
-      <c r="B492">
-        <v>240</v>
-      </c>
-      <c r="C492" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A493" t="s">
-        <v>486</v>
-      </c>
-      <c r="B493">
-        <v>240</v>
-      </c>
-      <c r="C493" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A494" t="s">
-        <v>487</v>
-      </c>
-      <c r="B494">
-        <v>240</v>
-      </c>
-      <c r="C494" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A495" t="s">
-        <v>488</v>
-      </c>
-      <c r="B495">
-        <v>240</v>
-      </c>
-      <c r="C495" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A496" t="s">
-        <v>489</v>
-      </c>
-      <c r="B496">
-        <v>240</v>
-      </c>
-      <c r="C496" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="497" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A497" t="s">
-        <v>490</v>
-      </c>
-      <c r="B497">
-        <v>240</v>
-      </c>
-      <c r="C497" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="498" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A498" t="s">
-        <v>491</v>
-      </c>
-      <c r="B498">
-        <v>240</v>
-      </c>
-      <c r="C498" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="499" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A499" t="s">
-        <v>492</v>
-      </c>
-      <c r="B499">
-        <v>240</v>
-      </c>
-      <c r="C499" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="500" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A500" t="s">
-        <v>493</v>
-      </c>
-      <c r="B500">
-        <v>240</v>
-      </c>
-      <c r="C500" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="501" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A501" t="s">
-        <v>535</v>
-      </c>
-      <c r="B501">
-        <v>240</v>
-      </c>
-      <c r="C501" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="502" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A502" t="s">
-        <v>534</v>
-      </c>
-      <c r="B502">
-        <v>240</v>
-      </c>
-      <c r="C502" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="503" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A503" t="s">
-        <v>494</v>
-      </c>
-      <c r="B503">
-        <v>240</v>
-      </c>
-      <c r="C503" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="504" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A504" t="s">
-        <v>65</v>
-      </c>
-      <c r="B504">
-        <v>240</v>
-      </c>
-      <c r="C504" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="505" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A505" t="s">
-        <v>495</v>
-      </c>
-      <c r="B505">
-        <v>240</v>
-      </c>
-      <c r="C505" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="506" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A506" t="s">
-        <v>496</v>
-      </c>
-      <c r="B506">
-        <v>240</v>
-      </c>
-      <c r="C506" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="507" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A507" t="s">
-        <v>497</v>
-      </c>
-      <c r="B507">
-        <v>240</v>
-      </c>
-      <c r="C507" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A508" t="s">
-        <v>498</v>
-      </c>
-      <c r="B508">
-        <v>240</v>
-      </c>
-      <c r="C508" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="509" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A509" t="s">
-        <v>499</v>
-      </c>
-      <c r="B509">
-        <v>240</v>
-      </c>
-      <c r="C509" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="510" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A510" t="s">
-        <v>66</v>
-      </c>
-      <c r="B510">
-        <v>240</v>
-      </c>
-      <c r="C510" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="511" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A511" t="s">
-        <v>500</v>
-      </c>
-      <c r="B511">
-        <v>240</v>
-      </c>
-      <c r="C511" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="512" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A512" t="s">
-        <v>501</v>
-      </c>
-      <c r="B512">
-        <v>240</v>
-      </c>
-      <c r="C512" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="513" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A513" t="s">
-        <v>502</v>
-      </c>
-      <c r="B513">
-        <v>240</v>
-      </c>
-      <c r="C513" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="514" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A514" t="s">
-        <v>67</v>
-      </c>
-      <c r="B514">
-        <v>240</v>
-      </c>
-      <c r="C514" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="515" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A515" t="s">
-        <v>503</v>
-      </c>
-      <c r="B515">
-        <v>240</v>
-      </c>
-      <c r="C515" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="516" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A516" t="s">
-        <v>504</v>
-      </c>
-      <c r="B516">
-        <v>240</v>
-      </c>
-      <c r="C516" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="517" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A517" t="s">
-        <v>68</v>
-      </c>
-      <c r="B517">
-        <v>240</v>
-      </c>
-      <c r="C517" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="518" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A518" t="s">
-        <v>505</v>
-      </c>
-      <c r="B518">
-        <v>240</v>
-      </c>
-      <c r="C518" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="519" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A519" t="s">
-        <v>506</v>
-      </c>
-      <c r="B519">
-        <v>240</v>
-      </c>
-      <c r="C519" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="520" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A520" t="s">
-        <v>507</v>
-      </c>
-      <c r="B520">
-        <v>240</v>
-      </c>
-      <c r="C520" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="521" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A521" t="s">
-        <v>508</v>
-      </c>
-      <c r="B521">
-        <v>240</v>
-      </c>
-      <c r="C521" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="522" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A522" t="s">
-        <v>509</v>
-      </c>
-      <c r="B522">
-        <v>240</v>
-      </c>
-      <c r="C522" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="523" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A523" t="s">
-        <v>510</v>
-      </c>
-      <c r="B523">
-        <v>240</v>
-      </c>
-      <c r="C523" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="524" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A524" t="s">
-        <v>511</v>
-      </c>
-      <c r="B524">
-        <v>240</v>
-      </c>
-      <c r="C524" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="525" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A525" t="s">
-        <v>512</v>
-      </c>
-      <c r="B525">
-        <v>240</v>
-      </c>
-      <c r="C525" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="526" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A526" t="s">
-        <v>69</v>
-      </c>
-      <c r="B526">
-        <v>240</v>
-      </c>
-      <c r="C526" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="527" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A527" t="s">
-        <v>513</v>
-      </c>
-      <c r="B527">
-        <v>240</v>
-      </c>
-      <c r="C527" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="528" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A528" t="s">
-        <v>514</v>
-      </c>
-      <c r="B528">
-        <v>240</v>
-      </c>
-      <c r="C528" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="529" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A529" t="s">
-        <v>515</v>
-      </c>
-      <c r="B529">
-        <v>240</v>
-      </c>
-      <c r="C529" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="530" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A530" t="s">
-        <v>516</v>
-      </c>
-      <c r="B530">
-        <v>240</v>
-      </c>
-      <c r="C530" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="531" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A531" t="s">
-        <v>517</v>
-      </c>
-      <c r="B531">
-        <v>240</v>
-      </c>
-      <c r="C531" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="532" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A532" t="s">
-        <v>518</v>
-      </c>
-      <c r="B532">
-        <v>240</v>
-      </c>
-      <c r="C532" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="533" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A533" t="s">
-        <v>519</v>
-      </c>
-      <c r="B533">
-        <v>240</v>
-      </c>
-      <c r="C533" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="534" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A534" t="s">
-        <v>520</v>
-      </c>
-      <c r="B534">
-        <v>240</v>
-      </c>
-      <c r="C534" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="535" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A535" t="s">
-        <v>521</v>
-      </c>
-      <c r="B535">
-        <v>240</v>
-      </c>
-      <c r="C535" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="536" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A536" t="s">
-        <v>70</v>
-      </c>
-      <c r="B536">
-        <v>240</v>
-      </c>
-      <c r="C536" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C467">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C432">
+    <sortCondition ref="A1:A432"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/ativos.xlsx
+++ b/ativos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\INVESTIMENTOS VARIAVEL\Bybit\bybit_setups\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F1BE5EE-3958-4A8C-8D1D-071948C7601B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC420B8-D5AE-4459-8C24-6DA924CCA4E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="413">
   <si>
     <t>Par</t>
   </si>
@@ -95,9 +95,6 @@
     <t>COTIUSDT</t>
   </si>
   <si>
-    <t>CTKUSDT</t>
-  </si>
-  <si>
     <t>DOGEUSDT</t>
   </si>
   <si>
@@ -173,15 +170,9 @@
     <t>POPCATUSDT</t>
   </si>
   <si>
-    <t>PROMUSDT</t>
-  </si>
-  <si>
     <t>PYTHUSDT</t>
   </si>
   <si>
-    <t>REQUSDT</t>
-  </si>
-  <si>
     <t>RUNEUSDT</t>
   </si>
   <si>
@@ -431,9 +422,6 @@
     <t>CLANKERUSDT</t>
   </si>
   <si>
-    <t>CLOUDUSDT</t>
-  </si>
-  <si>
     <t>COOKIEUSDT</t>
   </si>
   <si>
@@ -470,18 +458,12 @@
     <t>DEEPUSDT</t>
   </si>
   <si>
-    <t>DEGENUSDT</t>
-  </si>
-  <si>
     <t>DEXEUSDT</t>
   </si>
   <si>
     <t>DIAUSDT</t>
   </si>
   <si>
-    <t>DOGUSDT</t>
-  </si>
-  <si>
     <t>DOODUSDT</t>
   </si>
   <si>
@@ -539,9 +521,6 @@
     <t>FILUSDT</t>
   </si>
   <si>
-    <t>FIOUSDT</t>
-  </si>
-  <si>
     <t>FLOCKUSDT</t>
   </si>
   <si>
@@ -611,9 +590,6 @@
     <t>HIGHUSDT</t>
   </si>
   <si>
-    <t>HIPPOUSDT</t>
-  </si>
-  <si>
     <t>HIVEUSDT</t>
   </si>
   <si>
@@ -626,9 +602,6 @@
     <t>HOMEUSDT</t>
   </si>
   <si>
-    <t>HPOS10IUSDT</t>
-  </si>
-  <si>
     <t>HUMAUSDT</t>
   </si>
   <si>
@@ -701,9 +674,6 @@
     <t>LDOUSDT</t>
   </si>
   <si>
-    <t>LISTAUSDT</t>
-  </si>
-  <si>
     <t>LPTUSDT</t>
   </si>
   <si>
@@ -803,9 +773,6 @@
     <t>OGNUSDT</t>
   </si>
   <si>
-    <t>OLUSDT</t>
-  </si>
-  <si>
     <t>ONGUSDT</t>
   </si>
   <si>
@@ -821,9 +788,6 @@
     <t>ORDIUSDT</t>
   </si>
   <si>
-    <t>OXTUSDT</t>
-  </si>
-  <si>
     <t>PARTIUSDT</t>
   </si>
   <si>
@@ -893,9 +857,6 @@
     <t>RAYDIUMUSDT</t>
   </si>
   <si>
-    <t>RDNTUSDT</t>
-  </si>
-  <si>
     <t>REDUSDT</t>
   </si>
   <si>
@@ -1028,9 +989,6 @@
     <t>SWARMSUSDT</t>
   </si>
   <si>
-    <t>SYNUSDT</t>
-  </si>
-  <si>
     <t>SYRUPUSDT</t>
   </si>
   <si>
@@ -1061,9 +1019,6 @@
     <t>TNSRUSDT</t>
   </si>
   <si>
-    <t>TRUUSDT</t>
-  </si>
-  <si>
     <t>TRUMPUSDT</t>
   </si>
   <si>
@@ -1302,6 +1257,24 @@
   </si>
   <si>
     <t>PIEVERSEUSDT</t>
+  </si>
+  <si>
+    <t>ZKCUSDT</t>
+  </si>
+  <si>
+    <t>CLOUSDT</t>
+  </si>
+  <si>
+    <t>BTWUSDT</t>
+  </si>
+  <si>
+    <t>EVAAUSDT</t>
+  </si>
+  <si>
+    <t>OPGUSDT</t>
+  </si>
+  <si>
+    <t>D</t>
   </si>
 </sst>
 </file>
@@ -1669,7 +1642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C419"/>
+  <dimension ref="A1:C409"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.5703125" bestFit="1" customWidth="1"/>
@@ -1688,4600 +1661,4490 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>400</v>
-      </c>
-      <c r="B2">
-        <v>240</v>
+        <v>385</v>
+      </c>
+      <c r="B2" t="s">
+        <v>412</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3">
-        <v>240</v>
+        <v>59</v>
+      </c>
+      <c r="B3" t="s">
+        <v>412</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>387</v>
-      </c>
-      <c r="B4">
-        <v>240</v>
+        <v>372</v>
+      </c>
+      <c r="B4" t="s">
+        <v>412</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5">
-        <v>240</v>
+      <c r="B5" t="s">
+        <v>412</v>
       </c>
       <c r="C5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6">
-        <v>240</v>
+      <c r="B6" t="s">
+        <v>412</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7">
-        <v>240</v>
+        <v>60</v>
+      </c>
+      <c r="B7" t="s">
+        <v>412</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>388</v>
-      </c>
-      <c r="B8">
-        <v>240</v>
+        <v>373</v>
+      </c>
+      <c r="B8" t="s">
+        <v>412</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9">
-        <v>240</v>
+        <v>61</v>
+      </c>
+      <c r="B9" t="s">
+        <v>412</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
-      <c r="B10">
-        <v>240</v>
+      <c r="B10" t="s">
+        <v>412</v>
       </c>
       <c r="C10" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>401</v>
-      </c>
-      <c r="B11">
-        <v>240</v>
+        <v>386</v>
+      </c>
+      <c r="B11" t="s">
+        <v>412</v>
       </c>
       <c r="C11" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>66</v>
-      </c>
-      <c r="B12">
-        <v>240</v>
+        <v>63</v>
+      </c>
+      <c r="B12" t="s">
+        <v>412</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>67</v>
-      </c>
-      <c r="B13">
-        <v>240</v>
+        <v>64</v>
+      </c>
+      <c r="B13" t="s">
+        <v>412</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14">
-        <v>240</v>
+        <v>65</v>
+      </c>
+      <c r="B14" t="s">
+        <v>412</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B15">
-        <v>240</v>
+        <v>66</v>
+      </c>
+      <c r="B15" t="s">
+        <v>412</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16">
-        <v>240</v>
+        <v>67</v>
+      </c>
+      <c r="B16" t="s">
+        <v>412</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>6</v>
       </c>
-      <c r="B17">
-        <v>240</v>
+      <c r="B17" t="s">
+        <v>412</v>
       </c>
       <c r="C17" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>71</v>
-      </c>
-      <c r="B18">
-        <v>240</v>
+        <v>68</v>
+      </c>
+      <c r="B18" t="s">
+        <v>412</v>
       </c>
       <c r="C18" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>72</v>
-      </c>
-      <c r="B19">
-        <v>240</v>
+        <v>69</v>
+      </c>
+      <c r="B19" t="s">
+        <v>412</v>
       </c>
       <c r="C19" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>73</v>
-      </c>
-      <c r="B20">
-        <v>240</v>
+        <v>70</v>
+      </c>
+      <c r="B20" t="s">
+        <v>412</v>
       </c>
       <c r="C20" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>74</v>
-      </c>
-      <c r="B21">
-        <v>240</v>
+        <v>71</v>
+      </c>
+      <c r="B21" t="s">
+        <v>412</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>75</v>
-      </c>
-      <c r="B22">
-        <v>240</v>
+        <v>72</v>
+      </c>
+      <c r="B22" t="s">
+        <v>412</v>
       </c>
       <c r="C22" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>402</v>
-      </c>
-      <c r="B23">
-        <v>240</v>
+        <v>387</v>
+      </c>
+      <c r="B23" t="s">
+        <v>412</v>
       </c>
       <c r="C23" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>76</v>
-      </c>
-      <c r="B24">
-        <v>240</v>
+        <v>73</v>
+      </c>
+      <c r="B24" t="s">
+        <v>412</v>
       </c>
       <c r="C24" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>415</v>
-      </c>
-      <c r="B25">
-        <v>240</v>
+        <v>400</v>
+      </c>
+      <c r="B25" t="s">
+        <v>412</v>
       </c>
       <c r="C25" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>77</v>
-      </c>
-      <c r="B26">
-        <v>240</v>
+        <v>74</v>
+      </c>
+      <c r="B26" t="s">
+        <v>412</v>
       </c>
       <c r="C26" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>78</v>
-      </c>
-      <c r="B27">
-        <v>240</v>
+        <v>75</v>
+      </c>
+      <c r="B27" t="s">
+        <v>412</v>
       </c>
       <c r="C27" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>7</v>
       </c>
-      <c r="B28">
-        <v>240</v>
+      <c r="B28" t="s">
+        <v>412</v>
       </c>
       <c r="C28" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>79</v>
-      </c>
-      <c r="B29">
-        <v>240</v>
+        <v>76</v>
+      </c>
+      <c r="B29" t="s">
+        <v>412</v>
       </c>
       <c r="C29" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>403</v>
-      </c>
-      <c r="B30">
-        <v>240</v>
+        <v>388</v>
+      </c>
+      <c r="B30" t="s">
+        <v>412</v>
       </c>
       <c r="C30" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>80</v>
-      </c>
-      <c r="B31">
-        <v>240</v>
+        <v>77</v>
+      </c>
+      <c r="B31" t="s">
+        <v>412</v>
       </c>
       <c r="C31" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>81</v>
-      </c>
-      <c r="B32">
-        <v>240</v>
+        <v>78</v>
+      </c>
+      <c r="B32" t="s">
+        <v>412</v>
       </c>
       <c r="C32" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>82</v>
-      </c>
-      <c r="B33">
-        <v>240</v>
+        <v>79</v>
+      </c>
+      <c r="B33" t="s">
+        <v>412</v>
       </c>
       <c r="C33" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>8</v>
       </c>
-      <c r="B34">
-        <v>240</v>
+      <c r="B34" t="s">
+        <v>412</v>
       </c>
       <c r="C34" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>9</v>
       </c>
-      <c r="B35">
-        <v>240</v>
+      <c r="B35" t="s">
+        <v>412</v>
       </c>
       <c r="C35" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>404</v>
-      </c>
-      <c r="B36">
-        <v>240</v>
+        <v>389</v>
+      </c>
+      <c r="B36" t="s">
+        <v>412</v>
       </c>
       <c r="C36" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>83</v>
-      </c>
-      <c r="B37">
-        <v>240</v>
+        <v>80</v>
+      </c>
+      <c r="B37" t="s">
+        <v>412</v>
       </c>
       <c r="C37" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>84</v>
-      </c>
-      <c r="B38">
-        <v>240</v>
+        <v>81</v>
+      </c>
+      <c r="B38" t="s">
+        <v>412</v>
       </c>
       <c r="C38" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>10</v>
       </c>
-      <c r="B39">
-        <v>240</v>
+      <c r="B39" t="s">
+        <v>412</v>
       </c>
       <c r="C39" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>405</v>
-      </c>
-      <c r="B40">
-        <v>240</v>
+        <v>390</v>
+      </c>
+      <c r="B40" t="s">
+        <v>412</v>
       </c>
       <c r="C40" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>86</v>
-      </c>
-      <c r="B41">
-        <v>240</v>
+        <v>83</v>
+      </c>
+      <c r="B41" t="s">
+        <v>412</v>
       </c>
       <c r="C41" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>85</v>
-      </c>
-      <c r="B42">
-        <v>240</v>
+        <v>82</v>
+      </c>
+      <c r="B42" t="s">
+        <v>412</v>
       </c>
       <c r="C42" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>87</v>
-      </c>
-      <c r="B43">
-        <v>240</v>
+        <v>84</v>
+      </c>
+      <c r="B43" t="s">
+        <v>412</v>
       </c>
       <c r="C43" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>389</v>
-      </c>
-      <c r="B44">
-        <v>240</v>
+        <v>374</v>
+      </c>
+      <c r="B44" t="s">
+        <v>412</v>
       </c>
       <c r="C44" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>406</v>
-      </c>
-      <c r="B45">
-        <v>240</v>
+        <v>391</v>
+      </c>
+      <c r="B45" t="s">
+        <v>412</v>
       </c>
       <c r="C45" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>407</v>
-      </c>
-      <c r="B46">
-        <v>240</v>
+        <v>392</v>
+      </c>
+      <c r="B46" t="s">
+        <v>412</v>
       </c>
       <c r="C46" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>88</v>
-      </c>
-      <c r="B47">
-        <v>240</v>
+        <v>85</v>
+      </c>
+      <c r="B47" t="s">
+        <v>412</v>
       </c>
       <c r="C47" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>89</v>
-      </c>
-      <c r="B48">
-        <v>240</v>
+        <v>86</v>
+      </c>
+      <c r="B48" t="s">
+        <v>412</v>
       </c>
       <c r="C48" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>90</v>
-      </c>
-      <c r="B49">
-        <v>240</v>
+        <v>87</v>
+      </c>
+      <c r="B49" t="s">
+        <v>412</v>
       </c>
       <c r="C49" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>408</v>
-      </c>
-      <c r="B50">
-        <v>240</v>
+        <v>393</v>
+      </c>
+      <c r="B50" t="s">
+        <v>412</v>
       </c>
       <c r="C50" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>91</v>
-      </c>
-      <c r="B51">
-        <v>240</v>
+        <v>88</v>
+      </c>
+      <c r="B51" t="s">
+        <v>412</v>
       </c>
       <c r="C51" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>65</v>
-      </c>
-      <c r="B52">
-        <v>240</v>
+        <v>62</v>
+      </c>
+      <c r="B52" t="s">
+        <v>412</v>
       </c>
       <c r="C52" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>92</v>
-      </c>
-      <c r="B53">
-        <v>240</v>
+        <v>89</v>
+      </c>
+      <c r="B53" t="s">
+        <v>412</v>
       </c>
       <c r="C53" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>11</v>
       </c>
-      <c r="B54">
-        <v>240</v>
+      <c r="B54" t="s">
+        <v>412</v>
       </c>
       <c r="C54" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>409</v>
-      </c>
-      <c r="B55">
-        <v>240</v>
+        <v>394</v>
+      </c>
+      <c r="B55" t="s">
+        <v>412</v>
       </c>
       <c r="C55" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>93</v>
-      </c>
-      <c r="B56">
-        <v>240</v>
+        <v>90</v>
+      </c>
+      <c r="B56" t="s">
+        <v>412</v>
       </c>
       <c r="C56" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>94</v>
-      </c>
-      <c r="B57">
-        <v>240</v>
+        <v>91</v>
+      </c>
+      <c r="B57" t="s">
+        <v>412</v>
       </c>
       <c r="C57" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>95</v>
-      </c>
-      <c r="B58">
-        <v>240</v>
+        <v>92</v>
+      </c>
+      <c r="B58" t="s">
+        <v>412</v>
       </c>
       <c r="C58" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>96</v>
-      </c>
-      <c r="B59">
-        <v>240</v>
+        <v>93</v>
+      </c>
+      <c r="B59" t="s">
+        <v>412</v>
       </c>
       <c r="C59" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>97</v>
-      </c>
-      <c r="B60">
-        <v>240</v>
+        <v>94</v>
+      </c>
+      <c r="B60" t="s">
+        <v>412</v>
       </c>
       <c r="C60" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>98</v>
-      </c>
-      <c r="B61">
-        <v>240</v>
+        <v>95</v>
+      </c>
+      <c r="B61" t="s">
+        <v>412</v>
       </c>
       <c r="C61" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>100</v>
-      </c>
-      <c r="B62">
-        <v>240</v>
+        <v>97</v>
+      </c>
+      <c r="B62" t="s">
+        <v>412</v>
       </c>
       <c r="C62" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>101</v>
-      </c>
-      <c r="B63">
-        <v>240</v>
+        <v>98</v>
+      </c>
+      <c r="B63" t="s">
+        <v>412</v>
       </c>
       <c r="C63" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>102</v>
-      </c>
-      <c r="B64">
-        <v>240</v>
+        <v>99</v>
+      </c>
+      <c r="B64" t="s">
+        <v>412</v>
       </c>
       <c r="C64" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>99</v>
-      </c>
-      <c r="B65">
-        <v>240</v>
+        <v>96</v>
+      </c>
+      <c r="B65" t="s">
+        <v>412</v>
       </c>
       <c r="C65" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>103</v>
-      </c>
-      <c r="B66">
-        <v>240</v>
+        <v>100</v>
+      </c>
+      <c r="B66" t="s">
+        <v>412</v>
       </c>
       <c r="C66" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>104</v>
-      </c>
-      <c r="B67">
-        <v>240</v>
+        <v>101</v>
+      </c>
+      <c r="B67" t="s">
+        <v>412</v>
       </c>
       <c r="C67" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>105</v>
-      </c>
-      <c r="B68">
-        <v>240</v>
+        <v>102</v>
+      </c>
+      <c r="B68" t="s">
+        <v>412</v>
       </c>
       <c r="C68" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>106</v>
-      </c>
-      <c r="B69">
-        <v>240</v>
+        <v>103</v>
+      </c>
+      <c r="B69" t="s">
+        <v>412</v>
       </c>
       <c r="C69" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>412</v>
-      </c>
-      <c r="B70">
-        <v>240</v>
+        <v>397</v>
+      </c>
+      <c r="B70" t="s">
+        <v>412</v>
       </c>
       <c r="C70" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>107</v>
-      </c>
-      <c r="B71">
-        <v>240</v>
+        <v>104</v>
+      </c>
+      <c r="B71" t="s">
+        <v>412</v>
       </c>
       <c r="C71" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>108</v>
-      </c>
-      <c r="B72">
-        <v>240</v>
+        <v>105</v>
+      </c>
+      <c r="B72" t="s">
+        <v>412</v>
       </c>
       <c r="C72" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>109</v>
-      </c>
-      <c r="B73">
-        <v>240</v>
+        <v>106</v>
+      </c>
+      <c r="B73" t="s">
+        <v>412</v>
       </c>
       <c r="C73" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>12</v>
       </c>
-      <c r="B74">
-        <v>240</v>
+      <c r="B74" t="s">
+        <v>412</v>
       </c>
       <c r="C74" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>110</v>
-      </c>
-      <c r="B75">
-        <v>240</v>
+        <v>107</v>
+      </c>
+      <c r="B75" t="s">
+        <v>412</v>
       </c>
       <c r="C75" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>390</v>
-      </c>
-      <c r="B76">
-        <v>240</v>
+        <v>375</v>
+      </c>
+      <c r="B76" t="s">
+        <v>412</v>
       </c>
       <c r="C76" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>417</v>
-      </c>
-      <c r="B77">
-        <v>240</v>
+        <v>402</v>
+      </c>
+      <c r="B77" t="s">
+        <v>412</v>
       </c>
       <c r="C77" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>111</v>
-      </c>
-      <c r="B78">
-        <v>240</v>
+        <v>108</v>
+      </c>
+      <c r="B78" t="s">
+        <v>412</v>
       </c>
       <c r="C78" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>112</v>
-      </c>
-      <c r="B79">
-        <v>240</v>
+        <v>109</v>
+      </c>
+      <c r="B79" t="s">
+        <v>412</v>
       </c>
       <c r="C79" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>13</v>
       </c>
-      <c r="B80">
-        <v>240</v>
+      <c r="B80" t="s">
+        <v>412</v>
       </c>
       <c r="C80" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>113</v>
-      </c>
-      <c r="B81">
-        <v>240</v>
+        <v>110</v>
+      </c>
+      <c r="B81" t="s">
+        <v>412</v>
       </c>
       <c r="C81" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>114</v>
-      </c>
-      <c r="B82">
-        <v>240</v>
+        <v>111</v>
+      </c>
+      <c r="B82" t="s">
+        <v>412</v>
       </c>
       <c r="C82" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>115</v>
-      </c>
-      <c r="B83">
-        <v>240</v>
+        <v>112</v>
+      </c>
+      <c r="B83" t="s">
+        <v>412</v>
       </c>
       <c r="C83" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>14</v>
       </c>
-      <c r="B84">
-        <v>240</v>
+      <c r="B84" t="s">
+        <v>412</v>
       </c>
       <c r="C84" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>116</v>
-      </c>
-      <c r="B85">
-        <v>240</v>
+        <v>113</v>
+      </c>
+      <c r="B85" t="s">
+        <v>412</v>
       </c>
       <c r="C85" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>15</v>
       </c>
-      <c r="B86">
-        <v>240</v>
+      <c r="B86" t="s">
+        <v>412</v>
       </c>
       <c r="C86" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>117</v>
-      </c>
-      <c r="B87">
-        <v>240</v>
+        <v>114</v>
+      </c>
+      <c r="B87" t="s">
+        <v>412</v>
       </c>
       <c r="C87" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>411</v>
-      </c>
-      <c r="B88">
-        <v>240</v>
+        <v>396</v>
+      </c>
+      <c r="B88" t="s">
+        <v>412</v>
       </c>
       <c r="C88" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>119</v>
-      </c>
-      <c r="B89">
-        <v>240</v>
+        <v>409</v>
+      </c>
+      <c r="B89" t="s">
+        <v>412</v>
       </c>
       <c r="C89" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>120</v>
-      </c>
-      <c r="B90">
-        <v>240</v>
+        <v>116</v>
+      </c>
+      <c r="B90" t="s">
+        <v>412</v>
       </c>
       <c r="C90" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>121</v>
-      </c>
-      <c r="B91">
-        <v>240</v>
+        <v>117</v>
+      </c>
+      <c r="B91" t="s">
+        <v>412</v>
       </c>
       <c r="C91" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>122</v>
-      </c>
-      <c r="B92">
-        <v>240</v>
+        <v>118</v>
+      </c>
+      <c r="B92" t="s">
+        <v>412</v>
       </c>
       <c r="C92" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>123</v>
-      </c>
-      <c r="B93">
-        <v>240</v>
+        <v>119</v>
+      </c>
+      <c r="B93" t="s">
+        <v>412</v>
       </c>
       <c r="C93" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>124</v>
-      </c>
-      <c r="B94">
-        <v>240</v>
+        <v>120</v>
+      </c>
+      <c r="B94" t="s">
+        <v>412</v>
       </c>
       <c r="C94" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>125</v>
-      </c>
-      <c r="B95">
-        <v>240</v>
+        <v>121</v>
+      </c>
+      <c r="B95" t="s">
+        <v>412</v>
       </c>
       <c r="C95" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>126</v>
-      </c>
-      <c r="B96">
-        <v>240</v>
+        <v>122</v>
+      </c>
+      <c r="B96" t="s">
+        <v>412</v>
       </c>
       <c r="C96" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>127</v>
-      </c>
-      <c r="B97">
-        <v>240</v>
+        <v>123</v>
+      </c>
+      <c r="B97" t="s">
+        <v>412</v>
       </c>
       <c r="C97" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>128</v>
-      </c>
-      <c r="B98">
-        <v>240</v>
+        <v>124</v>
+      </c>
+      <c r="B98" t="s">
+        <v>412</v>
       </c>
       <c r="C98" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>129</v>
-      </c>
-      <c r="B99">
-        <v>240</v>
+        <v>125</v>
+      </c>
+      <c r="B99" t="s">
+        <v>412</v>
       </c>
       <c r="C99" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>391</v>
-      </c>
-      <c r="B100">
-        <v>240</v>
+        <v>126</v>
+      </c>
+      <c r="B100" t="s">
+        <v>412</v>
       </c>
       <c r="C100" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>130</v>
-      </c>
-      <c r="B101">
-        <v>240</v>
+        <v>376</v>
+      </c>
+      <c r="B101" t="s">
+        <v>412</v>
       </c>
       <c r="C101" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>131</v>
-      </c>
-      <c r="B102">
-        <v>240</v>
+        <v>127</v>
+      </c>
+      <c r="B102" t="s">
+        <v>412</v>
       </c>
       <c r="C102" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>16</v>
-      </c>
-      <c r="B103">
-        <v>240</v>
+        <v>408</v>
+      </c>
+      <c r="B103" t="s">
+        <v>412</v>
       </c>
       <c r="C103" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>132</v>
-      </c>
-      <c r="B104">
-        <v>240</v>
+        <v>16</v>
+      </c>
+      <c r="B104" t="s">
+        <v>412</v>
       </c>
       <c r="C104" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>17</v>
-      </c>
-      <c r="B105">
-        <v>240</v>
+        <v>128</v>
+      </c>
+      <c r="B105" t="s">
+        <v>412</v>
       </c>
       <c r="C105" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>18</v>
-      </c>
-      <c r="B106">
-        <v>240</v>
+        <v>17</v>
+      </c>
+      <c r="B106" t="s">
+        <v>412</v>
       </c>
       <c r="C106" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>133</v>
-      </c>
-      <c r="B107">
-        <v>240</v>
+        <v>18</v>
+      </c>
+      <c r="B107" t="s">
+        <v>412</v>
       </c>
       <c r="C107" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>135</v>
-      </c>
-      <c r="B108">
-        <v>240</v>
+        <v>129</v>
+      </c>
+      <c r="B108" t="s">
+        <v>412</v>
       </c>
       <c r="C108" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>134</v>
-      </c>
-      <c r="B109">
-        <v>240</v>
+        <v>131</v>
+      </c>
+      <c r="B109" t="s">
+        <v>412</v>
       </c>
       <c r="C109" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>136</v>
-      </c>
-      <c r="B110">
-        <v>240</v>
+        <v>130</v>
+      </c>
+      <c r="B110" t="s">
+        <v>412</v>
       </c>
       <c r="C110" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>137</v>
-      </c>
-      <c r="B111">
-        <v>240</v>
+        <v>132</v>
+      </c>
+      <c r="B111" t="s">
+        <v>412</v>
       </c>
       <c r="C111" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>19</v>
-      </c>
-      <c r="B112">
-        <v>240</v>
+        <v>133</v>
+      </c>
+      <c r="B112" t="s">
+        <v>412</v>
       </c>
       <c r="C112" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>118</v>
-      </c>
-      <c r="B113">
-        <v>240</v>
+        <v>115</v>
+      </c>
+      <c r="B113" t="s">
+        <v>412</v>
       </c>
       <c r="C113" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>138</v>
-      </c>
-      <c r="B114">
-        <v>240</v>
+        <v>134</v>
+      </c>
+      <c r="B114" t="s">
+        <v>412</v>
       </c>
       <c r="C114" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>139</v>
-      </c>
-      <c r="B115">
-        <v>240</v>
+        <v>135</v>
+      </c>
+      <c r="B115" t="s">
+        <v>412</v>
       </c>
       <c r="C115" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>140</v>
-      </c>
-      <c r="B116">
-        <v>240</v>
+        <v>136</v>
+      </c>
+      <c r="B116" t="s">
+        <v>412</v>
       </c>
       <c r="C116" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>141</v>
-      </c>
-      <c r="B117">
-        <v>240</v>
+        <v>137</v>
+      </c>
+      <c r="B117" t="s">
+        <v>412</v>
       </c>
       <c r="C117" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>142</v>
-      </c>
-      <c r="B118">
-        <v>240</v>
+        <v>138</v>
+      </c>
+      <c r="B118" t="s">
+        <v>412</v>
       </c>
       <c r="C118" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>143</v>
-      </c>
-      <c r="B119">
-        <v>240</v>
+        <v>139</v>
+      </c>
+      <c r="B119" t="s">
+        <v>412</v>
       </c>
       <c r="C119" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>144</v>
-      </c>
-      <c r="B120">
-        <v>240</v>
+        <v>140</v>
+      </c>
+      <c r="B120" t="s">
+        <v>412</v>
       </c>
       <c r="C120" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>145</v>
-      </c>
-      <c r="B121">
-        <v>240</v>
+        <v>141</v>
+      </c>
+      <c r="B121" t="s">
+        <v>412</v>
       </c>
       <c r="C121" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>146</v>
-      </c>
-      <c r="B122">
-        <v>240</v>
+        <v>19</v>
+      </c>
+      <c r="B122" t="s">
+        <v>412</v>
       </c>
       <c r="C122" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>20</v>
-      </c>
-      <c r="B123">
-        <v>240</v>
+        <v>142</v>
+      </c>
+      <c r="B123" t="s">
+        <v>412</v>
       </c>
       <c r="C123" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>147</v>
-      </c>
-      <c r="B124">
-        <v>240</v>
+        <v>143</v>
+      </c>
+      <c r="B124" t="s">
+        <v>412</v>
       </c>
       <c r="C124" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>148</v>
-      </c>
-      <c r="B125">
-        <v>240</v>
+        <v>144</v>
+      </c>
+      <c r="B125" t="s">
+        <v>412</v>
       </c>
       <c r="C125" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>149</v>
-      </c>
-      <c r="B126">
-        <v>240</v>
+        <v>145</v>
+      </c>
+      <c r="B126" t="s">
+        <v>412</v>
       </c>
       <c r="C126" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>150</v>
-      </c>
-      <c r="B127">
-        <v>240</v>
+        <v>146</v>
+      </c>
+      <c r="B127" t="s">
+        <v>412</v>
       </c>
       <c r="C127" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>151</v>
-      </c>
-      <c r="B128">
-        <v>240</v>
+        <v>147</v>
+      </c>
+      <c r="B128" t="s">
+        <v>412</v>
       </c>
       <c r="C128" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>152</v>
-      </c>
-      <c r="B129">
-        <v>240</v>
+        <v>403</v>
+      </c>
+      <c r="B129" t="s">
+        <v>412</v>
       </c>
       <c r="C129" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>153</v>
-      </c>
-      <c r="B130">
-        <v>240</v>
+        <v>148</v>
+      </c>
+      <c r="B130" t="s">
+        <v>412</v>
       </c>
       <c r="C130" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>418</v>
-      </c>
-      <c r="B131">
-        <v>240</v>
+        <v>149</v>
+      </c>
+      <c r="B131" t="s">
+        <v>412</v>
       </c>
       <c r="C131" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>154</v>
-      </c>
-      <c r="B132">
-        <v>240</v>
+        <v>150</v>
+      </c>
+      <c r="B132" t="s">
+        <v>412</v>
       </c>
       <c r="C132" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>155</v>
-      </c>
-      <c r="B133">
-        <v>240</v>
+        <v>20</v>
+      </c>
+      <c r="B133" t="s">
+        <v>412</v>
       </c>
       <c r="C133" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>156</v>
-      </c>
-      <c r="B134">
-        <v>240</v>
+        <v>151</v>
+      </c>
+      <c r="B134" t="s">
+        <v>412</v>
       </c>
       <c r="C134" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>21</v>
-      </c>
-      <c r="B135">
-        <v>240</v>
+        <v>152</v>
+      </c>
+      <c r="B135" t="s">
+        <v>412</v>
       </c>
       <c r="C135" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>157</v>
-      </c>
-      <c r="B136">
-        <v>240</v>
+        <v>153</v>
+      </c>
+      <c r="B136" t="s">
+        <v>412</v>
       </c>
       <c r="C136" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>158</v>
-      </c>
-      <c r="B137">
-        <v>240</v>
+        <v>154</v>
+      </c>
+      <c r="B137" t="s">
+        <v>412</v>
       </c>
       <c r="C137" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>159</v>
-      </c>
-      <c r="B138">
-        <v>240</v>
+        <v>155</v>
+      </c>
+      <c r="B138" t="s">
+        <v>412</v>
       </c>
       <c r="C138" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>160</v>
-      </c>
-      <c r="B139">
-        <v>240</v>
+        <v>156</v>
+      </c>
+      <c r="B139" t="s">
+        <v>412</v>
       </c>
       <c r="C139" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>161</v>
-      </c>
-      <c r="B140">
-        <v>240</v>
+        <v>157</v>
+      </c>
+      <c r="B140" t="s">
+        <v>412</v>
       </c>
       <c r="C140" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>162</v>
-      </c>
-      <c r="B141">
-        <v>240</v>
+        <v>158</v>
+      </c>
+      <c r="B141" t="s">
+        <v>412</v>
       </c>
       <c r="C141" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>163</v>
-      </c>
-      <c r="B142">
-        <v>240</v>
+        <v>21</v>
+      </c>
+      <c r="B142" t="s">
+        <v>412</v>
       </c>
       <c r="C142" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>164</v>
-      </c>
-      <c r="B143">
-        <v>240</v>
+        <v>410</v>
+      </c>
+      <c r="B143" t="s">
+        <v>412</v>
       </c>
       <c r="C143" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>22</v>
       </c>
-      <c r="B144">
-        <v>240</v>
+      <c r="B144" t="s">
+        <v>412</v>
       </c>
       <c r="C144" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>23</v>
-      </c>
-      <c r="B145">
-        <v>240</v>
+        <v>399</v>
+      </c>
+      <c r="B145" t="s">
+        <v>412</v>
       </c>
       <c r="C145" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>414</v>
-      </c>
-      <c r="B146">
-        <v>240</v>
+        <v>159</v>
+      </c>
+      <c r="B146" t="s">
+        <v>412</v>
       </c>
       <c r="C146" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>165</v>
-      </c>
-      <c r="B147">
-        <v>240</v>
+        <v>160</v>
+      </c>
+      <c r="B147" t="s">
+        <v>412</v>
       </c>
       <c r="C147" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>166</v>
-      </c>
-      <c r="B148">
-        <v>240</v>
+        <v>161</v>
+      </c>
+      <c r="B148" t="s">
+        <v>412</v>
       </c>
       <c r="C148" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>167</v>
-      </c>
-      <c r="B149">
-        <v>240</v>
+        <v>162</v>
+      </c>
+      <c r="B149" t="s">
+        <v>412</v>
       </c>
       <c r="C149" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>168</v>
-      </c>
-      <c r="B150">
-        <v>240</v>
+        <v>163</v>
+      </c>
+      <c r="B150" t="s">
+        <v>412</v>
       </c>
       <c r="C150" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>169</v>
-      </c>
-      <c r="B151">
-        <v>240</v>
+        <v>164</v>
+      </c>
+      <c r="B151" t="s">
+        <v>412</v>
       </c>
       <c r="C151" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>170</v>
-      </c>
-      <c r="B152">
-        <v>240</v>
+        <v>405</v>
+      </c>
+      <c r="B152" t="s">
+        <v>412</v>
       </c>
       <c r="C152" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>171</v>
-      </c>
-      <c r="B153">
-        <v>240</v>
+        <v>165</v>
+      </c>
+      <c r="B153" t="s">
+        <v>412</v>
       </c>
       <c r="C153" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>420</v>
-      </c>
-      <c r="B154">
-        <v>240</v>
+        <v>23</v>
+      </c>
+      <c r="B154" t="s">
+        <v>412</v>
       </c>
       <c r="C154" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>172</v>
-      </c>
-      <c r="B155">
-        <v>240</v>
+        <v>24</v>
+      </c>
+      <c r="B155" t="s">
+        <v>412</v>
       </c>
       <c r="C155" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>24</v>
-      </c>
-      <c r="B156">
-        <v>240</v>
+        <v>166</v>
+      </c>
+      <c r="B156" t="s">
+        <v>412</v>
       </c>
       <c r="C156" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>25</v>
-      </c>
-      <c r="B157">
-        <v>240</v>
+        <v>395</v>
+      </c>
+      <c r="B157" t="s">
+        <v>412</v>
       </c>
       <c r="C157" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>173</v>
-      </c>
-      <c r="B158">
-        <v>240</v>
+        <v>167</v>
+      </c>
+      <c r="B158" t="s">
+        <v>412</v>
       </c>
       <c r="C158" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>410</v>
-      </c>
-      <c r="B159">
-        <v>240</v>
+        <v>168</v>
+      </c>
+      <c r="B159" t="s">
+        <v>412</v>
       </c>
       <c r="C159" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>174</v>
-      </c>
-      <c r="B160">
-        <v>240</v>
+        <v>25</v>
+      </c>
+      <c r="B160" t="s">
+        <v>412</v>
       </c>
       <c r="C160" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>175</v>
-      </c>
-      <c r="B161">
-        <v>240</v>
+        <v>169</v>
+      </c>
+      <c r="B161" t="s">
+        <v>412</v>
       </c>
       <c r="C161" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>26</v>
-      </c>
-      <c r="B162">
-        <v>240</v>
+        <v>170</v>
+      </c>
+      <c r="B162" t="s">
+        <v>412</v>
       </c>
       <c r="C162" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>176</v>
-      </c>
-      <c r="B163">
-        <v>240</v>
+        <v>171</v>
+      </c>
+      <c r="B163" t="s">
+        <v>412</v>
       </c>
       <c r="C163" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>177</v>
-      </c>
-      <c r="B164">
-        <v>240</v>
+        <v>172</v>
+      </c>
+      <c r="B164" t="s">
+        <v>412</v>
       </c>
       <c r="C164" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>178</v>
-      </c>
-      <c r="B165">
-        <v>240</v>
+        <v>173</v>
+      </c>
+      <c r="B165" t="s">
+        <v>412</v>
       </c>
       <c r="C165" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>179</v>
-      </c>
-      <c r="B166">
-        <v>240</v>
+        <v>174</v>
+      </c>
+      <c r="B166" t="s">
+        <v>412</v>
       </c>
       <c r="C166" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>180</v>
-      </c>
-      <c r="B167">
-        <v>240</v>
+        <v>175</v>
+      </c>
+      <c r="B167" t="s">
+        <v>412</v>
       </c>
       <c r="C167" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>181</v>
-      </c>
-      <c r="B168">
-        <v>240</v>
+        <v>176</v>
+      </c>
+      <c r="B168" t="s">
+        <v>412</v>
       </c>
       <c r="C168" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>182</v>
-      </c>
-      <c r="B169">
-        <v>240</v>
+        <v>177</v>
+      </c>
+      <c r="B169" t="s">
+        <v>412</v>
       </c>
       <c r="C169" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>183</v>
-      </c>
-      <c r="B170">
-        <v>240</v>
+        <v>179</v>
+      </c>
+      <c r="B170" t="s">
+        <v>412</v>
       </c>
       <c r="C170" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>184</v>
-      </c>
-      <c r="B171">
-        <v>240</v>
+        <v>180</v>
+      </c>
+      <c r="B171" t="s">
+        <v>412</v>
       </c>
       <c r="C171" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>186</v>
-      </c>
-      <c r="B172">
-        <v>240</v>
+        <v>181</v>
+      </c>
+      <c r="B172" t="s">
+        <v>412</v>
       </c>
       <c r="C172" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>187</v>
-      </c>
-      <c r="B173">
-        <v>240</v>
+        <v>182</v>
+      </c>
+      <c r="B173" t="s">
+        <v>412</v>
       </c>
       <c r="C173" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>188</v>
-      </c>
-      <c r="B174">
-        <v>240</v>
+        <v>183</v>
+      </c>
+      <c r="B174" t="s">
+        <v>412</v>
       </c>
       <c r="C174" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>189</v>
-      </c>
-      <c r="B175">
-        <v>240</v>
+        <v>184</v>
+      </c>
+      <c r="B175" t="s">
+        <v>412</v>
       </c>
       <c r="C175" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>190</v>
-      </c>
-      <c r="B176">
-        <v>240</v>
+        <v>185</v>
+      </c>
+      <c r="B176" t="s">
+        <v>412</v>
       </c>
       <c r="C176" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>191</v>
-      </c>
-      <c r="B177">
-        <v>240</v>
+        <v>186</v>
+      </c>
+      <c r="B177" t="s">
+        <v>412</v>
       </c>
       <c r="C177" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>192</v>
-      </c>
-      <c r="B178">
-        <v>240</v>
+        <v>187</v>
+      </c>
+      <c r="B178" t="s">
+        <v>412</v>
       </c>
       <c r="C178" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>193</v>
-      </c>
-      <c r="B179">
-        <v>240</v>
+        <v>188</v>
+      </c>
+      <c r="B179" t="s">
+        <v>412</v>
       </c>
       <c r="C179" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>194</v>
-      </c>
-      <c r="B180">
-        <v>240</v>
+        <v>178</v>
+      </c>
+      <c r="B180" t="s">
+        <v>412</v>
       </c>
       <c r="C180" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>195</v>
-      </c>
-      <c r="B181">
-        <v>240</v>
+        <v>190</v>
+      </c>
+      <c r="B181" t="s">
+        <v>412</v>
       </c>
       <c r="C181" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>196</v>
-      </c>
-      <c r="B182">
-        <v>240</v>
+        <v>189</v>
+      </c>
+      <c r="B182" t="s">
+        <v>412</v>
       </c>
       <c r="C182" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>197</v>
-      </c>
-      <c r="B183">
-        <v>240</v>
+        <v>191</v>
+      </c>
+      <c r="B183" t="s">
+        <v>412</v>
       </c>
       <c r="C183" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>185</v>
-      </c>
-      <c r="B184">
-        <v>240</v>
+        <v>377</v>
+      </c>
+      <c r="B184" t="s">
+        <v>412</v>
       </c>
       <c r="C184" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>199</v>
-      </c>
-      <c r="B185">
-        <v>240</v>
+        <v>192</v>
+      </c>
+      <c r="B185" t="s">
+        <v>412</v>
       </c>
       <c r="C185" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>198</v>
-      </c>
-      <c r="B186">
-        <v>240</v>
+        <v>193</v>
+      </c>
+      <c r="B186" t="s">
+        <v>412</v>
       </c>
       <c r="C186" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>200</v>
-      </c>
-      <c r="B187">
-        <v>240</v>
+        <v>194</v>
+      </c>
+      <c r="B187" t="s">
+        <v>412</v>
       </c>
       <c r="C187" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>392</v>
-      </c>
-      <c r="B188">
-        <v>240</v>
+        <v>195</v>
+      </c>
+      <c r="B188" t="s">
+        <v>412</v>
       </c>
       <c r="C188" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>201</v>
-      </c>
-      <c r="B189">
-        <v>240</v>
+        <v>196</v>
+      </c>
+      <c r="B189" t="s">
+        <v>412</v>
       </c>
       <c r="C189" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>202</v>
-      </c>
-      <c r="B190">
-        <v>240</v>
+        <v>197</v>
+      </c>
+      <c r="B190" t="s">
+        <v>412</v>
       </c>
       <c r="C190" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>203</v>
-      </c>
-      <c r="B191">
-        <v>240</v>
+        <v>199</v>
+      </c>
+      <c r="B191" t="s">
+        <v>412</v>
       </c>
       <c r="C191" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>204</v>
-      </c>
-      <c r="B192">
-        <v>240</v>
+        <v>200</v>
+      </c>
+      <c r="B192" t="s">
+        <v>412</v>
       </c>
       <c r="C192" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>205</v>
-      </c>
-      <c r="B193">
-        <v>240</v>
+        <v>201</v>
+      </c>
+      <c r="B193" t="s">
+        <v>412</v>
       </c>
       <c r="C193" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>206</v>
-      </c>
-      <c r="B194">
-        <v>240</v>
+        <v>198</v>
+      </c>
+      <c r="B194" t="s">
+        <v>412</v>
       </c>
       <c r="C194" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>208</v>
-      </c>
-      <c r="B195">
-        <v>240</v>
+        <v>202</v>
+      </c>
+      <c r="B195" t="s">
+        <v>412</v>
       </c>
       <c r="C195" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>209</v>
-      </c>
-      <c r="B196">
-        <v>240</v>
+        <v>26</v>
+      </c>
+      <c r="B196" t="s">
+        <v>412</v>
       </c>
       <c r="C196" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>210</v>
-      </c>
-      <c r="B197">
-        <v>240</v>
+        <v>203</v>
+      </c>
+      <c r="B197" t="s">
+        <v>412</v>
       </c>
       <c r="C197" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>207</v>
-      </c>
-      <c r="B198">
-        <v>240</v>
+        <v>204</v>
+      </c>
+      <c r="B198" t="s">
+        <v>412</v>
       </c>
       <c r="C198" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>211</v>
-      </c>
-      <c r="B199">
-        <v>240</v>
+        <v>27</v>
+      </c>
+      <c r="B199" t="s">
+        <v>412</v>
       </c>
       <c r="C199" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>27</v>
-      </c>
-      <c r="B200">
-        <v>240</v>
+        <v>28</v>
+      </c>
+      <c r="B200" t="s">
+        <v>412</v>
       </c>
       <c r="C200" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>212</v>
-      </c>
-      <c r="B201">
-        <v>240</v>
+        <v>205</v>
+      </c>
+      <c r="B201" t="s">
+        <v>412</v>
       </c>
       <c r="C201" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>213</v>
-      </c>
-      <c r="B202">
-        <v>240</v>
+        <v>206</v>
+      </c>
+      <c r="B202" t="s">
+        <v>412</v>
       </c>
       <c r="C202" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>28</v>
-      </c>
-      <c r="B203">
-        <v>240</v>
+        <v>29</v>
+      </c>
+      <c r="B203" t="s">
+        <v>412</v>
       </c>
       <c r="C203" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>29</v>
-      </c>
-      <c r="B204">
-        <v>240</v>
+        <v>207</v>
+      </c>
+      <c r="B204" t="s">
+        <v>412</v>
       </c>
       <c r="C204" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>214</v>
-      </c>
-      <c r="B205">
-        <v>240</v>
+        <v>378</v>
+      </c>
+      <c r="B205" t="s">
+        <v>412</v>
       </c>
       <c r="C205" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>215</v>
-      </c>
-      <c r="B206">
-        <v>240</v>
+        <v>30</v>
+      </c>
+      <c r="B206" t="s">
+        <v>412</v>
       </c>
       <c r="C206" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>30</v>
-      </c>
-      <c r="B207">
-        <v>240</v>
+        <v>208</v>
+      </c>
+      <c r="B207" t="s">
+        <v>412</v>
       </c>
       <c r="C207" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>216</v>
-      </c>
-      <c r="B208">
-        <v>240</v>
+        <v>209</v>
+      </c>
+      <c r="B208" t="s">
+        <v>412</v>
       </c>
       <c r="C208" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>393</v>
-      </c>
-      <c r="B209">
-        <v>240</v>
+        <v>210</v>
+      </c>
+      <c r="B209" t="s">
+        <v>412</v>
       </c>
       <c r="C209" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>31</v>
-      </c>
-      <c r="B210">
-        <v>240</v>
+        <v>211</v>
+      </c>
+      <c r="B210" t="s">
+        <v>412</v>
       </c>
       <c r="C210" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>217</v>
-      </c>
-      <c r="B211">
-        <v>240</v>
+        <v>398</v>
+      </c>
+      <c r="B211" t="s">
+        <v>412</v>
       </c>
       <c r="C211" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>218</v>
-      </c>
-      <c r="B212">
-        <v>240</v>
+        <v>31</v>
+      </c>
+      <c r="B212" t="s">
+        <v>412</v>
       </c>
       <c r="C212" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>219</v>
-      </c>
-      <c r="B213">
-        <v>240</v>
+        <v>212</v>
+      </c>
+      <c r="B213" t="s">
+        <v>412</v>
       </c>
       <c r="C213" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>220</v>
-      </c>
-      <c r="B214">
-        <v>240</v>
+        <v>213</v>
+      </c>
+      <c r="B214" t="s">
+        <v>412</v>
       </c>
       <c r="C214" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>413</v>
-      </c>
-      <c r="B215">
-        <v>240</v>
+        <v>214</v>
+      </c>
+      <c r="B215" t="s">
+        <v>412</v>
       </c>
       <c r="C215" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>32</v>
-      </c>
-      <c r="B216">
-        <v>240</v>
+        <v>215</v>
+      </c>
+      <c r="B216" t="s">
+        <v>412</v>
       </c>
       <c r="C216" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>221</v>
-      </c>
-      <c r="B217">
-        <v>240</v>
+        <v>216</v>
+      </c>
+      <c r="B217" t="s">
+        <v>412</v>
       </c>
       <c r="C217" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>222</v>
-      </c>
-      <c r="B218">
-        <v>240</v>
+        <v>217</v>
+      </c>
+      <c r="B218" t="s">
+        <v>412</v>
       </c>
       <c r="C218" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>223</v>
-      </c>
-      <c r="B219">
-        <v>240</v>
+        <v>218</v>
+      </c>
+      <c r="B219" t="s">
+        <v>412</v>
       </c>
       <c r="C219" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>224</v>
-      </c>
-      <c r="B220">
-        <v>240</v>
+        <v>220</v>
+      </c>
+      <c r="B220" t="s">
+        <v>412</v>
       </c>
       <c r="C220" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>225</v>
-      </c>
-      <c r="B221">
-        <v>240</v>
+        <v>404</v>
+      </c>
+      <c r="B221" t="s">
+        <v>412</v>
       </c>
       <c r="C221" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>226</v>
-      </c>
-      <c r="B222">
-        <v>240</v>
+        <v>32</v>
+      </c>
+      <c r="B222" t="s">
+        <v>412</v>
       </c>
       <c r="C222" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>227</v>
-      </c>
-      <c r="B223">
-        <v>240</v>
+        <v>221</v>
+      </c>
+      <c r="B223" t="s">
+        <v>412</v>
       </c>
       <c r="C223" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>228</v>
-      </c>
-      <c r="B224">
-        <v>240</v>
+        <v>222</v>
+      </c>
+      <c r="B224" t="s">
+        <v>412</v>
       </c>
       <c r="C224" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>230</v>
-      </c>
-      <c r="B225">
-        <v>240</v>
+        <v>224</v>
+      </c>
+      <c r="B225" t="s">
+        <v>412</v>
       </c>
       <c r="C225" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>419</v>
-      </c>
-      <c r="B226">
-        <v>240</v>
+        <v>223</v>
+      </c>
+      <c r="B226" t="s">
+        <v>412</v>
       </c>
       <c r="C226" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>33</v>
-      </c>
-      <c r="B227">
-        <v>240</v>
+        <v>225</v>
+      </c>
+      <c r="B227" t="s">
+        <v>412</v>
       </c>
       <c r="C227" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>231</v>
-      </c>
-      <c r="B228">
-        <v>240</v>
+        <v>227</v>
+      </c>
+      <c r="B228" t="s">
+        <v>412</v>
       </c>
       <c r="C228" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>232</v>
-      </c>
-      <c r="B229">
-        <v>240</v>
+        <v>228</v>
+      </c>
+      <c r="B229" t="s">
+        <v>412</v>
       </c>
       <c r="C229" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>234</v>
-      </c>
-      <c r="B230">
-        <v>240</v>
+        <v>229</v>
+      </c>
+      <c r="B230" t="s">
+        <v>412</v>
       </c>
       <c r="C230" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>233</v>
-      </c>
-      <c r="B231">
-        <v>240</v>
+        <v>230</v>
+      </c>
+      <c r="B231" t="s">
+        <v>412</v>
       </c>
       <c r="C231" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>235</v>
-      </c>
-      <c r="B232">
-        <v>240</v>
+        <v>226</v>
+      </c>
+      <c r="B232" t="s">
+        <v>412</v>
       </c>
       <c r="C232" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>237</v>
-      </c>
-      <c r="B233">
-        <v>240</v>
+        <v>33</v>
+      </c>
+      <c r="B233" t="s">
+        <v>412</v>
       </c>
       <c r="C233" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>238</v>
-      </c>
-      <c r="B234">
-        <v>240</v>
+        <v>231</v>
+      </c>
+      <c r="B234" t="s">
+        <v>412</v>
       </c>
       <c r="C234" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>239</v>
-      </c>
-      <c r="B235">
-        <v>240</v>
+        <v>232</v>
+      </c>
+      <c r="B235" t="s">
+        <v>412</v>
       </c>
       <c r="C235" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>240</v>
-      </c>
-      <c r="B236">
-        <v>240</v>
+        <v>34</v>
+      </c>
+      <c r="B236" t="s">
+        <v>412</v>
       </c>
       <c r="C236" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>236</v>
-      </c>
-      <c r="B237">
-        <v>240</v>
+        <v>233</v>
+      </c>
+      <c r="B237" t="s">
+        <v>412</v>
       </c>
       <c r="C237" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>34</v>
-      </c>
-      <c r="B238">
-        <v>240</v>
+        <v>35</v>
+      </c>
+      <c r="B238" t="s">
+        <v>412</v>
       </c>
       <c r="C238" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>241</v>
-      </c>
-      <c r="B239">
-        <v>240</v>
+        <v>36</v>
+      </c>
+      <c r="B239" t="s">
+        <v>412</v>
       </c>
       <c r="C239" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>242</v>
-      </c>
-      <c r="B240">
-        <v>240</v>
+        <v>234</v>
+      </c>
+      <c r="B240" t="s">
+        <v>412</v>
       </c>
       <c r="C240" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>35</v>
-      </c>
-      <c r="B241">
-        <v>240</v>
+        <v>235</v>
+      </c>
+      <c r="B241" t="s">
+        <v>412</v>
       </c>
       <c r="C241" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>243</v>
-      </c>
-      <c r="B242">
-        <v>240</v>
+        <v>236</v>
+      </c>
+      <c r="B242" t="s">
+        <v>412</v>
       </c>
       <c r="C242" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>36</v>
-      </c>
-      <c r="B243">
-        <v>240</v>
+        <v>237</v>
+      </c>
+      <c r="B243" t="s">
+        <v>412</v>
       </c>
       <c r="C243" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>37</v>
-      </c>
-      <c r="B244">
-        <v>240</v>
+        <v>219</v>
+      </c>
+      <c r="B244" t="s">
+        <v>412</v>
       </c>
       <c r="C244" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>244</v>
-      </c>
-      <c r="B245">
-        <v>240</v>
+        <v>384</v>
+      </c>
+      <c r="B245" t="s">
+        <v>412</v>
       </c>
       <c r="C245" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>245</v>
-      </c>
-      <c r="B246">
-        <v>240</v>
+        <v>37</v>
+      </c>
+      <c r="B246" t="s">
+        <v>412</v>
       </c>
       <c r="C246" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>246</v>
-      </c>
-      <c r="B247">
-        <v>240</v>
+        <v>238</v>
+      </c>
+      <c r="B247" t="s">
+        <v>412</v>
       </c>
       <c r="C247" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>247</v>
-      </c>
-      <c r="B248">
-        <v>240</v>
+        <v>239</v>
+      </c>
+      <c r="B248" t="s">
+        <v>412</v>
       </c>
       <c r="C248" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>229</v>
-      </c>
-      <c r="B249">
         <v>240</v>
       </c>
+      <c r="B249" t="s">
+        <v>412</v>
+      </c>
       <c r="C249" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>399</v>
-      </c>
-      <c r="B250">
-        <v>240</v>
+        <v>241</v>
+      </c>
+      <c r="B250" t="s">
+        <v>412</v>
       </c>
       <c r="C250" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>38</v>
-      </c>
-      <c r="B251">
-        <v>240</v>
+        <v>401</v>
+      </c>
+      <c r="B251" t="s">
+        <v>412</v>
       </c>
       <c r="C251" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>248</v>
-      </c>
-      <c r="B252">
-        <v>240</v>
+        <v>38</v>
+      </c>
+      <c r="B252" t="s">
+        <v>412</v>
       </c>
       <c r="C252" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>249</v>
-      </c>
-      <c r="B253">
-        <v>240</v>
+        <v>242</v>
+      </c>
+      <c r="B253" t="s">
+        <v>412</v>
       </c>
       <c r="C253" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>250</v>
-      </c>
-      <c r="B254">
-        <v>240</v>
+        <v>244</v>
+      </c>
+      <c r="B254" t="s">
+        <v>412</v>
       </c>
       <c r="C254" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>251</v>
-      </c>
-      <c r="B255">
-        <v>240</v>
+        <v>243</v>
+      </c>
+      <c r="B255" t="s">
+        <v>412</v>
       </c>
       <c r="C255" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>416</v>
-      </c>
-      <c r="B256">
-        <v>240</v>
+        <v>39</v>
+      </c>
+      <c r="B256" t="s">
+        <v>412</v>
       </c>
       <c r="C256" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>39</v>
-      </c>
-      <c r="B257">
-        <v>240</v>
+        <v>245</v>
+      </c>
+      <c r="B257" t="s">
+        <v>412</v>
       </c>
       <c r="C257" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>252</v>
-      </c>
-      <c r="B258">
-        <v>240</v>
+        <v>246</v>
+      </c>
+      <c r="B258" t="s">
+        <v>412</v>
       </c>
       <c r="C258" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>254</v>
-      </c>
-      <c r="B259">
-        <v>240</v>
+        <v>411</v>
+      </c>
+      <c r="B259" t="s">
+        <v>412</v>
       </c>
       <c r="C259" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>253</v>
-      </c>
-      <c r="B260">
-        <v>240</v>
+        <v>40</v>
+      </c>
+      <c r="B260" t="s">
+        <v>412</v>
       </c>
       <c r="C260" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>255</v>
-      </c>
-      <c r="B261">
-        <v>240</v>
+        <v>247</v>
+      </c>
+      <c r="B261" t="s">
+        <v>412</v>
       </c>
       <c r="C261" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>40</v>
-      </c>
-      <c r="B262">
-        <v>240</v>
+        <v>41</v>
+      </c>
+      <c r="B262" t="s">
+        <v>412</v>
       </c>
       <c r="C262" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>256</v>
-      </c>
-      <c r="B263">
-        <v>240</v>
+        <v>248</v>
+      </c>
+      <c r="B263" t="s">
+        <v>412</v>
       </c>
       <c r="C263" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>257</v>
-      </c>
-      <c r="B264">
-        <v>240</v>
+        <v>249</v>
+      </c>
+      <c r="B264" t="s">
+        <v>412</v>
       </c>
       <c r="C264" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>41</v>
-      </c>
-      <c r="B265">
-        <v>240</v>
+        <v>250</v>
+      </c>
+      <c r="B265" t="s">
+        <v>412</v>
       </c>
       <c r="C265" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>258</v>
-      </c>
-      <c r="B266">
-        <v>240</v>
+        <v>251</v>
+      </c>
+      <c r="B266" t="s">
+        <v>412</v>
       </c>
       <c r="C266" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>42</v>
-      </c>
-      <c r="B267">
-        <v>240</v>
+        <v>252</v>
+      </c>
+      <c r="B267" t="s">
+        <v>412</v>
       </c>
       <c r="C267" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>259</v>
-      </c>
-      <c r="B268">
-        <v>240</v>
+        <v>42</v>
+      </c>
+      <c r="B268" t="s">
+        <v>412</v>
       </c>
       <c r="C268" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>260</v>
-      </c>
-      <c r="B269">
-        <v>240</v>
+        <v>253</v>
+      </c>
+      <c r="B269" t="s">
+        <v>412</v>
       </c>
       <c r="C269" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>261</v>
-      </c>
-      <c r="B270">
-        <v>240</v>
+        <v>254</v>
+      </c>
+      <c r="B270" t="s">
+        <v>412</v>
       </c>
       <c r="C270" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>262</v>
-      </c>
-      <c r="B271">
-        <v>240</v>
+        <v>406</v>
+      </c>
+      <c r="B271" t="s">
+        <v>412</v>
       </c>
       <c r="C271" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>263</v>
-      </c>
-      <c r="B272">
-        <v>240</v>
+        <v>255</v>
+      </c>
+      <c r="B272" t="s">
+        <v>412</v>
       </c>
       <c r="C272" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>264</v>
-      </c>
-      <c r="B273">
-        <v>240</v>
+        <v>256</v>
+      </c>
+      <c r="B273" t="s">
+        <v>412</v>
       </c>
       <c r="C273" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>43</v>
-      </c>
-      <c r="B274">
-        <v>240</v>
+        <v>257</v>
+      </c>
+      <c r="B274" t="s">
+        <v>412</v>
       </c>
       <c r="C274" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>265</v>
-      </c>
-      <c r="B275">
-        <v>240</v>
+        <v>258</v>
+      </c>
+      <c r="B275" t="s">
+        <v>412</v>
       </c>
       <c r="C275" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>266</v>
-      </c>
-      <c r="B276">
-        <v>240</v>
+        <v>259</v>
+      </c>
+      <c r="B276" t="s">
+        <v>412</v>
       </c>
       <c r="C276" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>421</v>
-      </c>
-      <c r="B277">
-        <v>240</v>
+        <v>260</v>
+      </c>
+      <c r="B277" t="s">
+        <v>412</v>
       </c>
       <c r="C277" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>267</v>
-      </c>
-      <c r="B278">
-        <v>240</v>
+        <v>261</v>
+      </c>
+      <c r="B278" t="s">
+        <v>412</v>
       </c>
       <c r="C278" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>268</v>
-      </c>
-      <c r="B279">
-        <v>240</v>
+        <v>43</v>
+      </c>
+      <c r="B279" t="s">
+        <v>412</v>
       </c>
       <c r="C279" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>269</v>
-      </c>
-      <c r="B280">
-        <v>240</v>
+        <v>262</v>
+      </c>
+      <c r="B280" t="s">
+        <v>412</v>
       </c>
       <c r="C280" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>270</v>
-      </c>
-      <c r="B281">
-        <v>240</v>
+        <v>263</v>
+      </c>
+      <c r="B281" t="s">
+        <v>412</v>
       </c>
       <c r="C281" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>271</v>
-      </c>
-      <c r="B282">
-        <v>240</v>
+        <v>264</v>
+      </c>
+      <c r="B282" t="s">
+        <v>412</v>
       </c>
       <c r="C282" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>272</v>
-      </c>
-      <c r="B283">
-        <v>240</v>
+        <v>265</v>
+      </c>
+      <c r="B283" t="s">
+        <v>412</v>
       </c>
       <c r="C283" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>273</v>
-      </c>
-      <c r="B284">
-        <v>240</v>
+        <v>266</v>
+      </c>
+      <c r="B284" t="s">
+        <v>412</v>
       </c>
       <c r="C284" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>44</v>
-      </c>
-      <c r="B285">
-        <v>240</v>
+        <v>267</v>
+      </c>
+      <c r="B285" t="s">
+        <v>412</v>
       </c>
       <c r="C285" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>274</v>
-      </c>
-      <c r="B286">
-        <v>240</v>
+        <v>379</v>
+      </c>
+      <c r="B286" t="s">
+        <v>412</v>
       </c>
       <c r="C286" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>275</v>
-      </c>
-      <c r="B287">
-        <v>240</v>
+        <v>268</v>
+      </c>
+      <c r="B287" t="s">
+        <v>412</v>
       </c>
       <c r="C287" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>276</v>
-      </c>
-      <c r="B288">
-        <v>240</v>
+        <v>44</v>
+      </c>
+      <c r="B288" t="s">
+        <v>412</v>
       </c>
       <c r="C288" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>45</v>
-      </c>
-      <c r="B289">
-        <v>240</v>
+        <v>269</v>
+      </c>
+      <c r="B289" t="s">
+        <v>412</v>
       </c>
       <c r="C289" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>277</v>
-      </c>
-      <c r="B290">
-        <v>240</v>
+        <v>270</v>
+      </c>
+      <c r="B290" t="s">
+        <v>412</v>
       </c>
       <c r="C290" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>278</v>
-      </c>
-      <c r="B291">
-        <v>240</v>
+        <v>271</v>
+      </c>
+      <c r="B291" t="s">
+        <v>412</v>
       </c>
       <c r="C291" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>279</v>
-      </c>
-      <c r="B292">
-        <v>240</v>
+        <v>272</v>
+      </c>
+      <c r="B292" t="s">
+        <v>412</v>
       </c>
       <c r="C292" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>394</v>
-      </c>
-      <c r="B293">
-        <v>240</v>
+        <v>273</v>
+      </c>
+      <c r="B293" t="s">
+        <v>412</v>
       </c>
       <c r="C293" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>280</v>
-      </c>
-      <c r="B294">
-        <v>240</v>
+        <v>274</v>
+      </c>
+      <c r="B294" t="s">
+        <v>412</v>
       </c>
       <c r="C294" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>46</v>
-      </c>
-      <c r="B295">
-        <v>240</v>
+        <v>275</v>
+      </c>
+      <c r="B295" t="s">
+        <v>412</v>
       </c>
       <c r="C295" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>281</v>
-      </c>
-      <c r="B296">
-        <v>240</v>
+        <v>276</v>
+      </c>
+      <c r="B296" t="s">
+        <v>412</v>
       </c>
       <c r="C296" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>282</v>
-      </c>
-      <c r="B297">
-        <v>240</v>
+        <v>277</v>
+      </c>
+      <c r="B297" t="s">
+        <v>412</v>
       </c>
       <c r="C297" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>283</v>
-      </c>
-      <c r="B298">
-        <v>240</v>
+        <v>278</v>
+      </c>
+      <c r="B298" t="s">
+        <v>412</v>
       </c>
       <c r="C298" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>284</v>
-      </c>
-      <c r="B299">
-        <v>240</v>
+        <v>380</v>
+      </c>
+      <c r="B299" t="s">
+        <v>412</v>
       </c>
       <c r="C299" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>285</v>
-      </c>
-      <c r="B300">
-        <v>240</v>
+        <v>279</v>
+      </c>
+      <c r="B300" t="s">
+        <v>412</v>
       </c>
       <c r="C300" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>286</v>
-      </c>
-      <c r="B301">
-        <v>240</v>
+        <v>280</v>
+      </c>
+      <c r="B301" t="s">
+        <v>412</v>
       </c>
       <c r="C301" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>287</v>
-      </c>
-      <c r="B302">
-        <v>240</v>
+        <v>281</v>
+      </c>
+      <c r="B302" t="s">
+        <v>412</v>
       </c>
       <c r="C302" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>47</v>
-      </c>
-      <c r="B303">
-        <v>240</v>
+        <v>45</v>
+      </c>
+      <c r="B303" t="s">
+        <v>412</v>
       </c>
       <c r="C303" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>288</v>
-      </c>
-      <c r="B304">
-        <v>240</v>
+        <v>282</v>
+      </c>
+      <c r="B304" t="s">
+        <v>412</v>
       </c>
       <c r="C304" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>289</v>
-      </c>
-      <c r="B305">
-        <v>240</v>
+        <v>284</v>
+      </c>
+      <c r="B305" t="s">
+        <v>412</v>
       </c>
       <c r="C305" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>290</v>
-      </c>
-      <c r="B306">
-        <v>240</v>
+        <v>285</v>
+      </c>
+      <c r="B306" t="s">
+        <v>412</v>
       </c>
       <c r="C306" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>291</v>
-      </c>
-      <c r="B307">
-        <v>240</v>
+        <v>286</v>
+      </c>
+      <c r="B307" t="s">
+        <v>412</v>
       </c>
       <c r="C307" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>395</v>
-      </c>
-      <c r="B308">
-        <v>240</v>
+        <v>287</v>
+      </c>
+      <c r="B308" t="s">
+        <v>412</v>
       </c>
       <c r="C308" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>292</v>
-      </c>
-      <c r="B309">
-        <v>240</v>
+        <v>290</v>
+      </c>
+      <c r="B309" t="s">
+        <v>412</v>
       </c>
       <c r="C309" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>293</v>
-      </c>
-      <c r="B310">
-        <v>240</v>
+        <v>289</v>
+      </c>
+      <c r="B310" t="s">
+        <v>412</v>
       </c>
       <c r="C310" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>294</v>
-      </c>
-      <c r="B311">
-        <v>240</v>
+        <v>288</v>
+      </c>
+      <c r="B311" t="s">
+        <v>412</v>
       </c>
       <c r="C311" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>48</v>
-      </c>
-      <c r="B312">
-        <v>240</v>
+        <v>291</v>
+      </c>
+      <c r="B312" t="s">
+        <v>412</v>
       </c>
       <c r="C312" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>295</v>
-      </c>
-      <c r="B313">
-        <v>240</v>
+        <v>292</v>
+      </c>
+      <c r="B313" t="s">
+        <v>412</v>
       </c>
       <c r="C313" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>297</v>
-      </c>
-      <c r="B314">
-        <v>240</v>
+        <v>46</v>
+      </c>
+      <c r="B314" t="s">
+        <v>412</v>
       </c>
       <c r="C314" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>298</v>
-      </c>
-      <c r="B315">
-        <v>240</v>
+        <v>293</v>
+      </c>
+      <c r="B315" t="s">
+        <v>412</v>
       </c>
       <c r="C315" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>299</v>
-      </c>
-      <c r="B316">
-        <v>240</v>
+        <v>294</v>
+      </c>
+      <c r="B316" t="s">
+        <v>412</v>
       </c>
       <c r="C316" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>300</v>
-      </c>
-      <c r="B317">
-        <v>240</v>
+        <v>295</v>
+      </c>
+      <c r="B317" t="s">
+        <v>412</v>
       </c>
       <c r="C317" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>303</v>
-      </c>
-      <c r="B318">
-        <v>240</v>
+        <v>296</v>
+      </c>
+      <c r="B318" t="s">
+        <v>412</v>
       </c>
       <c r="C318" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>302</v>
-      </c>
-      <c r="B319">
-        <v>240</v>
+        <v>47</v>
+      </c>
+      <c r="B319" t="s">
+        <v>412</v>
       </c>
       <c r="C319" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>301</v>
-      </c>
-      <c r="B320">
-        <v>240</v>
+        <v>297</v>
+      </c>
+      <c r="B320" t="s">
+        <v>412</v>
       </c>
       <c r="C320" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>304</v>
-      </c>
-      <c r="B321">
-        <v>240</v>
+        <v>48</v>
+      </c>
+      <c r="B321" t="s">
+        <v>412</v>
       </c>
       <c r="C321" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>305</v>
-      </c>
-      <c r="B322">
-        <v>240</v>
+        <v>298</v>
+      </c>
+      <c r="B322" t="s">
+        <v>412</v>
       </c>
       <c r="C322" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>49</v>
-      </c>
-      <c r="B323">
-        <v>240</v>
+        <v>299</v>
+      </c>
+      <c r="B323" t="s">
+        <v>412</v>
       </c>
       <c r="C323" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>306</v>
-      </c>
-      <c r="B324">
-        <v>240</v>
+        <v>300</v>
+      </c>
+      <c r="B324" t="s">
+        <v>412</v>
       </c>
       <c r="C324" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>307</v>
-      </c>
-      <c r="B325">
-        <v>240</v>
+        <v>301</v>
+      </c>
+      <c r="B325" t="s">
+        <v>412</v>
       </c>
       <c r="C325" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>308</v>
-      </c>
-      <c r="B326">
-        <v>240</v>
+        <v>302</v>
+      </c>
+      <c r="B326" t="s">
+        <v>412</v>
       </c>
       <c r="C326" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>309</v>
-      </c>
-      <c r="B327">
-        <v>240</v>
+        <v>303</v>
+      </c>
+      <c r="B327" t="s">
+        <v>412</v>
       </c>
       <c r="C327" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>50</v>
-      </c>
-      <c r="B328">
-        <v>240</v>
+        <v>49</v>
+      </c>
+      <c r="B328" t="s">
+        <v>412</v>
       </c>
       <c r="C328" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>310</v>
-      </c>
-      <c r="B329">
-        <v>240</v>
+        <v>304</v>
+      </c>
+      <c r="B329" t="s">
+        <v>412</v>
       </c>
       <c r="C329" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>51</v>
-      </c>
-      <c r="B330">
-        <v>240</v>
+        <v>305</v>
+      </c>
+      <c r="B330" t="s">
+        <v>412</v>
       </c>
       <c r="C330" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>311</v>
-      </c>
-      <c r="B331">
-        <v>240</v>
+        <v>306</v>
+      </c>
+      <c r="B331" t="s">
+        <v>412</v>
       </c>
       <c r="C331" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>312</v>
-      </c>
-      <c r="B332">
-        <v>240</v>
+        <v>307</v>
+      </c>
+      <c r="B332" t="s">
+        <v>412</v>
       </c>
       <c r="C332" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>313</v>
-      </c>
-      <c r="B333">
-        <v>240</v>
+        <v>309</v>
+      </c>
+      <c r="B333" t="s">
+        <v>412</v>
       </c>
       <c r="C333" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>314</v>
-      </c>
-      <c r="B334">
-        <v>240</v>
+        <v>308</v>
+      </c>
+      <c r="B334" t="s">
+        <v>412</v>
       </c>
       <c r="C334" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>315</v>
-      </c>
-      <c r="B335">
-        <v>240</v>
+        <v>310</v>
+      </c>
+      <c r="B335" t="s">
+        <v>412</v>
       </c>
       <c r="C335" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>316</v>
-      </c>
-      <c r="B336">
-        <v>240</v>
+        <v>311</v>
+      </c>
+      <c r="B336" t="s">
+        <v>412</v>
       </c>
       <c r="C336" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>52</v>
-      </c>
-      <c r="B337">
-        <v>240</v>
+        <v>312</v>
+      </c>
+      <c r="B337" t="s">
+        <v>412</v>
       </c>
       <c r="C337" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>317</v>
-      </c>
-      <c r="B338">
-        <v>240</v>
+        <v>313</v>
+      </c>
+      <c r="B338" t="s">
+        <v>412</v>
       </c>
       <c r="C338" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>318</v>
-      </c>
-      <c r="B339">
-        <v>240</v>
+        <v>314</v>
+      </c>
+      <c r="B339" t="s">
+        <v>412</v>
       </c>
       <c r="C339" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>319</v>
-      </c>
-      <c r="B340">
-        <v>240</v>
+        <v>283</v>
+      </c>
+      <c r="B340" t="s">
+        <v>412</v>
       </c>
       <c r="C340" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>320</v>
-      </c>
-      <c r="B341">
-        <v>240</v>
+        <v>315</v>
+      </c>
+      <c r="B341" t="s">
+        <v>412</v>
       </c>
       <c r="C341" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>322</v>
-      </c>
-      <c r="B342">
-        <v>240</v>
+        <v>316</v>
+      </c>
+      <c r="B342" t="s">
+        <v>412</v>
       </c>
       <c r="C342" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>321</v>
-      </c>
-      <c r="B343">
-        <v>240</v>
+        <v>317</v>
+      </c>
+      <c r="B343" t="s">
+        <v>412</v>
       </c>
       <c r="C343" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>323</v>
-      </c>
-      <c r="B344">
-        <v>240</v>
+        <v>320</v>
+      </c>
+      <c r="B344" t="s">
+        <v>412</v>
       </c>
       <c r="C344" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>324</v>
-      </c>
-      <c r="B345">
-        <v>240</v>
+        <v>381</v>
+      </c>
+      <c r="B345" t="s">
+        <v>412</v>
       </c>
       <c r="C345" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>325</v>
-      </c>
-      <c r="B346">
-        <v>240</v>
+        <v>321</v>
+      </c>
+      <c r="B346" t="s">
+        <v>412</v>
       </c>
       <c r="C346" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>326</v>
-      </c>
-      <c r="B347">
-        <v>240</v>
+        <v>319</v>
+      </c>
+      <c r="B347" t="s">
+        <v>412</v>
       </c>
       <c r="C347" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>327</v>
-      </c>
-      <c r="B348">
-        <v>240</v>
+        <v>323</v>
+      </c>
+      <c r="B348" t="s">
+        <v>412</v>
       </c>
       <c r="C348" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>296</v>
-      </c>
-      <c r="B349">
-        <v>240</v>
+        <v>322</v>
+      </c>
+      <c r="B349" t="s">
+        <v>412</v>
       </c>
       <c r="C349" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>328</v>
-      </c>
-      <c r="B350">
-        <v>240</v>
+        <v>324</v>
+      </c>
+      <c r="B350" t="s">
+        <v>412</v>
       </c>
       <c r="C350" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>329</v>
-      </c>
-      <c r="B351">
-        <v>240</v>
+        <v>325</v>
+      </c>
+      <c r="B351" t="s">
+        <v>412</v>
       </c>
       <c r="C351" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>330</v>
-      </c>
-      <c r="B352">
-        <v>240</v>
+        <v>326</v>
+      </c>
+      <c r="B352" t="s">
+        <v>412</v>
       </c>
       <c r="C352" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
-        <v>331</v>
-      </c>
-      <c r="B353">
-        <v>240</v>
+        <v>50</v>
+      </c>
+      <c r="B353" t="s">
+        <v>412</v>
       </c>
       <c r="C353" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>334</v>
-      </c>
-      <c r="B354">
-        <v>240</v>
+        <v>51</v>
+      </c>
+      <c r="B354" t="s">
+        <v>412</v>
       </c>
       <c r="C354" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>396</v>
-      </c>
-      <c r="B355">
-        <v>240</v>
+        <v>327</v>
+      </c>
+      <c r="B355" t="s">
+        <v>412</v>
       </c>
       <c r="C355" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>335</v>
-      </c>
-      <c r="B356">
-        <v>240</v>
+        <v>328</v>
+      </c>
+      <c r="B356" t="s">
+        <v>412</v>
       </c>
       <c r="C356" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>333</v>
-      </c>
-      <c r="B357">
-        <v>240</v>
+        <v>329</v>
+      </c>
+      <c r="B357" t="s">
+        <v>412</v>
       </c>
       <c r="C357" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>337</v>
-      </c>
-      <c r="B358">
-        <v>240</v>
+        <v>318</v>
+      </c>
+      <c r="B358" t="s">
+        <v>412</v>
       </c>
       <c r="C358" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>336</v>
-      </c>
-      <c r="B359">
-        <v>240</v>
+        <v>330</v>
+      </c>
+      <c r="B359" t="s">
+        <v>412</v>
       </c>
       <c r="C359" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>338</v>
-      </c>
-      <c r="B360">
-        <v>240</v>
+        <v>331</v>
+      </c>
+      <c r="B360" t="s">
+        <v>412</v>
       </c>
       <c r="C360" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>339</v>
-      </c>
-      <c r="B361">
-        <v>240</v>
+        <v>332</v>
+      </c>
+      <c r="B361" t="s">
+        <v>412</v>
       </c>
       <c r="C361" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>340</v>
-      </c>
-      <c r="B362">
-        <v>240</v>
+        <v>333</v>
+      </c>
+      <c r="B362" t="s">
+        <v>412</v>
       </c>
       <c r="C362" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>53</v>
-      </c>
-      <c r="B363">
-        <v>240</v>
+        <v>334</v>
+      </c>
+      <c r="B363" t="s">
+        <v>412</v>
       </c>
       <c r="C363" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>54</v>
-      </c>
-      <c r="B364">
-        <v>240</v>
+        <v>335</v>
+      </c>
+      <c r="B364" t="s">
+        <v>412</v>
       </c>
       <c r="C364" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>342</v>
-      </c>
-      <c r="B365">
-        <v>240</v>
+        <v>336</v>
+      </c>
+      <c r="B365" t="s">
+        <v>412</v>
       </c>
       <c r="C365" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>341</v>
-      </c>
-      <c r="B366">
-        <v>240</v>
+        <v>337</v>
+      </c>
+      <c r="B366" t="s">
+        <v>412</v>
       </c>
       <c r="C366" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>343</v>
-      </c>
-      <c r="B367">
-        <v>240</v>
+        <v>338</v>
+      </c>
+      <c r="B367" t="s">
+        <v>412</v>
       </c>
       <c r="C367" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>344</v>
-      </c>
-      <c r="B368">
-        <v>240</v>
+        <v>339</v>
+      </c>
+      <c r="B368" t="s">
+        <v>412</v>
       </c>
       <c r="C368" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>332</v>
-      </c>
-      <c r="B369">
-        <v>240</v>
+        <v>340</v>
+      </c>
+      <c r="B369" t="s">
+        <v>412</v>
       </c>
       <c r="C369" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>345</v>
-      </c>
-      <c r="B370">
-        <v>240</v>
+        <v>341</v>
+      </c>
+      <c r="B370" t="s">
+        <v>412</v>
       </c>
       <c r="C370" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>346</v>
-      </c>
-      <c r="B371">
-        <v>240</v>
+        <v>343</v>
+      </c>
+      <c r="B371" t="s">
+        <v>412</v>
       </c>
       <c r="C371" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>347</v>
-      </c>
-      <c r="B372">
-        <v>240</v>
+        <v>342</v>
+      </c>
+      <c r="B372" t="s">
+        <v>412</v>
       </c>
       <c r="C372" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>348</v>
-      </c>
-      <c r="B373">
-        <v>240</v>
+        <v>344</v>
+      </c>
+      <c r="B373" t="s">
+        <v>412</v>
       </c>
       <c r="C373" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>349</v>
-      </c>
-      <c r="B374">
-        <v>240</v>
+        <v>345</v>
+      </c>
+      <c r="B374" t="s">
+        <v>412</v>
       </c>
       <c r="C374" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>350</v>
-      </c>
-      <c r="B375">
-        <v>240</v>
+        <v>346</v>
+      </c>
+      <c r="B375" t="s">
+        <v>412</v>
       </c>
       <c r="C375" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>351</v>
-      </c>
-      <c r="B376">
-        <v>240</v>
+        <v>347</v>
+      </c>
+      <c r="B376" t="s">
+        <v>412</v>
       </c>
       <c r="C376" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>352</v>
-      </c>
-      <c r="B377">
-        <v>240</v>
+        <v>348</v>
+      </c>
+      <c r="B377" t="s">
+        <v>412</v>
       </c>
       <c r="C377" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>353</v>
-      </c>
-      <c r="B378">
-        <v>240</v>
+        <v>350</v>
+      </c>
+      <c r="B378" t="s">
+        <v>412</v>
       </c>
       <c r="C378" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>354</v>
-      </c>
-      <c r="B379">
-        <v>240</v>
+        <v>383</v>
+      </c>
+      <c r="B379" t="s">
+        <v>412</v>
       </c>
       <c r="C379" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>355</v>
-      </c>
-      <c r="B380">
-        <v>240</v>
+        <v>382</v>
+      </c>
+      <c r="B380" t="s">
+        <v>412</v>
       </c>
       <c r="C380" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>356</v>
-      </c>
-      <c r="B381">
-        <v>240</v>
+        <v>351</v>
+      </c>
+      <c r="B381" t="s">
+        <v>412</v>
       </c>
       <c r="C381" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>358</v>
-      </c>
-      <c r="B382">
-        <v>240</v>
+        <v>52</v>
+      </c>
+      <c r="B382" t="s">
+        <v>412</v>
       </c>
       <c r="C382" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>357</v>
-      </c>
-      <c r="B383">
-        <v>240</v>
+        <v>352</v>
+      </c>
+      <c r="B383" t="s">
+        <v>412</v>
       </c>
       <c r="C383" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>359</v>
-      </c>
-      <c r="B384">
-        <v>240</v>
+        <v>353</v>
+      </c>
+      <c r="B384" t="s">
+        <v>412</v>
       </c>
       <c r="C384" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>360</v>
-      </c>
-      <c r="B385">
-        <v>240</v>
+        <v>349</v>
+      </c>
+      <c r="B385" t="s">
+        <v>412</v>
       </c>
       <c r="C385" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>361</v>
-      </c>
-      <c r="B386">
-        <v>240</v>
+        <v>354</v>
+      </c>
+      <c r="B386" t="s">
+        <v>412</v>
       </c>
       <c r="C386" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>362</v>
-      </c>
-      <c r="B387">
-        <v>240</v>
+        <v>355</v>
+      </c>
+      <c r="B387" t="s">
+        <v>412</v>
       </c>
       <c r="C387" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>363</v>
-      </c>
-      <c r="B388">
-        <v>240</v>
+        <v>53</v>
+      </c>
+      <c r="B388" t="s">
+        <v>412</v>
       </c>
       <c r="C388" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>365</v>
-      </c>
-      <c r="B389">
-        <v>240</v>
+        <v>356</v>
+      </c>
+      <c r="B389" t="s">
+        <v>412</v>
       </c>
       <c r="C389" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>398</v>
-      </c>
-      <c r="B390">
-        <v>240</v>
+        <v>357</v>
+      </c>
+      <c r="B390" t="s">
+        <v>412</v>
       </c>
       <c r="C390" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>397</v>
-      </c>
-      <c r="B391">
-        <v>240</v>
+        <v>54</v>
+      </c>
+      <c r="B391" t="s">
+        <v>412</v>
       </c>
       <c r="C391" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>366</v>
-      </c>
-      <c r="B392">
-        <v>240</v>
+        <v>358</v>
+      </c>
+      <c r="B392" t="s">
+        <v>412</v>
       </c>
       <c r="C392" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>55</v>
       </c>
-      <c r="B393">
-        <v>240</v>
+      <c r="B393" t="s">
+        <v>412</v>
       </c>
       <c r="C393" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>367</v>
-      </c>
-      <c r="B394">
-        <v>240</v>
+        <v>359</v>
+      </c>
+      <c r="B394" t="s">
+        <v>412</v>
       </c>
       <c r="C394" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>368</v>
-      </c>
-      <c r="B395">
-        <v>240</v>
+        <v>360</v>
+      </c>
+      <c r="B395" t="s">
+        <v>412</v>
       </c>
       <c r="C395" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>364</v>
-      </c>
-      <c r="B396">
-        <v>240</v>
+        <v>361</v>
+      </c>
+      <c r="B396" t="s">
+        <v>412</v>
       </c>
       <c r="C396" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>369</v>
-      </c>
-      <c r="B397">
-        <v>240</v>
+        <v>362</v>
+      </c>
+      <c r="B397" t="s">
+        <v>412</v>
       </c>
       <c r="C397" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>370</v>
-      </c>
-      <c r="B398">
-        <v>240</v>
+        <v>363</v>
+      </c>
+      <c r="B398" t="s">
+        <v>412</v>
       </c>
       <c r="C398" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>56</v>
-      </c>
-      <c r="B399">
-        <v>240</v>
+        <v>364</v>
+      </c>
+      <c r="B399" t="s">
+        <v>412</v>
       </c>
       <c r="C399" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>371</v>
-      </c>
-      <c r="B400">
-        <v>240</v>
+        <v>365</v>
+      </c>
+      <c r="B400" t="s">
+        <v>412</v>
       </c>
       <c r="C400" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>372</v>
-      </c>
-      <c r="B401">
-        <v>240</v>
+        <v>56</v>
+      </c>
+      <c r="B401" t="s">
+        <v>412</v>
       </c>
       <c r="C401" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>57</v>
-      </c>
-      <c r="B402">
-        <v>240</v>
+        <v>366</v>
+      </c>
+      <c r="B402" t="s">
+        <v>412</v>
       </c>
       <c r="C402" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>373</v>
-      </c>
-      <c r="B403">
-        <v>240</v>
+        <v>367</v>
+      </c>
+      <c r="B403" t="s">
+        <v>412</v>
       </c>
       <c r="C403" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>58</v>
-      </c>
-      <c r="B404">
-        <v>240</v>
+        <v>368</v>
+      </c>
+      <c r="B404" t="s">
+        <v>412</v>
       </c>
       <c r="C404" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>374</v>
-      </c>
-      <c r="B405">
-        <v>240</v>
+        <v>407</v>
+      </c>
+      <c r="B405" t="s">
+        <v>412</v>
       </c>
       <c r="C405" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>375</v>
-      </c>
-      <c r="B406">
-        <v>240</v>
+        <v>369</v>
+      </c>
+      <c r="B406" t="s">
+        <v>412</v>
       </c>
       <c r="C406" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>376</v>
-      </c>
-      <c r="B407">
-        <v>240</v>
+        <v>370</v>
+      </c>
+      <c r="B407" t="s">
+        <v>412</v>
       </c>
       <c r="C407" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>377</v>
-      </c>
-      <c r="B408">
-        <v>240</v>
+        <v>371</v>
+      </c>
+      <c r="B408" t="s">
+        <v>412</v>
       </c>
       <c r="C408" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>378</v>
-      </c>
-      <c r="B409">
-        <v>240</v>
+        <v>57</v>
+      </c>
+      <c r="B409" t="s">
+        <v>412</v>
       </c>
       <c r="C409" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A410" t="s">
-        <v>379</v>
-      </c>
-      <c r="B410">
-        <v>240</v>
-      </c>
-      <c r="C410" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A411" t="s">
-        <v>380</v>
-      </c>
-      <c r="B411">
-        <v>240</v>
-      </c>
-      <c r="C411" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A412" t="s">
-        <v>59</v>
-      </c>
-      <c r="B412">
-        <v>240</v>
-      </c>
-      <c r="C412" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A413" t="s">
-        <v>381</v>
-      </c>
-      <c r="B413">
-        <v>240</v>
-      </c>
-      <c r="C413" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A414" t="s">
-        <v>382</v>
-      </c>
-      <c r="B414">
-        <v>240</v>
-      </c>
-      <c r="C414" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A415" t="s">
-        <v>383</v>
-      </c>
-      <c r="B415">
-        <v>240</v>
-      </c>
-      <c r="C415" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A416" t="s">
-        <v>384</v>
-      </c>
-      <c r="B416">
-        <v>240</v>
-      </c>
-      <c r="C416" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A417" t="s">
-        <v>385</v>
-      </c>
-      <c r="B417">
-        <v>240</v>
-      </c>
-      <c r="C417" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A418" t="s">
-        <v>386</v>
-      </c>
-      <c r="B418">
-        <v>240</v>
-      </c>
-      <c r="C418" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A419" t="s">
-        <v>60</v>
-      </c>
-      <c r="B419">
-        <v>240</v>
-      </c>
-      <c r="C419" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -6290,8 +6153,8 @@
       <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C432">
-    <sortCondition ref="A1:A432"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C422">
+    <sortCondition ref="A1:A422"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ativos.xlsx
+++ b/ativos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\INVESTIMENTOS VARIAVEL\Bybit\bybit_setups\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC420B8-D5AE-4459-8C24-6DA924CCA4E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC71C623-357A-4BCF-932C-EB363402890E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="412">
   <si>
     <t>Par</t>
   </si>
@@ -1272,9 +1272,6 @@
   </si>
   <si>
     <t>OPGUSDT</t>
-  </si>
-  <si>
-    <t>D</t>
   </si>
 </sst>
 </file>
@@ -1663,8 +1660,8 @@
       <c r="A2" t="s">
         <v>385</v>
       </c>
-      <c r="B2" t="s">
-        <v>412</v>
+      <c r="B2">
+        <v>360</v>
       </c>
       <c r="C2" t="s">
         <v>58</v>
@@ -1674,8 +1671,8 @@
       <c r="A3" t="s">
         <v>59</v>
       </c>
-      <c r="B3" t="s">
-        <v>412</v>
+      <c r="B3">
+        <v>360</v>
       </c>
       <c r="C3" t="s">
         <v>58</v>
@@ -1685,8 +1682,8 @@
       <c r="A4" t="s">
         <v>372</v>
       </c>
-      <c r="B4" t="s">
-        <v>412</v>
+      <c r="B4">
+        <v>360</v>
       </c>
       <c r="C4" t="s">
         <v>58</v>
@@ -1696,8 +1693,8 @@
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
-        <v>412</v>
+      <c r="B5">
+        <v>360</v>
       </c>
       <c r="C5" t="s">
         <v>58</v>
@@ -1707,8 +1704,8 @@
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
-        <v>412</v>
+      <c r="B6">
+        <v>360</v>
       </c>
       <c r="C6" t="s">
         <v>58</v>
@@ -1718,8 +1715,8 @@
       <c r="A7" t="s">
         <v>60</v>
       </c>
-      <c r="B7" t="s">
-        <v>412</v>
+      <c r="B7">
+        <v>360</v>
       </c>
       <c r="C7" t="s">
         <v>58</v>
@@ -1729,8 +1726,8 @@
       <c r="A8" t="s">
         <v>373</v>
       </c>
-      <c r="B8" t="s">
-        <v>412</v>
+      <c r="B8">
+        <v>360</v>
       </c>
       <c r="C8" t="s">
         <v>58</v>
@@ -1740,8 +1737,8 @@
       <c r="A9" t="s">
         <v>61</v>
       </c>
-      <c r="B9" t="s">
-        <v>412</v>
+      <c r="B9">
+        <v>360</v>
       </c>
       <c r="C9" t="s">
         <v>58</v>
@@ -1751,8 +1748,8 @@
       <c r="A10" t="s">
         <v>5</v>
       </c>
-      <c r="B10" t="s">
-        <v>412</v>
+      <c r="B10">
+        <v>360</v>
       </c>
       <c r="C10" t="s">
         <v>58</v>
@@ -1762,8 +1759,8 @@
       <c r="A11" t="s">
         <v>386</v>
       </c>
-      <c r="B11" t="s">
-        <v>412</v>
+      <c r="B11">
+        <v>360</v>
       </c>
       <c r="C11" t="s">
         <v>58</v>
@@ -1773,8 +1770,8 @@
       <c r="A12" t="s">
         <v>63</v>
       </c>
-      <c r="B12" t="s">
-        <v>412</v>
+      <c r="B12">
+        <v>360</v>
       </c>
       <c r="C12" t="s">
         <v>58</v>
@@ -1784,8 +1781,8 @@
       <c r="A13" t="s">
         <v>64</v>
       </c>
-      <c r="B13" t="s">
-        <v>412</v>
+      <c r="B13">
+        <v>360</v>
       </c>
       <c r="C13" t="s">
         <v>58</v>
@@ -1795,8 +1792,8 @@
       <c r="A14" t="s">
         <v>65</v>
       </c>
-      <c r="B14" t="s">
-        <v>412</v>
+      <c r="B14">
+        <v>360</v>
       </c>
       <c r="C14" t="s">
         <v>58</v>
@@ -1806,8 +1803,8 @@
       <c r="A15" t="s">
         <v>66</v>
       </c>
-      <c r="B15" t="s">
-        <v>412</v>
+      <c r="B15">
+        <v>360</v>
       </c>
       <c r="C15" t="s">
         <v>58</v>
@@ -1817,8 +1814,8 @@
       <c r="A16" t="s">
         <v>67</v>
       </c>
-      <c r="B16" t="s">
-        <v>412</v>
+      <c r="B16">
+        <v>360</v>
       </c>
       <c r="C16" t="s">
         <v>58</v>
@@ -1828,8 +1825,8 @@
       <c r="A17" t="s">
         <v>6</v>
       </c>
-      <c r="B17" t="s">
-        <v>412</v>
+      <c r="B17">
+        <v>360</v>
       </c>
       <c r="C17" t="s">
         <v>58</v>
@@ -1839,8 +1836,8 @@
       <c r="A18" t="s">
         <v>68</v>
       </c>
-      <c r="B18" t="s">
-        <v>412</v>
+      <c r="B18">
+        <v>360</v>
       </c>
       <c r="C18" t="s">
         <v>58</v>
@@ -1850,8 +1847,8 @@
       <c r="A19" t="s">
         <v>69</v>
       </c>
-      <c r="B19" t="s">
-        <v>412</v>
+      <c r="B19">
+        <v>360</v>
       </c>
       <c r="C19" t="s">
         <v>58</v>
@@ -1861,8 +1858,8 @@
       <c r="A20" t="s">
         <v>70</v>
       </c>
-      <c r="B20" t="s">
-        <v>412</v>
+      <c r="B20">
+        <v>360</v>
       </c>
       <c r="C20" t="s">
         <v>58</v>
@@ -1872,8 +1869,8 @@
       <c r="A21" t="s">
         <v>71</v>
       </c>
-      <c r="B21" t="s">
-        <v>412</v>
+      <c r="B21">
+        <v>360</v>
       </c>
       <c r="C21" t="s">
         <v>58</v>
@@ -1883,8 +1880,8 @@
       <c r="A22" t="s">
         <v>72</v>
       </c>
-      <c r="B22" t="s">
-        <v>412</v>
+      <c r="B22">
+        <v>360</v>
       </c>
       <c r="C22" t="s">
         <v>58</v>
@@ -1894,8 +1891,8 @@
       <c r="A23" t="s">
         <v>387</v>
       </c>
-      <c r="B23" t="s">
-        <v>412</v>
+      <c r="B23">
+        <v>360</v>
       </c>
       <c r="C23" t="s">
         <v>58</v>
@@ -1905,8 +1902,8 @@
       <c r="A24" t="s">
         <v>73</v>
       </c>
-      <c r="B24" t="s">
-        <v>412</v>
+      <c r="B24">
+        <v>360</v>
       </c>
       <c r="C24" t="s">
         <v>58</v>
@@ -1916,8 +1913,8 @@
       <c r="A25" t="s">
         <v>400</v>
       </c>
-      <c r="B25" t="s">
-        <v>412</v>
+      <c r="B25">
+        <v>360</v>
       </c>
       <c r="C25" t="s">
         <v>58</v>
@@ -1927,8 +1924,8 @@
       <c r="A26" t="s">
         <v>74</v>
       </c>
-      <c r="B26" t="s">
-        <v>412</v>
+      <c r="B26">
+        <v>360</v>
       </c>
       <c r="C26" t="s">
         <v>58</v>
@@ -1938,8 +1935,8 @@
       <c r="A27" t="s">
         <v>75</v>
       </c>
-      <c r="B27" t="s">
-        <v>412</v>
+      <c r="B27">
+        <v>360</v>
       </c>
       <c r="C27" t="s">
         <v>58</v>
@@ -1949,8 +1946,8 @@
       <c r="A28" t="s">
         <v>7</v>
       </c>
-      <c r="B28" t="s">
-        <v>412</v>
+      <c r="B28">
+        <v>360</v>
       </c>
       <c r="C28" t="s">
         <v>58</v>
@@ -1960,8 +1957,8 @@
       <c r="A29" t="s">
         <v>76</v>
       </c>
-      <c r="B29" t="s">
-        <v>412</v>
+      <c r="B29">
+        <v>360</v>
       </c>
       <c r="C29" t="s">
         <v>58</v>
@@ -1971,8 +1968,8 @@
       <c r="A30" t="s">
         <v>388</v>
       </c>
-      <c r="B30" t="s">
-        <v>412</v>
+      <c r="B30">
+        <v>360</v>
       </c>
       <c r="C30" t="s">
         <v>58</v>
@@ -1982,8 +1979,8 @@
       <c r="A31" t="s">
         <v>77</v>
       </c>
-      <c r="B31" t="s">
-        <v>412</v>
+      <c r="B31">
+        <v>360</v>
       </c>
       <c r="C31" t="s">
         <v>58</v>
@@ -1993,8 +1990,8 @@
       <c r="A32" t="s">
         <v>78</v>
       </c>
-      <c r="B32" t="s">
-        <v>412</v>
+      <c r="B32">
+        <v>360</v>
       </c>
       <c r="C32" t="s">
         <v>58</v>
@@ -2004,8 +2001,8 @@
       <c r="A33" t="s">
         <v>79</v>
       </c>
-      <c r="B33" t="s">
-        <v>412</v>
+      <c r="B33">
+        <v>360</v>
       </c>
       <c r="C33" t="s">
         <v>58</v>
@@ -2015,8 +2012,8 @@
       <c r="A34" t="s">
         <v>8</v>
       </c>
-      <c r="B34" t="s">
-        <v>412</v>
+      <c r="B34">
+        <v>360</v>
       </c>
       <c r="C34" t="s">
         <v>58</v>
@@ -2026,8 +2023,8 @@
       <c r="A35" t="s">
         <v>9</v>
       </c>
-      <c r="B35" t="s">
-        <v>412</v>
+      <c r="B35">
+        <v>360</v>
       </c>
       <c r="C35" t="s">
         <v>58</v>
@@ -2037,8 +2034,8 @@
       <c r="A36" t="s">
         <v>389</v>
       </c>
-      <c r="B36" t="s">
-        <v>412</v>
+      <c r="B36">
+        <v>360</v>
       </c>
       <c r="C36" t="s">
         <v>58</v>
@@ -2048,8 +2045,8 @@
       <c r="A37" t="s">
         <v>80</v>
       </c>
-      <c r="B37" t="s">
-        <v>412</v>
+      <c r="B37">
+        <v>360</v>
       </c>
       <c r="C37" t="s">
         <v>58</v>
@@ -2059,8 +2056,8 @@
       <c r="A38" t="s">
         <v>81</v>
       </c>
-      <c r="B38" t="s">
-        <v>412</v>
+      <c r="B38">
+        <v>360</v>
       </c>
       <c r="C38" t="s">
         <v>58</v>
@@ -2070,8 +2067,8 @@
       <c r="A39" t="s">
         <v>10</v>
       </c>
-      <c r="B39" t="s">
-        <v>412</v>
+      <c r="B39">
+        <v>360</v>
       </c>
       <c r="C39" t="s">
         <v>58</v>
@@ -2081,8 +2078,8 @@
       <c r="A40" t="s">
         <v>390</v>
       </c>
-      <c r="B40" t="s">
-        <v>412</v>
+      <c r="B40">
+        <v>360</v>
       </c>
       <c r="C40" t="s">
         <v>58</v>
@@ -2092,8 +2089,8 @@
       <c r="A41" t="s">
         <v>83</v>
       </c>
-      <c r="B41" t="s">
-        <v>412</v>
+      <c r="B41">
+        <v>360</v>
       </c>
       <c r="C41" t="s">
         <v>58</v>
@@ -2103,8 +2100,8 @@
       <c r="A42" t="s">
         <v>82</v>
       </c>
-      <c r="B42" t="s">
-        <v>412</v>
+      <c r="B42">
+        <v>360</v>
       </c>
       <c r="C42" t="s">
         <v>58</v>
@@ -2114,8 +2111,8 @@
       <c r="A43" t="s">
         <v>84</v>
       </c>
-      <c r="B43" t="s">
-        <v>412</v>
+      <c r="B43">
+        <v>360</v>
       </c>
       <c r="C43" t="s">
         <v>58</v>
@@ -2125,8 +2122,8 @@
       <c r="A44" t="s">
         <v>374</v>
       </c>
-      <c r="B44" t="s">
-        <v>412</v>
+      <c r="B44">
+        <v>360</v>
       </c>
       <c r="C44" t="s">
         <v>58</v>
@@ -2136,8 +2133,8 @@
       <c r="A45" t="s">
         <v>391</v>
       </c>
-      <c r="B45" t="s">
-        <v>412</v>
+      <c r="B45">
+        <v>360</v>
       </c>
       <c r="C45" t="s">
         <v>58</v>
@@ -2147,8 +2144,8 @@
       <c r="A46" t="s">
         <v>392</v>
       </c>
-      <c r="B46" t="s">
-        <v>412</v>
+      <c r="B46">
+        <v>360</v>
       </c>
       <c r="C46" t="s">
         <v>58</v>
@@ -2158,8 +2155,8 @@
       <c r="A47" t="s">
         <v>85</v>
       </c>
-      <c r="B47" t="s">
-        <v>412</v>
+      <c r="B47">
+        <v>360</v>
       </c>
       <c r="C47" t="s">
         <v>58</v>
@@ -2169,8 +2166,8 @@
       <c r="A48" t="s">
         <v>86</v>
       </c>
-      <c r="B48" t="s">
-        <v>412</v>
+      <c r="B48">
+        <v>360</v>
       </c>
       <c r="C48" t="s">
         <v>58</v>
@@ -2180,8 +2177,8 @@
       <c r="A49" t="s">
         <v>87</v>
       </c>
-      <c r="B49" t="s">
-        <v>412</v>
+      <c r="B49">
+        <v>360</v>
       </c>
       <c r="C49" t="s">
         <v>58</v>
@@ -2191,8 +2188,8 @@
       <c r="A50" t="s">
         <v>393</v>
       </c>
-      <c r="B50" t="s">
-        <v>412</v>
+      <c r="B50">
+        <v>360</v>
       </c>
       <c r="C50" t="s">
         <v>58</v>
@@ -2202,8 +2199,8 @@
       <c r="A51" t="s">
         <v>88</v>
       </c>
-      <c r="B51" t="s">
-        <v>412</v>
+      <c r="B51">
+        <v>360</v>
       </c>
       <c r="C51" t="s">
         <v>58</v>
@@ -2213,8 +2210,8 @@
       <c r="A52" t="s">
         <v>62</v>
       </c>
-      <c r="B52" t="s">
-        <v>412</v>
+      <c r="B52">
+        <v>360</v>
       </c>
       <c r="C52" t="s">
         <v>58</v>
@@ -2224,8 +2221,8 @@
       <c r="A53" t="s">
         <v>89</v>
       </c>
-      <c r="B53" t="s">
-        <v>412</v>
+      <c r="B53">
+        <v>360</v>
       </c>
       <c r="C53" t="s">
         <v>58</v>
@@ -2235,8 +2232,8 @@
       <c r="A54" t="s">
         <v>11</v>
       </c>
-      <c r="B54" t="s">
-        <v>412</v>
+      <c r="B54">
+        <v>360</v>
       </c>
       <c r="C54" t="s">
         <v>58</v>
@@ -2246,8 +2243,8 @@
       <c r="A55" t="s">
         <v>394</v>
       </c>
-      <c r="B55" t="s">
-        <v>412</v>
+      <c r="B55">
+        <v>360</v>
       </c>
       <c r="C55" t="s">
         <v>58</v>
@@ -2257,8 +2254,8 @@
       <c r="A56" t="s">
         <v>90</v>
       </c>
-      <c r="B56" t="s">
-        <v>412</v>
+      <c r="B56">
+        <v>360</v>
       </c>
       <c r="C56" t="s">
         <v>58</v>
@@ -2268,8 +2265,8 @@
       <c r="A57" t="s">
         <v>91</v>
       </c>
-      <c r="B57" t="s">
-        <v>412</v>
+      <c r="B57">
+        <v>360</v>
       </c>
       <c r="C57" t="s">
         <v>58</v>
@@ -2279,8 +2276,8 @@
       <c r="A58" t="s">
         <v>92</v>
       </c>
-      <c r="B58" t="s">
-        <v>412</v>
+      <c r="B58">
+        <v>360</v>
       </c>
       <c r="C58" t="s">
         <v>58</v>
@@ -2290,8 +2287,8 @@
       <c r="A59" t="s">
         <v>93</v>
       </c>
-      <c r="B59" t="s">
-        <v>412</v>
+      <c r="B59">
+        <v>360</v>
       </c>
       <c r="C59" t="s">
         <v>58</v>
@@ -2301,8 +2298,8 @@
       <c r="A60" t="s">
         <v>94</v>
       </c>
-      <c r="B60" t="s">
-        <v>412</v>
+      <c r="B60">
+        <v>360</v>
       </c>
       <c r="C60" t="s">
         <v>58</v>
@@ -2312,8 +2309,8 @@
       <c r="A61" t="s">
         <v>95</v>
       </c>
-      <c r="B61" t="s">
-        <v>412</v>
+      <c r="B61">
+        <v>360</v>
       </c>
       <c r="C61" t="s">
         <v>58</v>
@@ -2323,8 +2320,8 @@
       <c r="A62" t="s">
         <v>97</v>
       </c>
-      <c r="B62" t="s">
-        <v>412</v>
+      <c r="B62">
+        <v>360</v>
       </c>
       <c r="C62" t="s">
         <v>58</v>
@@ -2334,8 +2331,8 @@
       <c r="A63" t="s">
         <v>98</v>
       </c>
-      <c r="B63" t="s">
-        <v>412</v>
+      <c r="B63">
+        <v>360</v>
       </c>
       <c r="C63" t="s">
         <v>58</v>
@@ -2345,8 +2342,8 @@
       <c r="A64" t="s">
         <v>99</v>
       </c>
-      <c r="B64" t="s">
-        <v>412</v>
+      <c r="B64">
+        <v>360</v>
       </c>
       <c r="C64" t="s">
         <v>58</v>
@@ -2356,8 +2353,8 @@
       <c r="A65" t="s">
         <v>96</v>
       </c>
-      <c r="B65" t="s">
-        <v>412</v>
+      <c r="B65">
+        <v>360</v>
       </c>
       <c r="C65" t="s">
         <v>58</v>
@@ -2367,8 +2364,8 @@
       <c r="A66" t="s">
         <v>100</v>
       </c>
-      <c r="B66" t="s">
-        <v>412</v>
+      <c r="B66">
+        <v>360</v>
       </c>
       <c r="C66" t="s">
         <v>58</v>
@@ -2378,8 +2375,8 @@
       <c r="A67" t="s">
         <v>101</v>
       </c>
-      <c r="B67" t="s">
-        <v>412</v>
+      <c r="B67">
+        <v>360</v>
       </c>
       <c r="C67" t="s">
         <v>58</v>
@@ -2389,8 +2386,8 @@
       <c r="A68" t="s">
         <v>102</v>
       </c>
-      <c r="B68" t="s">
-        <v>412</v>
+      <c r="B68">
+        <v>360</v>
       </c>
       <c r="C68" t="s">
         <v>58</v>
@@ -2400,8 +2397,8 @@
       <c r="A69" t="s">
         <v>103</v>
       </c>
-      <c r="B69" t="s">
-        <v>412</v>
+      <c r="B69">
+        <v>360</v>
       </c>
       <c r="C69" t="s">
         <v>58</v>
@@ -2411,8 +2408,8 @@
       <c r="A70" t="s">
         <v>397</v>
       </c>
-      <c r="B70" t="s">
-        <v>412</v>
+      <c r="B70">
+        <v>360</v>
       </c>
       <c r="C70" t="s">
         <v>58</v>
@@ -2422,8 +2419,8 @@
       <c r="A71" t="s">
         <v>104</v>
       </c>
-      <c r="B71" t="s">
-        <v>412</v>
+      <c r="B71">
+        <v>360</v>
       </c>
       <c r="C71" t="s">
         <v>58</v>
@@ -2433,8 +2430,8 @@
       <c r="A72" t="s">
         <v>105</v>
       </c>
-      <c r="B72" t="s">
-        <v>412</v>
+      <c r="B72">
+        <v>360</v>
       </c>
       <c r="C72" t="s">
         <v>58</v>
@@ -2444,8 +2441,8 @@
       <c r="A73" t="s">
         <v>106</v>
       </c>
-      <c r="B73" t="s">
-        <v>412</v>
+      <c r="B73">
+        <v>360</v>
       </c>
       <c r="C73" t="s">
         <v>58</v>
@@ -2455,8 +2452,8 @@
       <c r="A74" t="s">
         <v>12</v>
       </c>
-      <c r="B74" t="s">
-        <v>412</v>
+      <c r="B74">
+        <v>360</v>
       </c>
       <c r="C74" t="s">
         <v>58</v>
@@ -2466,8 +2463,8 @@
       <c r="A75" t="s">
         <v>107</v>
       </c>
-      <c r="B75" t="s">
-        <v>412</v>
+      <c r="B75">
+        <v>360</v>
       </c>
       <c r="C75" t="s">
         <v>58</v>
@@ -2477,8 +2474,8 @@
       <c r="A76" t="s">
         <v>375</v>
       </c>
-      <c r="B76" t="s">
-        <v>412</v>
+      <c r="B76">
+        <v>360</v>
       </c>
       <c r="C76" t="s">
         <v>58</v>
@@ -2488,8 +2485,8 @@
       <c r="A77" t="s">
         <v>402</v>
       </c>
-      <c r="B77" t="s">
-        <v>412</v>
+      <c r="B77">
+        <v>360</v>
       </c>
       <c r="C77" t="s">
         <v>58</v>
@@ -2499,8 +2496,8 @@
       <c r="A78" t="s">
         <v>108</v>
       </c>
-      <c r="B78" t="s">
-        <v>412</v>
+      <c r="B78">
+        <v>360</v>
       </c>
       <c r="C78" t="s">
         <v>58</v>
@@ -2510,8 +2507,8 @@
       <c r="A79" t="s">
         <v>109</v>
       </c>
-      <c r="B79" t="s">
-        <v>412</v>
+      <c r="B79">
+        <v>360</v>
       </c>
       <c r="C79" t="s">
         <v>58</v>
@@ -2521,8 +2518,8 @@
       <c r="A80" t="s">
         <v>13</v>
       </c>
-      <c r="B80" t="s">
-        <v>412</v>
+      <c r="B80">
+        <v>360</v>
       </c>
       <c r="C80" t="s">
         <v>58</v>
@@ -2532,8 +2529,8 @@
       <c r="A81" t="s">
         <v>110</v>
       </c>
-      <c r="B81" t="s">
-        <v>412</v>
+      <c r="B81">
+        <v>360</v>
       </c>
       <c r="C81" t="s">
         <v>58</v>
@@ -2543,8 +2540,8 @@
       <c r="A82" t="s">
         <v>111</v>
       </c>
-      <c r="B82" t="s">
-        <v>412</v>
+      <c r="B82">
+        <v>360</v>
       </c>
       <c r="C82" t="s">
         <v>58</v>
@@ -2554,8 +2551,8 @@
       <c r="A83" t="s">
         <v>112</v>
       </c>
-      <c r="B83" t="s">
-        <v>412</v>
+      <c r="B83">
+        <v>360</v>
       </c>
       <c r="C83" t="s">
         <v>58</v>
@@ -2565,8 +2562,8 @@
       <c r="A84" t="s">
         <v>14</v>
       </c>
-      <c r="B84" t="s">
-        <v>412</v>
+      <c r="B84">
+        <v>360</v>
       </c>
       <c r="C84" t="s">
         <v>58</v>
@@ -2576,8 +2573,8 @@
       <c r="A85" t="s">
         <v>113</v>
       </c>
-      <c r="B85" t="s">
-        <v>412</v>
+      <c r="B85">
+        <v>360</v>
       </c>
       <c r="C85" t="s">
         <v>58</v>
@@ -2587,8 +2584,8 @@
       <c r="A86" t="s">
         <v>15</v>
       </c>
-      <c r="B86" t="s">
-        <v>412</v>
+      <c r="B86">
+        <v>360</v>
       </c>
       <c r="C86" t="s">
         <v>58</v>
@@ -2598,8 +2595,8 @@
       <c r="A87" t="s">
         <v>114</v>
       </c>
-      <c r="B87" t="s">
-        <v>412</v>
+      <c r="B87">
+        <v>360</v>
       </c>
       <c r="C87" t="s">
         <v>58</v>
@@ -2609,8 +2606,8 @@
       <c r="A88" t="s">
         <v>396</v>
       </c>
-      <c r="B88" t="s">
-        <v>412</v>
+      <c r="B88">
+        <v>360</v>
       </c>
       <c r="C88" t="s">
         <v>58</v>
@@ -2620,8 +2617,8 @@
       <c r="A89" t="s">
         <v>409</v>
       </c>
-      <c r="B89" t="s">
-        <v>412</v>
+      <c r="B89">
+        <v>360</v>
       </c>
       <c r="C89" t="s">
         <v>58</v>
@@ -2631,8 +2628,8 @@
       <c r="A90" t="s">
         <v>116</v>
       </c>
-      <c r="B90" t="s">
-        <v>412</v>
+      <c r="B90">
+        <v>360</v>
       </c>
       <c r="C90" t="s">
         <v>58</v>
@@ -2642,8 +2639,8 @@
       <c r="A91" t="s">
         <v>117</v>
       </c>
-      <c r="B91" t="s">
-        <v>412</v>
+      <c r="B91">
+        <v>360</v>
       </c>
       <c r="C91" t="s">
         <v>58</v>
@@ -2653,8 +2650,8 @@
       <c r="A92" t="s">
         <v>118</v>
       </c>
-      <c r="B92" t="s">
-        <v>412</v>
+      <c r="B92">
+        <v>360</v>
       </c>
       <c r="C92" t="s">
         <v>58</v>
@@ -2664,8 +2661,8 @@
       <c r="A93" t="s">
         <v>119</v>
       </c>
-      <c r="B93" t="s">
-        <v>412</v>
+      <c r="B93">
+        <v>360</v>
       </c>
       <c r="C93" t="s">
         <v>58</v>
@@ -2675,8 +2672,8 @@
       <c r="A94" t="s">
         <v>120</v>
       </c>
-      <c r="B94" t="s">
-        <v>412</v>
+      <c r="B94">
+        <v>360</v>
       </c>
       <c r="C94" t="s">
         <v>58</v>
@@ -2686,8 +2683,8 @@
       <c r="A95" t="s">
         <v>121</v>
       </c>
-      <c r="B95" t="s">
-        <v>412</v>
+      <c r="B95">
+        <v>360</v>
       </c>
       <c r="C95" t="s">
         <v>58</v>
@@ -2697,8 +2694,8 @@
       <c r="A96" t="s">
         <v>122</v>
       </c>
-      <c r="B96" t="s">
-        <v>412</v>
+      <c r="B96">
+        <v>360</v>
       </c>
       <c r="C96" t="s">
         <v>58</v>
@@ -2708,8 +2705,8 @@
       <c r="A97" t="s">
         <v>123</v>
       </c>
-      <c r="B97" t="s">
-        <v>412</v>
+      <c r="B97">
+        <v>360</v>
       </c>
       <c r="C97" t="s">
         <v>58</v>
@@ -2719,8 +2716,8 @@
       <c r="A98" t="s">
         <v>124</v>
       </c>
-      <c r="B98" t="s">
-        <v>412</v>
+      <c r="B98">
+        <v>360</v>
       </c>
       <c r="C98" t="s">
         <v>58</v>
@@ -2730,8 +2727,8 @@
       <c r="A99" t="s">
         <v>125</v>
       </c>
-      <c r="B99" t="s">
-        <v>412</v>
+      <c r="B99">
+        <v>360</v>
       </c>
       <c r="C99" t="s">
         <v>58</v>
@@ -2741,8 +2738,8 @@
       <c r="A100" t="s">
         <v>126</v>
       </c>
-      <c r="B100" t="s">
-        <v>412</v>
+      <c r="B100">
+        <v>360</v>
       </c>
       <c r="C100" t="s">
         <v>58</v>
@@ -2752,8 +2749,8 @@
       <c r="A101" t="s">
         <v>376</v>
       </c>
-      <c r="B101" t="s">
-        <v>412</v>
+      <c r="B101">
+        <v>360</v>
       </c>
       <c r="C101" t="s">
         <v>58</v>
@@ -2763,8 +2760,8 @@
       <c r="A102" t="s">
         <v>127</v>
       </c>
-      <c r="B102" t="s">
-        <v>412</v>
+      <c r="B102">
+        <v>360</v>
       </c>
       <c r="C102" t="s">
         <v>58</v>
@@ -2774,8 +2771,8 @@
       <c r="A103" t="s">
         <v>408</v>
       </c>
-      <c r="B103" t="s">
-        <v>412</v>
+      <c r="B103">
+        <v>360</v>
       </c>
       <c r="C103" t="s">
         <v>58</v>
@@ -2785,8 +2782,8 @@
       <c r="A104" t="s">
         <v>16</v>
       </c>
-      <c r="B104" t="s">
-        <v>412</v>
+      <c r="B104">
+        <v>360</v>
       </c>
       <c r="C104" t="s">
         <v>58</v>
@@ -2796,8 +2793,8 @@
       <c r="A105" t="s">
         <v>128</v>
       </c>
-      <c r="B105" t="s">
-        <v>412</v>
+      <c r="B105">
+        <v>360</v>
       </c>
       <c r="C105" t="s">
         <v>58</v>
@@ -2807,8 +2804,8 @@
       <c r="A106" t="s">
         <v>17</v>
       </c>
-      <c r="B106" t="s">
-        <v>412</v>
+      <c r="B106">
+        <v>360</v>
       </c>
       <c r="C106" t="s">
         <v>58</v>
@@ -2818,8 +2815,8 @@
       <c r="A107" t="s">
         <v>18</v>
       </c>
-      <c r="B107" t="s">
-        <v>412</v>
+      <c r="B107">
+        <v>360</v>
       </c>
       <c r="C107" t="s">
         <v>58</v>
@@ -2829,8 +2826,8 @@
       <c r="A108" t="s">
         <v>129</v>
       </c>
-      <c r="B108" t="s">
-        <v>412</v>
+      <c r="B108">
+        <v>360</v>
       </c>
       <c r="C108" t="s">
         <v>58</v>
@@ -2840,8 +2837,8 @@
       <c r="A109" t="s">
         <v>131</v>
       </c>
-      <c r="B109" t="s">
-        <v>412</v>
+      <c r="B109">
+        <v>360</v>
       </c>
       <c r="C109" t="s">
         <v>58</v>
@@ -2851,8 +2848,8 @@
       <c r="A110" t="s">
         <v>130</v>
       </c>
-      <c r="B110" t="s">
-        <v>412</v>
+      <c r="B110">
+        <v>360</v>
       </c>
       <c r="C110" t="s">
         <v>58</v>
@@ -2862,8 +2859,8 @@
       <c r="A111" t="s">
         <v>132</v>
       </c>
-      <c r="B111" t="s">
-        <v>412</v>
+      <c r="B111">
+        <v>360</v>
       </c>
       <c r="C111" t="s">
         <v>58</v>
@@ -2873,8 +2870,8 @@
       <c r="A112" t="s">
         <v>133</v>
       </c>
-      <c r="B112" t="s">
-        <v>412</v>
+      <c r="B112">
+        <v>360</v>
       </c>
       <c r="C112" t="s">
         <v>58</v>
@@ -2884,8 +2881,8 @@
       <c r="A113" t="s">
         <v>115</v>
       </c>
-      <c r="B113" t="s">
-        <v>412</v>
+      <c r="B113">
+        <v>360</v>
       </c>
       <c r="C113" t="s">
         <v>58</v>
@@ -2895,8 +2892,8 @@
       <c r="A114" t="s">
         <v>134</v>
       </c>
-      <c r="B114" t="s">
-        <v>412</v>
+      <c r="B114">
+        <v>360</v>
       </c>
       <c r="C114" t="s">
         <v>58</v>
@@ -2906,8 +2903,8 @@
       <c r="A115" t="s">
         <v>135</v>
       </c>
-      <c r="B115" t="s">
-        <v>412</v>
+      <c r="B115">
+        <v>360</v>
       </c>
       <c r="C115" t="s">
         <v>58</v>
@@ -2917,8 +2914,8 @@
       <c r="A116" t="s">
         <v>136</v>
       </c>
-      <c r="B116" t="s">
-        <v>412</v>
+      <c r="B116">
+        <v>360</v>
       </c>
       <c r="C116" t="s">
         <v>58</v>
@@ -2928,8 +2925,8 @@
       <c r="A117" t="s">
         <v>137</v>
       </c>
-      <c r="B117" t="s">
-        <v>412</v>
+      <c r="B117">
+        <v>360</v>
       </c>
       <c r="C117" t="s">
         <v>58</v>
@@ -2939,8 +2936,8 @@
       <c r="A118" t="s">
         <v>138</v>
       </c>
-      <c r="B118" t="s">
-        <v>412</v>
+      <c r="B118">
+        <v>360</v>
       </c>
       <c r="C118" t="s">
         <v>58</v>
@@ -2950,8 +2947,8 @@
       <c r="A119" t="s">
         <v>139</v>
       </c>
-      <c r="B119" t="s">
-        <v>412</v>
+      <c r="B119">
+        <v>360</v>
       </c>
       <c r="C119" t="s">
         <v>58</v>
@@ -2961,8 +2958,8 @@
       <c r="A120" t="s">
         <v>140</v>
       </c>
-      <c r="B120" t="s">
-        <v>412</v>
+      <c r="B120">
+        <v>360</v>
       </c>
       <c r="C120" t="s">
         <v>58</v>
@@ -2972,8 +2969,8 @@
       <c r="A121" t="s">
         <v>141</v>
       </c>
-      <c r="B121" t="s">
-        <v>412</v>
+      <c r="B121">
+        <v>360</v>
       </c>
       <c r="C121" t="s">
         <v>58</v>
@@ -2983,8 +2980,8 @@
       <c r="A122" t="s">
         <v>19</v>
       </c>
-      <c r="B122" t="s">
-        <v>412</v>
+      <c r="B122">
+        <v>360</v>
       </c>
       <c r="C122" t="s">
         <v>58</v>
@@ -2994,8 +2991,8 @@
       <c r="A123" t="s">
         <v>142</v>
       </c>
-      <c r="B123" t="s">
-        <v>412</v>
+      <c r="B123">
+        <v>360</v>
       </c>
       <c r="C123" t="s">
         <v>58</v>
@@ -3005,8 +3002,8 @@
       <c r="A124" t="s">
         <v>143</v>
       </c>
-      <c r="B124" t="s">
-        <v>412</v>
+      <c r="B124">
+        <v>360</v>
       </c>
       <c r="C124" t="s">
         <v>58</v>
@@ -3016,8 +3013,8 @@
       <c r="A125" t="s">
         <v>144</v>
       </c>
-      <c r="B125" t="s">
-        <v>412</v>
+      <c r="B125">
+        <v>360</v>
       </c>
       <c r="C125" t="s">
         <v>58</v>
@@ -3027,8 +3024,8 @@
       <c r="A126" t="s">
         <v>145</v>
       </c>
-      <c r="B126" t="s">
-        <v>412</v>
+      <c r="B126">
+        <v>360</v>
       </c>
       <c r="C126" t="s">
         <v>58</v>
@@ -3038,8 +3035,8 @@
       <c r="A127" t="s">
         <v>146</v>
       </c>
-      <c r="B127" t="s">
-        <v>412</v>
+      <c r="B127">
+        <v>360</v>
       </c>
       <c r="C127" t="s">
         <v>58</v>
@@ -3049,8 +3046,8 @@
       <c r="A128" t="s">
         <v>147</v>
       </c>
-      <c r="B128" t="s">
-        <v>412</v>
+      <c r="B128">
+        <v>360</v>
       </c>
       <c r="C128" t="s">
         <v>58</v>
@@ -3060,8 +3057,8 @@
       <c r="A129" t="s">
         <v>403</v>
       </c>
-      <c r="B129" t="s">
-        <v>412</v>
+      <c r="B129">
+        <v>360</v>
       </c>
       <c r="C129" t="s">
         <v>58</v>
@@ -3071,8 +3068,8 @@
       <c r="A130" t="s">
         <v>148</v>
       </c>
-      <c r="B130" t="s">
-        <v>412</v>
+      <c r="B130">
+        <v>360</v>
       </c>
       <c r="C130" t="s">
         <v>58</v>
@@ -3082,8 +3079,8 @@
       <c r="A131" t="s">
         <v>149</v>
       </c>
-      <c r="B131" t="s">
-        <v>412</v>
+      <c r="B131">
+        <v>360</v>
       </c>
       <c r="C131" t="s">
         <v>58</v>
@@ -3093,8 +3090,8 @@
       <c r="A132" t="s">
         <v>150</v>
       </c>
-      <c r="B132" t="s">
-        <v>412</v>
+      <c r="B132">
+        <v>360</v>
       </c>
       <c r="C132" t="s">
         <v>58</v>
@@ -3104,8 +3101,8 @@
       <c r="A133" t="s">
         <v>20</v>
       </c>
-      <c r="B133" t="s">
-        <v>412</v>
+      <c r="B133">
+        <v>360</v>
       </c>
       <c r="C133" t="s">
         <v>58</v>
@@ -3115,8 +3112,8 @@
       <c r="A134" t="s">
         <v>151</v>
       </c>
-      <c r="B134" t="s">
-        <v>412</v>
+      <c r="B134">
+        <v>360</v>
       </c>
       <c r="C134" t="s">
         <v>58</v>
@@ -3126,8 +3123,8 @@
       <c r="A135" t="s">
         <v>152</v>
       </c>
-      <c r="B135" t="s">
-        <v>412</v>
+      <c r="B135">
+        <v>360</v>
       </c>
       <c r="C135" t="s">
         <v>58</v>
@@ -3137,8 +3134,8 @@
       <c r="A136" t="s">
         <v>153</v>
       </c>
-      <c r="B136" t="s">
-        <v>412</v>
+      <c r="B136">
+        <v>360</v>
       </c>
       <c r="C136" t="s">
         <v>58</v>
@@ -3148,8 +3145,8 @@
       <c r="A137" t="s">
         <v>154</v>
       </c>
-      <c r="B137" t="s">
-        <v>412</v>
+      <c r="B137">
+        <v>360</v>
       </c>
       <c r="C137" t="s">
         <v>58</v>
@@ -3159,8 +3156,8 @@
       <c r="A138" t="s">
         <v>155</v>
       </c>
-      <c r="B138" t="s">
-        <v>412</v>
+      <c r="B138">
+        <v>360</v>
       </c>
       <c r="C138" t="s">
         <v>58</v>
@@ -3170,8 +3167,8 @@
       <c r="A139" t="s">
         <v>156</v>
       </c>
-      <c r="B139" t="s">
-        <v>412</v>
+      <c r="B139">
+        <v>360</v>
       </c>
       <c r="C139" t="s">
         <v>58</v>
@@ -3181,8 +3178,8 @@
       <c r="A140" t="s">
         <v>157</v>
       </c>
-      <c r="B140" t="s">
-        <v>412</v>
+      <c r="B140">
+        <v>360</v>
       </c>
       <c r="C140" t="s">
         <v>58</v>
@@ -3192,8 +3189,8 @@
       <c r="A141" t="s">
         <v>158</v>
       </c>
-      <c r="B141" t="s">
-        <v>412</v>
+      <c r="B141">
+        <v>360</v>
       </c>
       <c r="C141" t="s">
         <v>58</v>
@@ -3203,8 +3200,8 @@
       <c r="A142" t="s">
         <v>21</v>
       </c>
-      <c r="B142" t="s">
-        <v>412</v>
+      <c r="B142">
+        <v>360</v>
       </c>
       <c r="C142" t="s">
         <v>58</v>
@@ -3214,8 +3211,8 @@
       <c r="A143" t="s">
         <v>410</v>
       </c>
-      <c r="B143" t="s">
-        <v>412</v>
+      <c r="B143">
+        <v>360</v>
       </c>
       <c r="C143" t="s">
         <v>58</v>
@@ -3225,8 +3222,8 @@
       <c r="A144" t="s">
         <v>22</v>
       </c>
-      <c r="B144" t="s">
-        <v>412</v>
+      <c r="B144">
+        <v>360</v>
       </c>
       <c r="C144" t="s">
         <v>58</v>
@@ -3236,8 +3233,8 @@
       <c r="A145" t="s">
         <v>399</v>
       </c>
-      <c r="B145" t="s">
-        <v>412</v>
+      <c r="B145">
+        <v>360</v>
       </c>
       <c r="C145" t="s">
         <v>58</v>
@@ -3247,8 +3244,8 @@
       <c r="A146" t="s">
         <v>159</v>
       </c>
-      <c r="B146" t="s">
-        <v>412</v>
+      <c r="B146">
+        <v>360</v>
       </c>
       <c r="C146" t="s">
         <v>58</v>
@@ -3258,8 +3255,8 @@
       <c r="A147" t="s">
         <v>160</v>
       </c>
-      <c r="B147" t="s">
-        <v>412</v>
+      <c r="B147">
+        <v>360</v>
       </c>
       <c r="C147" t="s">
         <v>58</v>
@@ -3269,8 +3266,8 @@
       <c r="A148" t="s">
         <v>161</v>
       </c>
-      <c r="B148" t="s">
-        <v>412</v>
+      <c r="B148">
+        <v>360</v>
       </c>
       <c r="C148" t="s">
         <v>58</v>
@@ -3280,8 +3277,8 @@
       <c r="A149" t="s">
         <v>162</v>
       </c>
-      <c r="B149" t="s">
-        <v>412</v>
+      <c r="B149">
+        <v>360</v>
       </c>
       <c r="C149" t="s">
         <v>58</v>
@@ -3291,8 +3288,8 @@
       <c r="A150" t="s">
         <v>163</v>
       </c>
-      <c r="B150" t="s">
-        <v>412</v>
+      <c r="B150">
+        <v>360</v>
       </c>
       <c r="C150" t="s">
         <v>58</v>
@@ -3302,8 +3299,8 @@
       <c r="A151" t="s">
         <v>164</v>
       </c>
-      <c r="B151" t="s">
-        <v>412</v>
+      <c r="B151">
+        <v>360</v>
       </c>
       <c r="C151" t="s">
         <v>58</v>
@@ -3313,8 +3310,8 @@
       <c r="A152" t="s">
         <v>405</v>
       </c>
-      <c r="B152" t="s">
-        <v>412</v>
+      <c r="B152">
+        <v>360</v>
       </c>
       <c r="C152" t="s">
         <v>58</v>
@@ -3324,8 +3321,8 @@
       <c r="A153" t="s">
         <v>165</v>
       </c>
-      <c r="B153" t="s">
-        <v>412</v>
+      <c r="B153">
+        <v>360</v>
       </c>
       <c r="C153" t="s">
         <v>58</v>
@@ -3335,8 +3332,8 @@
       <c r="A154" t="s">
         <v>23</v>
       </c>
-      <c r="B154" t="s">
-        <v>412</v>
+      <c r="B154">
+        <v>360</v>
       </c>
       <c r="C154" t="s">
         <v>58</v>
@@ -3346,8 +3343,8 @@
       <c r="A155" t="s">
         <v>24</v>
       </c>
-      <c r="B155" t="s">
-        <v>412</v>
+      <c r="B155">
+        <v>360</v>
       </c>
       <c r="C155" t="s">
         <v>58</v>
@@ -3357,8 +3354,8 @@
       <c r="A156" t="s">
         <v>166</v>
       </c>
-      <c r="B156" t="s">
-        <v>412</v>
+      <c r="B156">
+        <v>360</v>
       </c>
       <c r="C156" t="s">
         <v>58</v>
@@ -3368,8 +3365,8 @@
       <c r="A157" t="s">
         <v>395</v>
       </c>
-      <c r="B157" t="s">
-        <v>412</v>
+      <c r="B157">
+        <v>360</v>
       </c>
       <c r="C157" t="s">
         <v>58</v>
@@ -3379,8 +3376,8 @@
       <c r="A158" t="s">
         <v>167</v>
       </c>
-      <c r="B158" t="s">
-        <v>412</v>
+      <c r="B158">
+        <v>360</v>
       </c>
       <c r="C158" t="s">
         <v>58</v>
@@ -3390,8 +3387,8 @@
       <c r="A159" t="s">
         <v>168</v>
       </c>
-      <c r="B159" t="s">
-        <v>412</v>
+      <c r="B159">
+        <v>360</v>
       </c>
       <c r="C159" t="s">
         <v>58</v>
@@ -3401,8 +3398,8 @@
       <c r="A160" t="s">
         <v>25</v>
       </c>
-      <c r="B160" t="s">
-        <v>412</v>
+      <c r="B160">
+        <v>360</v>
       </c>
       <c r="C160" t="s">
         <v>58</v>
@@ -3412,8 +3409,8 @@
       <c r="A161" t="s">
         <v>169</v>
       </c>
-      <c r="B161" t="s">
-        <v>412</v>
+      <c r="B161">
+        <v>360</v>
       </c>
       <c r="C161" t="s">
         <v>58</v>
@@ -3423,8 +3420,8 @@
       <c r="A162" t="s">
         <v>170</v>
       </c>
-      <c r="B162" t="s">
-        <v>412</v>
+      <c r="B162">
+        <v>360</v>
       </c>
       <c r="C162" t="s">
         <v>58</v>
@@ -3434,8 +3431,8 @@
       <c r="A163" t="s">
         <v>171</v>
       </c>
-      <c r="B163" t="s">
-        <v>412</v>
+      <c r="B163">
+        <v>360</v>
       </c>
       <c r="C163" t="s">
         <v>58</v>
@@ -3445,8 +3442,8 @@
       <c r="A164" t="s">
         <v>172</v>
       </c>
-      <c r="B164" t="s">
-        <v>412</v>
+      <c r="B164">
+        <v>360</v>
       </c>
       <c r="C164" t="s">
         <v>58</v>
@@ -3456,8 +3453,8 @@
       <c r="A165" t="s">
         <v>173</v>
       </c>
-      <c r="B165" t="s">
-        <v>412</v>
+      <c r="B165">
+        <v>360</v>
       </c>
       <c r="C165" t="s">
         <v>58</v>
@@ -3467,8 +3464,8 @@
       <c r="A166" t="s">
         <v>174</v>
       </c>
-      <c r="B166" t="s">
-        <v>412</v>
+      <c r="B166">
+        <v>360</v>
       </c>
       <c r="C166" t="s">
         <v>58</v>
@@ -3478,8 +3475,8 @@
       <c r="A167" t="s">
         <v>175</v>
       </c>
-      <c r="B167" t="s">
-        <v>412</v>
+      <c r="B167">
+        <v>360</v>
       </c>
       <c r="C167" t="s">
         <v>58</v>
@@ -3489,8 +3486,8 @@
       <c r="A168" t="s">
         <v>176</v>
       </c>
-      <c r="B168" t="s">
-        <v>412</v>
+      <c r="B168">
+        <v>360</v>
       </c>
       <c r="C168" t="s">
         <v>58</v>
@@ -3500,8 +3497,8 @@
       <c r="A169" t="s">
         <v>177</v>
       </c>
-      <c r="B169" t="s">
-        <v>412</v>
+      <c r="B169">
+        <v>360</v>
       </c>
       <c r="C169" t="s">
         <v>58</v>
@@ -3511,8 +3508,8 @@
       <c r="A170" t="s">
         <v>179</v>
       </c>
-      <c r="B170" t="s">
-        <v>412</v>
+      <c r="B170">
+        <v>360</v>
       </c>
       <c r="C170" t="s">
         <v>58</v>
@@ -3522,8 +3519,8 @@
       <c r="A171" t="s">
         <v>180</v>
       </c>
-      <c r="B171" t="s">
-        <v>412</v>
+      <c r="B171">
+        <v>360</v>
       </c>
       <c r="C171" t="s">
         <v>58</v>
@@ -3533,8 +3530,8 @@
       <c r="A172" t="s">
         <v>181</v>
       </c>
-      <c r="B172" t="s">
-        <v>412</v>
+      <c r="B172">
+        <v>360</v>
       </c>
       <c r="C172" t="s">
         <v>58</v>
@@ -3544,8 +3541,8 @@
       <c r="A173" t="s">
         <v>182</v>
       </c>
-      <c r="B173" t="s">
-        <v>412</v>
+      <c r="B173">
+        <v>360</v>
       </c>
       <c r="C173" t="s">
         <v>58</v>
@@ -3555,8 +3552,8 @@
       <c r="A174" t="s">
         <v>183</v>
       </c>
-      <c r="B174" t="s">
-        <v>412</v>
+      <c r="B174">
+        <v>360</v>
       </c>
       <c r="C174" t="s">
         <v>58</v>
@@ -3566,8 +3563,8 @@
       <c r="A175" t="s">
         <v>184</v>
       </c>
-      <c r="B175" t="s">
-        <v>412</v>
+      <c r="B175">
+        <v>360</v>
       </c>
       <c r="C175" t="s">
         <v>58</v>
@@ -3577,8 +3574,8 @@
       <c r="A176" t="s">
         <v>185</v>
       </c>
-      <c r="B176" t="s">
-        <v>412</v>
+      <c r="B176">
+        <v>360</v>
       </c>
       <c r="C176" t="s">
         <v>58</v>
@@ -3588,8 +3585,8 @@
       <c r="A177" t="s">
         <v>186</v>
       </c>
-      <c r="B177" t="s">
-        <v>412</v>
+      <c r="B177">
+        <v>360</v>
       </c>
       <c r="C177" t="s">
         <v>58</v>
@@ -3599,8 +3596,8 @@
       <c r="A178" t="s">
         <v>187</v>
       </c>
-      <c r="B178" t="s">
-        <v>412</v>
+      <c r="B178">
+        <v>360</v>
       </c>
       <c r="C178" t="s">
         <v>58</v>
@@ -3610,8 +3607,8 @@
       <c r="A179" t="s">
         <v>188</v>
       </c>
-      <c r="B179" t="s">
-        <v>412</v>
+      <c r="B179">
+        <v>360</v>
       </c>
       <c r="C179" t="s">
         <v>58</v>
@@ -3621,8 +3618,8 @@
       <c r="A180" t="s">
         <v>178</v>
       </c>
-      <c r="B180" t="s">
-        <v>412</v>
+      <c r="B180">
+        <v>360</v>
       </c>
       <c r="C180" t="s">
         <v>58</v>
@@ -3632,8 +3629,8 @@
       <c r="A181" t="s">
         <v>190</v>
       </c>
-      <c r="B181" t="s">
-        <v>412</v>
+      <c r="B181">
+        <v>360</v>
       </c>
       <c r="C181" t="s">
         <v>58</v>
@@ -3643,8 +3640,8 @@
       <c r="A182" t="s">
         <v>189</v>
       </c>
-      <c r="B182" t="s">
-        <v>412</v>
+      <c r="B182">
+        <v>360</v>
       </c>
       <c r="C182" t="s">
         <v>58</v>
@@ -3654,8 +3651,8 @@
       <c r="A183" t="s">
         <v>191</v>
       </c>
-      <c r="B183" t="s">
-        <v>412</v>
+      <c r="B183">
+        <v>360</v>
       </c>
       <c r="C183" t="s">
         <v>58</v>
@@ -3665,8 +3662,8 @@
       <c r="A184" t="s">
         <v>377</v>
       </c>
-      <c r="B184" t="s">
-        <v>412</v>
+      <c r="B184">
+        <v>360</v>
       </c>
       <c r="C184" t="s">
         <v>58</v>
@@ -3676,8 +3673,8 @@
       <c r="A185" t="s">
         <v>192</v>
       </c>
-      <c r="B185" t="s">
-        <v>412</v>
+      <c r="B185">
+        <v>360</v>
       </c>
       <c r="C185" t="s">
         <v>58</v>
@@ -3687,8 +3684,8 @@
       <c r="A186" t="s">
         <v>193</v>
       </c>
-      <c r="B186" t="s">
-        <v>412</v>
+      <c r="B186">
+        <v>360</v>
       </c>
       <c r="C186" t="s">
         <v>58</v>
@@ -3698,8 +3695,8 @@
       <c r="A187" t="s">
         <v>194</v>
       </c>
-      <c r="B187" t="s">
-        <v>412</v>
+      <c r="B187">
+        <v>360</v>
       </c>
       <c r="C187" t="s">
         <v>58</v>
@@ -3709,8 +3706,8 @@
       <c r="A188" t="s">
         <v>195</v>
       </c>
-      <c r="B188" t="s">
-        <v>412</v>
+      <c r="B188">
+        <v>360</v>
       </c>
       <c r="C188" t="s">
         <v>58</v>
@@ -3720,8 +3717,8 @@
       <c r="A189" t="s">
         <v>196</v>
       </c>
-      <c r="B189" t="s">
-        <v>412</v>
+      <c r="B189">
+        <v>360</v>
       </c>
       <c r="C189" t="s">
         <v>58</v>
@@ -3731,8 +3728,8 @@
       <c r="A190" t="s">
         <v>197</v>
       </c>
-      <c r="B190" t="s">
-        <v>412</v>
+      <c r="B190">
+        <v>360</v>
       </c>
       <c r="C190" t="s">
         <v>58</v>
@@ -3742,8 +3739,8 @@
       <c r="A191" t="s">
         <v>199</v>
       </c>
-      <c r="B191" t="s">
-        <v>412</v>
+      <c r="B191">
+        <v>360</v>
       </c>
       <c r="C191" t="s">
         <v>58</v>
@@ -3753,8 +3750,8 @@
       <c r="A192" t="s">
         <v>200</v>
       </c>
-      <c r="B192" t="s">
-        <v>412</v>
+      <c r="B192">
+        <v>360</v>
       </c>
       <c r="C192" t="s">
         <v>58</v>
@@ -3764,8 +3761,8 @@
       <c r="A193" t="s">
         <v>201</v>
       </c>
-      <c r="B193" t="s">
-        <v>412</v>
+      <c r="B193">
+        <v>360</v>
       </c>
       <c r="C193" t="s">
         <v>58</v>
@@ -3775,8 +3772,8 @@
       <c r="A194" t="s">
         <v>198</v>
       </c>
-      <c r="B194" t="s">
-        <v>412</v>
+      <c r="B194">
+        <v>360</v>
       </c>
       <c r="C194" t="s">
         <v>58</v>
@@ -3786,8 +3783,8 @@
       <c r="A195" t="s">
         <v>202</v>
       </c>
-      <c r="B195" t="s">
-        <v>412</v>
+      <c r="B195">
+        <v>360</v>
       </c>
       <c r="C195" t="s">
         <v>58</v>
@@ -3797,8 +3794,8 @@
       <c r="A196" t="s">
         <v>26</v>
       </c>
-      <c r="B196" t="s">
-        <v>412</v>
+      <c r="B196">
+        <v>360</v>
       </c>
       <c r="C196" t="s">
         <v>58</v>
@@ -3808,8 +3805,8 @@
       <c r="A197" t="s">
         <v>203</v>
       </c>
-      <c r="B197" t="s">
-        <v>412</v>
+      <c r="B197">
+        <v>360</v>
       </c>
       <c r="C197" t="s">
         <v>58</v>
@@ -3819,8 +3816,8 @@
       <c r="A198" t="s">
         <v>204</v>
       </c>
-      <c r="B198" t="s">
-        <v>412</v>
+      <c r="B198">
+        <v>360</v>
       </c>
       <c r="C198" t="s">
         <v>58</v>
@@ -3830,8 +3827,8 @@
       <c r="A199" t="s">
         <v>27</v>
       </c>
-      <c r="B199" t="s">
-        <v>412</v>
+      <c r="B199">
+        <v>360</v>
       </c>
       <c r="C199" t="s">
         <v>58</v>
@@ -3841,8 +3838,8 @@
       <c r="A200" t="s">
         <v>28</v>
       </c>
-      <c r="B200" t="s">
-        <v>412</v>
+      <c r="B200">
+        <v>360</v>
       </c>
       <c r="C200" t="s">
         <v>58</v>
@@ -3852,8 +3849,8 @@
       <c r="A201" t="s">
         <v>205</v>
       </c>
-      <c r="B201" t="s">
-        <v>412</v>
+      <c r="B201">
+        <v>360</v>
       </c>
       <c r="C201" t="s">
         <v>58</v>
@@ -3863,8 +3860,8 @@
       <c r="A202" t="s">
         <v>206</v>
       </c>
-      <c r="B202" t="s">
-        <v>412</v>
+      <c r="B202">
+        <v>360</v>
       </c>
       <c r="C202" t="s">
         <v>58</v>
@@ -3874,8 +3871,8 @@
       <c r="A203" t="s">
         <v>29</v>
       </c>
-      <c r="B203" t="s">
-        <v>412</v>
+      <c r="B203">
+        <v>360</v>
       </c>
       <c r="C203" t="s">
         <v>58</v>
@@ -3885,8 +3882,8 @@
       <c r="A204" t="s">
         <v>207</v>
       </c>
-      <c r="B204" t="s">
-        <v>412</v>
+      <c r="B204">
+        <v>360</v>
       </c>
       <c r="C204" t="s">
         <v>58</v>
@@ -3896,8 +3893,8 @@
       <c r="A205" t="s">
         <v>378</v>
       </c>
-      <c r="B205" t="s">
-        <v>412</v>
+      <c r="B205">
+        <v>360</v>
       </c>
       <c r="C205" t="s">
         <v>58</v>
@@ -3907,8 +3904,8 @@
       <c r="A206" t="s">
         <v>30</v>
       </c>
-      <c r="B206" t="s">
-        <v>412</v>
+      <c r="B206">
+        <v>360</v>
       </c>
       <c r="C206" t="s">
         <v>58</v>
@@ -3918,8 +3915,8 @@
       <c r="A207" t="s">
         <v>208</v>
       </c>
-      <c r="B207" t="s">
-        <v>412</v>
+      <c r="B207">
+        <v>360</v>
       </c>
       <c r="C207" t="s">
         <v>58</v>
@@ -3929,8 +3926,8 @@
       <c r="A208" t="s">
         <v>209</v>
       </c>
-      <c r="B208" t="s">
-        <v>412</v>
+      <c r="B208">
+        <v>360</v>
       </c>
       <c r="C208" t="s">
         <v>58</v>
@@ -3940,8 +3937,8 @@
       <c r="A209" t="s">
         <v>210</v>
       </c>
-      <c r="B209" t="s">
-        <v>412</v>
+      <c r="B209">
+        <v>360</v>
       </c>
       <c r="C209" t="s">
         <v>58</v>
@@ -3951,8 +3948,8 @@
       <c r="A210" t="s">
         <v>211</v>
       </c>
-      <c r="B210" t="s">
-        <v>412</v>
+      <c r="B210">
+        <v>360</v>
       </c>
       <c r="C210" t="s">
         <v>58</v>
@@ -3962,8 +3959,8 @@
       <c r="A211" t="s">
         <v>398</v>
       </c>
-      <c r="B211" t="s">
-        <v>412</v>
+      <c r="B211">
+        <v>360</v>
       </c>
       <c r="C211" t="s">
         <v>58</v>
@@ -3973,8 +3970,8 @@
       <c r="A212" t="s">
         <v>31</v>
       </c>
-      <c r="B212" t="s">
-        <v>412</v>
+      <c r="B212">
+        <v>360</v>
       </c>
       <c r="C212" t="s">
         <v>58</v>
@@ -3984,8 +3981,8 @@
       <c r="A213" t="s">
         <v>212</v>
       </c>
-      <c r="B213" t="s">
-        <v>412</v>
+      <c r="B213">
+        <v>360</v>
       </c>
       <c r="C213" t="s">
         <v>58</v>
@@ -3995,8 +3992,8 @@
       <c r="A214" t="s">
         <v>213</v>
       </c>
-      <c r="B214" t="s">
-        <v>412</v>
+      <c r="B214">
+        <v>360</v>
       </c>
       <c r="C214" t="s">
         <v>58</v>
@@ -4006,8 +4003,8 @@
       <c r="A215" t="s">
         <v>214</v>
       </c>
-      <c r="B215" t="s">
-        <v>412</v>
+      <c r="B215">
+        <v>360</v>
       </c>
       <c r="C215" t="s">
         <v>58</v>
@@ -4017,8 +4014,8 @@
       <c r="A216" t="s">
         <v>215</v>
       </c>
-      <c r="B216" t="s">
-        <v>412</v>
+      <c r="B216">
+        <v>360</v>
       </c>
       <c r="C216" t="s">
         <v>58</v>
@@ -4028,8 +4025,8 @@
       <c r="A217" t="s">
         <v>216</v>
       </c>
-      <c r="B217" t="s">
-        <v>412</v>
+      <c r="B217">
+        <v>360</v>
       </c>
       <c r="C217" t="s">
         <v>58</v>
@@ -4039,8 +4036,8 @@
       <c r="A218" t="s">
         <v>217</v>
       </c>
-      <c r="B218" t="s">
-        <v>412</v>
+      <c r="B218">
+        <v>360</v>
       </c>
       <c r="C218" t="s">
         <v>58</v>
@@ -4050,8 +4047,8 @@
       <c r="A219" t="s">
         <v>218</v>
       </c>
-      <c r="B219" t="s">
-        <v>412</v>
+      <c r="B219">
+        <v>360</v>
       </c>
       <c r="C219" t="s">
         <v>58</v>
@@ -4061,8 +4058,8 @@
       <c r="A220" t="s">
         <v>220</v>
       </c>
-      <c r="B220" t="s">
-        <v>412</v>
+      <c r="B220">
+        <v>360</v>
       </c>
       <c r="C220" t="s">
         <v>58</v>
@@ -4072,8 +4069,8 @@
       <c r="A221" t="s">
         <v>404</v>
       </c>
-      <c r="B221" t="s">
-        <v>412</v>
+      <c r="B221">
+        <v>360</v>
       </c>
       <c r="C221" t="s">
         <v>58</v>
@@ -4083,8 +4080,8 @@
       <c r="A222" t="s">
         <v>32</v>
       </c>
-      <c r="B222" t="s">
-        <v>412</v>
+      <c r="B222">
+        <v>360</v>
       </c>
       <c r="C222" t="s">
         <v>58</v>
@@ -4094,8 +4091,8 @@
       <c r="A223" t="s">
         <v>221</v>
       </c>
-      <c r="B223" t="s">
-        <v>412</v>
+      <c r="B223">
+        <v>360</v>
       </c>
       <c r="C223" t="s">
         <v>58</v>
@@ -4105,8 +4102,8 @@
       <c r="A224" t="s">
         <v>222</v>
       </c>
-      <c r="B224" t="s">
-        <v>412</v>
+      <c r="B224">
+        <v>360</v>
       </c>
       <c r="C224" t="s">
         <v>58</v>
@@ -4116,8 +4113,8 @@
       <c r="A225" t="s">
         <v>224</v>
       </c>
-      <c r="B225" t="s">
-        <v>412</v>
+      <c r="B225">
+        <v>360</v>
       </c>
       <c r="C225" t="s">
         <v>58</v>
@@ -4127,8 +4124,8 @@
       <c r="A226" t="s">
         <v>223</v>
       </c>
-      <c r="B226" t="s">
-        <v>412</v>
+      <c r="B226">
+        <v>360</v>
       </c>
       <c r="C226" t="s">
         <v>58</v>
@@ -4138,8 +4135,8 @@
       <c r="A227" t="s">
         <v>225</v>
       </c>
-      <c r="B227" t="s">
-        <v>412</v>
+      <c r="B227">
+        <v>360</v>
       </c>
       <c r="C227" t="s">
         <v>58</v>
@@ -4149,8 +4146,8 @@
       <c r="A228" t="s">
         <v>227</v>
       </c>
-      <c r="B228" t="s">
-        <v>412</v>
+      <c r="B228">
+        <v>360</v>
       </c>
       <c r="C228" t="s">
         <v>58</v>
@@ -4160,8 +4157,8 @@
       <c r="A229" t="s">
         <v>228</v>
       </c>
-      <c r="B229" t="s">
-        <v>412</v>
+      <c r="B229">
+        <v>360</v>
       </c>
       <c r="C229" t="s">
         <v>58</v>
@@ -4171,8 +4168,8 @@
       <c r="A230" t="s">
         <v>229</v>
       </c>
-      <c r="B230" t="s">
-        <v>412</v>
+      <c r="B230">
+        <v>360</v>
       </c>
       <c r="C230" t="s">
         <v>58</v>
@@ -4182,8 +4179,8 @@
       <c r="A231" t="s">
         <v>230</v>
       </c>
-      <c r="B231" t="s">
-        <v>412</v>
+      <c r="B231">
+        <v>360</v>
       </c>
       <c r="C231" t="s">
         <v>58</v>
@@ -4193,8 +4190,8 @@
       <c r="A232" t="s">
         <v>226</v>
       </c>
-      <c r="B232" t="s">
-        <v>412</v>
+      <c r="B232">
+        <v>360</v>
       </c>
       <c r="C232" t="s">
         <v>58</v>
@@ -4204,8 +4201,8 @@
       <c r="A233" t="s">
         <v>33</v>
       </c>
-      <c r="B233" t="s">
-        <v>412</v>
+      <c r="B233">
+        <v>360</v>
       </c>
       <c r="C233" t="s">
         <v>58</v>
@@ -4215,8 +4212,8 @@
       <c r="A234" t="s">
         <v>231</v>
       </c>
-      <c r="B234" t="s">
-        <v>412</v>
+      <c r="B234">
+        <v>360</v>
       </c>
       <c r="C234" t="s">
         <v>58</v>
@@ -4226,8 +4223,8 @@
       <c r="A235" t="s">
         <v>232</v>
       </c>
-      <c r="B235" t="s">
-        <v>412</v>
+      <c r="B235">
+        <v>360</v>
       </c>
       <c r="C235" t="s">
         <v>58</v>
@@ -4237,8 +4234,8 @@
       <c r="A236" t="s">
         <v>34</v>
       </c>
-      <c r="B236" t="s">
-        <v>412</v>
+      <c r="B236">
+        <v>360</v>
       </c>
       <c r="C236" t="s">
         <v>58</v>
@@ -4248,8 +4245,8 @@
       <c r="A237" t="s">
         <v>233</v>
       </c>
-      <c r="B237" t="s">
-        <v>412</v>
+      <c r="B237">
+        <v>360</v>
       </c>
       <c r="C237" t="s">
         <v>58</v>
@@ -4259,8 +4256,8 @@
       <c r="A238" t="s">
         <v>35</v>
       </c>
-      <c r="B238" t="s">
-        <v>412</v>
+      <c r="B238">
+        <v>360</v>
       </c>
       <c r="C238" t="s">
         <v>58</v>
@@ -4270,8 +4267,8 @@
       <c r="A239" t="s">
         <v>36</v>
       </c>
-      <c r="B239" t="s">
-        <v>412</v>
+      <c r="B239">
+        <v>360</v>
       </c>
       <c r="C239" t="s">
         <v>58</v>
@@ -4281,8 +4278,8 @@
       <c r="A240" t="s">
         <v>234</v>
       </c>
-      <c r="B240" t="s">
-        <v>412</v>
+      <c r="B240">
+        <v>360</v>
       </c>
       <c r="C240" t="s">
         <v>58</v>
@@ -4292,8 +4289,8 @@
       <c r="A241" t="s">
         <v>235</v>
       </c>
-      <c r="B241" t="s">
-        <v>412</v>
+      <c r="B241">
+        <v>360</v>
       </c>
       <c r="C241" t="s">
         <v>58</v>
@@ -4303,8 +4300,8 @@
       <c r="A242" t="s">
         <v>236</v>
       </c>
-      <c r="B242" t="s">
-        <v>412</v>
+      <c r="B242">
+        <v>360</v>
       </c>
       <c r="C242" t="s">
         <v>58</v>
@@ -4314,8 +4311,8 @@
       <c r="A243" t="s">
         <v>237</v>
       </c>
-      <c r="B243" t="s">
-        <v>412</v>
+      <c r="B243">
+        <v>360</v>
       </c>
       <c r="C243" t="s">
         <v>58</v>
@@ -4325,8 +4322,8 @@
       <c r="A244" t="s">
         <v>219</v>
       </c>
-      <c r="B244" t="s">
-        <v>412</v>
+      <c r="B244">
+        <v>360</v>
       </c>
       <c r="C244" t="s">
         <v>58</v>
@@ -4336,8 +4333,8 @@
       <c r="A245" t="s">
         <v>384</v>
       </c>
-      <c r="B245" t="s">
-        <v>412</v>
+      <c r="B245">
+        <v>360</v>
       </c>
       <c r="C245" t="s">
         <v>58</v>
@@ -4347,8 +4344,8 @@
       <c r="A246" t="s">
         <v>37</v>
       </c>
-      <c r="B246" t="s">
-        <v>412</v>
+      <c r="B246">
+        <v>360</v>
       </c>
       <c r="C246" t="s">
         <v>58</v>
@@ -4358,8 +4355,8 @@
       <c r="A247" t="s">
         <v>238</v>
       </c>
-      <c r="B247" t="s">
-        <v>412</v>
+      <c r="B247">
+        <v>360</v>
       </c>
       <c r="C247" t="s">
         <v>58</v>
@@ -4369,8 +4366,8 @@
       <c r="A248" t="s">
         <v>239</v>
       </c>
-      <c r="B248" t="s">
-        <v>412</v>
+      <c r="B248">
+        <v>360</v>
       </c>
       <c r="C248" t="s">
         <v>58</v>
@@ -4380,8 +4377,8 @@
       <c r="A249" t="s">
         <v>240</v>
       </c>
-      <c r="B249" t="s">
-        <v>412</v>
+      <c r="B249">
+        <v>360</v>
       </c>
       <c r="C249" t="s">
         <v>58</v>
@@ -4391,8 +4388,8 @@
       <c r="A250" t="s">
         <v>241</v>
       </c>
-      <c r="B250" t="s">
-        <v>412</v>
+      <c r="B250">
+        <v>360</v>
       </c>
       <c r="C250" t="s">
         <v>58</v>
@@ -4402,8 +4399,8 @@
       <c r="A251" t="s">
         <v>401</v>
       </c>
-      <c r="B251" t="s">
-        <v>412</v>
+      <c r="B251">
+        <v>360</v>
       </c>
       <c r="C251" t="s">
         <v>58</v>
@@ -4413,8 +4410,8 @@
       <c r="A252" t="s">
         <v>38</v>
       </c>
-      <c r="B252" t="s">
-        <v>412</v>
+      <c r="B252">
+        <v>360</v>
       </c>
       <c r="C252" t="s">
         <v>58</v>
@@ -4424,8 +4421,8 @@
       <c r="A253" t="s">
         <v>242</v>
       </c>
-      <c r="B253" t="s">
-        <v>412</v>
+      <c r="B253">
+        <v>360</v>
       </c>
       <c r="C253" t="s">
         <v>58</v>
@@ -4435,8 +4432,8 @@
       <c r="A254" t="s">
         <v>244</v>
       </c>
-      <c r="B254" t="s">
-        <v>412</v>
+      <c r="B254">
+        <v>360</v>
       </c>
       <c r="C254" t="s">
         <v>58</v>
@@ -4446,8 +4443,8 @@
       <c r="A255" t="s">
         <v>243</v>
       </c>
-      <c r="B255" t="s">
-        <v>412</v>
+      <c r="B255">
+        <v>360</v>
       </c>
       <c r="C255" t="s">
         <v>58</v>
@@ -4457,8 +4454,8 @@
       <c r="A256" t="s">
         <v>39</v>
       </c>
-      <c r="B256" t="s">
-        <v>412</v>
+      <c r="B256">
+        <v>360</v>
       </c>
       <c r="C256" t="s">
         <v>58</v>
@@ -4468,8 +4465,8 @@
       <c r="A257" t="s">
         <v>245</v>
       </c>
-      <c r="B257" t="s">
-        <v>412</v>
+      <c r="B257">
+        <v>360</v>
       </c>
       <c r="C257" t="s">
         <v>58</v>
@@ -4479,8 +4476,8 @@
       <c r="A258" t="s">
         <v>246</v>
       </c>
-      <c r="B258" t="s">
-        <v>412</v>
+      <c r="B258">
+        <v>360</v>
       </c>
       <c r="C258" t="s">
         <v>58</v>
@@ -4490,8 +4487,8 @@
       <c r="A259" t="s">
         <v>411</v>
       </c>
-      <c r="B259" t="s">
-        <v>412</v>
+      <c r="B259">
+        <v>360</v>
       </c>
       <c r="C259" t="s">
         <v>58</v>
@@ -4501,8 +4498,8 @@
       <c r="A260" t="s">
         <v>40</v>
       </c>
-      <c r="B260" t="s">
-        <v>412</v>
+      <c r="B260">
+        <v>360</v>
       </c>
       <c r="C260" t="s">
         <v>58</v>
@@ -4512,8 +4509,8 @@
       <c r="A261" t="s">
         <v>247</v>
       </c>
-      <c r="B261" t="s">
-        <v>412</v>
+      <c r="B261">
+        <v>360</v>
       </c>
       <c r="C261" t="s">
         <v>58</v>
@@ -4523,8 +4520,8 @@
       <c r="A262" t="s">
         <v>41</v>
       </c>
-      <c r="B262" t="s">
-        <v>412</v>
+      <c r="B262">
+        <v>360</v>
       </c>
       <c r="C262" t="s">
         <v>58</v>
@@ -4534,8 +4531,8 @@
       <c r="A263" t="s">
         <v>248</v>
       </c>
-      <c r="B263" t="s">
-        <v>412</v>
+      <c r="B263">
+        <v>360</v>
       </c>
       <c r="C263" t="s">
         <v>58</v>
@@ -4545,8 +4542,8 @@
       <c r="A264" t="s">
         <v>249</v>
       </c>
-      <c r="B264" t="s">
-        <v>412</v>
+      <c r="B264">
+        <v>360</v>
       </c>
       <c r="C264" t="s">
         <v>58</v>
@@ -4556,8 +4553,8 @@
       <c r="A265" t="s">
         <v>250</v>
       </c>
-      <c r="B265" t="s">
-        <v>412</v>
+      <c r="B265">
+        <v>360</v>
       </c>
       <c r="C265" t="s">
         <v>58</v>
@@ -4567,8 +4564,8 @@
       <c r="A266" t="s">
         <v>251</v>
       </c>
-      <c r="B266" t="s">
-        <v>412</v>
+      <c r="B266">
+        <v>360</v>
       </c>
       <c r="C266" t="s">
         <v>58</v>
@@ -4578,8 +4575,8 @@
       <c r="A267" t="s">
         <v>252</v>
       </c>
-      <c r="B267" t="s">
-        <v>412</v>
+      <c r="B267">
+        <v>360</v>
       </c>
       <c r="C267" t="s">
         <v>58</v>
@@ -4589,8 +4586,8 @@
       <c r="A268" t="s">
         <v>42</v>
       </c>
-      <c r="B268" t="s">
-        <v>412</v>
+      <c r="B268">
+        <v>360</v>
       </c>
       <c r="C268" t="s">
         <v>58</v>
@@ -4600,8 +4597,8 @@
       <c r="A269" t="s">
         <v>253</v>
       </c>
-      <c r="B269" t="s">
-        <v>412</v>
+      <c r="B269">
+        <v>360</v>
       </c>
       <c r="C269" t="s">
         <v>58</v>
@@ -4611,8 +4608,8 @@
       <c r="A270" t="s">
         <v>254</v>
       </c>
-      <c r="B270" t="s">
-        <v>412</v>
+      <c r="B270">
+        <v>360</v>
       </c>
       <c r="C270" t="s">
         <v>58</v>
@@ -4622,8 +4619,8 @@
       <c r="A271" t="s">
         <v>406</v>
       </c>
-      <c r="B271" t="s">
-        <v>412</v>
+      <c r="B271">
+        <v>360</v>
       </c>
       <c r="C271" t="s">
         <v>58</v>
@@ -4633,8 +4630,8 @@
       <c r="A272" t="s">
         <v>255</v>
       </c>
-      <c r="B272" t="s">
-        <v>412</v>
+      <c r="B272">
+        <v>360</v>
       </c>
       <c r="C272" t="s">
         <v>58</v>
@@ -4644,8 +4641,8 @@
       <c r="A273" t="s">
         <v>256</v>
       </c>
-      <c r="B273" t="s">
-        <v>412</v>
+      <c r="B273">
+        <v>360</v>
       </c>
       <c r="C273" t="s">
         <v>58</v>
@@ -4655,8 +4652,8 @@
       <c r="A274" t="s">
         <v>257</v>
       </c>
-      <c r="B274" t="s">
-        <v>412</v>
+      <c r="B274">
+        <v>360</v>
       </c>
       <c r="C274" t="s">
         <v>58</v>
@@ -4666,8 +4663,8 @@
       <c r="A275" t="s">
         <v>258</v>
       </c>
-      <c r="B275" t="s">
-        <v>412</v>
+      <c r="B275">
+        <v>360</v>
       </c>
       <c r="C275" t="s">
         <v>58</v>
@@ -4677,8 +4674,8 @@
       <c r="A276" t="s">
         <v>259</v>
       </c>
-      <c r="B276" t="s">
-        <v>412</v>
+      <c r="B276">
+        <v>360</v>
       </c>
       <c r="C276" t="s">
         <v>58</v>
@@ -4688,8 +4685,8 @@
       <c r="A277" t="s">
         <v>260</v>
       </c>
-      <c r="B277" t="s">
-        <v>412</v>
+      <c r="B277">
+        <v>360</v>
       </c>
       <c r="C277" t="s">
         <v>58</v>
@@ -4699,8 +4696,8 @@
       <c r="A278" t="s">
         <v>261</v>
       </c>
-      <c r="B278" t="s">
-        <v>412</v>
+      <c r="B278">
+        <v>360</v>
       </c>
       <c r="C278" t="s">
         <v>58</v>
@@ -4710,8 +4707,8 @@
       <c r="A279" t="s">
         <v>43</v>
       </c>
-      <c r="B279" t="s">
-        <v>412</v>
+      <c r="B279">
+        <v>360</v>
       </c>
       <c r="C279" t="s">
         <v>58</v>
@@ -4721,8 +4718,8 @@
       <c r="A280" t="s">
         <v>262</v>
       </c>
-      <c r="B280" t="s">
-        <v>412</v>
+      <c r="B280">
+        <v>360</v>
       </c>
       <c r="C280" t="s">
         <v>58</v>
@@ -4732,8 +4729,8 @@
       <c r="A281" t="s">
         <v>263</v>
       </c>
-      <c r="B281" t="s">
-        <v>412</v>
+      <c r="B281">
+        <v>360</v>
       </c>
       <c r="C281" t="s">
         <v>58</v>
@@ -4743,8 +4740,8 @@
       <c r="A282" t="s">
         <v>264</v>
       </c>
-      <c r="B282" t="s">
-        <v>412</v>
+      <c r="B282">
+        <v>360</v>
       </c>
       <c r="C282" t="s">
         <v>58</v>
@@ -4754,8 +4751,8 @@
       <c r="A283" t="s">
         <v>265</v>
       </c>
-      <c r="B283" t="s">
-        <v>412</v>
+      <c r="B283">
+        <v>360</v>
       </c>
       <c r="C283" t="s">
         <v>58</v>
@@ -4765,8 +4762,8 @@
       <c r="A284" t="s">
         <v>266</v>
       </c>
-      <c r="B284" t="s">
-        <v>412</v>
+      <c r="B284">
+        <v>360</v>
       </c>
       <c r="C284" t="s">
         <v>58</v>
@@ -4776,8 +4773,8 @@
       <c r="A285" t="s">
         <v>267</v>
       </c>
-      <c r="B285" t="s">
-        <v>412</v>
+      <c r="B285">
+        <v>360</v>
       </c>
       <c r="C285" t="s">
         <v>58</v>
@@ -4787,8 +4784,8 @@
       <c r="A286" t="s">
         <v>379</v>
       </c>
-      <c r="B286" t="s">
-        <v>412</v>
+      <c r="B286">
+        <v>360</v>
       </c>
       <c r="C286" t="s">
         <v>58</v>
@@ -4798,8 +4795,8 @@
       <c r="A287" t="s">
         <v>268</v>
       </c>
-      <c r="B287" t="s">
-        <v>412</v>
+      <c r="B287">
+        <v>360</v>
       </c>
       <c r="C287" t="s">
         <v>58</v>
@@ -4809,8 +4806,8 @@
       <c r="A288" t="s">
         <v>44</v>
       </c>
-      <c r="B288" t="s">
-        <v>412</v>
+      <c r="B288">
+        <v>360</v>
       </c>
       <c r="C288" t="s">
         <v>58</v>
@@ -4820,8 +4817,8 @@
       <c r="A289" t="s">
         <v>269</v>
       </c>
-      <c r="B289" t="s">
-        <v>412</v>
+      <c r="B289">
+        <v>360</v>
       </c>
       <c r="C289" t="s">
         <v>58</v>
@@ -4831,8 +4828,8 @@
       <c r="A290" t="s">
         <v>270</v>
       </c>
-      <c r="B290" t="s">
-        <v>412</v>
+      <c r="B290">
+        <v>360</v>
       </c>
       <c r="C290" t="s">
         <v>58</v>
@@ -4842,8 +4839,8 @@
       <c r="A291" t="s">
         <v>271</v>
       </c>
-      <c r="B291" t="s">
-        <v>412</v>
+      <c r="B291">
+        <v>360</v>
       </c>
       <c r="C291" t="s">
         <v>58</v>
@@ -4853,8 +4850,8 @@
       <c r="A292" t="s">
         <v>272</v>
       </c>
-      <c r="B292" t="s">
-        <v>412</v>
+      <c r="B292">
+        <v>360</v>
       </c>
       <c r="C292" t="s">
         <v>58</v>
@@ -4864,8 +4861,8 @@
       <c r="A293" t="s">
         <v>273</v>
       </c>
-      <c r="B293" t="s">
-        <v>412</v>
+      <c r="B293">
+        <v>360</v>
       </c>
       <c r="C293" t="s">
         <v>58</v>
@@ -4875,8 +4872,8 @@
       <c r="A294" t="s">
         <v>274</v>
       </c>
-      <c r="B294" t="s">
-        <v>412</v>
+      <c r="B294">
+        <v>360</v>
       </c>
       <c r="C294" t="s">
         <v>58</v>
@@ -4886,8 +4883,8 @@
       <c r="A295" t="s">
         <v>275</v>
       </c>
-      <c r="B295" t="s">
-        <v>412</v>
+      <c r="B295">
+        <v>360</v>
       </c>
       <c r="C295" t="s">
         <v>58</v>
@@ -4897,8 +4894,8 @@
       <c r="A296" t="s">
         <v>276</v>
       </c>
-      <c r="B296" t="s">
-        <v>412</v>
+      <c r="B296">
+        <v>360</v>
       </c>
       <c r="C296" t="s">
         <v>58</v>
@@ -4908,8 +4905,8 @@
       <c r="A297" t="s">
         <v>277</v>
       </c>
-      <c r="B297" t="s">
-        <v>412</v>
+      <c r="B297">
+        <v>360</v>
       </c>
       <c r="C297" t="s">
         <v>58</v>
@@ -4919,8 +4916,8 @@
       <c r="A298" t="s">
         <v>278</v>
       </c>
-      <c r="B298" t="s">
-        <v>412</v>
+      <c r="B298">
+        <v>360</v>
       </c>
       <c r="C298" t="s">
         <v>58</v>
@@ -4930,8 +4927,8 @@
       <c r="A299" t="s">
         <v>380</v>
       </c>
-      <c r="B299" t="s">
-        <v>412</v>
+      <c r="B299">
+        <v>360</v>
       </c>
       <c r="C299" t="s">
         <v>58</v>
@@ -4941,8 +4938,8 @@
       <c r="A300" t="s">
         <v>279</v>
       </c>
-      <c r="B300" t="s">
-        <v>412</v>
+      <c r="B300">
+        <v>360</v>
       </c>
       <c r="C300" t="s">
         <v>58</v>
@@ -4952,8 +4949,8 @@
       <c r="A301" t="s">
         <v>280</v>
       </c>
-      <c r="B301" t="s">
-        <v>412</v>
+      <c r="B301">
+        <v>360</v>
       </c>
       <c r="C301" t="s">
         <v>58</v>
@@ -4963,8 +4960,8 @@
       <c r="A302" t="s">
         <v>281</v>
       </c>
-      <c r="B302" t="s">
-        <v>412</v>
+      <c r="B302">
+        <v>360</v>
       </c>
       <c r="C302" t="s">
         <v>58</v>
@@ -4974,8 +4971,8 @@
       <c r="A303" t="s">
         <v>45</v>
       </c>
-      <c r="B303" t="s">
-        <v>412</v>
+      <c r="B303">
+        <v>360</v>
       </c>
       <c r="C303" t="s">
         <v>58</v>
@@ -4985,8 +4982,8 @@
       <c r="A304" t="s">
         <v>282</v>
       </c>
-      <c r="B304" t="s">
-        <v>412</v>
+      <c r="B304">
+        <v>360</v>
       </c>
       <c r="C304" t="s">
         <v>58</v>
@@ -4996,8 +4993,8 @@
       <c r="A305" t="s">
         <v>284</v>
       </c>
-      <c r="B305" t="s">
-        <v>412</v>
+      <c r="B305">
+        <v>360</v>
       </c>
       <c r="C305" t="s">
         <v>58</v>
@@ -5007,8 +5004,8 @@
       <c r="A306" t="s">
         <v>285</v>
       </c>
-      <c r="B306" t="s">
-        <v>412</v>
+      <c r="B306">
+        <v>360</v>
       </c>
       <c r="C306" t="s">
         <v>58</v>
@@ -5018,8 +5015,8 @@
       <c r="A307" t="s">
         <v>286</v>
       </c>
-      <c r="B307" t="s">
-        <v>412</v>
+      <c r="B307">
+        <v>360</v>
       </c>
       <c r="C307" t="s">
         <v>58</v>
@@ -5029,8 +5026,8 @@
       <c r="A308" t="s">
         <v>287</v>
       </c>
-      <c r="B308" t="s">
-        <v>412</v>
+      <c r="B308">
+        <v>360</v>
       </c>
       <c r="C308" t="s">
         <v>58</v>
@@ -5040,8 +5037,8 @@
       <c r="A309" t="s">
         <v>290</v>
       </c>
-      <c r="B309" t="s">
-        <v>412</v>
+      <c r="B309">
+        <v>360</v>
       </c>
       <c r="C309" t="s">
         <v>58</v>
@@ -5051,8 +5048,8 @@
       <c r="A310" t="s">
         <v>289</v>
       </c>
-      <c r="B310" t="s">
-        <v>412</v>
+      <c r="B310">
+        <v>360</v>
       </c>
       <c r="C310" t="s">
         <v>58</v>
@@ -5062,8 +5059,8 @@
       <c r="A311" t="s">
         <v>288</v>
       </c>
-      <c r="B311" t="s">
-        <v>412</v>
+      <c r="B311">
+        <v>360</v>
       </c>
       <c r="C311" t="s">
         <v>58</v>
@@ -5073,8 +5070,8 @@
       <c r="A312" t="s">
         <v>291</v>
       </c>
-      <c r="B312" t="s">
-        <v>412</v>
+      <c r="B312">
+        <v>360</v>
       </c>
       <c r="C312" t="s">
         <v>58</v>
@@ -5084,8 +5081,8 @@
       <c r="A313" t="s">
         <v>292</v>
       </c>
-      <c r="B313" t="s">
-        <v>412</v>
+      <c r="B313">
+        <v>360</v>
       </c>
       <c r="C313" t="s">
         <v>58</v>
@@ -5095,8 +5092,8 @@
       <c r="A314" t="s">
         <v>46</v>
       </c>
-      <c r="B314" t="s">
-        <v>412</v>
+      <c r="B314">
+        <v>360</v>
       </c>
       <c r="C314" t="s">
         <v>58</v>
@@ -5106,8 +5103,8 @@
       <c r="A315" t="s">
         <v>293</v>
       </c>
-      <c r="B315" t="s">
-        <v>412</v>
+      <c r="B315">
+        <v>360</v>
       </c>
       <c r="C315" t="s">
         <v>58</v>
@@ -5117,8 +5114,8 @@
       <c r="A316" t="s">
         <v>294</v>
       </c>
-      <c r="B316" t="s">
-        <v>412</v>
+      <c r="B316">
+        <v>360</v>
       </c>
       <c r="C316" t="s">
         <v>58</v>
@@ -5128,8 +5125,8 @@
       <c r="A317" t="s">
         <v>295</v>
       </c>
-      <c r="B317" t="s">
-        <v>412</v>
+      <c r="B317">
+        <v>360</v>
       </c>
       <c r="C317" t="s">
         <v>58</v>
@@ -5139,8 +5136,8 @@
       <c r="A318" t="s">
         <v>296</v>
       </c>
-      <c r="B318" t="s">
-        <v>412</v>
+      <c r="B318">
+        <v>360</v>
       </c>
       <c r="C318" t="s">
         <v>58</v>
@@ -5150,8 +5147,8 @@
       <c r="A319" t="s">
         <v>47</v>
       </c>
-      <c r="B319" t="s">
-        <v>412</v>
+      <c r="B319">
+        <v>360</v>
       </c>
       <c r="C319" t="s">
         <v>58</v>
@@ -5161,8 +5158,8 @@
       <c r="A320" t="s">
         <v>297</v>
       </c>
-      <c r="B320" t="s">
-        <v>412</v>
+      <c r="B320">
+        <v>360</v>
       </c>
       <c r="C320" t="s">
         <v>58</v>
@@ -5172,8 +5169,8 @@
       <c r="A321" t="s">
         <v>48</v>
       </c>
-      <c r="B321" t="s">
-        <v>412</v>
+      <c r="B321">
+        <v>360</v>
       </c>
       <c r="C321" t="s">
         <v>58</v>
@@ -5183,8 +5180,8 @@
       <c r="A322" t="s">
         <v>298</v>
       </c>
-      <c r="B322" t="s">
-        <v>412</v>
+      <c r="B322">
+        <v>360</v>
       </c>
       <c r="C322" t="s">
         <v>58</v>
@@ -5194,8 +5191,8 @@
       <c r="A323" t="s">
         <v>299</v>
       </c>
-      <c r="B323" t="s">
-        <v>412</v>
+      <c r="B323">
+        <v>360</v>
       </c>
       <c r="C323" t="s">
         <v>58</v>
@@ -5205,8 +5202,8 @@
       <c r="A324" t="s">
         <v>300</v>
       </c>
-      <c r="B324" t="s">
-        <v>412</v>
+      <c r="B324">
+        <v>360</v>
       </c>
       <c r="C324" t="s">
         <v>58</v>
@@ -5216,8 +5213,8 @@
       <c r="A325" t="s">
         <v>301</v>
       </c>
-      <c r="B325" t="s">
-        <v>412</v>
+      <c r="B325">
+        <v>360</v>
       </c>
       <c r="C325" t="s">
         <v>58</v>
@@ -5227,8 +5224,8 @@
       <c r="A326" t="s">
         <v>302</v>
       </c>
-      <c r="B326" t="s">
-        <v>412</v>
+      <c r="B326">
+        <v>360</v>
       </c>
       <c r="C326" t="s">
         <v>58</v>
@@ -5238,8 +5235,8 @@
       <c r="A327" t="s">
         <v>303</v>
       </c>
-      <c r="B327" t="s">
-        <v>412</v>
+      <c r="B327">
+        <v>360</v>
       </c>
       <c r="C327" t="s">
         <v>58</v>
@@ -5249,8 +5246,8 @@
       <c r="A328" t="s">
         <v>49</v>
       </c>
-      <c r="B328" t="s">
-        <v>412</v>
+      <c r="B328">
+        <v>360</v>
       </c>
       <c r="C328" t="s">
         <v>58</v>
@@ -5260,8 +5257,8 @@
       <c r="A329" t="s">
         <v>304</v>
       </c>
-      <c r="B329" t="s">
-        <v>412</v>
+      <c r="B329">
+        <v>360</v>
       </c>
       <c r="C329" t="s">
         <v>58</v>
@@ -5271,8 +5268,8 @@
       <c r="A330" t="s">
         <v>305</v>
       </c>
-      <c r="B330" t="s">
-        <v>412</v>
+      <c r="B330">
+        <v>360</v>
       </c>
       <c r="C330" t="s">
         <v>58</v>
@@ -5282,8 +5279,8 @@
       <c r="A331" t="s">
         <v>306</v>
       </c>
-      <c r="B331" t="s">
-        <v>412</v>
+      <c r="B331">
+        <v>360</v>
       </c>
       <c r="C331" t="s">
         <v>58</v>
@@ -5293,8 +5290,8 @@
       <c r="A332" t="s">
         <v>307</v>
       </c>
-      <c r="B332" t="s">
-        <v>412</v>
+      <c r="B332">
+        <v>360</v>
       </c>
       <c r="C332" t="s">
         <v>58</v>
@@ -5304,8 +5301,8 @@
       <c r="A333" t="s">
         <v>309</v>
       </c>
-      <c r="B333" t="s">
-        <v>412</v>
+      <c r="B333">
+        <v>360</v>
       </c>
       <c r="C333" t="s">
         <v>58</v>
@@ -5315,8 +5312,8 @@
       <c r="A334" t="s">
         <v>308</v>
       </c>
-      <c r="B334" t="s">
-        <v>412</v>
+      <c r="B334">
+        <v>360</v>
       </c>
       <c r="C334" t="s">
         <v>58</v>
@@ -5326,8 +5323,8 @@
       <c r="A335" t="s">
         <v>310</v>
       </c>
-      <c r="B335" t="s">
-        <v>412</v>
+      <c r="B335">
+        <v>360</v>
       </c>
       <c r="C335" t="s">
         <v>58</v>
@@ -5337,8 +5334,8 @@
       <c r="A336" t="s">
         <v>311</v>
       </c>
-      <c r="B336" t="s">
-        <v>412</v>
+      <c r="B336">
+        <v>360</v>
       </c>
       <c r="C336" t="s">
         <v>58</v>
@@ -5348,8 +5345,8 @@
       <c r="A337" t="s">
         <v>312</v>
       </c>
-      <c r="B337" t="s">
-        <v>412</v>
+      <c r="B337">
+        <v>360</v>
       </c>
       <c r="C337" t="s">
         <v>58</v>
@@ -5359,8 +5356,8 @@
       <c r="A338" t="s">
         <v>313</v>
       </c>
-      <c r="B338" t="s">
-        <v>412</v>
+      <c r="B338">
+        <v>360</v>
       </c>
       <c r="C338" t="s">
         <v>58</v>
@@ -5370,8 +5367,8 @@
       <c r="A339" t="s">
         <v>314</v>
       </c>
-      <c r="B339" t="s">
-        <v>412</v>
+      <c r="B339">
+        <v>360</v>
       </c>
       <c r="C339" t="s">
         <v>58</v>
@@ -5381,8 +5378,8 @@
       <c r="A340" t="s">
         <v>283</v>
       </c>
-      <c r="B340" t="s">
-        <v>412</v>
+      <c r="B340">
+        <v>360</v>
       </c>
       <c r="C340" t="s">
         <v>58</v>
@@ -5392,8 +5389,8 @@
       <c r="A341" t="s">
         <v>315</v>
       </c>
-      <c r="B341" t="s">
-        <v>412</v>
+      <c r="B341">
+        <v>360</v>
       </c>
       <c r="C341" t="s">
         <v>58</v>
@@ -5403,8 +5400,8 @@
       <c r="A342" t="s">
         <v>316</v>
       </c>
-      <c r="B342" t="s">
-        <v>412</v>
+      <c r="B342">
+        <v>360</v>
       </c>
       <c r="C342" t="s">
         <v>58</v>
@@ -5414,8 +5411,8 @@
       <c r="A343" t="s">
         <v>317</v>
       </c>
-      <c r="B343" t="s">
-        <v>412</v>
+      <c r="B343">
+        <v>360</v>
       </c>
       <c r="C343" t="s">
         <v>58</v>
@@ -5425,8 +5422,8 @@
       <c r="A344" t="s">
         <v>320</v>
       </c>
-      <c r="B344" t="s">
-        <v>412</v>
+      <c r="B344">
+        <v>360</v>
       </c>
       <c r="C344" t="s">
         <v>58</v>
@@ -5436,8 +5433,8 @@
       <c r="A345" t="s">
         <v>381</v>
       </c>
-      <c r="B345" t="s">
-        <v>412</v>
+      <c r="B345">
+        <v>360</v>
       </c>
       <c r="C345" t="s">
         <v>58</v>
@@ -5447,8 +5444,8 @@
       <c r="A346" t="s">
         <v>321</v>
       </c>
-      <c r="B346" t="s">
-        <v>412</v>
+      <c r="B346">
+        <v>360</v>
       </c>
       <c r="C346" t="s">
         <v>58</v>
@@ -5458,8 +5455,8 @@
       <c r="A347" t="s">
         <v>319</v>
       </c>
-      <c r="B347" t="s">
-        <v>412</v>
+      <c r="B347">
+        <v>360</v>
       </c>
       <c r="C347" t="s">
         <v>58</v>
@@ -5469,8 +5466,8 @@
       <c r="A348" t="s">
         <v>323</v>
       </c>
-      <c r="B348" t="s">
-        <v>412</v>
+      <c r="B348">
+        <v>360</v>
       </c>
       <c r="C348" t="s">
         <v>58</v>
@@ -5480,8 +5477,8 @@
       <c r="A349" t="s">
         <v>322</v>
       </c>
-      <c r="B349" t="s">
-        <v>412</v>
+      <c r="B349">
+        <v>360</v>
       </c>
       <c r="C349" t="s">
         <v>58</v>
@@ -5491,8 +5488,8 @@
       <c r="A350" t="s">
         <v>324</v>
       </c>
-      <c r="B350" t="s">
-        <v>412</v>
+      <c r="B350">
+        <v>360</v>
       </c>
       <c r="C350" t="s">
         <v>58</v>
@@ -5502,8 +5499,8 @@
       <c r="A351" t="s">
         <v>325</v>
       </c>
-      <c r="B351" t="s">
-        <v>412</v>
+      <c r="B351">
+        <v>360</v>
       </c>
       <c r="C351" t="s">
         <v>58</v>
@@ -5513,8 +5510,8 @@
       <c r="A352" t="s">
         <v>326</v>
       </c>
-      <c r="B352" t="s">
-        <v>412</v>
+      <c r="B352">
+        <v>360</v>
       </c>
       <c r="C352" t="s">
         <v>58</v>
@@ -5524,8 +5521,8 @@
       <c r="A353" t="s">
         <v>50</v>
       </c>
-      <c r="B353" t="s">
-        <v>412</v>
+      <c r="B353">
+        <v>360</v>
       </c>
       <c r="C353" t="s">
         <v>58</v>
@@ -5535,8 +5532,8 @@
       <c r="A354" t="s">
         <v>51</v>
       </c>
-      <c r="B354" t="s">
-        <v>412</v>
+      <c r="B354">
+        <v>360</v>
       </c>
       <c r="C354" t="s">
         <v>58</v>
@@ -5546,8 +5543,8 @@
       <c r="A355" t="s">
         <v>327</v>
       </c>
-      <c r="B355" t="s">
-        <v>412</v>
+      <c r="B355">
+        <v>360</v>
       </c>
       <c r="C355" t="s">
         <v>58</v>
@@ -5557,8 +5554,8 @@
       <c r="A356" t="s">
         <v>328</v>
       </c>
-      <c r="B356" t="s">
-        <v>412</v>
+      <c r="B356">
+        <v>360</v>
       </c>
       <c r="C356" t="s">
         <v>58</v>
@@ -5568,8 +5565,8 @@
       <c r="A357" t="s">
         <v>329</v>
       </c>
-      <c r="B357" t="s">
-        <v>412</v>
+      <c r="B357">
+        <v>360</v>
       </c>
       <c r="C357" t="s">
         <v>58</v>
@@ -5579,8 +5576,8 @@
       <c r="A358" t="s">
         <v>318</v>
       </c>
-      <c r="B358" t="s">
-        <v>412</v>
+      <c r="B358">
+        <v>360</v>
       </c>
       <c r="C358" t="s">
         <v>58</v>
@@ -5590,8 +5587,8 @@
       <c r="A359" t="s">
         <v>330</v>
       </c>
-      <c r="B359" t="s">
-        <v>412</v>
+      <c r="B359">
+        <v>360</v>
       </c>
       <c r="C359" t="s">
         <v>58</v>
@@ -5601,8 +5598,8 @@
       <c r="A360" t="s">
         <v>331</v>
       </c>
-      <c r="B360" t="s">
-        <v>412</v>
+      <c r="B360">
+        <v>360</v>
       </c>
       <c r="C360" t="s">
         <v>58</v>
@@ -5612,8 +5609,8 @@
       <c r="A361" t="s">
         <v>332</v>
       </c>
-      <c r="B361" t="s">
-        <v>412</v>
+      <c r="B361">
+        <v>360</v>
       </c>
       <c r="C361" t="s">
         <v>58</v>
@@ -5623,8 +5620,8 @@
       <c r="A362" t="s">
         <v>333</v>
       </c>
-      <c r="B362" t="s">
-        <v>412</v>
+      <c r="B362">
+        <v>360</v>
       </c>
       <c r="C362" t="s">
         <v>58</v>
@@ -5634,8 +5631,8 @@
       <c r="A363" t="s">
         <v>334</v>
       </c>
-      <c r="B363" t="s">
-        <v>412</v>
+      <c r="B363">
+        <v>360</v>
       </c>
       <c r="C363" t="s">
         <v>58</v>
@@ -5645,8 +5642,8 @@
       <c r="A364" t="s">
         <v>335</v>
       </c>
-      <c r="B364" t="s">
-        <v>412</v>
+      <c r="B364">
+        <v>360</v>
       </c>
       <c r="C364" t="s">
         <v>58</v>
@@ -5656,8 +5653,8 @@
       <c r="A365" t="s">
         <v>336</v>
       </c>
-      <c r="B365" t="s">
-        <v>412</v>
+      <c r="B365">
+        <v>360</v>
       </c>
       <c r="C365" t="s">
         <v>58</v>
@@ -5667,8 +5664,8 @@
       <c r="A366" t="s">
         <v>337</v>
       </c>
-      <c r="B366" t="s">
-        <v>412</v>
+      <c r="B366">
+        <v>360</v>
       </c>
       <c r="C366" t="s">
         <v>58</v>
@@ -5678,8 +5675,8 @@
       <c r="A367" t="s">
         <v>338</v>
       </c>
-      <c r="B367" t="s">
-        <v>412</v>
+      <c r="B367">
+        <v>360</v>
       </c>
       <c r="C367" t="s">
         <v>58</v>
@@ -5689,8 +5686,8 @@
       <c r="A368" t="s">
         <v>339</v>
       </c>
-      <c r="B368" t="s">
-        <v>412</v>
+      <c r="B368">
+        <v>360</v>
       </c>
       <c r="C368" t="s">
         <v>58</v>
@@ -5700,8 +5697,8 @@
       <c r="A369" t="s">
         <v>340</v>
       </c>
-      <c r="B369" t="s">
-        <v>412</v>
+      <c r="B369">
+        <v>360</v>
       </c>
       <c r="C369" t="s">
         <v>58</v>
@@ -5711,8 +5708,8 @@
       <c r="A370" t="s">
         <v>341</v>
       </c>
-      <c r="B370" t="s">
-        <v>412</v>
+      <c r="B370">
+        <v>360</v>
       </c>
       <c r="C370" t="s">
         <v>58</v>
@@ -5722,8 +5719,8 @@
       <c r="A371" t="s">
         <v>343</v>
       </c>
-      <c r="B371" t="s">
-        <v>412</v>
+      <c r="B371">
+        <v>360</v>
       </c>
       <c r="C371" t="s">
         <v>58</v>
@@ -5733,8 +5730,8 @@
       <c r="A372" t="s">
         <v>342</v>
       </c>
-      <c r="B372" t="s">
-        <v>412</v>
+      <c r="B372">
+        <v>360</v>
       </c>
       <c r="C372" t="s">
         <v>58</v>
@@ -5744,8 +5741,8 @@
       <c r="A373" t="s">
         <v>344</v>
       </c>
-      <c r="B373" t="s">
-        <v>412</v>
+      <c r="B373">
+        <v>360</v>
       </c>
       <c r="C373" t="s">
         <v>58</v>
@@ -5755,8 +5752,8 @@
       <c r="A374" t="s">
         <v>345</v>
       </c>
-      <c r="B374" t="s">
-        <v>412</v>
+      <c r="B374">
+        <v>360</v>
       </c>
       <c r="C374" t="s">
         <v>58</v>
@@ -5766,8 +5763,8 @@
       <c r="A375" t="s">
         <v>346</v>
       </c>
-      <c r="B375" t="s">
-        <v>412</v>
+      <c r="B375">
+        <v>360</v>
       </c>
       <c r="C375" t="s">
         <v>58</v>
@@ -5777,8 +5774,8 @@
       <c r="A376" t="s">
         <v>347</v>
       </c>
-      <c r="B376" t="s">
-        <v>412</v>
+      <c r="B376">
+        <v>360</v>
       </c>
       <c r="C376" t="s">
         <v>58</v>
@@ -5788,8 +5785,8 @@
       <c r="A377" t="s">
         <v>348</v>
       </c>
-      <c r="B377" t="s">
-        <v>412</v>
+      <c r="B377">
+        <v>360</v>
       </c>
       <c r="C377" t="s">
         <v>58</v>
@@ -5799,8 +5796,8 @@
       <c r="A378" t="s">
         <v>350</v>
       </c>
-      <c r="B378" t="s">
-        <v>412</v>
+      <c r="B378">
+        <v>360</v>
       </c>
       <c r="C378" t="s">
         <v>58</v>
@@ -5810,8 +5807,8 @@
       <c r="A379" t="s">
         <v>383</v>
       </c>
-      <c r="B379" t="s">
-        <v>412</v>
+      <c r="B379">
+        <v>360</v>
       </c>
       <c r="C379" t="s">
         <v>58</v>
@@ -5821,8 +5818,8 @@
       <c r="A380" t="s">
         <v>382</v>
       </c>
-      <c r="B380" t="s">
-        <v>412</v>
+      <c r="B380">
+        <v>360</v>
       </c>
       <c r="C380" t="s">
         <v>58</v>
@@ -5832,8 +5829,8 @@
       <c r="A381" t="s">
         <v>351</v>
       </c>
-      <c r="B381" t="s">
-        <v>412</v>
+      <c r="B381">
+        <v>360</v>
       </c>
       <c r="C381" t="s">
         <v>58</v>
@@ -5843,8 +5840,8 @@
       <c r="A382" t="s">
         <v>52</v>
       </c>
-      <c r="B382" t="s">
-        <v>412</v>
+      <c r="B382">
+        <v>360</v>
       </c>
       <c r="C382" t="s">
         <v>58</v>
@@ -5854,8 +5851,8 @@
       <c r="A383" t="s">
         <v>352</v>
       </c>
-      <c r="B383" t="s">
-        <v>412</v>
+      <c r="B383">
+        <v>360</v>
       </c>
       <c r="C383" t="s">
         <v>58</v>
@@ -5865,8 +5862,8 @@
       <c r="A384" t="s">
         <v>353</v>
       </c>
-      <c r="B384" t="s">
-        <v>412</v>
+      <c r="B384">
+        <v>360</v>
       </c>
       <c r="C384" t="s">
         <v>58</v>
@@ -5876,8 +5873,8 @@
       <c r="A385" t="s">
         <v>349</v>
       </c>
-      <c r="B385" t="s">
-        <v>412</v>
+      <c r="B385">
+        <v>360</v>
       </c>
       <c r="C385" t="s">
         <v>58</v>
@@ -5887,8 +5884,8 @@
       <c r="A386" t="s">
         <v>354</v>
       </c>
-      <c r="B386" t="s">
-        <v>412</v>
+      <c r="B386">
+        <v>360</v>
       </c>
       <c r="C386" t="s">
         <v>58</v>
@@ -5898,8 +5895,8 @@
       <c r="A387" t="s">
         <v>355</v>
       </c>
-      <c r="B387" t="s">
-        <v>412</v>
+      <c r="B387">
+        <v>360</v>
       </c>
       <c r="C387" t="s">
         <v>58</v>
@@ -5909,8 +5906,8 @@
       <c r="A388" t="s">
         <v>53</v>
       </c>
-      <c r="B388" t="s">
-        <v>412</v>
+      <c r="B388">
+        <v>360</v>
       </c>
       <c r="C388" t="s">
         <v>58</v>
@@ -5920,8 +5917,8 @@
       <c r="A389" t="s">
         <v>356</v>
       </c>
-      <c r="B389" t="s">
-        <v>412</v>
+      <c r="B389">
+        <v>360</v>
       </c>
       <c r="C389" t="s">
         <v>58</v>
@@ -5931,8 +5928,8 @@
       <c r="A390" t="s">
         <v>357</v>
       </c>
-      <c r="B390" t="s">
-        <v>412</v>
+      <c r="B390">
+        <v>360</v>
       </c>
       <c r="C390" t="s">
         <v>58</v>
@@ -5942,8 +5939,8 @@
       <c r="A391" t="s">
         <v>54</v>
       </c>
-      <c r="B391" t="s">
-        <v>412</v>
+      <c r="B391">
+        <v>360</v>
       </c>
       <c r="C391" t="s">
         <v>58</v>
@@ -5953,8 +5950,8 @@
       <c r="A392" t="s">
         <v>358</v>
       </c>
-      <c r="B392" t="s">
-        <v>412</v>
+      <c r="B392">
+        <v>360</v>
       </c>
       <c r="C392" t="s">
         <v>58</v>
@@ -5964,8 +5961,8 @@
       <c r="A393" t="s">
         <v>55</v>
       </c>
-      <c r="B393" t="s">
-        <v>412</v>
+      <c r="B393">
+        <v>360</v>
       </c>
       <c r="C393" t="s">
         <v>58</v>
@@ -5975,8 +5972,8 @@
       <c r="A394" t="s">
         <v>359</v>
       </c>
-      <c r="B394" t="s">
-        <v>412</v>
+      <c r="B394">
+        <v>360</v>
       </c>
       <c r="C394" t="s">
         <v>58</v>
@@ -5986,8 +5983,8 @@
       <c r="A395" t="s">
         <v>360</v>
       </c>
-      <c r="B395" t="s">
-        <v>412</v>
+      <c r="B395">
+        <v>360</v>
       </c>
       <c r="C395" t="s">
         <v>58</v>
@@ -5997,8 +5994,8 @@
       <c r="A396" t="s">
         <v>361</v>
       </c>
-      <c r="B396" t="s">
-        <v>412</v>
+      <c r="B396">
+        <v>360</v>
       </c>
       <c r="C396" t="s">
         <v>58</v>
@@ -6008,8 +6005,8 @@
       <c r="A397" t="s">
         <v>362</v>
       </c>
-      <c r="B397" t="s">
-        <v>412</v>
+      <c r="B397">
+        <v>360</v>
       </c>
       <c r="C397" t="s">
         <v>58</v>
@@ -6019,8 +6016,8 @@
       <c r="A398" t="s">
         <v>363</v>
       </c>
-      <c r="B398" t="s">
-        <v>412</v>
+      <c r="B398">
+        <v>360</v>
       </c>
       <c r="C398" t="s">
         <v>58</v>
@@ -6030,8 +6027,8 @@
       <c r="A399" t="s">
         <v>364</v>
       </c>
-      <c r="B399" t="s">
-        <v>412</v>
+      <c r="B399">
+        <v>360</v>
       </c>
       <c r="C399" t="s">
         <v>58</v>
@@ -6041,8 +6038,8 @@
       <c r="A400" t="s">
         <v>365</v>
       </c>
-      <c r="B400" t="s">
-        <v>412</v>
+      <c r="B400">
+        <v>360</v>
       </c>
       <c r="C400" t="s">
         <v>58</v>
@@ -6052,8 +6049,8 @@
       <c r="A401" t="s">
         <v>56</v>
       </c>
-      <c r="B401" t="s">
-        <v>412</v>
+      <c r="B401">
+        <v>360</v>
       </c>
       <c r="C401" t="s">
         <v>58</v>
@@ -6063,8 +6060,8 @@
       <c r="A402" t="s">
         <v>366</v>
       </c>
-      <c r="B402" t="s">
-        <v>412</v>
+      <c r="B402">
+        <v>360</v>
       </c>
       <c r="C402" t="s">
         <v>58</v>
@@ -6074,8 +6071,8 @@
       <c r="A403" t="s">
         <v>367</v>
       </c>
-      <c r="B403" t="s">
-        <v>412</v>
+      <c r="B403">
+        <v>360</v>
       </c>
       <c r="C403" t="s">
         <v>58</v>
@@ -6085,8 +6082,8 @@
       <c r="A404" t="s">
         <v>368</v>
       </c>
-      <c r="B404" t="s">
-        <v>412</v>
+      <c r="B404">
+        <v>360</v>
       </c>
       <c r="C404" t="s">
         <v>58</v>
@@ -6096,8 +6093,8 @@
       <c r="A405" t="s">
         <v>407</v>
       </c>
-      <c r="B405" t="s">
-        <v>412</v>
+      <c r="B405">
+        <v>360</v>
       </c>
       <c r="C405" t="s">
         <v>58</v>
@@ -6107,8 +6104,8 @@
       <c r="A406" t="s">
         <v>369</v>
       </c>
-      <c r="B406" t="s">
-        <v>412</v>
+      <c r="B406">
+        <v>360</v>
       </c>
       <c r="C406" t="s">
         <v>58</v>
@@ -6118,8 +6115,8 @@
       <c r="A407" t="s">
         <v>370</v>
       </c>
-      <c r="B407" t="s">
-        <v>412</v>
+      <c r="B407">
+        <v>360</v>
       </c>
       <c r="C407" t="s">
         <v>58</v>
@@ -6129,8 +6126,8 @@
       <c r="A408" t="s">
         <v>371</v>
       </c>
-      <c r="B408" t="s">
-        <v>412</v>
+      <c r="B408">
+        <v>360</v>
       </c>
       <c r="C408" t="s">
         <v>58</v>
@@ -6140,8 +6137,8 @@
       <c r="A409" t="s">
         <v>57</v>
       </c>
-      <c r="B409" t="s">
-        <v>412</v>
+      <c r="B409">
+        <v>360</v>
       </c>
       <c r="C409" t="s">
         <v>58</v>

--- a/ativos.xlsx
+++ b/ativos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\INVESTIMENTOS VARIAVEL\Bybit\bybit_setups\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\INVESTIMENTOS VARIAVEL\Bybit\bybit_setups\complementos\GitHub\bybit_setups\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC71C623-357A-4BCF-932C-EB363402890E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E118378-A4CB-462D-8011-FFA246FEB3D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1661,7 +1661,7 @@
         <v>385</v>
       </c>
       <c r="B2">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C2" t="s">
         <v>58</v>
@@ -1672,7 +1672,7 @@
         <v>59</v>
       </c>
       <c r="B3">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C3" t="s">
         <v>58</v>
@@ -1683,7 +1683,7 @@
         <v>372</v>
       </c>
       <c r="B4">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C4" t="s">
         <v>58</v>
@@ -1694,7 +1694,7 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C5" t="s">
         <v>58</v>
@@ -1705,7 +1705,7 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C6" t="s">
         <v>58</v>
@@ -1716,7 +1716,7 @@
         <v>60</v>
       </c>
       <c r="B7">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C7" t="s">
         <v>58</v>
@@ -1727,7 +1727,7 @@
         <v>373</v>
       </c>
       <c r="B8">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C8" t="s">
         <v>58</v>
@@ -1738,7 +1738,7 @@
         <v>61</v>
       </c>
       <c r="B9">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C9" t="s">
         <v>58</v>
@@ -1749,7 +1749,7 @@
         <v>5</v>
       </c>
       <c r="B10">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C10" t="s">
         <v>58</v>
@@ -1760,7 +1760,7 @@
         <v>386</v>
       </c>
       <c r="B11">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C11" t="s">
         <v>58</v>
@@ -1771,7 +1771,7 @@
         <v>63</v>
       </c>
       <c r="B12">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C12" t="s">
         <v>58</v>
@@ -1782,7 +1782,7 @@
         <v>64</v>
       </c>
       <c r="B13">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C13" t="s">
         <v>58</v>
@@ -1793,7 +1793,7 @@
         <v>65</v>
       </c>
       <c r="B14">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C14" t="s">
         <v>58</v>
@@ -1804,7 +1804,7 @@
         <v>66</v>
       </c>
       <c r="B15">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C15" t="s">
         <v>58</v>
@@ -1815,7 +1815,7 @@
         <v>67</v>
       </c>
       <c r="B16">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C16" t="s">
         <v>58</v>
@@ -1826,7 +1826,7 @@
         <v>6</v>
       </c>
       <c r="B17">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C17" t="s">
         <v>58</v>
@@ -1837,7 +1837,7 @@
         <v>68</v>
       </c>
       <c r="B18">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C18" t="s">
         <v>58</v>
@@ -1848,7 +1848,7 @@
         <v>69</v>
       </c>
       <c r="B19">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C19" t="s">
         <v>58</v>
@@ -1859,7 +1859,7 @@
         <v>70</v>
       </c>
       <c r="B20">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C20" t="s">
         <v>58</v>
@@ -1870,7 +1870,7 @@
         <v>71</v>
       </c>
       <c r="B21">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C21" t="s">
         <v>58</v>
@@ -1881,7 +1881,7 @@
         <v>72</v>
       </c>
       <c r="B22">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C22" t="s">
         <v>58</v>
@@ -1892,7 +1892,7 @@
         <v>387</v>
       </c>
       <c r="B23">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C23" t="s">
         <v>58</v>
@@ -1903,7 +1903,7 @@
         <v>73</v>
       </c>
       <c r="B24">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C24" t="s">
         <v>58</v>
@@ -1914,7 +1914,7 @@
         <v>400</v>
       </c>
       <c r="B25">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C25" t="s">
         <v>58</v>
@@ -1925,7 +1925,7 @@
         <v>74</v>
       </c>
       <c r="B26">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C26" t="s">
         <v>58</v>
@@ -1936,7 +1936,7 @@
         <v>75</v>
       </c>
       <c r="B27">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C27" t="s">
         <v>58</v>
@@ -1947,7 +1947,7 @@
         <v>7</v>
       </c>
       <c r="B28">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C28" t="s">
         <v>58</v>
@@ -1958,7 +1958,7 @@
         <v>76</v>
       </c>
       <c r="B29">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C29" t="s">
         <v>58</v>
@@ -1969,7 +1969,7 @@
         <v>388</v>
       </c>
       <c r="B30">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C30" t="s">
         <v>58</v>
@@ -1980,7 +1980,7 @@
         <v>77</v>
       </c>
       <c r="B31">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C31" t="s">
         <v>58</v>
@@ -1991,7 +1991,7 @@
         <v>78</v>
       </c>
       <c r="B32">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C32" t="s">
         <v>58</v>
@@ -2002,7 +2002,7 @@
         <v>79</v>
       </c>
       <c r="B33">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C33" t="s">
         <v>58</v>
@@ -2013,7 +2013,7 @@
         <v>8</v>
       </c>
       <c r="B34">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C34" t="s">
         <v>58</v>
@@ -2024,7 +2024,7 @@
         <v>9</v>
       </c>
       <c r="B35">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C35" t="s">
         <v>58</v>
@@ -2035,7 +2035,7 @@
         <v>389</v>
       </c>
       <c r="B36">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C36" t="s">
         <v>58</v>
@@ -2046,7 +2046,7 @@
         <v>80</v>
       </c>
       <c r="B37">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C37" t="s">
         <v>58</v>
@@ -2057,7 +2057,7 @@
         <v>81</v>
       </c>
       <c r="B38">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C38" t="s">
         <v>58</v>
@@ -2068,7 +2068,7 @@
         <v>10</v>
       </c>
       <c r="B39">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C39" t="s">
         <v>58</v>
@@ -2079,7 +2079,7 @@
         <v>390</v>
       </c>
       <c r="B40">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C40" t="s">
         <v>58</v>
@@ -2090,7 +2090,7 @@
         <v>83</v>
       </c>
       <c r="B41">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C41" t="s">
         <v>58</v>
@@ -2101,7 +2101,7 @@
         <v>82</v>
       </c>
       <c r="B42">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C42" t="s">
         <v>58</v>
@@ -2112,7 +2112,7 @@
         <v>84</v>
       </c>
       <c r="B43">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C43" t="s">
         <v>58</v>
@@ -2123,7 +2123,7 @@
         <v>374</v>
       </c>
       <c r="B44">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C44" t="s">
         <v>58</v>
@@ -2134,7 +2134,7 @@
         <v>391</v>
       </c>
       <c r="B45">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C45" t="s">
         <v>58</v>
@@ -2145,7 +2145,7 @@
         <v>392</v>
       </c>
       <c r="B46">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C46" t="s">
         <v>58</v>
@@ -2156,7 +2156,7 @@
         <v>85</v>
       </c>
       <c r="B47">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C47" t="s">
         <v>58</v>
@@ -2167,7 +2167,7 @@
         <v>86</v>
       </c>
       <c r="B48">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C48" t="s">
         <v>58</v>
@@ -2178,7 +2178,7 @@
         <v>87</v>
       </c>
       <c r="B49">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C49" t="s">
         <v>58</v>
@@ -2189,7 +2189,7 @@
         <v>393</v>
       </c>
       <c r="B50">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C50" t="s">
         <v>58</v>
@@ -2200,7 +2200,7 @@
         <v>88</v>
       </c>
       <c r="B51">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C51" t="s">
         <v>58</v>
@@ -2211,7 +2211,7 @@
         <v>62</v>
       </c>
       <c r="B52">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C52" t="s">
         <v>58</v>
@@ -2222,7 +2222,7 @@
         <v>89</v>
       </c>
       <c r="B53">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C53" t="s">
         <v>58</v>
@@ -2233,7 +2233,7 @@
         <v>11</v>
       </c>
       <c r="B54">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C54" t="s">
         <v>58</v>
@@ -2244,7 +2244,7 @@
         <v>394</v>
       </c>
       <c r="B55">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C55" t="s">
         <v>58</v>
@@ -2255,7 +2255,7 @@
         <v>90</v>
       </c>
       <c r="B56">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C56" t="s">
         <v>58</v>
@@ -2266,7 +2266,7 @@
         <v>91</v>
       </c>
       <c r="B57">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C57" t="s">
         <v>58</v>
@@ -2277,7 +2277,7 @@
         <v>92</v>
       </c>
       <c r="B58">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C58" t="s">
         <v>58</v>
@@ -2288,7 +2288,7 @@
         <v>93</v>
       </c>
       <c r="B59">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C59" t="s">
         <v>58</v>
@@ -2299,7 +2299,7 @@
         <v>94</v>
       </c>
       <c r="B60">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C60" t="s">
         <v>58</v>
@@ -2310,7 +2310,7 @@
         <v>95</v>
       </c>
       <c r="B61">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C61" t="s">
         <v>58</v>
@@ -2321,7 +2321,7 @@
         <v>97</v>
       </c>
       <c r="B62">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C62" t="s">
         <v>58</v>
@@ -2332,7 +2332,7 @@
         <v>98</v>
       </c>
       <c r="B63">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C63" t="s">
         <v>58</v>
@@ -2343,7 +2343,7 @@
         <v>99</v>
       </c>
       <c r="B64">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C64" t="s">
         <v>58</v>
@@ -2354,7 +2354,7 @@
         <v>96</v>
       </c>
       <c r="B65">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C65" t="s">
         <v>58</v>
@@ -2365,7 +2365,7 @@
         <v>100</v>
       </c>
       <c r="B66">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C66" t="s">
         <v>58</v>
@@ -2376,7 +2376,7 @@
         <v>101</v>
       </c>
       <c r="B67">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C67" t="s">
         <v>58</v>
@@ -2387,7 +2387,7 @@
         <v>102</v>
       </c>
       <c r="B68">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C68" t="s">
         <v>58</v>
@@ -2398,7 +2398,7 @@
         <v>103</v>
       </c>
       <c r="B69">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C69" t="s">
         <v>58</v>
@@ -2409,7 +2409,7 @@
         <v>397</v>
       </c>
       <c r="B70">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C70" t="s">
         <v>58</v>
@@ -2420,7 +2420,7 @@
         <v>104</v>
       </c>
       <c r="B71">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C71" t="s">
         <v>58</v>
@@ -2431,7 +2431,7 @@
         <v>105</v>
       </c>
       <c r="B72">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C72" t="s">
         <v>58</v>
@@ -2442,7 +2442,7 @@
         <v>106</v>
       </c>
       <c r="B73">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C73" t="s">
         <v>58</v>
@@ -2453,7 +2453,7 @@
         <v>12</v>
       </c>
       <c r="B74">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C74" t="s">
         <v>58</v>
@@ -2464,7 +2464,7 @@
         <v>107</v>
       </c>
       <c r="B75">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C75" t="s">
         <v>58</v>
@@ -2475,7 +2475,7 @@
         <v>375</v>
       </c>
       <c r="B76">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C76" t="s">
         <v>58</v>
@@ -2486,7 +2486,7 @@
         <v>402</v>
       </c>
       <c r="B77">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C77" t="s">
         <v>58</v>
@@ -2497,7 +2497,7 @@
         <v>108</v>
       </c>
       <c r="B78">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C78" t="s">
         <v>58</v>
@@ -2508,7 +2508,7 @@
         <v>109</v>
       </c>
       <c r="B79">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C79" t="s">
         <v>58</v>
@@ -2519,7 +2519,7 @@
         <v>13</v>
       </c>
       <c r="B80">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C80" t="s">
         <v>58</v>
@@ -2530,7 +2530,7 @@
         <v>110</v>
       </c>
       <c r="B81">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C81" t="s">
         <v>58</v>
@@ -2541,7 +2541,7 @@
         <v>111</v>
       </c>
       <c r="B82">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C82" t="s">
         <v>58</v>
@@ -2552,7 +2552,7 @@
         <v>112</v>
       </c>
       <c r="B83">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C83" t="s">
         <v>58</v>
@@ -2563,7 +2563,7 @@
         <v>14</v>
       </c>
       <c r="B84">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C84" t="s">
         <v>58</v>
@@ -2574,7 +2574,7 @@
         <v>113</v>
       </c>
       <c r="B85">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C85" t="s">
         <v>58</v>
@@ -2585,7 +2585,7 @@
         <v>15</v>
       </c>
       <c r="B86">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C86" t="s">
         <v>58</v>
@@ -2596,7 +2596,7 @@
         <v>114</v>
       </c>
       <c r="B87">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C87" t="s">
         <v>58</v>
@@ -2607,7 +2607,7 @@
         <v>396</v>
       </c>
       <c r="B88">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C88" t="s">
         <v>58</v>
@@ -2618,7 +2618,7 @@
         <v>409</v>
       </c>
       <c r="B89">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C89" t="s">
         <v>58</v>
@@ -2629,7 +2629,7 @@
         <v>116</v>
       </c>
       <c r="B90">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C90" t="s">
         <v>58</v>
@@ -2640,7 +2640,7 @@
         <v>117</v>
       </c>
       <c r="B91">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C91" t="s">
         <v>58</v>
@@ -2651,7 +2651,7 @@
         <v>118</v>
       </c>
       <c r="B92">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C92" t="s">
         <v>58</v>
@@ -2662,7 +2662,7 @@
         <v>119</v>
       </c>
       <c r="B93">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C93" t="s">
         <v>58</v>
@@ -2673,7 +2673,7 @@
         <v>120</v>
       </c>
       <c r="B94">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C94" t="s">
         <v>58</v>
@@ -2684,7 +2684,7 @@
         <v>121</v>
       </c>
       <c r="B95">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C95" t="s">
         <v>58</v>
@@ -2695,7 +2695,7 @@
         <v>122</v>
       </c>
       <c r="B96">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C96" t="s">
         <v>58</v>
@@ -2706,7 +2706,7 @@
         <v>123</v>
       </c>
       <c r="B97">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C97" t="s">
         <v>58</v>
@@ -2717,7 +2717,7 @@
         <v>124</v>
       </c>
       <c r="B98">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C98" t="s">
         <v>58</v>
@@ -2728,7 +2728,7 @@
         <v>125</v>
       </c>
       <c r="B99">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C99" t="s">
         <v>58</v>
@@ -2739,7 +2739,7 @@
         <v>126</v>
       </c>
       <c r="B100">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C100" t="s">
         <v>58</v>
@@ -2750,7 +2750,7 @@
         <v>376</v>
       </c>
       <c r="B101">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C101" t="s">
         <v>58</v>
@@ -2761,7 +2761,7 @@
         <v>127</v>
       </c>
       <c r="B102">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C102" t="s">
         <v>58</v>
@@ -2772,7 +2772,7 @@
         <v>408</v>
       </c>
       <c r="B103">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C103" t="s">
         <v>58</v>
@@ -2783,7 +2783,7 @@
         <v>16</v>
       </c>
       <c r="B104">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C104" t="s">
         <v>58</v>
@@ -2794,7 +2794,7 @@
         <v>128</v>
       </c>
       <c r="B105">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C105" t="s">
         <v>58</v>
@@ -2805,7 +2805,7 @@
         <v>17</v>
       </c>
       <c r="B106">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C106" t="s">
         <v>58</v>
@@ -2816,7 +2816,7 @@
         <v>18</v>
       </c>
       <c r="B107">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C107" t="s">
         <v>58</v>
@@ -2827,7 +2827,7 @@
         <v>129</v>
       </c>
       <c r="B108">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C108" t="s">
         <v>58</v>
@@ -2838,7 +2838,7 @@
         <v>131</v>
       </c>
       <c r="B109">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C109" t="s">
         <v>58</v>
@@ -2849,7 +2849,7 @@
         <v>130</v>
       </c>
       <c r="B110">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C110" t="s">
         <v>58</v>
@@ -2860,7 +2860,7 @@
         <v>132</v>
       </c>
       <c r="B111">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C111" t="s">
         <v>58</v>
@@ -2871,7 +2871,7 @@
         <v>133</v>
       </c>
       <c r="B112">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C112" t="s">
         <v>58</v>
@@ -2882,7 +2882,7 @@
         <v>115</v>
       </c>
       <c r="B113">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C113" t="s">
         <v>58</v>
@@ -2893,7 +2893,7 @@
         <v>134</v>
       </c>
       <c r="B114">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C114" t="s">
         <v>58</v>
@@ -2904,7 +2904,7 @@
         <v>135</v>
       </c>
       <c r="B115">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C115" t="s">
         <v>58</v>
@@ -2915,7 +2915,7 @@
         <v>136</v>
       </c>
       <c r="B116">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C116" t="s">
         <v>58</v>
@@ -2926,7 +2926,7 @@
         <v>137</v>
       </c>
       <c r="B117">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C117" t="s">
         <v>58</v>
@@ -2937,7 +2937,7 @@
         <v>138</v>
       </c>
       <c r="B118">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C118" t="s">
         <v>58</v>
@@ -2948,7 +2948,7 @@
         <v>139</v>
       </c>
       <c r="B119">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C119" t="s">
         <v>58</v>
@@ -2959,7 +2959,7 @@
         <v>140</v>
       </c>
       <c r="B120">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C120" t="s">
         <v>58</v>
@@ -2970,7 +2970,7 @@
         <v>141</v>
       </c>
       <c r="B121">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C121" t="s">
         <v>58</v>
@@ -2981,7 +2981,7 @@
         <v>19</v>
       </c>
       <c r="B122">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C122" t="s">
         <v>58</v>
@@ -2992,7 +2992,7 @@
         <v>142</v>
       </c>
       <c r="B123">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C123" t="s">
         <v>58</v>
@@ -3003,7 +3003,7 @@
         <v>143</v>
       </c>
       <c r="B124">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C124" t="s">
         <v>58</v>
@@ -3014,7 +3014,7 @@
         <v>144</v>
       </c>
       <c r="B125">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C125" t="s">
         <v>58</v>
@@ -3025,7 +3025,7 @@
         <v>145</v>
       </c>
       <c r="B126">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C126" t="s">
         <v>58</v>
@@ -3036,7 +3036,7 @@
         <v>146</v>
       </c>
       <c r="B127">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C127" t="s">
         <v>58</v>
@@ -3047,7 +3047,7 @@
         <v>147</v>
       </c>
       <c r="B128">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C128" t="s">
         <v>58</v>
@@ -3058,7 +3058,7 @@
         <v>403</v>
       </c>
       <c r="B129">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C129" t="s">
         <v>58</v>
@@ -3069,7 +3069,7 @@
         <v>148</v>
       </c>
       <c r="B130">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C130" t="s">
         <v>58</v>
@@ -3080,7 +3080,7 @@
         <v>149</v>
       </c>
       <c r="B131">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C131" t="s">
         <v>58</v>
@@ -3091,7 +3091,7 @@
         <v>150</v>
       </c>
       <c r="B132">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C132" t="s">
         <v>58</v>
@@ -3102,7 +3102,7 @@
         <v>20</v>
       </c>
       <c r="B133">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C133" t="s">
         <v>58</v>
@@ -3113,7 +3113,7 @@
         <v>151</v>
       </c>
       <c r="B134">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C134" t="s">
         <v>58</v>
@@ -3124,7 +3124,7 @@
         <v>152</v>
       </c>
       <c r="B135">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C135" t="s">
         <v>58</v>
@@ -3135,7 +3135,7 @@
         <v>153</v>
       </c>
       <c r="B136">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C136" t="s">
         <v>58</v>
@@ -3146,7 +3146,7 @@
         <v>154</v>
       </c>
       <c r="B137">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C137" t="s">
         <v>58</v>
@@ -3157,7 +3157,7 @@
         <v>155</v>
       </c>
       <c r="B138">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C138" t="s">
         <v>58</v>
@@ -3168,7 +3168,7 @@
         <v>156</v>
       </c>
       <c r="B139">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C139" t="s">
         <v>58</v>
@@ -3179,7 +3179,7 @@
         <v>157</v>
       </c>
       <c r="B140">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C140" t="s">
         <v>58</v>
@@ -3190,7 +3190,7 @@
         <v>158</v>
       </c>
       <c r="B141">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C141" t="s">
         <v>58</v>
@@ -3201,7 +3201,7 @@
         <v>21</v>
       </c>
       <c r="B142">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C142" t="s">
         <v>58</v>
@@ -3212,7 +3212,7 @@
         <v>410</v>
       </c>
       <c r="B143">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C143" t="s">
         <v>58</v>
@@ -3223,7 +3223,7 @@
         <v>22</v>
       </c>
       <c r="B144">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C144" t="s">
         <v>58</v>
@@ -3234,7 +3234,7 @@
         <v>399</v>
       </c>
       <c r="B145">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C145" t="s">
         <v>58</v>
@@ -3245,7 +3245,7 @@
         <v>159</v>
       </c>
       <c r="B146">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C146" t="s">
         <v>58</v>
@@ -3256,7 +3256,7 @@
         <v>160</v>
       </c>
       <c r="B147">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C147" t="s">
         <v>58</v>
@@ -3267,7 +3267,7 @@
         <v>161</v>
       </c>
       <c r="B148">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C148" t="s">
         <v>58</v>
@@ -3278,7 +3278,7 @@
         <v>162</v>
       </c>
       <c r="B149">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C149" t="s">
         <v>58</v>
@@ -3289,7 +3289,7 @@
         <v>163</v>
       </c>
       <c r="B150">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C150" t="s">
         <v>58</v>
@@ -3300,7 +3300,7 @@
         <v>164</v>
       </c>
       <c r="B151">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C151" t="s">
         <v>58</v>
@@ -3311,7 +3311,7 @@
         <v>405</v>
       </c>
       <c r="B152">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C152" t="s">
         <v>58</v>
@@ -3322,7 +3322,7 @@
         <v>165</v>
       </c>
       <c r="B153">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C153" t="s">
         <v>58</v>
@@ -3333,7 +3333,7 @@
         <v>23</v>
       </c>
       <c r="B154">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C154" t="s">
         <v>58</v>
@@ -3344,7 +3344,7 @@
         <v>24</v>
       </c>
       <c r="B155">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C155" t="s">
         <v>58</v>
@@ -3355,7 +3355,7 @@
         <v>166</v>
       </c>
       <c r="B156">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C156" t="s">
         <v>58</v>
@@ -3366,7 +3366,7 @@
         <v>395</v>
       </c>
       <c r="B157">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C157" t="s">
         <v>58</v>
@@ -3377,7 +3377,7 @@
         <v>167</v>
       </c>
       <c r="B158">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C158" t="s">
         <v>58</v>
@@ -3388,7 +3388,7 @@
         <v>168</v>
       </c>
       <c r="B159">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C159" t="s">
         <v>58</v>
@@ -3399,7 +3399,7 @@
         <v>25</v>
       </c>
       <c r="B160">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C160" t="s">
         <v>58</v>
@@ -3410,7 +3410,7 @@
         <v>169</v>
       </c>
       <c r="B161">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C161" t="s">
         <v>58</v>
@@ -3421,7 +3421,7 @@
         <v>170</v>
       </c>
       <c r="B162">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C162" t="s">
         <v>58</v>
@@ -3432,7 +3432,7 @@
         <v>171</v>
       </c>
       <c r="B163">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C163" t="s">
         <v>58</v>
@@ -3443,7 +3443,7 @@
         <v>172</v>
       </c>
       <c r="B164">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C164" t="s">
         <v>58</v>
@@ -3454,7 +3454,7 @@
         <v>173</v>
       </c>
       <c r="B165">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C165" t="s">
         <v>58</v>
@@ -3465,7 +3465,7 @@
         <v>174</v>
       </c>
       <c r="B166">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C166" t="s">
         <v>58</v>
@@ -3476,7 +3476,7 @@
         <v>175</v>
       </c>
       <c r="B167">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C167" t="s">
         <v>58</v>
@@ -3487,7 +3487,7 @@
         <v>176</v>
       </c>
       <c r="B168">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C168" t="s">
         <v>58</v>
@@ -3498,7 +3498,7 @@
         <v>177</v>
       </c>
       <c r="B169">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C169" t="s">
         <v>58</v>
@@ -3509,7 +3509,7 @@
         <v>179</v>
       </c>
       <c r="B170">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C170" t="s">
         <v>58</v>
@@ -3520,7 +3520,7 @@
         <v>180</v>
       </c>
       <c r="B171">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C171" t="s">
         <v>58</v>
@@ -3531,7 +3531,7 @@
         <v>181</v>
       </c>
       <c r="B172">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C172" t="s">
         <v>58</v>
@@ -3542,7 +3542,7 @@
         <v>182</v>
       </c>
       <c r="B173">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C173" t="s">
         <v>58</v>
@@ -3553,7 +3553,7 @@
         <v>183</v>
       </c>
       <c r="B174">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C174" t="s">
         <v>58</v>
@@ -3564,7 +3564,7 @@
         <v>184</v>
       </c>
       <c r="B175">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C175" t="s">
         <v>58</v>
@@ -3575,7 +3575,7 @@
         <v>185</v>
       </c>
       <c r="B176">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C176" t="s">
         <v>58</v>
@@ -3586,7 +3586,7 @@
         <v>186</v>
       </c>
       <c r="B177">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C177" t="s">
         <v>58</v>
@@ -3597,7 +3597,7 @@
         <v>187</v>
       </c>
       <c r="B178">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C178" t="s">
         <v>58</v>
@@ -3608,7 +3608,7 @@
         <v>188</v>
       </c>
       <c r="B179">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C179" t="s">
         <v>58</v>
@@ -3619,7 +3619,7 @@
         <v>178</v>
       </c>
       <c r="B180">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C180" t="s">
         <v>58</v>
@@ -3630,7 +3630,7 @@
         <v>190</v>
       </c>
       <c r="B181">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C181" t="s">
         <v>58</v>
@@ -3641,7 +3641,7 @@
         <v>189</v>
       </c>
       <c r="B182">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C182" t="s">
         <v>58</v>
@@ -3652,7 +3652,7 @@
         <v>191</v>
       </c>
       <c r="B183">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C183" t="s">
         <v>58</v>
@@ -3663,7 +3663,7 @@
         <v>377</v>
       </c>
       <c r="B184">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C184" t="s">
         <v>58</v>
@@ -3674,7 +3674,7 @@
         <v>192</v>
       </c>
       <c r="B185">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C185" t="s">
         <v>58</v>
@@ -3685,7 +3685,7 @@
         <v>193</v>
       </c>
       <c r="B186">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C186" t="s">
         <v>58</v>
@@ -3696,7 +3696,7 @@
         <v>194</v>
       </c>
       <c r="B187">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C187" t="s">
         <v>58</v>
@@ -3707,7 +3707,7 @@
         <v>195</v>
       </c>
       <c r="B188">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C188" t="s">
         <v>58</v>
@@ -3718,7 +3718,7 @@
         <v>196</v>
       </c>
       <c r="B189">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C189" t="s">
         <v>58</v>
@@ -3729,7 +3729,7 @@
         <v>197</v>
       </c>
       <c r="B190">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C190" t="s">
         <v>58</v>
@@ -3740,7 +3740,7 @@
         <v>199</v>
       </c>
       <c r="B191">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C191" t="s">
         <v>58</v>
@@ -3751,7 +3751,7 @@
         <v>200</v>
       </c>
       <c r="B192">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C192" t="s">
         <v>58</v>
@@ -3762,7 +3762,7 @@
         <v>201</v>
       </c>
       <c r="B193">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C193" t="s">
         <v>58</v>
@@ -3773,7 +3773,7 @@
         <v>198</v>
       </c>
       <c r="B194">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C194" t="s">
         <v>58</v>
@@ -3784,7 +3784,7 @@
         <v>202</v>
       </c>
       <c r="B195">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C195" t="s">
         <v>58</v>
@@ -3795,7 +3795,7 @@
         <v>26</v>
       </c>
       <c r="B196">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C196" t="s">
         <v>58</v>
@@ -3806,7 +3806,7 @@
         <v>203</v>
       </c>
       <c r="B197">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C197" t="s">
         <v>58</v>
@@ -3817,7 +3817,7 @@
         <v>204</v>
       </c>
       <c r="B198">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C198" t="s">
         <v>58</v>
@@ -3828,7 +3828,7 @@
         <v>27</v>
       </c>
       <c r="B199">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C199" t="s">
         <v>58</v>
@@ -3839,7 +3839,7 @@
         <v>28</v>
       </c>
       <c r="B200">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C200" t="s">
         <v>58</v>
@@ -3850,7 +3850,7 @@
         <v>205</v>
       </c>
       <c r="B201">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C201" t="s">
         <v>58</v>
@@ -3861,7 +3861,7 @@
         <v>206</v>
       </c>
       <c r="B202">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C202" t="s">
         <v>58</v>
@@ -3872,7 +3872,7 @@
         <v>29</v>
       </c>
       <c r="B203">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C203" t="s">
         <v>58</v>
@@ -3883,7 +3883,7 @@
         <v>207</v>
       </c>
       <c r="B204">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C204" t="s">
         <v>58</v>
@@ -3894,7 +3894,7 @@
         <v>378</v>
       </c>
       <c r="B205">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C205" t="s">
         <v>58</v>
@@ -3905,7 +3905,7 @@
         <v>30</v>
       </c>
       <c r="B206">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C206" t="s">
         <v>58</v>
@@ -3916,7 +3916,7 @@
         <v>208</v>
       </c>
       <c r="B207">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C207" t="s">
         <v>58</v>
@@ -3927,7 +3927,7 @@
         <v>209</v>
       </c>
       <c r="B208">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C208" t="s">
         <v>58</v>
@@ -3938,7 +3938,7 @@
         <v>210</v>
       </c>
       <c r="B209">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C209" t="s">
         <v>58</v>
@@ -3949,7 +3949,7 @@
         <v>211</v>
       </c>
       <c r="B210">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C210" t="s">
         <v>58</v>
@@ -3960,7 +3960,7 @@
         <v>398</v>
       </c>
       <c r="B211">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C211" t="s">
         <v>58</v>
@@ -3971,7 +3971,7 @@
         <v>31</v>
       </c>
       <c r="B212">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C212" t="s">
         <v>58</v>
@@ -3982,7 +3982,7 @@
         <v>212</v>
       </c>
       <c r="B213">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C213" t="s">
         <v>58</v>
@@ -3993,7 +3993,7 @@
         <v>213</v>
       </c>
       <c r="B214">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C214" t="s">
         <v>58</v>
@@ -4004,7 +4004,7 @@
         <v>214</v>
       </c>
       <c r="B215">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C215" t="s">
         <v>58</v>
@@ -4015,7 +4015,7 @@
         <v>215</v>
       </c>
       <c r="B216">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C216" t="s">
         <v>58</v>
@@ -4026,7 +4026,7 @@
         <v>216</v>
       </c>
       <c r="B217">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C217" t="s">
         <v>58</v>
@@ -4037,7 +4037,7 @@
         <v>217</v>
       </c>
       <c r="B218">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C218" t="s">
         <v>58</v>
@@ -4048,7 +4048,7 @@
         <v>218</v>
       </c>
       <c r="B219">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C219" t="s">
         <v>58</v>
@@ -4059,7 +4059,7 @@
         <v>220</v>
       </c>
       <c r="B220">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C220" t="s">
         <v>58</v>
@@ -4070,7 +4070,7 @@
         <v>404</v>
       </c>
       <c r="B221">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C221" t="s">
         <v>58</v>
@@ -4081,7 +4081,7 @@
         <v>32</v>
       </c>
       <c r="B222">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C222" t="s">
         <v>58</v>
@@ -4092,7 +4092,7 @@
         <v>221</v>
       </c>
       <c r="B223">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C223" t="s">
         <v>58</v>
@@ -4103,7 +4103,7 @@
         <v>222</v>
       </c>
       <c r="B224">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C224" t="s">
         <v>58</v>
@@ -4114,7 +4114,7 @@
         <v>224</v>
       </c>
       <c r="B225">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C225" t="s">
         <v>58</v>
@@ -4125,7 +4125,7 @@
         <v>223</v>
       </c>
       <c r="B226">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C226" t="s">
         <v>58</v>
@@ -4136,7 +4136,7 @@
         <v>225</v>
       </c>
       <c r="B227">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C227" t="s">
         <v>58</v>
@@ -4147,7 +4147,7 @@
         <v>227</v>
       </c>
       <c r="B228">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C228" t="s">
         <v>58</v>
@@ -4158,7 +4158,7 @@
         <v>228</v>
       </c>
       <c r="B229">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C229" t="s">
         <v>58</v>
@@ -4169,7 +4169,7 @@
         <v>229</v>
       </c>
       <c r="B230">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C230" t="s">
         <v>58</v>
@@ -4180,7 +4180,7 @@
         <v>230</v>
       </c>
       <c r="B231">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C231" t="s">
         <v>58</v>
@@ -4191,7 +4191,7 @@
         <v>226</v>
       </c>
       <c r="B232">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C232" t="s">
         <v>58</v>
@@ -4202,7 +4202,7 @@
         <v>33</v>
       </c>
       <c r="B233">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C233" t="s">
         <v>58</v>
@@ -4213,7 +4213,7 @@
         <v>231</v>
       </c>
       <c r="B234">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C234" t="s">
         <v>58</v>
@@ -4224,7 +4224,7 @@
         <v>232</v>
       </c>
       <c r="B235">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C235" t="s">
         <v>58</v>
@@ -4235,7 +4235,7 @@
         <v>34</v>
       </c>
       <c r="B236">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C236" t="s">
         <v>58</v>
@@ -4246,7 +4246,7 @@
         <v>233</v>
       </c>
       <c r="B237">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C237" t="s">
         <v>58</v>
@@ -4257,7 +4257,7 @@
         <v>35</v>
       </c>
       <c r="B238">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C238" t="s">
         <v>58</v>
@@ -4268,7 +4268,7 @@
         <v>36</v>
       </c>
       <c r="B239">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C239" t="s">
         <v>58</v>
@@ -4279,7 +4279,7 @@
         <v>234</v>
       </c>
       <c r="B240">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C240" t="s">
         <v>58</v>
@@ -4290,7 +4290,7 @@
         <v>235</v>
       </c>
       <c r="B241">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C241" t="s">
         <v>58</v>
@@ -4301,7 +4301,7 @@
         <v>236</v>
       </c>
       <c r="B242">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C242" t="s">
         <v>58</v>
@@ -4312,7 +4312,7 @@
         <v>237</v>
       </c>
       <c r="B243">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C243" t="s">
         <v>58</v>
@@ -4323,7 +4323,7 @@
         <v>219</v>
       </c>
       <c r="B244">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C244" t="s">
         <v>58</v>
@@ -4334,7 +4334,7 @@
         <v>384</v>
       </c>
       <c r="B245">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C245" t="s">
         <v>58</v>
@@ -4345,7 +4345,7 @@
         <v>37</v>
       </c>
       <c r="B246">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C246" t="s">
         <v>58</v>
@@ -4356,7 +4356,7 @@
         <v>238</v>
       </c>
       <c r="B247">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C247" t="s">
         <v>58</v>
@@ -4367,7 +4367,7 @@
         <v>239</v>
       </c>
       <c r="B248">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C248" t="s">
         <v>58</v>
@@ -4378,7 +4378,7 @@
         <v>240</v>
       </c>
       <c r="B249">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C249" t="s">
         <v>58</v>
@@ -4389,7 +4389,7 @@
         <v>241</v>
       </c>
       <c r="B250">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C250" t="s">
         <v>58</v>
@@ -4400,7 +4400,7 @@
         <v>401</v>
       </c>
       <c r="B251">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C251" t="s">
         <v>58</v>
@@ -4411,7 +4411,7 @@
         <v>38</v>
       </c>
       <c r="B252">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C252" t="s">
         <v>58</v>
@@ -4422,7 +4422,7 @@
         <v>242</v>
       </c>
       <c r="B253">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C253" t="s">
         <v>58</v>
@@ -4433,7 +4433,7 @@
         <v>244</v>
       </c>
       <c r="B254">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C254" t="s">
         <v>58</v>
@@ -4444,7 +4444,7 @@
         <v>243</v>
       </c>
       <c r="B255">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C255" t="s">
         <v>58</v>
@@ -4455,7 +4455,7 @@
         <v>39</v>
       </c>
       <c r="B256">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C256" t="s">
         <v>58</v>
@@ -4466,7 +4466,7 @@
         <v>245</v>
       </c>
       <c r="B257">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C257" t="s">
         <v>58</v>
@@ -4477,7 +4477,7 @@
         <v>246</v>
       </c>
       <c r="B258">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C258" t="s">
         <v>58</v>
@@ -4488,7 +4488,7 @@
         <v>411</v>
       </c>
       <c r="B259">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C259" t="s">
         <v>58</v>
@@ -4499,7 +4499,7 @@
         <v>40</v>
       </c>
       <c r="B260">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C260" t="s">
         <v>58</v>
@@ -4510,7 +4510,7 @@
         <v>247</v>
       </c>
       <c r="B261">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C261" t="s">
         <v>58</v>
@@ -4521,7 +4521,7 @@
         <v>41</v>
       </c>
       <c r="B262">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C262" t="s">
         <v>58</v>
@@ -4532,7 +4532,7 @@
         <v>248</v>
       </c>
       <c r="B263">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C263" t="s">
         <v>58</v>
@@ -4543,7 +4543,7 @@
         <v>249</v>
       </c>
       <c r="B264">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C264" t="s">
         <v>58</v>
@@ -4554,7 +4554,7 @@
         <v>250</v>
       </c>
       <c r="B265">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C265" t="s">
         <v>58</v>
@@ -4565,7 +4565,7 @@
         <v>251</v>
       </c>
       <c r="B266">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C266" t="s">
         <v>58</v>
@@ -4576,7 +4576,7 @@
         <v>252</v>
       </c>
       <c r="B267">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C267" t="s">
         <v>58</v>
@@ -4587,7 +4587,7 @@
         <v>42</v>
       </c>
       <c r="B268">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C268" t="s">
         <v>58</v>
@@ -4598,7 +4598,7 @@
         <v>253</v>
       </c>
       <c r="B269">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C269" t="s">
         <v>58</v>
@@ -4609,7 +4609,7 @@
         <v>254</v>
       </c>
       <c r="B270">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C270" t="s">
         <v>58</v>
@@ -4620,7 +4620,7 @@
         <v>406</v>
       </c>
       <c r="B271">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C271" t="s">
         <v>58</v>
@@ -4631,7 +4631,7 @@
         <v>255</v>
       </c>
       <c r="B272">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C272" t="s">
         <v>58</v>
@@ -4642,7 +4642,7 @@
         <v>256</v>
       </c>
       <c r="B273">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C273" t="s">
         <v>58</v>
@@ -4653,7 +4653,7 @@
         <v>257</v>
       </c>
       <c r="B274">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C274" t="s">
         <v>58</v>
@@ -4664,7 +4664,7 @@
         <v>258</v>
       </c>
       <c r="B275">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C275" t="s">
         <v>58</v>
@@ -4675,7 +4675,7 @@
         <v>259</v>
       </c>
       <c r="B276">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C276" t="s">
         <v>58</v>
@@ -4686,7 +4686,7 @@
         <v>260</v>
       </c>
       <c r="B277">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C277" t="s">
         <v>58</v>
@@ -4697,7 +4697,7 @@
         <v>261</v>
       </c>
       <c r="B278">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C278" t="s">
         <v>58</v>
@@ -4708,7 +4708,7 @@
         <v>43</v>
       </c>
       <c r="B279">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C279" t="s">
         <v>58</v>
@@ -4719,7 +4719,7 @@
         <v>262</v>
       </c>
       <c r="B280">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C280" t="s">
         <v>58</v>
@@ -4730,7 +4730,7 @@
         <v>263</v>
       </c>
       <c r="B281">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C281" t="s">
         <v>58</v>
@@ -4741,7 +4741,7 @@
         <v>264</v>
       </c>
       <c r="B282">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C282" t="s">
         <v>58</v>
@@ -4752,7 +4752,7 @@
         <v>265</v>
       </c>
       <c r="B283">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C283" t="s">
         <v>58</v>
@@ -4763,7 +4763,7 @@
         <v>266</v>
       </c>
       <c r="B284">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C284" t="s">
         <v>58</v>
@@ -4774,7 +4774,7 @@
         <v>267</v>
       </c>
       <c r="B285">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C285" t="s">
         <v>58</v>
@@ -4785,7 +4785,7 @@
         <v>379</v>
       </c>
       <c r="B286">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C286" t="s">
         <v>58</v>
@@ -4796,7 +4796,7 @@
         <v>268</v>
       </c>
       <c r="B287">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C287" t="s">
         <v>58</v>
@@ -4807,7 +4807,7 @@
         <v>44</v>
       </c>
       <c r="B288">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C288" t="s">
         <v>58</v>
@@ -4818,7 +4818,7 @@
         <v>269</v>
       </c>
       <c r="B289">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C289" t="s">
         <v>58</v>
@@ -4829,7 +4829,7 @@
         <v>270</v>
       </c>
       <c r="B290">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C290" t="s">
         <v>58</v>
@@ -4840,7 +4840,7 @@
         <v>271</v>
       </c>
       <c r="B291">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C291" t="s">
         <v>58</v>
@@ -4851,7 +4851,7 @@
         <v>272</v>
       </c>
       <c r="B292">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C292" t="s">
         <v>58</v>
@@ -4862,7 +4862,7 @@
         <v>273</v>
       </c>
       <c r="B293">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C293" t="s">
         <v>58</v>
@@ -4873,7 +4873,7 @@
         <v>274</v>
       </c>
       <c r="B294">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C294" t="s">
         <v>58</v>
@@ -4884,7 +4884,7 @@
         <v>275</v>
       </c>
       <c r="B295">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C295" t="s">
         <v>58</v>
@@ -4895,7 +4895,7 @@
         <v>276</v>
       </c>
       <c r="B296">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C296" t="s">
         <v>58</v>
@@ -4906,7 +4906,7 @@
         <v>277</v>
       </c>
       <c r="B297">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C297" t="s">
         <v>58</v>
@@ -4917,7 +4917,7 @@
         <v>278</v>
       </c>
       <c r="B298">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C298" t="s">
         <v>58</v>
@@ -4928,7 +4928,7 @@
         <v>380</v>
       </c>
       <c r="B299">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C299" t="s">
         <v>58</v>
@@ -4939,7 +4939,7 @@
         <v>279</v>
       </c>
       <c r="B300">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C300" t="s">
         <v>58</v>
@@ -4950,7 +4950,7 @@
         <v>280</v>
       </c>
       <c r="B301">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C301" t="s">
         <v>58</v>
@@ -4961,7 +4961,7 @@
         <v>281</v>
       </c>
       <c r="B302">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C302" t="s">
         <v>58</v>
@@ -4972,7 +4972,7 @@
         <v>45</v>
       </c>
       <c r="B303">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C303" t="s">
         <v>58</v>
@@ -4983,7 +4983,7 @@
         <v>282</v>
       </c>
       <c r="B304">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C304" t="s">
         <v>58</v>
@@ -4994,7 +4994,7 @@
         <v>284</v>
       </c>
       <c r="B305">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C305" t="s">
         <v>58</v>
@@ -5005,7 +5005,7 @@
         <v>285</v>
       </c>
       <c r="B306">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C306" t="s">
         <v>58</v>
@@ -5016,7 +5016,7 @@
         <v>286</v>
       </c>
       <c r="B307">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C307" t="s">
         <v>58</v>
@@ -5027,7 +5027,7 @@
         <v>287</v>
       </c>
       <c r="B308">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C308" t="s">
         <v>58</v>
@@ -5038,7 +5038,7 @@
         <v>290</v>
       </c>
       <c r="B309">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C309" t="s">
         <v>58</v>
@@ -5049,7 +5049,7 @@
         <v>289</v>
       </c>
       <c r="B310">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C310" t="s">
         <v>58</v>
@@ -5060,7 +5060,7 @@
         <v>288</v>
       </c>
       <c r="B311">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C311" t="s">
         <v>58</v>
@@ -5071,7 +5071,7 @@
         <v>291</v>
       </c>
       <c r="B312">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C312" t="s">
         <v>58</v>
@@ -5082,7 +5082,7 @@
         <v>292</v>
       </c>
       <c r="B313">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C313" t="s">
         <v>58</v>
@@ -5093,7 +5093,7 @@
         <v>46</v>
       </c>
       <c r="B314">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C314" t="s">
         <v>58</v>
@@ -5104,7 +5104,7 @@
         <v>293</v>
       </c>
       <c r="B315">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C315" t="s">
         <v>58</v>
@@ -5115,7 +5115,7 @@
         <v>294</v>
       </c>
       <c r="B316">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C316" t="s">
         <v>58</v>
@@ -5126,7 +5126,7 @@
         <v>295</v>
       </c>
       <c r="B317">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C317" t="s">
         <v>58</v>
@@ -5137,7 +5137,7 @@
         <v>296</v>
       </c>
       <c r="B318">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C318" t="s">
         <v>58</v>
@@ -5148,7 +5148,7 @@
         <v>47</v>
       </c>
       <c r="B319">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C319" t="s">
         <v>58</v>
@@ -5159,7 +5159,7 @@
         <v>297</v>
       </c>
       <c r="B320">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C320" t="s">
         <v>58</v>
@@ -5170,7 +5170,7 @@
         <v>48</v>
       </c>
       <c r="B321">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C321" t="s">
         <v>58</v>
@@ -5181,7 +5181,7 @@
         <v>298</v>
       </c>
       <c r="B322">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C322" t="s">
         <v>58</v>
@@ -5192,7 +5192,7 @@
         <v>299</v>
       </c>
       <c r="B323">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C323" t="s">
         <v>58</v>
@@ -5203,7 +5203,7 @@
         <v>300</v>
       </c>
       <c r="B324">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C324" t="s">
         <v>58</v>
@@ -5214,7 +5214,7 @@
         <v>301</v>
       </c>
       <c r="B325">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C325" t="s">
         <v>58</v>
@@ -5225,7 +5225,7 @@
         <v>302</v>
       </c>
       <c r="B326">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C326" t="s">
         <v>58</v>
@@ -5236,7 +5236,7 @@
         <v>303</v>
       </c>
       <c r="B327">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C327" t="s">
         <v>58</v>
@@ -5247,7 +5247,7 @@
         <v>49</v>
       </c>
       <c r="B328">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C328" t="s">
         <v>58</v>
@@ -5258,7 +5258,7 @@
         <v>304</v>
       </c>
       <c r="B329">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C329" t="s">
         <v>58</v>
@@ -5269,7 +5269,7 @@
         <v>305</v>
       </c>
       <c r="B330">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C330" t="s">
         <v>58</v>
@@ -5280,7 +5280,7 @@
         <v>306</v>
       </c>
       <c r="B331">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C331" t="s">
         <v>58</v>
@@ -5291,7 +5291,7 @@
         <v>307</v>
       </c>
       <c r="B332">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C332" t="s">
         <v>58</v>
@@ -5302,7 +5302,7 @@
         <v>309</v>
       </c>
       <c r="B333">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C333" t="s">
         <v>58</v>
@@ -5313,7 +5313,7 @@
         <v>308</v>
       </c>
       <c r="B334">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C334" t="s">
         <v>58</v>
@@ -5324,7 +5324,7 @@
         <v>310</v>
       </c>
       <c r="B335">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C335" t="s">
         <v>58</v>
@@ -5335,7 +5335,7 @@
         <v>311</v>
       </c>
       <c r="B336">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C336" t="s">
         <v>58</v>
@@ -5346,7 +5346,7 @@
         <v>312</v>
       </c>
       <c r="B337">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C337" t="s">
         <v>58</v>
@@ -5357,7 +5357,7 @@
         <v>313</v>
       </c>
       <c r="B338">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C338" t="s">
         <v>58</v>
@@ -5368,7 +5368,7 @@
         <v>314</v>
       </c>
       <c r="B339">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C339" t="s">
         <v>58</v>
@@ -5379,7 +5379,7 @@
         <v>283</v>
       </c>
       <c r="B340">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C340" t="s">
         <v>58</v>
@@ -5390,7 +5390,7 @@
         <v>315</v>
       </c>
       <c r="B341">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C341" t="s">
         <v>58</v>
@@ -5401,7 +5401,7 @@
         <v>316</v>
       </c>
       <c r="B342">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C342" t="s">
         <v>58</v>
@@ -5412,7 +5412,7 @@
         <v>317</v>
       </c>
       <c r="B343">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C343" t="s">
         <v>58</v>
@@ -5423,7 +5423,7 @@
         <v>320</v>
       </c>
       <c r="B344">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C344" t="s">
         <v>58</v>
@@ -5434,7 +5434,7 @@
         <v>381</v>
       </c>
       <c r="B345">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C345" t="s">
         <v>58</v>
@@ -5445,7 +5445,7 @@
         <v>321</v>
       </c>
       <c r="B346">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C346" t="s">
         <v>58</v>
@@ -5456,7 +5456,7 @@
         <v>319</v>
       </c>
       <c r="B347">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C347" t="s">
         <v>58</v>
@@ -5467,7 +5467,7 @@
         <v>323</v>
       </c>
       <c r="B348">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C348" t="s">
         <v>58</v>
@@ -5478,7 +5478,7 @@
         <v>322</v>
       </c>
       <c r="B349">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C349" t="s">
         <v>58</v>
@@ -5489,7 +5489,7 @@
         <v>324</v>
       </c>
       <c r="B350">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C350" t="s">
         <v>58</v>
@@ -5500,7 +5500,7 @@
         <v>325</v>
       </c>
       <c r="B351">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C351" t="s">
         <v>58</v>
@@ -5511,7 +5511,7 @@
         <v>326</v>
       </c>
       <c r="B352">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C352" t="s">
         <v>58</v>
@@ -5522,7 +5522,7 @@
         <v>50</v>
       </c>
       <c r="B353">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C353" t="s">
         <v>58</v>
@@ -5533,7 +5533,7 @@
         <v>51</v>
       </c>
       <c r="B354">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C354" t="s">
         <v>58</v>
@@ -5544,7 +5544,7 @@
         <v>327</v>
       </c>
       <c r="B355">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C355" t="s">
         <v>58</v>
@@ -5555,7 +5555,7 @@
         <v>328</v>
       </c>
       <c r="B356">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C356" t="s">
         <v>58</v>
@@ -5566,7 +5566,7 @@
         <v>329</v>
       </c>
       <c r="B357">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C357" t="s">
         <v>58</v>
@@ -5577,7 +5577,7 @@
         <v>318</v>
       </c>
       <c r="B358">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C358" t="s">
         <v>58</v>
@@ -5588,7 +5588,7 @@
         <v>330</v>
       </c>
       <c r="B359">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C359" t="s">
         <v>58</v>
@@ -5599,7 +5599,7 @@
         <v>331</v>
       </c>
       <c r="B360">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C360" t="s">
         <v>58</v>
@@ -5610,7 +5610,7 @@
         <v>332</v>
       </c>
       <c r="B361">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C361" t="s">
         <v>58</v>
@@ -5621,7 +5621,7 @@
         <v>333</v>
       </c>
       <c r="B362">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C362" t="s">
         <v>58</v>
@@ -5632,7 +5632,7 @@
         <v>334</v>
       </c>
       <c r="B363">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C363" t="s">
         <v>58</v>
@@ -5643,7 +5643,7 @@
         <v>335</v>
       </c>
       <c r="B364">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C364" t="s">
         <v>58</v>
@@ -5654,7 +5654,7 @@
         <v>336</v>
       </c>
       <c r="B365">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C365" t="s">
         <v>58</v>
@@ -5665,7 +5665,7 @@
         <v>337</v>
       </c>
       <c r="B366">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C366" t="s">
         <v>58</v>
@@ -5676,7 +5676,7 @@
         <v>338</v>
       </c>
       <c r="B367">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C367" t="s">
         <v>58</v>
@@ -5687,7 +5687,7 @@
         <v>339</v>
       </c>
       <c r="B368">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C368" t="s">
         <v>58</v>
@@ -5698,7 +5698,7 @@
         <v>340</v>
       </c>
       <c r="B369">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C369" t="s">
         <v>58</v>
@@ -5709,7 +5709,7 @@
         <v>341</v>
       </c>
       <c r="B370">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C370" t="s">
         <v>58</v>
@@ -5720,7 +5720,7 @@
         <v>343</v>
       </c>
       <c r="B371">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C371" t="s">
         <v>58</v>
@@ -5731,7 +5731,7 @@
         <v>342</v>
       </c>
       <c r="B372">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C372" t="s">
         <v>58</v>
@@ -5742,7 +5742,7 @@
         <v>344</v>
       </c>
       <c r="B373">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C373" t="s">
         <v>58</v>
@@ -5753,7 +5753,7 @@
         <v>345</v>
       </c>
       <c r="B374">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C374" t="s">
         <v>58</v>
@@ -5764,7 +5764,7 @@
         <v>346</v>
       </c>
       <c r="B375">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C375" t="s">
         <v>58</v>
@@ -5775,7 +5775,7 @@
         <v>347</v>
       </c>
       <c r="B376">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C376" t="s">
         <v>58</v>
@@ -5786,7 +5786,7 @@
         <v>348</v>
       </c>
       <c r="B377">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C377" t="s">
         <v>58</v>
@@ -5797,7 +5797,7 @@
         <v>350</v>
       </c>
       <c r="B378">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C378" t="s">
         <v>58</v>
@@ -5808,7 +5808,7 @@
         <v>383</v>
       </c>
       <c r="B379">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C379" t="s">
         <v>58</v>
@@ -5819,7 +5819,7 @@
         <v>382</v>
       </c>
       <c r="B380">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C380" t="s">
         <v>58</v>
@@ -5830,7 +5830,7 @@
         <v>351</v>
       </c>
       <c r="B381">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C381" t="s">
         <v>58</v>
@@ -5841,7 +5841,7 @@
         <v>52</v>
       </c>
       <c r="B382">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C382" t="s">
         <v>58</v>
@@ -5852,7 +5852,7 @@
         <v>352</v>
       </c>
       <c r="B383">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C383" t="s">
         <v>58</v>
@@ -5863,7 +5863,7 @@
         <v>353</v>
       </c>
       <c r="B384">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C384" t="s">
         <v>58</v>
@@ -5874,7 +5874,7 @@
         <v>349</v>
       </c>
       <c r="B385">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C385" t="s">
         <v>58</v>
@@ -5885,7 +5885,7 @@
         <v>354</v>
       </c>
       <c r="B386">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C386" t="s">
         <v>58</v>
@@ -5896,7 +5896,7 @@
         <v>355</v>
       </c>
       <c r="B387">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C387" t="s">
         <v>58</v>
@@ -5907,7 +5907,7 @@
         <v>53</v>
       </c>
       <c r="B388">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C388" t="s">
         <v>58</v>
@@ -5918,7 +5918,7 @@
         <v>356</v>
       </c>
       <c r="B389">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C389" t="s">
         <v>58</v>
@@ -5929,7 +5929,7 @@
         <v>357</v>
       </c>
       <c r="B390">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C390" t="s">
         <v>58</v>
@@ -5940,7 +5940,7 @@
         <v>54</v>
       </c>
       <c r="B391">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C391" t="s">
         <v>58</v>
@@ -5951,7 +5951,7 @@
         <v>358</v>
       </c>
       <c r="B392">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C392" t="s">
         <v>58</v>
@@ -5962,7 +5962,7 @@
         <v>55</v>
       </c>
       <c r="B393">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C393" t="s">
         <v>58</v>
@@ -5973,7 +5973,7 @@
         <v>359</v>
       </c>
       <c r="B394">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C394" t="s">
         <v>58</v>
@@ -5984,7 +5984,7 @@
         <v>360</v>
       </c>
       <c r="B395">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C395" t="s">
         <v>58</v>
@@ -5995,7 +5995,7 @@
         <v>361</v>
       </c>
       <c r="B396">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C396" t="s">
         <v>58</v>
@@ -6006,7 +6006,7 @@
         <v>362</v>
       </c>
       <c r="B397">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C397" t="s">
         <v>58</v>
@@ -6017,7 +6017,7 @@
         <v>363</v>
       </c>
       <c r="B398">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C398" t="s">
         <v>58</v>
@@ -6028,7 +6028,7 @@
         <v>364</v>
       </c>
       <c r="B399">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C399" t="s">
         <v>58</v>
@@ -6039,7 +6039,7 @@
         <v>365</v>
       </c>
       <c r="B400">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C400" t="s">
         <v>58</v>
@@ -6050,7 +6050,7 @@
         <v>56</v>
       </c>
       <c r="B401">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C401" t="s">
         <v>58</v>
@@ -6061,7 +6061,7 @@
         <v>366</v>
       </c>
       <c r="B402">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C402" t="s">
         <v>58</v>
@@ -6072,7 +6072,7 @@
         <v>367</v>
       </c>
       <c r="B403">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C403" t="s">
         <v>58</v>
@@ -6083,7 +6083,7 @@
         <v>368</v>
       </c>
       <c r="B404">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C404" t="s">
         <v>58</v>
@@ -6094,7 +6094,7 @@
         <v>407</v>
       </c>
       <c r="B405">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C405" t="s">
         <v>58</v>
@@ -6105,7 +6105,7 @@
         <v>369</v>
       </c>
       <c r="B406">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C406" t="s">
         <v>58</v>
@@ -6116,7 +6116,7 @@
         <v>370</v>
       </c>
       <c r="B407">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C407" t="s">
         <v>58</v>
@@ -6127,7 +6127,7 @@
         <v>371</v>
       </c>
       <c r="B408">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C408" t="s">
         <v>58</v>
@@ -6138,7 +6138,7 @@
         <v>57</v>
       </c>
       <c r="B409">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="C409" t="s">
         <v>58</v>

--- a/ativos.xlsx
+++ b/ativos.xlsx
@@ -1,22 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\INVESTIMENTOS VARIAVEL\Bybit\bybit_setups\complementos\GitHub\bybit_setups\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E118378-A4CB-462D-8011-FFA246FEB3D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B0280B-E961-443A-8119-28EC508648B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="PARES" sheetId="1" r:id="rId1"/>
+    <sheet name="CONFIG_UNIVERSO" sheetId="3" r:id="rId2"/>
+    <sheet name="CONFIG_REGIME" sheetId="4" r:id="rId3"/>
+    <sheet name="CONFIG_FORCA_RELATIVA" sheetId="5" r:id="rId4"/>
+    <sheet name="CONFIG_FUNDING_OI" sheetId="6" r:id="rId5"/>
+    <sheet name="CONFIG_GRID" sheetId="7" r:id="rId6"/>
+    <sheet name="EXCECOES_ATIVOS" sheetId="8" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">PARES!$A$1:$C$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="516">
   <si>
     <t>Par</t>
   </si>
@@ -1272,13 +1278,325 @@
   </si>
   <si>
     <t>OPGUSDT</t>
+  </si>
+  <si>
+    <t>Parametro</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>Descricao</t>
+  </si>
+  <si>
+    <t>modo_universo</t>
+  </si>
+  <si>
+    <t>HIBRIDO</t>
+  </si>
+  <si>
+    <t>AUTO busca tudo na Bybit; MANUAL usa ativos.xlsx; HIBRIDO usa Bybit + exceções.</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>Categoria Bybit V5.</t>
+  </si>
+  <si>
+    <t>quote_coin</t>
+  </si>
+  <si>
+    <t>USDT</t>
+  </si>
+  <si>
+    <t>Moeda de cotação.</t>
+  </si>
+  <si>
+    <t>settle_coin</t>
+  </si>
+  <si>
+    <t>Moeda de liquidação.</t>
+  </si>
+  <si>
+    <t>contract_type</t>
+  </si>
+  <si>
+    <t>LinearPerpetual</t>
+  </si>
+  <si>
+    <t>Tipo de contrato.</t>
+  </si>
+  <si>
+    <t>min_age_days</t>
+  </si>
+  <si>
+    <t>Idade mínima desde listagem.</t>
+  </si>
+  <si>
+    <t>default_timeframes</t>
+  </si>
+  <si>
+    <t>240</t>
+  </si>
+  <si>
+    <t>Timeframes padrão para ativos automáticos. Ex.: 240 ou 120,240.</t>
+  </si>
+  <si>
+    <t>kline_limit</t>
+  </si>
+  <si>
+    <t>Quantidade de candles por par/timeframe.</t>
+  </si>
+  <si>
+    <t>min_turnover24h_usdt</t>
+  </si>
+  <si>
+    <t>Turnover financeiro mínimo em 24h.</t>
+  </si>
+  <si>
+    <t>max_spread_pct</t>
+  </si>
+  <si>
+    <t>Spread máximo bid/ask. 0,0005 = 0,05%.</t>
+  </si>
+  <si>
+    <t>min_open_interest_value</t>
+  </si>
+  <si>
+    <t>Open Interest Value mínimo.</t>
+  </si>
+  <si>
+    <t>orderbook_limit</t>
+  </si>
+  <si>
+    <t>Profundidade do book consultada.</t>
+  </si>
+  <si>
+    <t>min_depth_1pct_usdt</t>
+  </si>
+  <si>
+    <t>Profundidade mínima até 1% no lado mais fraco.</t>
+  </si>
+  <si>
+    <t>max_slippage_pct</t>
+  </si>
+  <si>
+    <t>Slippage estimado máximo. 0,003 = 0,30%.</t>
+  </si>
+  <si>
+    <t>capturar_orderbook</t>
+  </si>
+  <si>
+    <t>SIM</t>
+  </si>
+  <si>
+    <t>Capturar profundidade, imbalance e slippage estimado.</t>
+  </si>
+  <si>
+    <t>capturar_oi_historico</t>
+  </si>
+  <si>
+    <t>Capturar histórico de Open Interest.</t>
+  </si>
+  <si>
+    <t>capturar_funding_historico</t>
+  </si>
+  <si>
+    <t>Capturar histórico de funding para z-score.</t>
+  </si>
+  <si>
+    <t>capturar_long_short</t>
+  </si>
+  <si>
+    <t>Capturar long/short ratio.</t>
+  </si>
+  <si>
+    <t>adx_period</t>
+  </si>
+  <si>
+    <t>Período do ADX.</t>
+  </si>
+  <si>
+    <t>atr_period</t>
+  </si>
+  <si>
+    <t>Período do ATR para regime.</t>
+  </si>
+  <si>
+    <t>chop_period</t>
+  </si>
+  <si>
+    <t>Período do Choppiness Index.</t>
+  </si>
+  <si>
+    <t>er_period</t>
+  </si>
+  <si>
+    <t>Período do Efficiency Ratio.</t>
+  </si>
+  <si>
+    <t>bb_period</t>
+  </si>
+  <si>
+    <t>Período das Bandas de Bollinger.</t>
+  </si>
+  <si>
+    <t>bb_std</t>
+  </si>
+  <si>
+    <t>Desvio padrão das Bandas de Bollinger.</t>
+  </si>
+  <si>
+    <t>percentile_lookback</t>
+  </si>
+  <si>
+    <t>Janela para percentis de ATR/BB Width.</t>
+  </si>
+  <si>
+    <t>adx_min_trend</t>
+  </si>
+  <si>
+    <t>ADX mínimo para regime de tendência.</t>
+  </si>
+  <si>
+    <t>chop_max_trend</t>
+  </si>
+  <si>
+    <t>CHOP máximo para tendência.</t>
+  </si>
+  <si>
+    <t>er_min_trend</t>
+  </si>
+  <si>
+    <t>Efficiency Ratio mínimo.</t>
+  </si>
+  <si>
+    <t>atr_percentile_min</t>
+  </si>
+  <si>
+    <t>ATR percentil mínimo.</t>
+  </si>
+  <si>
+    <t>atr_percentile_max</t>
+  </si>
+  <si>
+    <t>ATR percentil máximo.</t>
+  </si>
+  <si>
+    <t>bb_width_percentile_compression</t>
+  </si>
+  <si>
+    <t>BB Width percentil abaixo disso indica compressão.</t>
+  </si>
+  <si>
+    <t>rs_short_window</t>
+  </si>
+  <si>
+    <t>Janela curta de retorno em candles.</t>
+  </si>
+  <si>
+    <t>rs_mid_window</t>
+  </si>
+  <si>
+    <t>Janela média de retorno em candles.</t>
+  </si>
+  <si>
+    <t>rs_long_window</t>
+  </si>
+  <si>
+    <t>Janela longa de retorno em candles.</t>
+  </si>
+  <si>
+    <t>rs_min_long</t>
+  </si>
+  <si>
+    <t>Rank mínimo para compra/long.</t>
+  </si>
+  <si>
+    <t>rs_max_short</t>
+  </si>
+  <si>
+    <t>Rank máximo para venda/short.</t>
+  </si>
+  <si>
+    <t>score_min_setup</t>
+  </si>
+  <si>
+    <t>Score mínimo para APROVADO_SCORE.</t>
+  </si>
+  <si>
+    <t>max_abs_funding_rate</t>
+  </si>
+  <si>
+    <t>Funding absoluto máximo. 0,003 = 0,30%.</t>
+  </si>
+  <si>
+    <t>max_funding_zscore</t>
+  </si>
+  <si>
+    <t>Z-score máximo de funding.</t>
+  </si>
+  <si>
+    <t>oi_interval</t>
+  </si>
+  <si>
+    <t>4h</t>
+  </si>
+  <si>
+    <t>Intervalo do Open Interest histórico.</t>
+  </si>
+  <si>
+    <t>account_ratio_period</t>
+  </si>
+  <si>
+    <t>Intervalo do long/short ratio.</t>
+  </si>
+  <si>
+    <t>api_sleep_s</t>
+  </si>
+  <si>
+    <t>Pausa entre chamadas REST públicas.</t>
+  </si>
+  <si>
+    <t>grid_spacing_pct</t>
+  </si>
+  <si>
+    <t>Espaçamento de referência para estimar número de grids. 0,005 = 0,50%.</t>
+  </si>
+  <si>
+    <t>Acao</t>
+  </si>
+  <si>
+    <t>Timeframes</t>
+  </si>
+  <si>
+    <t>Observacao</t>
+  </si>
+  <si>
+    <t>BTCUSDT</t>
+  </si>
+  <si>
+    <t>FORCAR_INCLUSAO</t>
+  </si>
+  <si>
+    <t>Exemplo: sempre analisar.</t>
+  </si>
+  <si>
+    <t>TOKENXYZUSDT</t>
+  </si>
+  <si>
+    <t>EXCLUIR</t>
+  </si>
+  <si>
+    <t>Exemplo: bloquear ativo manualmente.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1294,13 +1612,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0F766E"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -1327,17 +1661,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{3FE34418-C5A5-4AF1-A5F7-3EE7E148DFB4}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1640,12 +1980,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C409"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1656,7 +1996,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>385</v>
       </c>
@@ -1667,7 +2007,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>59</v>
       </c>
@@ -1678,7 +2018,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>372</v>
       </c>
@@ -1689,7 +2029,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1700,7 +2040,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1711,7 +2051,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>60</v>
       </c>
@@ -1722,7 +2062,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>373</v>
       </c>
@@ -1733,7 +2073,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>61</v>
       </c>
@@ -1744,7 +2084,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -1755,7 +2095,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>386</v>
       </c>
@@ -1766,7 +2106,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -1777,7 +2117,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>64</v>
       </c>
@@ -1788,7 +2128,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -1799,7 +2139,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>66</v>
       </c>
@@ -1810,7 +2150,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -1821,7 +2161,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -1832,7 +2172,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>68</v>
       </c>
@@ -1843,7 +2183,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>69</v>
       </c>
@@ -1854,7 +2194,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>70</v>
       </c>
@@ -1865,7 +2205,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>71</v>
       </c>
@@ -1876,7 +2216,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>72</v>
       </c>
@@ -1887,7 +2227,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>387</v>
       </c>
@@ -1898,7 +2238,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>73</v>
       </c>
@@ -1909,7 +2249,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>400</v>
       </c>
@@ -1920,7 +2260,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>74</v>
       </c>
@@ -1931,7 +2271,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>75</v>
       </c>
@@ -1942,7 +2282,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>7</v>
       </c>
@@ -1953,7 +2293,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>76</v>
       </c>
@@ -1964,7 +2304,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>388</v>
       </c>
@@ -1975,7 +2315,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>77</v>
       </c>
@@ -1986,7 +2326,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>78</v>
       </c>
@@ -1997,7 +2337,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>79</v>
       </c>
@@ -2008,7 +2348,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>8</v>
       </c>
@@ -2019,7 +2359,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>9</v>
       </c>
@@ -2030,7 +2370,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>389</v>
       </c>
@@ -2041,7 +2381,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>80</v>
       </c>
@@ -2052,7 +2392,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>81</v>
       </c>
@@ -2063,7 +2403,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>10</v>
       </c>
@@ -2074,7 +2414,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>390</v>
       </c>
@@ -2085,7 +2425,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>83</v>
       </c>
@@ -2096,7 +2436,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>82</v>
       </c>
@@ -2107,7 +2447,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>84</v>
       </c>
@@ -2118,7 +2458,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>374</v>
       </c>
@@ -2129,7 +2469,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>391</v>
       </c>
@@ -2140,7 +2480,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>392</v>
       </c>
@@ -2151,7 +2491,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>85</v>
       </c>
@@ -2162,7 +2502,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>86</v>
       </c>
@@ -2173,7 +2513,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>87</v>
       </c>
@@ -2184,7 +2524,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>393</v>
       </c>
@@ -2195,7 +2535,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>88</v>
       </c>
@@ -2206,7 +2546,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>62</v>
       </c>
@@ -2217,7 +2557,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>89</v>
       </c>
@@ -2228,7 +2568,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>11</v>
       </c>
@@ -2239,7 +2579,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>394</v>
       </c>
@@ -2250,7 +2590,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>90</v>
       </c>
@@ -2261,7 +2601,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>91</v>
       </c>
@@ -2272,7 +2612,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>92</v>
       </c>
@@ -2283,7 +2623,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>93</v>
       </c>
@@ -2294,7 +2634,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>94</v>
       </c>
@@ -2305,7 +2645,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>95</v>
       </c>
@@ -2316,7 +2656,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>97</v>
       </c>
@@ -2327,7 +2667,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>98</v>
       </c>
@@ -2338,7 +2678,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>99</v>
       </c>
@@ -2349,7 +2689,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>96</v>
       </c>
@@ -2360,7 +2700,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>100</v>
       </c>
@@ -2371,7 +2711,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>101</v>
       </c>
@@ -2382,7 +2722,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>102</v>
       </c>
@@ -2393,7 +2733,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>103</v>
       </c>
@@ -2404,7 +2744,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>397</v>
       </c>
@@ -2415,7 +2755,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>104</v>
       </c>
@@ -2426,7 +2766,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>105</v>
       </c>
@@ -2437,7 +2777,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>106</v>
       </c>
@@ -2448,7 +2788,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>12</v>
       </c>
@@ -2459,7 +2799,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>107</v>
       </c>
@@ -2470,7 +2810,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>375</v>
       </c>
@@ -2481,7 +2821,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>402</v>
       </c>
@@ -2492,7 +2832,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>108</v>
       </c>
@@ -2503,7 +2843,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>109</v>
       </c>
@@ -2514,7 +2854,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>13</v>
       </c>
@@ -2525,7 +2865,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>110</v>
       </c>
@@ -2536,7 +2876,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>111</v>
       </c>
@@ -2547,7 +2887,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>112</v>
       </c>
@@ -2558,7 +2898,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>14</v>
       </c>
@@ -2569,7 +2909,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>113</v>
       </c>
@@ -2580,7 +2920,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>15</v>
       </c>
@@ -2591,7 +2931,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>114</v>
       </c>
@@ -2602,7 +2942,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>396</v>
       </c>
@@ -2613,7 +2953,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>409</v>
       </c>
@@ -2624,7 +2964,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>116</v>
       </c>
@@ -2635,7 +2975,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>117</v>
       </c>
@@ -2646,7 +2986,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>118</v>
       </c>
@@ -2657,7 +2997,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>119</v>
       </c>
@@ -2668,7 +3008,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>120</v>
       </c>
@@ -2679,7 +3019,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>121</v>
       </c>
@@ -2690,7 +3030,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>122</v>
       </c>
@@ -2701,7 +3041,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>123</v>
       </c>
@@ -2712,7 +3052,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>124</v>
       </c>
@@ -2723,7 +3063,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>125</v>
       </c>
@@ -2734,7 +3074,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>126</v>
       </c>
@@ -2745,7 +3085,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>376</v>
       </c>
@@ -2756,7 +3096,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>127</v>
       </c>
@@ -2767,7 +3107,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>408</v>
       </c>
@@ -2778,7 +3118,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>16</v>
       </c>
@@ -2789,7 +3129,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>128</v>
       </c>
@@ -2800,7 +3140,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>17</v>
       </c>
@@ -2811,7 +3151,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -2822,7 +3162,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>129</v>
       </c>
@@ -2833,7 +3173,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>131</v>
       </c>
@@ -2844,7 +3184,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>130</v>
       </c>
@@ -2855,7 +3195,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>132</v>
       </c>
@@ -2866,7 +3206,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>133</v>
       </c>
@@ -2877,7 +3217,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>115</v>
       </c>
@@ -2888,7 +3228,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>134</v>
       </c>
@@ -2899,7 +3239,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>135</v>
       </c>
@@ -2910,7 +3250,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>136</v>
       </c>
@@ -2921,7 +3261,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>137</v>
       </c>
@@ -2932,7 +3272,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>138</v>
       </c>
@@ -2943,7 +3283,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>139</v>
       </c>
@@ -2954,7 +3294,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>140</v>
       </c>
@@ -2965,7 +3305,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>141</v>
       </c>
@@ -2976,7 +3316,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>19</v>
       </c>
@@ -2987,7 +3327,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>142</v>
       </c>
@@ -2998,7 +3338,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>143</v>
       </c>
@@ -3009,7 +3349,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>144</v>
       </c>
@@ -3020,7 +3360,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>145</v>
       </c>
@@ -3031,7 +3371,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>146</v>
       </c>
@@ -3042,7 +3382,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>147</v>
       </c>
@@ -3053,7 +3393,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>403</v>
       </c>
@@ -3064,7 +3404,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>148</v>
       </c>
@@ -3075,7 +3415,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>149</v>
       </c>
@@ -3086,7 +3426,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>150</v>
       </c>
@@ -3097,7 +3437,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>20</v>
       </c>
@@ -3108,7 +3448,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>151</v>
       </c>
@@ -3119,7 +3459,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>152</v>
       </c>
@@ -3130,7 +3470,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>153</v>
       </c>
@@ -3141,7 +3481,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>154</v>
       </c>
@@ -3152,7 +3492,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>155</v>
       </c>
@@ -3163,7 +3503,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>156</v>
       </c>
@@ -3174,7 +3514,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>157</v>
       </c>
@@ -3185,7 +3525,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>158</v>
       </c>
@@ -3196,7 +3536,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>21</v>
       </c>
@@ -3207,7 +3547,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>410</v>
       </c>
@@ -3218,7 +3558,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>22</v>
       </c>
@@ -3229,7 +3569,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>399</v>
       </c>
@@ -3240,7 +3580,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>159</v>
       </c>
@@ -3251,7 +3591,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>160</v>
       </c>
@@ -3262,7 +3602,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>161</v>
       </c>
@@ -3273,7 +3613,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>162</v>
       </c>
@@ -3284,7 +3624,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>163</v>
       </c>
@@ -3295,7 +3635,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>164</v>
       </c>
@@ -3306,7 +3646,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>405</v>
       </c>
@@ -3317,7 +3657,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>165</v>
       </c>
@@ -3328,7 +3668,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>23</v>
       </c>
@@ -3339,7 +3679,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>24</v>
       </c>
@@ -3350,7 +3690,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>166</v>
       </c>
@@ -3361,7 +3701,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>395</v>
       </c>
@@ -3372,7 +3712,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>167</v>
       </c>
@@ -3383,7 +3723,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>168</v>
       </c>
@@ -3394,7 +3734,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>25</v>
       </c>
@@ -3405,7 +3745,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>169</v>
       </c>
@@ -3416,7 +3756,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>170</v>
       </c>
@@ -3427,7 +3767,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>171</v>
       </c>
@@ -3438,7 +3778,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>172</v>
       </c>
@@ -3449,7 +3789,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>173</v>
       </c>
@@ -3460,7 +3800,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>174</v>
       </c>
@@ -3471,7 +3811,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>175</v>
       </c>
@@ -3482,7 +3822,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>176</v>
       </c>
@@ -3493,7 +3833,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>177</v>
       </c>
@@ -3504,7 +3844,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>179</v>
       </c>
@@ -3515,7 +3855,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>180</v>
       </c>
@@ -3526,7 +3866,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>181</v>
       </c>
@@ -3537,7 +3877,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>182</v>
       </c>
@@ -3548,7 +3888,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>183</v>
       </c>
@@ -3559,7 +3899,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>184</v>
       </c>
@@ -3570,7 +3910,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>185</v>
       </c>
@@ -3581,7 +3921,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>186</v>
       </c>
@@ -3592,7 +3932,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>187</v>
       </c>
@@ -3603,7 +3943,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>188</v>
       </c>
@@ -3614,7 +3954,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>178</v>
       </c>
@@ -3625,7 +3965,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>190</v>
       </c>
@@ -3636,7 +3976,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>189</v>
       </c>
@@ -3647,7 +3987,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>191</v>
       </c>
@@ -3658,7 +3998,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>377</v>
       </c>
@@ -3669,7 +4009,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>192</v>
       </c>
@@ -3680,7 +4020,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>193</v>
       </c>
@@ -3691,7 +4031,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>194</v>
       </c>
@@ -3702,7 +4042,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>195</v>
       </c>
@@ -3713,7 +4053,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>196</v>
       </c>
@@ -3724,7 +4064,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>197</v>
       </c>
@@ -3735,7 +4075,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>199</v>
       </c>
@@ -3746,7 +4086,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>200</v>
       </c>
@@ -3757,7 +4097,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>201</v>
       </c>
@@ -3768,7 +4108,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>198</v>
       </c>
@@ -3779,7 +4119,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>202</v>
       </c>
@@ -3790,7 +4130,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>26</v>
       </c>
@@ -3801,7 +4141,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>203</v>
       </c>
@@ -3812,7 +4152,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>204</v>
       </c>
@@ -3823,7 +4163,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>27</v>
       </c>
@@ -3834,7 +4174,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>28</v>
       </c>
@@ -3845,7 +4185,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>205</v>
       </c>
@@ -3856,7 +4196,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>206</v>
       </c>
@@ -3867,7 +4207,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>29</v>
       </c>
@@ -3878,7 +4218,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>207</v>
       </c>
@@ -3889,7 +4229,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>378</v>
       </c>
@@ -3900,7 +4240,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>30</v>
       </c>
@@ -3911,7 +4251,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>208</v>
       </c>
@@ -3922,7 +4262,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>209</v>
       </c>
@@ -3933,7 +4273,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>210</v>
       </c>
@@ -3944,7 +4284,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>211</v>
       </c>
@@ -3955,7 +4295,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>398</v>
       </c>
@@ -3966,7 +4306,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>31</v>
       </c>
@@ -3977,7 +4317,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>212</v>
       </c>
@@ -3988,7 +4328,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>213</v>
       </c>
@@ -3999,7 +4339,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>214</v>
       </c>
@@ -4010,7 +4350,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>215</v>
       </c>
@@ -4021,7 +4361,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>216</v>
       </c>
@@ -4032,7 +4372,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>217</v>
       </c>
@@ -4043,7 +4383,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>218</v>
       </c>
@@ -4054,7 +4394,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>220</v>
       </c>
@@ -4065,7 +4405,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>404</v>
       </c>
@@ -4076,7 +4416,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>32</v>
       </c>
@@ -4087,7 +4427,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>221</v>
       </c>
@@ -4098,7 +4438,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>222</v>
       </c>
@@ -4109,7 +4449,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>224</v>
       </c>
@@ -4120,7 +4460,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>223</v>
       </c>
@@ -4131,7 +4471,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>225</v>
       </c>
@@ -4142,7 +4482,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>227</v>
       </c>
@@ -4153,7 +4493,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>228</v>
       </c>
@@ -4164,7 +4504,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>229</v>
       </c>
@@ -4175,7 +4515,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>230</v>
       </c>
@@ -4186,7 +4526,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>226</v>
       </c>
@@ -4197,7 +4537,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>33</v>
       </c>
@@ -4208,7 +4548,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>231</v>
       </c>
@@ -4219,7 +4559,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>232</v>
       </c>
@@ -4230,7 +4570,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>34</v>
       </c>
@@ -4241,7 +4581,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>233</v>
       </c>
@@ -4252,7 +4592,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>35</v>
       </c>
@@ -4263,7 +4603,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>36</v>
       </c>
@@ -4274,7 +4614,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>234</v>
       </c>
@@ -4285,7 +4625,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>235</v>
       </c>
@@ -4296,7 +4636,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>236</v>
       </c>
@@ -4307,7 +4647,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>237</v>
       </c>
@@ -4318,7 +4658,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>219</v>
       </c>
@@ -4329,7 +4669,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>384</v>
       </c>
@@ -4340,7 +4680,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>37</v>
       </c>
@@ -4351,7 +4691,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>238</v>
       </c>
@@ -4362,7 +4702,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>239</v>
       </c>
@@ -4373,7 +4713,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>240</v>
       </c>
@@ -4384,7 +4724,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>241</v>
       </c>
@@ -4395,7 +4735,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>401</v>
       </c>
@@ -4406,7 +4746,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>38</v>
       </c>
@@ -4417,7 +4757,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>242</v>
       </c>
@@ -4428,7 +4768,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>244</v>
       </c>
@@ -4439,7 +4779,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>243</v>
       </c>
@@ -4450,7 +4790,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>39</v>
       </c>
@@ -4461,7 +4801,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>245</v>
       </c>
@@ -4472,7 +4812,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>246</v>
       </c>
@@ -4483,7 +4823,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>411</v>
       </c>
@@ -4494,7 +4834,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>40</v>
       </c>
@@ -4505,7 +4845,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>247</v>
       </c>
@@ -4516,7 +4856,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>41</v>
       </c>
@@ -4527,7 +4867,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>248</v>
       </c>
@@ -4538,7 +4878,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>249</v>
       </c>
@@ -4549,7 +4889,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>250</v>
       </c>
@@ -4560,7 +4900,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>251</v>
       </c>
@@ -4571,7 +4911,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>252</v>
       </c>
@@ -4582,7 +4922,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>42</v>
       </c>
@@ -4593,7 +4933,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>253</v>
       </c>
@@ -4604,7 +4944,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>254</v>
       </c>
@@ -4615,7 +4955,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>406</v>
       </c>
@@ -4626,7 +4966,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>255</v>
       </c>
@@ -4637,7 +4977,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>256</v>
       </c>
@@ -4648,7 +4988,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>257</v>
       </c>
@@ -4659,7 +4999,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>258</v>
       </c>
@@ -4670,7 +5010,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>259</v>
       </c>
@@ -4681,7 +5021,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>260</v>
       </c>
@@ -4692,7 +5032,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>261</v>
       </c>
@@ -4703,7 +5043,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>43</v>
       </c>
@@ -4714,7 +5054,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>262</v>
       </c>
@@ -4725,7 +5065,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>263</v>
       </c>
@@ -4736,7 +5076,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>264</v>
       </c>
@@ -4747,7 +5087,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>265</v>
       </c>
@@ -4758,7 +5098,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>266</v>
       </c>
@@ -4769,7 +5109,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>267</v>
       </c>
@@ -4780,7 +5120,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>379</v>
       </c>
@@ -4791,7 +5131,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>268</v>
       </c>
@@ -4802,7 +5142,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>44</v>
       </c>
@@ -4813,7 +5153,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>269</v>
       </c>
@@ -4824,7 +5164,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>270</v>
       </c>
@@ -4835,7 +5175,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>271</v>
       </c>
@@ -4846,7 +5186,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>272</v>
       </c>
@@ -4857,7 +5197,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>273</v>
       </c>
@@ -4868,7 +5208,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>274</v>
       </c>
@@ -4879,7 +5219,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>275</v>
       </c>
@@ -4890,7 +5230,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>276</v>
       </c>
@@ -4901,7 +5241,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>277</v>
       </c>
@@ -4912,7 +5252,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>278</v>
       </c>
@@ -4923,7 +5263,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>380</v>
       </c>
@@ -4934,7 +5274,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>279</v>
       </c>
@@ -4945,7 +5285,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>280</v>
       </c>
@@ -4956,7 +5296,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>281</v>
       </c>
@@ -4967,7 +5307,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>45</v>
       </c>
@@ -4978,7 +5318,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>282</v>
       </c>
@@ -4989,7 +5329,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>284</v>
       </c>
@@ -5000,7 +5340,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>285</v>
       </c>
@@ -5011,7 +5351,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>286</v>
       </c>
@@ -5022,7 +5362,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>287</v>
       </c>
@@ -5033,7 +5373,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>290</v>
       </c>
@@ -5044,7 +5384,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>289</v>
       </c>
@@ -5055,7 +5395,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>288</v>
       </c>
@@ -5066,7 +5406,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>291</v>
       </c>
@@ -5077,7 +5417,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>292</v>
       </c>
@@ -5088,7 +5428,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>46</v>
       </c>
@@ -5099,7 +5439,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>293</v>
       </c>
@@ -5110,7 +5450,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>294</v>
       </c>
@@ -5121,7 +5461,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>295</v>
       </c>
@@ -5132,7 +5472,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>296</v>
       </c>
@@ -5143,7 +5483,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>47</v>
       </c>
@@ -5154,7 +5494,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>297</v>
       </c>
@@ -5165,7 +5505,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>48</v>
       </c>
@@ -5176,7 +5516,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>298</v>
       </c>
@@ -5187,7 +5527,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>299</v>
       </c>
@@ -5198,7 +5538,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>300</v>
       </c>
@@ -5209,7 +5549,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>301</v>
       </c>
@@ -5220,7 +5560,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>302</v>
       </c>
@@ -5231,7 +5571,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>303</v>
       </c>
@@ -5242,7 +5582,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>49</v>
       </c>
@@ -5253,7 +5593,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>304</v>
       </c>
@@ -5264,7 +5604,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>305</v>
       </c>
@@ -5275,7 +5615,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>306</v>
       </c>
@@ -5286,7 +5626,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>307</v>
       </c>
@@ -5297,7 +5637,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>309</v>
       </c>
@@ -5308,7 +5648,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>308</v>
       </c>
@@ -5319,7 +5659,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>310</v>
       </c>
@@ -5330,7 +5670,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>311</v>
       </c>
@@ -5341,7 +5681,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>312</v>
       </c>
@@ -5352,7 +5692,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>313</v>
       </c>
@@ -5363,7 +5703,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>314</v>
       </c>
@@ -5374,7 +5714,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>283</v>
       </c>
@@ -5385,7 +5725,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>315</v>
       </c>
@@ -5396,7 +5736,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>316</v>
       </c>
@@ -5407,7 +5747,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>317</v>
       </c>
@@ -5418,7 +5758,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>320</v>
       </c>
@@ -5429,7 +5769,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>381</v>
       </c>
@@ -5440,7 +5780,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>321</v>
       </c>
@@ -5451,7 +5791,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>319</v>
       </c>
@@ -5462,7 +5802,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>323</v>
       </c>
@@ -5473,7 +5813,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>322</v>
       </c>
@@ -5484,7 +5824,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>324</v>
       </c>
@@ -5495,7 +5835,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>325</v>
       </c>
@@ -5506,7 +5846,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>326</v>
       </c>
@@ -5517,7 +5857,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>50</v>
       </c>
@@ -5528,7 +5868,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>51</v>
       </c>
@@ -5539,7 +5879,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>327</v>
       </c>
@@ -5550,7 +5890,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>328</v>
       </c>
@@ -5561,7 +5901,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>329</v>
       </c>
@@ -5572,7 +5912,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>318</v>
       </c>
@@ -5583,7 +5923,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>330</v>
       </c>
@@ -5594,7 +5934,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>331</v>
       </c>
@@ -5605,7 +5945,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>332</v>
       </c>
@@ -5616,7 +5956,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>333</v>
       </c>
@@ -5627,7 +5967,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>334</v>
       </c>
@@ -5638,7 +5978,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>335</v>
       </c>
@@ -5649,7 +5989,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>336</v>
       </c>
@@ -5660,7 +6000,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>337</v>
       </c>
@@ -5671,7 +6011,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>338</v>
       </c>
@@ -5682,7 +6022,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>339</v>
       </c>
@@ -5693,7 +6033,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>340</v>
       </c>
@@ -5704,7 +6044,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>341</v>
       </c>
@@ -5715,7 +6055,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>343</v>
       </c>
@@ -5726,7 +6066,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>342</v>
       </c>
@@ -5737,7 +6077,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>344</v>
       </c>
@@ -5748,7 +6088,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>345</v>
       </c>
@@ -5759,7 +6099,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>346</v>
       </c>
@@ -5770,7 +6110,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>347</v>
       </c>
@@ -5781,7 +6121,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>348</v>
       </c>
@@ -5792,7 +6132,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>350</v>
       </c>
@@ -5803,7 +6143,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>383</v>
       </c>
@@ -5814,7 +6154,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>382</v>
       </c>
@@ -5825,7 +6165,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>351</v>
       </c>
@@ -5836,7 +6176,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>52</v>
       </c>
@@ -5847,7 +6187,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>352</v>
       </c>
@@ -5858,7 +6198,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>353</v>
       </c>
@@ -5869,7 +6209,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>349</v>
       </c>
@@ -5880,7 +6220,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>354</v>
       </c>
@@ -5891,7 +6231,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>355</v>
       </c>
@@ -5902,7 +6242,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>53</v>
       </c>
@@ -5913,7 +6253,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>356</v>
       </c>
@@ -5924,7 +6264,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>357</v>
       </c>
@@ -5935,7 +6275,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>54</v>
       </c>
@@ -5946,7 +6286,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>358</v>
       </c>
@@ -5957,7 +6297,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>55</v>
       </c>
@@ -5968,7 +6308,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>359</v>
       </c>
@@ -5979,7 +6319,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>360</v>
       </c>
@@ -5990,7 +6330,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>361</v>
       </c>
@@ -6001,7 +6341,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>362</v>
       </c>
@@ -6012,7 +6352,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>363</v>
       </c>
@@ -6023,7 +6363,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>364</v>
       </c>
@@ -6034,7 +6374,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>365</v>
       </c>
@@ -6045,7 +6385,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>56</v>
       </c>
@@ -6056,7 +6396,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>366</v>
       </c>
@@ -6067,7 +6407,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>367</v>
       </c>
@@ -6078,7 +6418,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>368</v>
       </c>
@@ -6089,7 +6429,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>407</v>
       </c>
@@ -6100,7 +6440,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>369</v>
       </c>
@@ -6111,7 +6451,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>370</v>
       </c>
@@ -6122,7 +6462,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>371</v>
       </c>
@@ -6133,7 +6473,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>57</v>
       </c>
@@ -6155,4 +6495,703 @@
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93F0B986-6F00-4898-AAF8-4225C5C7F5F4}">
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="28" style="3" customWidth="1"/>
+    <col min="2" max="2" width="20" style="3" customWidth="1"/>
+    <col min="3" max="3" width="70" style="3" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="B7" s="3">
+        <v>90</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B9" s="3">
+        <v>200</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="B10" s="3">
+        <v>10000000</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="B11" s="3">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1000000</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="B13" s="3">
+        <v>200</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="B14" s="3">
+        <v>250000</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="B15" s="3">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>455</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AD8DA9F-2545-4FA1-99BD-09F9BD908DA4}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="28" style="3" customWidth="1"/>
+    <col min="2" max="2" width="20" style="3" customWidth="1"/>
+    <col min="3" max="3" width="70" style="3" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="B2" s="3">
+        <v>14</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="B3" s="3">
+        <v>14</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="B4" s="3">
+        <v>14</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="B5" s="3">
+        <v>10</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="B6" s="3">
+        <v>20</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="B7" s="3">
+        <v>2</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="B8" s="3">
+        <v>90</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="B9" s="3">
+        <v>18</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="B10" s="3">
+        <v>55</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="B12" s="3">
+        <v>25</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="B13" s="3">
+        <v>85</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="B14" s="3">
+        <v>20</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>481</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2959A29D-B2C8-4AE1-B616-61180D6215F2}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="28" style="3" customWidth="1"/>
+    <col min="2" max="2" width="20" style="3" customWidth="1"/>
+    <col min="3" max="3" width="70" style="3" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="B2" s="3">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="B3" s="3">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="B4" s="3">
+        <v>12</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="B5" s="3">
+        <v>65</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="B6" s="3">
+        <v>35</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="B7" s="3">
+        <v>70</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>493</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BB6560A-5865-43EC-BBFA-28BB0B0E8C87}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="28" style="3" customWidth="1"/>
+    <col min="2" max="2" width="20" style="3" customWidth="1"/>
+    <col min="3" max="3" width="70" style="3" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="B2" s="3">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="B3" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0.08</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>504</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A338FB6F-4D01-4F24-AC37-909EB973780A}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="28" style="3" customWidth="1"/>
+    <col min="2" max="2" width="20" style="3" customWidth="1"/>
+    <col min="3" max="3" width="70" style="3" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B2" s="3">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>506</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EDA6476-619C-437C-94BC-2AF48BA6BE85}">
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18" style="3" customWidth="1"/>
+    <col min="2" max="2" width="20" style="3" customWidth="1"/>
+    <col min="3" max="3" width="18" style="3" customWidth="1"/>
+    <col min="4" max="4" width="12" style="3" customWidth="1"/>
+    <col min="5" max="5" width="60" style="3" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>515</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="B2:B500" xr:uid="{89E22ECE-CA94-4B55-B0BE-434F5CBBD119}">
+      <formula1>"AUTO,FORCAR_INCLUSAO,EXCLUIR"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/ativos.xlsx
+++ b/ativos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\INVESTIMENTOS VARIAVEL\Bybit\bybit_setups\complementos\GitHub\bybit_setups\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\INVESTIMENTOS VARIAVEL\Bybit\bybit_setups\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B0280B-E961-443A-8119-28EC508648B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3AF1526-005B-4EB6-A394-F71EB2B2D1E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PARES" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="517">
   <si>
     <t>Par</t>
   </si>
@@ -1590,6 +1590,9 @@
   </si>
   <si>
     <t>Exemplo: bloquear ativo manualmente.</t>
+  </si>
+  <si>
+    <t>240,D</t>
   </si>
 </sst>
 </file>
@@ -1616,12 +1619,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -6590,7 +6595,7 @@
         <v>430</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>431</v>
+        <v>516</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>432</v>

--- a/ativos.xlsx
+++ b/ativos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\INVESTIMENTOS VARIAVEL\Bybit\bybit_setups\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\INVESTIMENTOS VARIAVEL\Bybit\bybit_setups\complementos\GitHub\bybit_setups\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3AF1526-005B-4EB6-A394-F71EB2B2D1E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5039445-1660-43FE-ABD5-EBF79C9F63AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1592,7 +1592,7 @@
     <t>Exemplo: bloquear ativo manualmente.</t>
   </si>
   <si>
-    <t>240,D</t>
+    <t>240,D,360</t>
   </si>
 </sst>
 </file>

--- a/ativos.xlsx
+++ b/ativos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\INVESTIMENTOS VARIAVEL\Bybit\bybit_setups\complementos\GitHub\bybit_setups\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5039445-1660-43FE-ABD5-EBF79C9F63AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39BF460B-4B2C-4558-A5CB-E5C10924AC7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1592,7 +1592,7 @@
     <t>Exemplo: bloquear ativo manualmente.</t>
   </si>
   <si>
-    <t>240,D,360</t>
+    <t>120,240,D,360</t>
   </si>
 </sst>
 </file>
